--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="95">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -218,12 +218,96 @@
   </si>
   <si>
     <t>Nº</t>
+  </si>
+  <si>
+    <t>China Chinese Super League</t>
+  </si>
+  <si>
+    <t>2025</t>
+  </si>
+  <si>
+    <t>Chengdu Better City FC</t>
+  </si>
+  <si>
+    <t>Shanghai Shenhua</t>
+  </si>
+  <si>
+    <t>Yunnan Yukun</t>
+  </si>
+  <si>
+    <t>Qingdao Jonoon</t>
+  </si>
+  <si>
+    <t>Zhejiang FC</t>
+  </si>
+  <si>
+    <t>Shandong Luneng</t>
+  </si>
+  <si>
+    <t>Tianjin Teda</t>
+  </si>
+  <si>
+    <t>Wuhan Three Towns</t>
+  </si>
+  <si>
+    <t>Changchun Yatai</t>
+  </si>
+  <si>
+    <t>Beijing Guoan</t>
+  </si>
+  <si>
+    <t>Qingdao Youth Island</t>
+  </si>
+  <si>
+    <t>Dalian Zhixing</t>
+  </si>
+  <si>
+    <t>Henan Jianye</t>
+  </si>
+  <si>
+    <t>Meizhou Hakka</t>
+  </si>
+  <si>
+    <t>['59']</t>
+  </si>
+  <si>
+    <t>['29', '90+7']</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>['11', '42']</t>
+  </si>
+  <si>
+    <t>['10']</t>
+  </si>
+  <si>
+    <t>['90', '90+12']</t>
+  </si>
+  <si>
+    <t>['42']</t>
+  </si>
+  <si>
+    <t>['53', '79']</t>
+  </si>
+  <si>
+    <t>['15', '69']</t>
+  </si>
+  <si>
+    <t>['58']</t>
+  </si>
+  <si>
+    <t>['6', '64']</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -276,11 +360,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -575,7 +660,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP1"/>
+  <dimension ref="A1:BP8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -784,6 +869,1448 @@
         <v>66</v>
       </c>
     </row>
+    <row r="2" spans="1:68">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>7825192</v>
+      </c>
+      <c r="C2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" s="2">
+        <v>45710.35763888889</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="O2" t="s">
+        <v>84</v>
+      </c>
+      <c r="P2" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q2">
+        <v>1.83</v>
+      </c>
+      <c r="R2">
+        <v>2.5</v>
+      </c>
+      <c r="S2">
+        <v>8</v>
+      </c>
+      <c r="T2">
+        <v>1.33</v>
+      </c>
+      <c r="U2">
+        <v>3.25</v>
+      </c>
+      <c r="V2">
+        <v>2.5</v>
+      </c>
+      <c r="W2">
+        <v>1.5</v>
+      </c>
+      <c r="X2">
+        <v>6.5</v>
+      </c>
+      <c r="Y2">
+        <v>1.11</v>
+      </c>
+      <c r="Z2">
+        <v>1.33</v>
+      </c>
+      <c r="AA2">
+        <v>5.2</v>
+      </c>
+      <c r="AB2">
+        <v>8</v>
+      </c>
+      <c r="AC2">
+        <v>1.04</v>
+      </c>
+      <c r="AD2">
+        <v>9.5</v>
+      </c>
+      <c r="AE2">
+        <v>1.2</v>
+      </c>
+      <c r="AF2">
+        <v>4.2</v>
+      </c>
+      <c r="AG2">
+        <v>1.61</v>
+      </c>
+      <c r="AH2">
+        <v>2.05</v>
+      </c>
+      <c r="AI2">
+        <v>2</v>
+      </c>
+      <c r="AJ2">
+        <v>1.75</v>
+      </c>
+      <c r="AK2">
+        <v>1.03</v>
+      </c>
+      <c r="AL2">
+        <v>1.17</v>
+      </c>
+      <c r="AM2">
+        <v>3.2</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <v>3</v>
+      </c>
+      <c r="AQ2">
+        <v>0</v>
+      </c>
+      <c r="AR2">
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <v>10</v>
+      </c>
+      <c r="AV2">
+        <v>3</v>
+      </c>
+      <c r="AW2">
+        <v>16</v>
+      </c>
+      <c r="AX2">
+        <v>6</v>
+      </c>
+      <c r="AY2">
+        <v>33</v>
+      </c>
+      <c r="AZ2">
+        <v>10</v>
+      </c>
+      <c r="BA2">
+        <v>8</v>
+      </c>
+      <c r="BB2">
+        <v>2</v>
+      </c>
+      <c r="BC2">
+        <v>10</v>
+      </c>
+      <c r="BD2">
+        <v>1.3</v>
+      </c>
+      <c r="BE2">
+        <v>7.5</v>
+      </c>
+      <c r="BF2">
+        <v>3.8</v>
+      </c>
+      <c r="BG2">
+        <v>1.23</v>
+      </c>
+      <c r="BH2">
+        <v>3.65</v>
+      </c>
+      <c r="BI2">
+        <v>1.4</v>
+      </c>
+      <c r="BJ2">
+        <v>2.65</v>
+      </c>
+      <c r="BK2">
+        <v>1.66</v>
+      </c>
+      <c r="BL2">
+        <v>2.07</v>
+      </c>
+      <c r="BM2">
+        <v>2</v>
+      </c>
+      <c r="BN2">
+        <v>1.7</v>
+      </c>
+      <c r="BO2">
+        <v>2.55</v>
+      </c>
+      <c r="BP2">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:68">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>7825193</v>
+      </c>
+      <c r="C3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" s="2">
+        <v>45710.375</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H3" t="s">
+        <v>78</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3">
+        <v>3</v>
+      </c>
+      <c r="O3" t="s">
+        <v>85</v>
+      </c>
+      <c r="P3" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q3">
+        <v>1.7</v>
+      </c>
+      <c r="R3">
+        <v>2.85</v>
+      </c>
+      <c r="S3">
+        <v>6.8</v>
+      </c>
+      <c r="T3">
+        <v>1.2</v>
+      </c>
+      <c r="U3">
+        <v>4.05</v>
+      </c>
+      <c r="V3">
+        <v>1.99</v>
+      </c>
+      <c r="W3">
+        <v>1.74</v>
+      </c>
+      <c r="X3">
+        <v>4.05</v>
+      </c>
+      <c r="Y3">
+        <v>1.2</v>
+      </c>
+      <c r="Z3">
+        <v>1.3</v>
+      </c>
+      <c r="AA3">
+        <v>5.7</v>
+      </c>
+      <c r="AB3">
+        <v>7.9</v>
+      </c>
+      <c r="AC3">
+        <v>1.01</v>
+      </c>
+      <c r="AD3">
+        <v>17.5</v>
+      </c>
+      <c r="AE3">
+        <v>1.13</v>
+      </c>
+      <c r="AF3">
+        <v>5.6</v>
+      </c>
+      <c r="AG3">
+        <v>1.4</v>
+      </c>
+      <c r="AH3">
+        <v>2.73</v>
+      </c>
+      <c r="AI3">
+        <v>1.68</v>
+      </c>
+      <c r="AJ3">
+        <v>2.06</v>
+      </c>
+      <c r="AK3">
+        <v>1.09</v>
+      </c>
+      <c r="AL3">
+        <v>1.13</v>
+      </c>
+      <c r="AM3">
+        <v>3.1</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>3</v>
+      </c>
+      <c r="AQ3">
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <v>8</v>
+      </c>
+      <c r="AV3">
+        <v>4</v>
+      </c>
+      <c r="AW3">
+        <v>13</v>
+      </c>
+      <c r="AX3">
+        <v>2</v>
+      </c>
+      <c r="AY3">
+        <v>22</v>
+      </c>
+      <c r="AZ3">
+        <v>6</v>
+      </c>
+      <c r="BA3">
+        <v>6</v>
+      </c>
+      <c r="BB3">
+        <v>1</v>
+      </c>
+      <c r="BC3">
+        <v>7</v>
+      </c>
+      <c r="BD3">
+        <v>1.32</v>
+      </c>
+      <c r="BE3">
+        <v>7.5</v>
+      </c>
+      <c r="BF3">
+        <v>3.8</v>
+      </c>
+      <c r="BG3">
+        <v>1.27</v>
+      </c>
+      <c r="BH3">
+        <v>3.3</v>
+      </c>
+      <c r="BI3">
+        <v>1.47</v>
+      </c>
+      <c r="BJ3">
+        <v>2.48</v>
+      </c>
+      <c r="BK3">
+        <v>1.75</v>
+      </c>
+      <c r="BL3">
+        <v>1.95</v>
+      </c>
+      <c r="BM3">
+        <v>2.18</v>
+      </c>
+      <c r="BN3">
+        <v>1.58</v>
+      </c>
+      <c r="BO3">
+        <v>2.75</v>
+      </c>
+      <c r="BP3">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:68">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>7825194</v>
+      </c>
+      <c r="C4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E4" s="2">
+        <v>45710.375</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H4" t="s">
+        <v>79</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
+      </c>
+      <c r="N4">
+        <v>2</v>
+      </c>
+      <c r="O4" t="s">
+        <v>86</v>
+      </c>
+      <c r="P4" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q4">
+        <v>4</v>
+      </c>
+      <c r="R4">
+        <v>2.38</v>
+      </c>
+      <c r="S4">
+        <v>2.5</v>
+      </c>
+      <c r="T4">
+        <v>1.3</v>
+      </c>
+      <c r="U4">
+        <v>3.4</v>
+      </c>
+      <c r="V4">
+        <v>2.5</v>
+      </c>
+      <c r="W4">
+        <v>1.5</v>
+      </c>
+      <c r="X4">
+        <v>6</v>
+      </c>
+      <c r="Y4">
+        <v>1.13</v>
+      </c>
+      <c r="Z4">
+        <v>3.67</v>
+      </c>
+      <c r="AA4">
+        <v>3.63</v>
+      </c>
+      <c r="AB4">
+        <v>1.92</v>
+      </c>
+      <c r="AC4">
+        <v>1.04</v>
+      </c>
+      <c r="AD4">
+        <v>9</v>
+      </c>
+      <c r="AE4">
+        <v>1.21</v>
+      </c>
+      <c r="AF4">
+        <v>4</v>
+      </c>
+      <c r="AG4">
+        <v>1.65</v>
+      </c>
+      <c r="AH4">
+        <v>2</v>
+      </c>
+      <c r="AI4">
+        <v>1.57</v>
+      </c>
+      <c r="AJ4">
+        <v>2.25</v>
+      </c>
+      <c r="AK4">
+        <v>2.1</v>
+      </c>
+      <c r="AL4">
+        <v>1.24</v>
+      </c>
+      <c r="AM4">
+        <v>1.19</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <v>3</v>
+      </c>
+      <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <v>3</v>
+      </c>
+      <c r="AV4">
+        <v>6</v>
+      </c>
+      <c r="AW4">
+        <v>8</v>
+      </c>
+      <c r="AX4">
+        <v>4</v>
+      </c>
+      <c r="AY4">
+        <v>11</v>
+      </c>
+      <c r="AZ4">
+        <v>10</v>
+      </c>
+      <c r="BA4">
+        <v>0</v>
+      </c>
+      <c r="BB4">
+        <v>7</v>
+      </c>
+      <c r="BC4">
+        <v>7</v>
+      </c>
+      <c r="BD4">
+        <v>2.1</v>
+      </c>
+      <c r="BE4">
+        <v>8.5</v>
+      </c>
+      <c r="BF4">
+        <v>1.85</v>
+      </c>
+      <c r="BG4">
+        <v>1.16</v>
+      </c>
+      <c r="BH4">
+        <v>4.1</v>
+      </c>
+      <c r="BI4">
+        <v>1.33</v>
+      </c>
+      <c r="BJ4">
+        <v>2.81</v>
+      </c>
+      <c r="BK4">
+        <v>1.7</v>
+      </c>
+      <c r="BL4">
+        <v>2.05</v>
+      </c>
+      <c r="BM4">
+        <v>1.95</v>
+      </c>
+      <c r="BN4">
+        <v>1.77</v>
+      </c>
+      <c r="BO4">
+        <v>2.64</v>
+      </c>
+      <c r="BP4">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:68">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>7825195</v>
+      </c>
+      <c r="C5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="2">
+        <v>45711.1875</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>73</v>
+      </c>
+      <c r="H5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+      <c r="N5">
+        <v>4</v>
+      </c>
+      <c r="O5" t="s">
+        <v>87</v>
+      </c>
+      <c r="P5" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q5">
+        <v>2.85</v>
+      </c>
+      <c r="R5">
+        <v>2.27</v>
+      </c>
+      <c r="S5">
+        <v>3.5</v>
+      </c>
+      <c r="T5">
+        <v>1.34</v>
+      </c>
+      <c r="U5">
+        <v>3</v>
+      </c>
+      <c r="V5">
+        <v>2.45</v>
+      </c>
+      <c r="W5">
+        <v>1.48</v>
+      </c>
+      <c r="X5">
+        <v>5.7</v>
+      </c>
+      <c r="Y5">
+        <v>1.11</v>
+      </c>
+      <c r="Z5">
+        <v>2.35</v>
+      </c>
+      <c r="AA5">
+        <v>2.85</v>
+      </c>
+      <c r="AB5">
+        <v>3.05</v>
+      </c>
+      <c r="AC5">
+        <v>1.02</v>
+      </c>
+      <c r="AD5">
+        <v>10</v>
+      </c>
+      <c r="AE5">
+        <v>1.23</v>
+      </c>
+      <c r="AF5">
+        <v>3.75</v>
+      </c>
+      <c r="AG5">
+        <v>1.77</v>
+      </c>
+      <c r="AH5">
+        <v>1.98</v>
+      </c>
+      <c r="AI5">
+        <v>1.57</v>
+      </c>
+      <c r="AJ5">
+        <v>2.25</v>
+      </c>
+      <c r="AK5">
+        <v>1.35</v>
+      </c>
+      <c r="AL5">
+        <v>1.34</v>
+      </c>
+      <c r="AM5">
+        <v>1.54</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>1</v>
+      </c>
+      <c r="AQ5">
+        <v>1</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <v>6</v>
+      </c>
+      <c r="AV5">
+        <v>6</v>
+      </c>
+      <c r="AW5">
+        <v>7</v>
+      </c>
+      <c r="AX5">
+        <v>8</v>
+      </c>
+      <c r="AY5">
+        <v>14</v>
+      </c>
+      <c r="AZ5">
+        <v>17</v>
+      </c>
+      <c r="BA5">
+        <v>3</v>
+      </c>
+      <c r="BB5">
+        <v>3</v>
+      </c>
+      <c r="BC5">
+        <v>6</v>
+      </c>
+      <c r="BD5">
+        <v>1.89</v>
+      </c>
+      <c r="BE5">
+        <v>6.5</v>
+      </c>
+      <c r="BF5">
+        <v>2.12</v>
+      </c>
+      <c r="BG5">
+        <v>1.21</v>
+      </c>
+      <c r="BH5">
+        <v>3.7</v>
+      </c>
+      <c r="BI5">
+        <v>1.4</v>
+      </c>
+      <c r="BJ5">
+        <v>2.7</v>
+      </c>
+      <c r="BK5">
+        <v>1.63</v>
+      </c>
+      <c r="BL5">
+        <v>2.1</v>
+      </c>
+      <c r="BM5">
+        <v>2</v>
+      </c>
+      <c r="BN5">
+        <v>1.71</v>
+      </c>
+      <c r="BO5">
+        <v>2.5</v>
+      </c>
+      <c r="BP5">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:68">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>7825196</v>
+      </c>
+      <c r="C6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="2">
+        <v>45711.1875</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H6" t="s">
+        <v>81</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>2</v>
+      </c>
+      <c r="O6" t="s">
+        <v>88</v>
+      </c>
+      <c r="P6" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q6">
+        <v>2.2</v>
+      </c>
+      <c r="R6">
+        <v>2.5</v>
+      </c>
+      <c r="S6">
+        <v>4.5</v>
+      </c>
+      <c r="T6">
+        <v>1.25</v>
+      </c>
+      <c r="U6">
+        <v>3.75</v>
+      </c>
+      <c r="V6">
+        <v>2.2</v>
+      </c>
+      <c r="W6">
+        <v>1.62</v>
+      </c>
+      <c r="X6">
+        <v>5</v>
+      </c>
+      <c r="Y6">
+        <v>1.17</v>
+      </c>
+      <c r="Z6">
+        <v>1.63</v>
+      </c>
+      <c r="AA6">
+        <v>4.3</v>
+      </c>
+      <c r="AB6">
+        <v>4.5</v>
+      </c>
+      <c r="AC6">
+        <v>1.01</v>
+      </c>
+      <c r="AD6">
+        <v>17</v>
+      </c>
+      <c r="AE6">
+        <v>1.09</v>
+      </c>
+      <c r="AF6">
+        <v>5.3</v>
+      </c>
+      <c r="AG6">
+        <v>1.42</v>
+      </c>
+      <c r="AH6">
+        <v>2.65</v>
+      </c>
+      <c r="AI6">
+        <v>1.53</v>
+      </c>
+      <c r="AJ6">
+        <v>2.38</v>
+      </c>
+      <c r="AK6">
+        <v>1.18</v>
+      </c>
+      <c r="AL6">
+        <v>1.19</v>
+      </c>
+      <c r="AM6">
+        <v>2.2</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>1</v>
+      </c>
+      <c r="AQ6">
+        <v>1</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <v>5</v>
+      </c>
+      <c r="AV6">
+        <v>4</v>
+      </c>
+      <c r="AW6">
+        <v>6</v>
+      </c>
+      <c r="AX6">
+        <v>9</v>
+      </c>
+      <c r="AY6">
+        <v>13</v>
+      </c>
+      <c r="AZ6">
+        <v>17</v>
+      </c>
+      <c r="BA6">
+        <v>5</v>
+      </c>
+      <c r="BB6">
+        <v>7</v>
+      </c>
+      <c r="BC6">
+        <v>12</v>
+      </c>
+      <c r="BD6">
+        <v>1.53</v>
+      </c>
+      <c r="BE6">
+        <v>6.75</v>
+      </c>
+      <c r="BF6">
+        <v>2.8</v>
+      </c>
+      <c r="BG6">
+        <v>1.22</v>
+      </c>
+      <c r="BH6">
+        <v>3.65</v>
+      </c>
+      <c r="BI6">
+        <v>1.41</v>
+      </c>
+      <c r="BJ6">
+        <v>2.65</v>
+      </c>
+      <c r="BK6">
+        <v>1.68</v>
+      </c>
+      <c r="BL6">
+        <v>2.02</v>
+      </c>
+      <c r="BM6">
+        <v>2.06</v>
+      </c>
+      <c r="BN6">
+        <v>1.66</v>
+      </c>
+      <c r="BO6">
+        <v>2.6</v>
+      </c>
+      <c r="BP6">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:68">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>7825197</v>
+      </c>
+      <c r="C7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45711.1875</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7" t="s">
+        <v>75</v>
+      </c>
+      <c r="H7" t="s">
+        <v>82</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7" t="s">
+        <v>86</v>
+      </c>
+      <c r="P7" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q7">
+        <v>2.38</v>
+      </c>
+      <c r="R7">
+        <v>2.25</v>
+      </c>
+      <c r="S7">
+        <v>4.75</v>
+      </c>
+      <c r="T7">
+        <v>1.36</v>
+      </c>
+      <c r="U7">
+        <v>3</v>
+      </c>
+      <c r="V7">
+        <v>2.63</v>
+      </c>
+      <c r="W7">
+        <v>1.44</v>
+      </c>
+      <c r="X7">
+        <v>7</v>
+      </c>
+      <c r="Y7">
+        <v>1.1</v>
+      </c>
+      <c r="Z7">
+        <v>1.58</v>
+      </c>
+      <c r="AA7">
+        <v>4.1</v>
+      </c>
+      <c r="AB7">
+        <v>5.1</v>
+      </c>
+      <c r="AC7">
+        <v>1.01</v>
+      </c>
+      <c r="AD7">
+        <v>12.5</v>
+      </c>
+      <c r="AE7">
+        <v>1.21</v>
+      </c>
+      <c r="AF7">
+        <v>4.14</v>
+      </c>
+      <c r="AG7">
+        <v>1.67</v>
+      </c>
+      <c r="AH7">
+        <v>2</v>
+      </c>
+      <c r="AI7">
+        <v>1.75</v>
+      </c>
+      <c r="AJ7">
+        <v>2</v>
+      </c>
+      <c r="AK7">
+        <v>1.18</v>
+      </c>
+      <c r="AL7">
+        <v>1.23</v>
+      </c>
+      <c r="AM7">
+        <v>2.1</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>1</v>
+      </c>
+      <c r="AQ7">
+        <v>1</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>4</v>
+      </c>
+      <c r="AV7">
+        <v>5</v>
+      </c>
+      <c r="AW7">
+        <v>19</v>
+      </c>
+      <c r="AX7">
+        <v>10</v>
+      </c>
+      <c r="AY7">
+        <v>27</v>
+      </c>
+      <c r="AZ7">
+        <v>20</v>
+      </c>
+      <c r="BA7">
+        <v>9</v>
+      </c>
+      <c r="BB7">
+        <v>8</v>
+      </c>
+      <c r="BC7">
+        <v>17</v>
+      </c>
+      <c r="BD7">
+        <v>1.49</v>
+      </c>
+      <c r="BE7">
+        <v>6.75</v>
+      </c>
+      <c r="BF7">
+        <v>2.9</v>
+      </c>
+      <c r="BG7">
+        <v>1.21</v>
+      </c>
+      <c r="BH7">
+        <v>3.8</v>
+      </c>
+      <c r="BI7">
+        <v>1.38</v>
+      </c>
+      <c r="BJ7">
+        <v>2.7</v>
+      </c>
+      <c r="BK7">
+        <v>1.61</v>
+      </c>
+      <c r="BL7">
+        <v>2.14</v>
+      </c>
+      <c r="BM7">
+        <v>1.98</v>
+      </c>
+      <c r="BN7">
+        <v>1.82</v>
+      </c>
+      <c r="BO7">
+        <v>2.45</v>
+      </c>
+      <c r="BP7">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:68">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>7825198</v>
+      </c>
+      <c r="C8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="2">
+        <v>45711.1875</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8" t="s">
+        <v>76</v>
+      </c>
+      <c r="H8" t="s">
+        <v>83</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>2</v>
+      </c>
+      <c r="M8">
+        <v>2</v>
+      </c>
+      <c r="N8">
+        <v>4</v>
+      </c>
+      <c r="O8" t="s">
+        <v>89</v>
+      </c>
+      <c r="P8" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q8">
+        <v>2.04</v>
+      </c>
+      <c r="R8">
+        <v>2.5</v>
+      </c>
+      <c r="S8">
+        <v>5.2</v>
+      </c>
+      <c r="T8">
+        <v>1.28</v>
+      </c>
+      <c r="U8">
+        <v>3.4</v>
+      </c>
+      <c r="V8">
+        <v>2.26</v>
+      </c>
+      <c r="W8">
+        <v>1.58</v>
+      </c>
+      <c r="X8">
+        <v>4.95</v>
+      </c>
+      <c r="Y8">
+        <v>1.14</v>
+      </c>
+      <c r="Z8">
+        <v>1.56</v>
+      </c>
+      <c r="AA8">
+        <v>4.4</v>
+      </c>
+      <c r="AB8">
+        <v>5</v>
+      </c>
+      <c r="AC8">
+        <v>1.01</v>
+      </c>
+      <c r="AD8">
+        <v>13</v>
+      </c>
+      <c r="AE8">
+        <v>1.18</v>
+      </c>
+      <c r="AF8">
+        <v>4.4</v>
+      </c>
+      <c r="AG8">
+        <v>1.55</v>
+      </c>
+      <c r="AH8">
+        <v>2.2</v>
+      </c>
+      <c r="AI8">
+        <v>1.63</v>
+      </c>
+      <c r="AJ8">
+        <v>2.14</v>
+      </c>
+      <c r="AK8">
+        <v>1.16</v>
+      </c>
+      <c r="AL8">
+        <v>1.21</v>
+      </c>
+      <c r="AM8">
+        <v>2.24</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <v>1</v>
+      </c>
+      <c r="AQ8">
+        <v>1</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <v>11</v>
+      </c>
+      <c r="AV8">
+        <v>3</v>
+      </c>
+      <c r="AW8">
+        <v>20</v>
+      </c>
+      <c r="AX8">
+        <v>11</v>
+      </c>
+      <c r="AY8">
+        <v>32</v>
+      </c>
+      <c r="AZ8">
+        <v>18</v>
+      </c>
+      <c r="BA8">
+        <v>14</v>
+      </c>
+      <c r="BB8">
+        <v>7</v>
+      </c>
+      <c r="BC8">
+        <v>21</v>
+      </c>
+      <c r="BD8">
+        <v>1.42</v>
+      </c>
+      <c r="BE8">
+        <v>7</v>
+      </c>
+      <c r="BF8">
+        <v>3.15</v>
+      </c>
+      <c r="BG8">
+        <v>1.18</v>
+      </c>
+      <c r="BH8">
+        <v>4.1</v>
+      </c>
+      <c r="BI8">
+        <v>1.32</v>
+      </c>
+      <c r="BJ8">
+        <v>3.05</v>
+      </c>
+      <c r="BK8">
+        <v>1.53</v>
+      </c>
+      <c r="BL8">
+        <v>2.32</v>
+      </c>
+      <c r="BM8">
+        <v>1.9</v>
+      </c>
+      <c r="BN8">
+        <v>1.9</v>
+      </c>
+      <c r="BO8">
+        <v>2.28</v>
+      </c>
+      <c r="BP8">
+        <v>1.55</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="99">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -247,6 +247,9 @@
     <t>Tianjin Teda</t>
   </si>
   <si>
+    <t>Shanghai SIPG</t>
+  </si>
+  <si>
     <t>Wuhan Three Towns</t>
   </si>
   <si>
@@ -268,6 +271,9 @@
     <t>Meizhou Hakka</t>
   </si>
   <si>
+    <t>Sichuan Jiuniu</t>
+  </si>
+  <si>
     <t>['59']</t>
   </si>
   <si>
@@ -286,6 +292,9 @@
     <t>['90', '90+12']</t>
   </si>
   <si>
+    <t>['3', '62', '90+3']</t>
+  </si>
+  <si>
     <t>['42']</t>
   </si>
   <si>
@@ -299,6 +308,9 @@
   </si>
   <si>
     <t>['6', '64']</t>
+  </si>
+  <si>
+    <t>['80']</t>
   </si>
 </sst>
 </file>
@@ -660,7 +672,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP8"/>
+  <dimension ref="A1:BP9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -892,7 +904,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -913,10 +925,10 @@
         <v>1</v>
       </c>
       <c r="O2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="Q2">
         <v>1.83</v>
@@ -1098,7 +1110,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -1119,10 +1131,10 @@
         <v>3</v>
       </c>
       <c r="O3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="P3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="Q3">
         <v>1.7</v>
@@ -1304,7 +1316,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1325,10 +1337,10 @@
         <v>2</v>
       </c>
       <c r="O4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -1510,7 +1522,7 @@
         <v>73</v>
       </c>
       <c r="H5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I5">
         <v>2</v>
@@ -1531,10 +1543,10 @@
         <v>4</v>
       </c>
       <c r="O5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="Q5">
         <v>2.85</v>
@@ -1716,7 +1728,7 @@
         <v>74</v>
       </c>
       <c r="H6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -1737,10 +1749,10 @@
         <v>2</v>
       </c>
       <c r="O6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="Q6">
         <v>2.2</v>
@@ -1922,7 +1934,7 @@
         <v>75</v>
       </c>
       <c r="H7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1943,10 +1955,10 @@
         <v>0</v>
       </c>
       <c r="O7" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="P7" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -2128,7 +2140,7 @@
         <v>76</v>
       </c>
       <c r="H8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -2149,10 +2161,10 @@
         <v>4</v>
       </c>
       <c r="O8" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="Q8">
         <v>2.04</v>
@@ -2309,6 +2321,212 @@
       </c>
       <c r="BP8">
         <v>1.55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:68">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>7825199</v>
+      </c>
+      <c r="C9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" s="2">
+        <v>45711.35763888889</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9" t="s">
+        <v>77</v>
+      </c>
+      <c r="H9" t="s">
+        <v>85</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>3</v>
+      </c>
+      <c r="M9">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>4</v>
+      </c>
+      <c r="O9" t="s">
+        <v>92</v>
+      </c>
+      <c r="P9" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q9">
+        <v>1.5</v>
+      </c>
+      <c r="R9">
+        <v>3.35</v>
+      </c>
+      <c r="S9">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="T9">
+        <v>1.14</v>
+      </c>
+      <c r="U9">
+        <v>4.95</v>
+      </c>
+      <c r="V9">
+        <v>1.76</v>
+      </c>
+      <c r="W9">
+        <v>1.98</v>
+      </c>
+      <c r="X9">
+        <v>3.25</v>
+      </c>
+      <c r="Y9">
+        <v>1.3</v>
+      </c>
+      <c r="Z9">
+        <v>1.18</v>
+      </c>
+      <c r="AA9">
+        <v>6.8</v>
+      </c>
+      <c r="AB9">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC9">
+        <v>1.01</v>
+      </c>
+      <c r="AD9">
+        <v>23</v>
+      </c>
+      <c r="AE9">
+        <v>1.02</v>
+      </c>
+      <c r="AF9">
+        <v>7.9</v>
+      </c>
+      <c r="AG9">
+        <v>1.28</v>
+      </c>
+      <c r="AH9">
+        <v>3.5</v>
+      </c>
+      <c r="AI9">
+        <v>1.68</v>
+      </c>
+      <c r="AJ9">
+        <v>2.05</v>
+      </c>
+      <c r="AK9">
+        <v>1.04</v>
+      </c>
+      <c r="AL9">
+        <v>1.08</v>
+      </c>
+      <c r="AM9">
+        <v>4.2</v>
+      </c>
+      <c r="AN9">
+        <v>0</v>
+      </c>
+      <c r="AO9">
+        <v>0</v>
+      </c>
+      <c r="AP9">
+        <v>3</v>
+      </c>
+      <c r="AQ9">
+        <v>0</v>
+      </c>
+      <c r="AR9">
+        <v>0</v>
+      </c>
+      <c r="AS9">
+        <v>0</v>
+      </c>
+      <c r="AT9">
+        <v>0</v>
+      </c>
+      <c r="AU9">
+        <v>7</v>
+      </c>
+      <c r="AV9">
+        <v>5</v>
+      </c>
+      <c r="AW9">
+        <v>10</v>
+      </c>
+      <c r="AX9">
+        <v>8</v>
+      </c>
+      <c r="AY9">
+        <v>19</v>
+      </c>
+      <c r="AZ9">
+        <v>15</v>
+      </c>
+      <c r="BA9">
+        <v>5</v>
+      </c>
+      <c r="BB9">
+        <v>6</v>
+      </c>
+      <c r="BC9">
+        <v>11</v>
+      </c>
+      <c r="BD9">
+        <v>1.25</v>
+      </c>
+      <c r="BE9">
+        <v>8</v>
+      </c>
+      <c r="BF9">
+        <v>4.3</v>
+      </c>
+      <c r="BG9">
+        <v>1.26</v>
+      </c>
+      <c r="BH9">
+        <v>3.4</v>
+      </c>
+      <c r="BI9">
+        <v>1.44</v>
+      </c>
+      <c r="BJ9">
+        <v>2.55</v>
+      </c>
+      <c r="BK9">
+        <v>1.73</v>
+      </c>
+      <c r="BL9">
+        <v>1.97</v>
+      </c>
+      <c r="BM9">
+        <v>2.12</v>
+      </c>
+      <c r="BN9">
+        <v>1.63</v>
+      </c>
+      <c r="BO9">
+        <v>2.65</v>
+      </c>
+      <c r="BP9">
+        <v>1.41</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="102">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -295,6 +295,12 @@
     <t>['3', '62', '90+3']</t>
   </si>
   <si>
+    <t>['12', '57', '85', '90+10']</t>
+  </si>
+  <si>
+    <t>['54', '90+8']</t>
+  </si>
+  <si>
     <t>['42']</t>
   </si>
   <si>
@@ -311,6 +317,9 @@
   </si>
   <si>
     <t>['80']</t>
+  </si>
+  <si>
+    <t>['20']</t>
   </si>
 </sst>
 </file>
@@ -672,7 +681,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP9"/>
+  <dimension ref="A1:BP11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1134,7 +1143,7 @@
         <v>87</v>
       </c>
       <c r="P3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="Q3">
         <v>1.7</v>
@@ -1340,7 +1349,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -1546,7 +1555,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="Q5">
         <v>2.85</v>
@@ -1752,7 +1761,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q6">
         <v>2.2</v>
@@ -1833,7 +1842,7 @@
         <v>1</v>
       </c>
       <c r="AQ6">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2036,7 +2045,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ7">
         <v>1</v>
@@ -2164,7 +2173,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="Q8">
         <v>2.04</v>
@@ -2370,7 +2379,7 @@
         <v>92</v>
       </c>
       <c r="P9" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="Q9">
         <v>1.5</v>
@@ -2527,6 +2536,418 @@
       </c>
       <c r="BP9">
         <v>1.41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:68">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>7825200</v>
+      </c>
+      <c r="C10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" s="2">
+        <v>45716.1875</v>
+      </c>
+      <c r="F10">
+        <v>2</v>
+      </c>
+      <c r="G10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H10" t="s">
+        <v>82</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>2</v>
+      </c>
+      <c r="L10">
+        <v>4</v>
+      </c>
+      <c r="M10">
+        <v>1</v>
+      </c>
+      <c r="N10">
+        <v>5</v>
+      </c>
+      <c r="O10" t="s">
+        <v>93</v>
+      </c>
+      <c r="P10" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q10">
+        <v>2.1</v>
+      </c>
+      <c r="R10">
+        <v>2.5</v>
+      </c>
+      <c r="S10">
+        <v>5</v>
+      </c>
+      <c r="T10">
+        <v>1.29</v>
+      </c>
+      <c r="U10">
+        <v>3.5</v>
+      </c>
+      <c r="V10">
+        <v>2.25</v>
+      </c>
+      <c r="W10">
+        <v>1.57</v>
+      </c>
+      <c r="X10">
+        <v>5.5</v>
+      </c>
+      <c r="Y10">
+        <v>1.14</v>
+      </c>
+      <c r="Z10">
+        <v>1.43</v>
+      </c>
+      <c r="AA10">
+        <v>4.6</v>
+      </c>
+      <c r="AB10">
+        <v>6.6</v>
+      </c>
+      <c r="AC10">
+        <v>1.03</v>
+      </c>
+      <c r="AD10">
+        <v>10</v>
+      </c>
+      <c r="AE10">
+        <v>1.17</v>
+      </c>
+      <c r="AF10">
+        <v>4.6</v>
+      </c>
+      <c r="AG10">
+        <v>1.55</v>
+      </c>
+      <c r="AH10">
+        <v>2.29</v>
+      </c>
+      <c r="AI10">
+        <v>1.67</v>
+      </c>
+      <c r="AJ10">
+        <v>2.1</v>
+      </c>
+      <c r="AK10">
+        <v>1.16</v>
+      </c>
+      <c r="AL10">
+        <v>1.19</v>
+      </c>
+      <c r="AM10">
+        <v>2.32</v>
+      </c>
+      <c r="AN10">
+        <v>1</v>
+      </c>
+      <c r="AO10">
+        <v>1</v>
+      </c>
+      <c r="AP10">
+        <v>2</v>
+      </c>
+      <c r="AQ10">
+        <v>0.5</v>
+      </c>
+      <c r="AR10">
+        <v>2.21</v>
+      </c>
+      <c r="AS10">
+        <v>1.44</v>
+      </c>
+      <c r="AT10">
+        <v>3.65</v>
+      </c>
+      <c r="AU10">
+        <v>13</v>
+      </c>
+      <c r="AV10">
+        <v>3</v>
+      </c>
+      <c r="AW10">
+        <v>7</v>
+      </c>
+      <c r="AX10">
+        <v>5</v>
+      </c>
+      <c r="AY10">
+        <v>24</v>
+      </c>
+      <c r="AZ10">
+        <v>11</v>
+      </c>
+      <c r="BA10">
+        <v>5</v>
+      </c>
+      <c r="BB10">
+        <v>6</v>
+      </c>
+      <c r="BC10">
+        <v>11</v>
+      </c>
+      <c r="BD10">
+        <v>1.47</v>
+      </c>
+      <c r="BE10">
+        <v>6.75</v>
+      </c>
+      <c r="BF10">
+        <v>2.95</v>
+      </c>
+      <c r="BG10">
+        <v>1.32</v>
+      </c>
+      <c r="BH10">
+        <v>3.05</v>
+      </c>
+      <c r="BI10">
+        <v>1.55</v>
+      </c>
+      <c r="BJ10">
+        <v>2.28</v>
+      </c>
+      <c r="BK10">
+        <v>1.89</v>
+      </c>
+      <c r="BL10">
+        <v>1.8</v>
+      </c>
+      <c r="BM10">
+        <v>2.38</v>
+      </c>
+      <c r="BN10">
+        <v>1.5</v>
+      </c>
+      <c r="BO10">
+        <v>3.05</v>
+      </c>
+      <c r="BP10">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:68">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>7825201</v>
+      </c>
+      <c r="C11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" s="2">
+        <v>45716.35763888889</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+      <c r="G11" t="s">
+        <v>77</v>
+      </c>
+      <c r="H11" t="s">
+        <v>79</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>2</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>2</v>
+      </c>
+      <c r="O11" t="s">
+        <v>94</v>
+      </c>
+      <c r="P11" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q11">
+        <v>1.65</v>
+      </c>
+      <c r="R11">
+        <v>2.88</v>
+      </c>
+      <c r="S11">
+        <v>6.25</v>
+      </c>
+      <c r="T11">
+        <v>1.18</v>
+      </c>
+      <c r="U11">
+        <v>4.2</v>
+      </c>
+      <c r="V11">
+        <v>1.93</v>
+      </c>
+      <c r="W11">
+        <v>1.77</v>
+      </c>
+      <c r="X11">
+        <v>4.2</v>
+      </c>
+      <c r="Y11">
+        <v>1.18</v>
+      </c>
+      <c r="Z11">
+        <v>1.29</v>
+      </c>
+      <c r="AA11">
+        <v>5.7</v>
+      </c>
+      <c r="AB11">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC11">
+        <v>1.01</v>
+      </c>
+      <c r="AD11">
+        <v>19</v>
+      </c>
+      <c r="AE11">
+        <v>1.1</v>
+      </c>
+      <c r="AF11">
+        <v>6.25</v>
+      </c>
+      <c r="AG11">
+        <v>1.35</v>
+      </c>
+      <c r="AH11">
+        <v>2.85</v>
+      </c>
+      <c r="AI11">
+        <v>1.65</v>
+      </c>
+      <c r="AJ11">
+        <v>2.05</v>
+      </c>
+      <c r="AK11">
+        <v>1.04</v>
+      </c>
+      <c r="AL11">
+        <v>1.09</v>
+      </c>
+      <c r="AM11">
+        <v>3.4</v>
+      </c>
+      <c r="AN11">
+        <v>3</v>
+      </c>
+      <c r="AO11">
+        <v>0</v>
+      </c>
+      <c r="AP11">
+        <v>3</v>
+      </c>
+      <c r="AQ11">
+        <v>0</v>
+      </c>
+      <c r="AR11">
+        <v>1.91</v>
+      </c>
+      <c r="AS11">
+        <v>0.86</v>
+      </c>
+      <c r="AT11">
+        <v>2.77</v>
+      </c>
+      <c r="AU11">
+        <v>7</v>
+      </c>
+      <c r="AV11">
+        <v>0</v>
+      </c>
+      <c r="AW11">
+        <v>18</v>
+      </c>
+      <c r="AX11">
+        <v>10</v>
+      </c>
+      <c r="AY11">
+        <v>30</v>
+      </c>
+      <c r="AZ11">
+        <v>13</v>
+      </c>
+      <c r="BA11">
+        <v>5</v>
+      </c>
+      <c r="BB11">
+        <v>3</v>
+      </c>
+      <c r="BC11">
+        <v>8</v>
+      </c>
+      <c r="BD11">
+        <v>1.33</v>
+      </c>
+      <c r="BE11">
+        <v>7</v>
+      </c>
+      <c r="BF11">
+        <v>3.65</v>
+      </c>
+      <c r="BG11">
+        <v>1.28</v>
+      </c>
+      <c r="BH11">
+        <v>3.3</v>
+      </c>
+      <c r="BI11">
+        <v>1.47</v>
+      </c>
+      <c r="BJ11">
+        <v>2.43</v>
+      </c>
+      <c r="BK11">
+        <v>1.78</v>
+      </c>
+      <c r="BL11">
+        <v>1.91</v>
+      </c>
+      <c r="BM11">
+        <v>2.23</v>
+      </c>
+      <c r="BN11">
+        <v>1.57</v>
+      </c>
+      <c r="BO11">
+        <v>2.8</v>
+      </c>
+      <c r="BP11">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="102">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -295,7 +295,7 @@
     <t>['3', '62', '90+3']</t>
   </si>
   <si>
-    <t>['12', '57', '85', '90+10']</t>
+    <t>['12', '57', '86', '90+10']</t>
   </si>
   <si>
     <t>['54', '90+8']</t>
@@ -681,7 +681,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP11"/>
+  <dimension ref="A1:BP12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AQ5">
         <v>1</v>
@@ -2460,7 +2460,7 @@
         <v>3</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -2948,6 +2948,212 @@
       </c>
       <c r="BP11">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:68">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>7825202</v>
+      </c>
+      <c r="C12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E12" s="2">
+        <v>45717.1875</v>
+      </c>
+      <c r="F12">
+        <v>2</v>
+      </c>
+      <c r="G12" t="s">
+        <v>73</v>
+      </c>
+      <c r="H12" t="s">
+        <v>85</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>1</v>
+      </c>
+      <c r="N12">
+        <v>1</v>
+      </c>
+      <c r="O12" t="s">
+        <v>88</v>
+      </c>
+      <c r="P12" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q12">
+        <v>3.1</v>
+      </c>
+      <c r="R12">
+        <v>2.17</v>
+      </c>
+      <c r="S12">
+        <v>3.35</v>
+      </c>
+      <c r="T12">
+        <v>1.39</v>
+      </c>
+      <c r="U12">
+        <v>2.8</v>
+      </c>
+      <c r="V12">
+        <v>2.7</v>
+      </c>
+      <c r="W12">
+        <v>1.41</v>
+      </c>
+      <c r="X12">
+        <v>6.6</v>
+      </c>
+      <c r="Y12">
+        <v>1.06</v>
+      </c>
+      <c r="Z12">
+        <v>2.5</v>
+      </c>
+      <c r="AA12">
+        <v>2.85</v>
+      </c>
+      <c r="AB12">
+        <v>3.17</v>
+      </c>
+      <c r="AC12">
+        <v>1.01</v>
+      </c>
+      <c r="AD12">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AE12">
+        <v>1.28</v>
+      </c>
+      <c r="AF12">
+        <v>3.35</v>
+      </c>
+      <c r="AG12">
+        <v>1.94</v>
+      </c>
+      <c r="AH12">
+        <v>1.85</v>
+      </c>
+      <c r="AI12">
+        <v>1.66</v>
+      </c>
+      <c r="AJ12">
+        <v>2.1</v>
+      </c>
+      <c r="AK12">
+        <v>1.39</v>
+      </c>
+      <c r="AL12">
+        <v>1.36</v>
+      </c>
+      <c r="AM12">
+        <v>1.46</v>
+      </c>
+      <c r="AN12">
+        <v>1</v>
+      </c>
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>0.5</v>
+      </c>
+      <c r="AQ12">
+        <v>1.5</v>
+      </c>
+      <c r="AR12">
+        <v>1.44</v>
+      </c>
+      <c r="AS12">
+        <v>1.67</v>
+      </c>
+      <c r="AT12">
+        <v>3.11</v>
+      </c>
+      <c r="AU12">
+        <v>0</v>
+      </c>
+      <c r="AV12">
+        <v>4</v>
+      </c>
+      <c r="AW12">
+        <v>12</v>
+      </c>
+      <c r="AX12">
+        <v>7</v>
+      </c>
+      <c r="AY12">
+        <v>14</v>
+      </c>
+      <c r="AZ12">
+        <v>14</v>
+      </c>
+      <c r="BA12">
+        <v>5</v>
+      </c>
+      <c r="BB12">
+        <v>3</v>
+      </c>
+      <c r="BC12">
+        <v>8</v>
+      </c>
+      <c r="BD12">
+        <v>1.98</v>
+      </c>
+      <c r="BE12">
+        <v>6.4</v>
+      </c>
+      <c r="BF12">
+        <v>1.98</v>
+      </c>
+      <c r="BG12">
+        <v>1.41</v>
+      </c>
+      <c r="BH12">
+        <v>2.65</v>
+      </c>
+      <c r="BI12">
+        <v>1.67</v>
+      </c>
+      <c r="BJ12">
+        <v>2.05</v>
+      </c>
+      <c r="BK12">
+        <v>2.08</v>
+      </c>
+      <c r="BL12">
+        <v>1.65</v>
+      </c>
+      <c r="BM12">
+        <v>2.7</v>
+      </c>
+      <c r="BN12">
+        <v>1.4</v>
+      </c>
+      <c r="BO12">
+        <v>3.65</v>
+      </c>
+      <c r="BP12">
+        <v>1.23</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="108">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -250,6 +250,9 @@
     <t>Shanghai SIPG</t>
   </si>
   <si>
+    <t>Meizhou Hakka</t>
+  </si>
+  <si>
     <t>Wuhan Three Towns</t>
   </si>
   <si>
@@ -268,9 +271,6 @@
     <t>Henan Jianye</t>
   </si>
   <si>
-    <t>Meizhou Hakka</t>
-  </si>
-  <si>
     <t>Sichuan Jiuniu</t>
   </si>
   <si>
@@ -301,6 +301,15 @@
     <t>['54', '90+8']</t>
   </si>
   <si>
+    <t>['44', '47']</t>
+  </si>
+  <si>
+    <t>['38', '45+4']</t>
+  </si>
+  <si>
+    <t>['68']</t>
+  </si>
+  <si>
     <t>['42']</t>
   </si>
   <si>
@@ -320,6 +329,15 @@
   </si>
   <si>
     <t>['20']</t>
+  </si>
+  <si>
+    <t>['76']</t>
+  </si>
+  <si>
+    <t>['11', '90+3']</t>
+  </si>
+  <si>
+    <t>['45+3']</t>
   </si>
 </sst>
 </file>
@@ -681,7 +699,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP12"/>
+  <dimension ref="A1:BP15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -913,7 +931,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -1119,7 +1137,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -1143,7 +1161,7 @@
         <v>87</v>
       </c>
       <c r="P3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="Q3">
         <v>1.7</v>
@@ -1221,7 +1239,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ3">
         <v>0</v>
@@ -1325,7 +1343,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1349,7 +1367,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -1427,10 +1445,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AQ4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1531,7 +1549,7 @@
         <v>73</v>
       </c>
       <c r="H5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I5">
         <v>2</v>
@@ -1555,7 +1573,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="Q5">
         <v>2.85</v>
@@ -1737,7 +1755,7 @@
         <v>74</v>
       </c>
       <c r="H6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -1761,7 +1779,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="Q6">
         <v>2.2</v>
@@ -1943,7 +1961,7 @@
         <v>75</v>
       </c>
       <c r="H7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -2048,7 +2066,7 @@
         <v>2</v>
       </c>
       <c r="AQ7">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2149,7 +2167,7 @@
         <v>76</v>
       </c>
       <c r="H8" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -2173,7 +2191,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="Q8">
         <v>2.04</v>
@@ -2379,7 +2397,7 @@
         <v>92</v>
       </c>
       <c r="P9" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="Q9">
         <v>1.5</v>
@@ -2561,7 +2579,7 @@
         <v>75</v>
       </c>
       <c r="H10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I10">
         <v>1</v>
@@ -2585,7 +2603,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="Q10">
         <v>2.1</v>
@@ -2767,7 +2785,7 @@
         <v>77</v>
       </c>
       <c r="H11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -2997,7 +3015,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="Q12">
         <v>3.1</v>
@@ -3154,6 +3172,624 @@
       </c>
       <c r="BP12">
         <v>1.23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:68">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>7825203</v>
+      </c>
+      <c r="C13" t="s">
+        <v>68</v>
+      </c>
+      <c r="D13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E13" s="2">
+        <v>45717.35763888889</v>
+      </c>
+      <c r="F13">
+        <v>2</v>
+      </c>
+      <c r="G13" t="s">
+        <v>78</v>
+      </c>
+      <c r="H13" t="s">
+        <v>84</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>2</v>
+      </c>
+      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="N13">
+        <v>3</v>
+      </c>
+      <c r="O13" t="s">
+        <v>95</v>
+      </c>
+      <c r="P13" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q13">
+        <v>3.6</v>
+      </c>
+      <c r="R13">
+        <v>2.2</v>
+      </c>
+      <c r="S13">
+        <v>2.88</v>
+      </c>
+      <c r="T13">
+        <v>1.36</v>
+      </c>
+      <c r="U13">
+        <v>3</v>
+      </c>
+      <c r="V13">
+        <v>2.75</v>
+      </c>
+      <c r="W13">
+        <v>1.4</v>
+      </c>
+      <c r="X13">
+        <v>8</v>
+      </c>
+      <c r="Y13">
+        <v>1.08</v>
+      </c>
+      <c r="Z13">
+        <v>3.21</v>
+      </c>
+      <c r="AA13">
+        <v>3.31</v>
+      </c>
+      <c r="AB13">
+        <v>2.19</v>
+      </c>
+      <c r="AC13">
+        <v>1.05</v>
+      </c>
+      <c r="AD13">
+        <v>8.5</v>
+      </c>
+      <c r="AE13">
+        <v>1.26</v>
+      </c>
+      <c r="AF13">
+        <v>3.45</v>
+      </c>
+      <c r="AG13">
+        <v>1.85</v>
+      </c>
+      <c r="AH13">
+        <v>1.89</v>
+      </c>
+      <c r="AI13">
+        <v>1.7</v>
+      </c>
+      <c r="AJ13">
+        <v>2.05</v>
+      </c>
+      <c r="AK13">
+        <v>1.58</v>
+      </c>
+      <c r="AL13">
+        <v>1.3</v>
+      </c>
+      <c r="AM13">
+        <v>1.35</v>
+      </c>
+      <c r="AN13">
+        <v>0</v>
+      </c>
+      <c r="AO13">
+        <v>1</v>
+      </c>
+      <c r="AP13">
+        <v>3</v>
+      </c>
+      <c r="AQ13">
+        <v>0.5</v>
+      </c>
+      <c r="AR13">
+        <v>0</v>
+      </c>
+      <c r="AS13">
+        <v>1.57</v>
+      </c>
+      <c r="AT13">
+        <v>1.57</v>
+      </c>
+      <c r="AU13">
+        <v>8</v>
+      </c>
+      <c r="AV13">
+        <v>4</v>
+      </c>
+      <c r="AW13">
+        <v>7</v>
+      </c>
+      <c r="AX13">
+        <v>10</v>
+      </c>
+      <c r="AY13">
+        <v>18</v>
+      </c>
+      <c r="AZ13">
+        <v>17</v>
+      </c>
+      <c r="BA13">
+        <v>4</v>
+      </c>
+      <c r="BB13">
+        <v>6</v>
+      </c>
+      <c r="BC13">
+        <v>10</v>
+      </c>
+      <c r="BD13">
+        <v>2.12</v>
+      </c>
+      <c r="BE13">
+        <v>6.25</v>
+      </c>
+      <c r="BF13">
+        <v>1.9</v>
+      </c>
+      <c r="BG13">
+        <v>1.4</v>
+      </c>
+      <c r="BH13">
+        <v>2.7</v>
+      </c>
+      <c r="BI13">
+        <v>1.66</v>
+      </c>
+      <c r="BJ13">
+        <v>2.06</v>
+      </c>
+      <c r="BK13">
+        <v>2.07</v>
+      </c>
+      <c r="BL13">
+        <v>1.66</v>
+      </c>
+      <c r="BM13">
+        <v>2.65</v>
+      </c>
+      <c r="BN13">
+        <v>1.41</v>
+      </c>
+      <c r="BO13">
+        <v>3.55</v>
+      </c>
+      <c r="BP13">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:68">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>7825204</v>
+      </c>
+      <c r="C14" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14" s="2">
+        <v>45717.35763888889</v>
+      </c>
+      <c r="F14">
+        <v>2</v>
+      </c>
+      <c r="G14" t="s">
+        <v>71</v>
+      </c>
+      <c r="H14" t="s">
+        <v>81</v>
+      </c>
+      <c r="I14">
+        <v>2</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14">
+        <v>3</v>
+      </c>
+      <c r="L14">
+        <v>2</v>
+      </c>
+      <c r="M14">
+        <v>2</v>
+      </c>
+      <c r="N14">
+        <v>4</v>
+      </c>
+      <c r="O14" t="s">
+        <v>96</v>
+      </c>
+      <c r="P14" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q14">
+        <v>2.13</v>
+      </c>
+      <c r="R14">
+        <v>2.46</v>
+      </c>
+      <c r="S14">
+        <v>4.8</v>
+      </c>
+      <c r="T14">
+        <v>1.28</v>
+      </c>
+      <c r="U14">
+        <v>3.35</v>
+      </c>
+      <c r="V14">
+        <v>2.28</v>
+      </c>
+      <c r="W14">
+        <v>1.57</v>
+      </c>
+      <c r="X14">
+        <v>4.95</v>
+      </c>
+      <c r="Y14">
+        <v>1.14</v>
+      </c>
+      <c r="Z14">
+        <v>2.08</v>
+      </c>
+      <c r="AA14">
+        <v>3.7</v>
+      </c>
+      <c r="AB14">
+        <v>3.14</v>
+      </c>
+      <c r="AC14">
+        <v>1.01</v>
+      </c>
+      <c r="AD14">
+        <v>13</v>
+      </c>
+      <c r="AE14">
+        <v>1.19</v>
+      </c>
+      <c r="AF14">
+        <v>4.4</v>
+      </c>
+      <c r="AG14">
+        <v>1.6</v>
+      </c>
+      <c r="AH14">
+        <v>2.1</v>
+      </c>
+      <c r="AI14">
+        <v>1.59</v>
+      </c>
+      <c r="AJ14">
+        <v>2.22</v>
+      </c>
+      <c r="AK14">
+        <v>1.19</v>
+      </c>
+      <c r="AL14">
+        <v>1.25</v>
+      </c>
+      <c r="AM14">
+        <v>2.02</v>
+      </c>
+      <c r="AN14">
+        <v>3</v>
+      </c>
+      <c r="AO14">
+        <v>3</v>
+      </c>
+      <c r="AP14">
+        <v>2</v>
+      </c>
+      <c r="AQ14">
+        <v>2</v>
+      </c>
+      <c r="AR14">
+        <v>2.29</v>
+      </c>
+      <c r="AS14">
+        <v>1.3</v>
+      </c>
+      <c r="AT14">
+        <v>3.59</v>
+      </c>
+      <c r="AU14">
+        <v>5</v>
+      </c>
+      <c r="AV14">
+        <v>4</v>
+      </c>
+      <c r="AW14">
+        <v>9</v>
+      </c>
+      <c r="AX14">
+        <v>5</v>
+      </c>
+      <c r="AY14">
+        <v>14</v>
+      </c>
+      <c r="AZ14">
+        <v>9</v>
+      </c>
+      <c r="BA14">
+        <v>8</v>
+      </c>
+      <c r="BB14">
+        <v>2</v>
+      </c>
+      <c r="BC14">
+        <v>10</v>
+      </c>
+      <c r="BD14">
+        <v>1.54</v>
+      </c>
+      <c r="BE14">
+        <v>6.75</v>
+      </c>
+      <c r="BF14">
+        <v>2.7</v>
+      </c>
+      <c r="BG14">
+        <v>1.35</v>
+      </c>
+      <c r="BH14">
+        <v>2.9</v>
+      </c>
+      <c r="BI14">
+        <v>1.6</v>
+      </c>
+      <c r="BJ14">
+        <v>2.17</v>
+      </c>
+      <c r="BK14">
+        <v>1.96</v>
+      </c>
+      <c r="BL14">
+        <v>1.73</v>
+      </c>
+      <c r="BM14">
+        <v>2.48</v>
+      </c>
+      <c r="BN14">
+        <v>1.47</v>
+      </c>
+      <c r="BO14">
+        <v>3.2</v>
+      </c>
+      <c r="BP14">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:68">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>7825205</v>
+      </c>
+      <c r="C15" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" s="2">
+        <v>45717.375</v>
+      </c>
+      <c r="F15">
+        <v>2</v>
+      </c>
+      <c r="G15" t="s">
+        <v>72</v>
+      </c>
+      <c r="H15" t="s">
+        <v>74</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+      <c r="M15">
+        <v>1</v>
+      </c>
+      <c r="N15">
+        <v>2</v>
+      </c>
+      <c r="O15" t="s">
+        <v>97</v>
+      </c>
+      <c r="P15" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q15">
+        <v>3.2</v>
+      </c>
+      <c r="R15">
+        <v>2.3</v>
+      </c>
+      <c r="S15">
+        <v>3</v>
+      </c>
+      <c r="T15">
+        <v>1.33</v>
+      </c>
+      <c r="U15">
+        <v>3.25</v>
+      </c>
+      <c r="V15">
+        <v>2.5</v>
+      </c>
+      <c r="W15">
+        <v>1.5</v>
+      </c>
+      <c r="X15">
+        <v>6.5</v>
+      </c>
+      <c r="Y15">
+        <v>1.11</v>
+      </c>
+      <c r="Z15">
+        <v>2.7</v>
+      </c>
+      <c r="AA15">
+        <v>3.47</v>
+      </c>
+      <c r="AB15">
+        <v>2.43</v>
+      </c>
+      <c r="AC15">
+        <v>1.04</v>
+      </c>
+      <c r="AD15">
+        <v>9</v>
+      </c>
+      <c r="AE15">
+        <v>1.22</v>
+      </c>
+      <c r="AF15">
+        <v>3.9</v>
+      </c>
+      <c r="AG15">
+        <v>1.67</v>
+      </c>
+      <c r="AH15">
+        <v>2</v>
+      </c>
+      <c r="AI15">
+        <v>1.53</v>
+      </c>
+      <c r="AJ15">
+        <v>2.38</v>
+      </c>
+      <c r="AK15">
+        <v>1.51</v>
+      </c>
+      <c r="AL15">
+        <v>1.29</v>
+      </c>
+      <c r="AM15">
+        <v>1.43</v>
+      </c>
+      <c r="AN15">
+        <v>0</v>
+      </c>
+      <c r="AO15">
+        <v>0</v>
+      </c>
+      <c r="AP15">
+        <v>0.5</v>
+      </c>
+      <c r="AQ15">
+        <v>1</v>
+      </c>
+      <c r="AR15">
+        <v>1.22</v>
+      </c>
+      <c r="AS15">
+        <v>0</v>
+      </c>
+      <c r="AT15">
+        <v>1.22</v>
+      </c>
+      <c r="AU15">
+        <v>4</v>
+      </c>
+      <c r="AV15">
+        <v>4</v>
+      </c>
+      <c r="AW15">
+        <v>5</v>
+      </c>
+      <c r="AX15">
+        <v>9</v>
+      </c>
+      <c r="AY15">
+        <v>9</v>
+      </c>
+      <c r="AZ15">
+        <v>13</v>
+      </c>
+      <c r="BA15">
+        <v>5</v>
+      </c>
+      <c r="BB15">
+        <v>8</v>
+      </c>
+      <c r="BC15">
+        <v>13</v>
+      </c>
+      <c r="BD15">
+        <v>2.05</v>
+      </c>
+      <c r="BE15">
+        <v>6.4</v>
+      </c>
+      <c r="BF15">
+        <v>1.95</v>
+      </c>
+      <c r="BG15">
+        <v>1.37</v>
+      </c>
+      <c r="BH15">
+        <v>2.8</v>
+      </c>
+      <c r="BI15">
+        <v>1.64</v>
+      </c>
+      <c r="BJ15">
+        <v>2.1</v>
+      </c>
+      <c r="BK15">
+        <v>2.04</v>
+      </c>
+      <c r="BL15">
+        <v>1.68</v>
+      </c>
+      <c r="BM15">
+        <v>2.63</v>
+      </c>
+      <c r="BN15">
+        <v>1.41</v>
+      </c>
+      <c r="BO15">
+        <v>3.45</v>
+      </c>
+      <c r="BP15">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="110">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -310,6 +310,9 @@
     <t>['68']</t>
   </si>
   <si>
+    <t>['25']</t>
+  </si>
+  <si>
     <t>['42']</t>
   </si>
   <si>
@@ -338,6 +341,9 @@
   </si>
   <si>
     <t>['45+3']</t>
+  </si>
+  <si>
+    <t>['12', '59']</t>
   </si>
 </sst>
 </file>
@@ -699,7 +705,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP15"/>
+  <dimension ref="A1:BP16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1033,7 +1039,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AQ2">
         <v>0</v>
@@ -1161,7 +1167,7 @@
         <v>87</v>
       </c>
       <c r="P3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q3">
         <v>1.7</v>
@@ -1367,7 +1373,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -1573,7 +1579,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q5">
         <v>2.85</v>
@@ -1779,7 +1785,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q6">
         <v>2.2</v>
@@ -2191,7 +2197,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q8">
         <v>2.04</v>
@@ -2397,7 +2403,7 @@
         <v>92</v>
       </c>
       <c r="P9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q9">
         <v>1.5</v>
@@ -2603,7 +2609,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q10">
         <v>2.1</v>
@@ -3015,7 +3021,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q12">
         <v>3.1</v>
@@ -3221,7 +3227,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -3427,7 +3433,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q14">
         <v>2.13</v>
@@ -3633,7 +3639,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q15">
         <v>3.2</v>
@@ -3790,6 +3796,212 @@
       </c>
       <c r="BP15">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:68">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>7825207</v>
+      </c>
+      <c r="C16" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" s="2">
+        <v>45718.3125</v>
+      </c>
+      <c r="F16">
+        <v>2</v>
+      </c>
+      <c r="G16" t="s">
+        <v>70</v>
+      </c>
+      <c r="H16" t="s">
+        <v>76</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="K16">
+        <v>2</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
+      <c r="M16">
+        <v>2</v>
+      </c>
+      <c r="N16">
+        <v>3</v>
+      </c>
+      <c r="O16" t="s">
+        <v>98</v>
+      </c>
+      <c r="P16" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q16">
+        <v>1.78</v>
+      </c>
+      <c r="R16">
+        <v>2.65</v>
+      </c>
+      <c r="S16">
+        <v>7</v>
+      </c>
+      <c r="T16">
+        <v>1.27</v>
+      </c>
+      <c r="U16">
+        <v>3.45</v>
+      </c>
+      <c r="V16">
+        <v>2.26</v>
+      </c>
+      <c r="W16">
+        <v>1.58</v>
+      </c>
+      <c r="X16">
+        <v>4.95</v>
+      </c>
+      <c r="Y16">
+        <v>1.14</v>
+      </c>
+      <c r="Z16">
+        <v>1.36</v>
+      </c>
+      <c r="AA16">
+        <v>4.6</v>
+      </c>
+      <c r="AB16">
+        <v>7</v>
+      </c>
+      <c r="AC16">
+        <v>1.01</v>
+      </c>
+      <c r="AD16">
+        <v>13</v>
+      </c>
+      <c r="AE16">
+        <v>1.19</v>
+      </c>
+      <c r="AF16">
+        <v>4.3</v>
+      </c>
+      <c r="AG16">
+        <v>1.6</v>
+      </c>
+      <c r="AH16">
+        <v>2.26</v>
+      </c>
+      <c r="AI16">
+        <v>1.84</v>
+      </c>
+      <c r="AJ16">
+        <v>1.86</v>
+      </c>
+      <c r="AK16">
+        <v>1.09</v>
+      </c>
+      <c r="AL16">
+        <v>1.15</v>
+      </c>
+      <c r="AM16">
+        <v>2.85</v>
+      </c>
+      <c r="AN16">
+        <v>3</v>
+      </c>
+      <c r="AO16">
+        <v>0</v>
+      </c>
+      <c r="AP16">
+        <v>1.5</v>
+      </c>
+      <c r="AQ16">
+        <v>3</v>
+      </c>
+      <c r="AR16">
+        <v>2.91</v>
+      </c>
+      <c r="AS16">
+        <v>0</v>
+      </c>
+      <c r="AT16">
+        <v>2.91</v>
+      </c>
+      <c r="AU16">
+        <v>5</v>
+      </c>
+      <c r="AV16">
+        <v>5</v>
+      </c>
+      <c r="AW16">
+        <v>9</v>
+      </c>
+      <c r="AX16">
+        <v>5</v>
+      </c>
+      <c r="AY16">
+        <v>18</v>
+      </c>
+      <c r="AZ16">
+        <v>11</v>
+      </c>
+      <c r="BA16">
+        <v>4</v>
+      </c>
+      <c r="BB16">
+        <v>3</v>
+      </c>
+      <c r="BC16">
+        <v>7</v>
+      </c>
+      <c r="BD16">
+        <v>1.3</v>
+      </c>
+      <c r="BE16">
+        <v>7.5</v>
+      </c>
+      <c r="BF16">
+        <v>3.8</v>
+      </c>
+      <c r="BG16">
+        <v>1.23</v>
+      </c>
+      <c r="BH16">
+        <v>3.65</v>
+      </c>
+      <c r="BI16">
+        <v>1.41</v>
+      </c>
+      <c r="BJ16">
+        <v>2.65</v>
+      </c>
+      <c r="BK16">
+        <v>1.66</v>
+      </c>
+      <c r="BL16">
+        <v>2.06</v>
+      </c>
+      <c r="BM16">
+        <v>2.02</v>
+      </c>
+      <c r="BN16">
+        <v>1.68</v>
+      </c>
+      <c r="BO16">
+        <v>2.55</v>
+      </c>
+      <c r="BP16">
+        <v>1.44</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="111">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -253,6 +253,9 @@
     <t>Meizhou Hakka</t>
   </si>
   <si>
+    <t>Qingdao Youth Island</t>
+  </si>
+  <si>
     <t>Wuhan Three Towns</t>
   </si>
   <si>
@@ -262,9 +265,6 @@
     <t>Beijing Guoan</t>
   </si>
   <si>
-    <t>Qingdao Youth Island</t>
-  </si>
-  <si>
     <t>Dalian Zhixing</t>
   </si>
   <si>
@@ -311,6 +311,9 @@
   </si>
   <si>
     <t>['25']</t>
+  </si>
+  <si>
+    <t>['4', '80']</t>
   </si>
   <si>
     <t>['42']</t>
@@ -705,7 +708,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP16"/>
+  <dimension ref="A1:BP17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -937,7 +940,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -1143,7 +1146,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -1167,7 +1170,7 @@
         <v>87</v>
       </c>
       <c r="P3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q3">
         <v>1.7</v>
@@ -1349,7 +1352,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1373,7 +1376,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -1555,7 +1558,7 @@
         <v>73</v>
       </c>
       <c r="H5" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I5">
         <v>2</v>
@@ -1579,7 +1582,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q5">
         <v>2.85</v>
@@ -1785,7 +1788,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q6">
         <v>2.2</v>
@@ -2197,7 +2200,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q8">
         <v>2.04</v>
@@ -2403,7 +2406,7 @@
         <v>92</v>
       </c>
       <c r="P9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q9">
         <v>1.5</v>
@@ -2609,7 +2612,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q10">
         <v>2.1</v>
@@ -2791,7 +2794,7 @@
         <v>77</v>
       </c>
       <c r="H11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -3021,7 +3024,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q12">
         <v>3.1</v>
@@ -3227,7 +3230,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -3409,7 +3412,7 @@
         <v>71</v>
       </c>
       <c r="H14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I14">
         <v>2</v>
@@ -3433,7 +3436,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q14">
         <v>2.13</v>
@@ -3639,7 +3642,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q15">
         <v>3.2</v>
@@ -3845,7 +3848,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q16">
         <v>1.78</v>
@@ -4002,6 +4005,212 @@
       </c>
       <c r="BP16">
         <v>1.44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:68">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>7825206</v>
+      </c>
+      <c r="C17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D17" t="s">
+        <v>69</v>
+      </c>
+      <c r="E17" s="2">
+        <v>45719.125</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
+      </c>
+      <c r="G17" t="s">
+        <v>79</v>
+      </c>
+      <c r="H17" t="s">
+        <v>80</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17">
+        <v>2</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>2</v>
+      </c>
+      <c r="O17" t="s">
+        <v>99</v>
+      </c>
+      <c r="P17" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q17">
+        <v>2.88</v>
+      </c>
+      <c r="R17">
+        <v>2.3</v>
+      </c>
+      <c r="S17">
+        <v>3.4</v>
+      </c>
+      <c r="T17">
+        <v>1.33</v>
+      </c>
+      <c r="U17">
+        <v>3.25</v>
+      </c>
+      <c r="V17">
+        <v>2.5</v>
+      </c>
+      <c r="W17">
+        <v>1.5</v>
+      </c>
+      <c r="X17">
+        <v>6.5</v>
+      </c>
+      <c r="Y17">
+        <v>1.11</v>
+      </c>
+      <c r="Z17">
+        <v>2.36</v>
+      </c>
+      <c r="AA17">
+        <v>3.51</v>
+      </c>
+      <c r="AB17">
+        <v>2.76</v>
+      </c>
+      <c r="AC17">
+        <v>1.01</v>
+      </c>
+      <c r="AD17">
+        <v>13</v>
+      </c>
+      <c r="AE17">
+        <v>1.2</v>
+      </c>
+      <c r="AF17">
+        <v>4.31</v>
+      </c>
+      <c r="AG17">
+        <v>1.87</v>
+      </c>
+      <c r="AH17">
+        <v>1.87</v>
+      </c>
+      <c r="AI17">
+        <v>1.57</v>
+      </c>
+      <c r="AJ17">
+        <v>2.25</v>
+      </c>
+      <c r="AK17">
+        <v>1.39</v>
+      </c>
+      <c r="AL17">
+        <v>1.26</v>
+      </c>
+      <c r="AM17">
+        <v>1.6</v>
+      </c>
+      <c r="AN17">
+        <v>0</v>
+      </c>
+      <c r="AO17">
+        <v>0</v>
+      </c>
+      <c r="AP17">
+        <v>3</v>
+      </c>
+      <c r="AQ17">
+        <v>0</v>
+      </c>
+      <c r="AR17">
+        <v>0</v>
+      </c>
+      <c r="AS17">
+        <v>0.95</v>
+      </c>
+      <c r="AT17">
+        <v>0.95</v>
+      </c>
+      <c r="AU17">
+        <v>3</v>
+      </c>
+      <c r="AV17">
+        <v>0</v>
+      </c>
+      <c r="AW17">
+        <v>5</v>
+      </c>
+      <c r="AX17">
+        <v>2</v>
+      </c>
+      <c r="AY17">
+        <v>8</v>
+      </c>
+      <c r="AZ17">
+        <v>2</v>
+      </c>
+      <c r="BA17">
+        <v>3</v>
+      </c>
+      <c r="BB17">
+        <v>0</v>
+      </c>
+      <c r="BC17">
+        <v>3</v>
+      </c>
+      <c r="BD17">
+        <v>1.9</v>
+      </c>
+      <c r="BE17">
+        <v>6.25</v>
+      </c>
+      <c r="BF17">
+        <v>2.15</v>
+      </c>
+      <c r="BG17">
+        <v>1.34</v>
+      </c>
+      <c r="BH17">
+        <v>2.9</v>
+      </c>
+      <c r="BI17">
+        <v>1.58</v>
+      </c>
+      <c r="BJ17">
+        <v>2.18</v>
+      </c>
+      <c r="BK17">
+        <v>1.96</v>
+      </c>
+      <c r="BL17">
+        <v>1.73</v>
+      </c>
+      <c r="BM17">
+        <v>2.48</v>
+      </c>
+      <c r="BN17">
+        <v>1.47</v>
+      </c>
+      <c r="BO17">
+        <v>3.2</v>
+      </c>
+      <c r="BP17">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="119">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -259,21 +259,21 @@
     <t>Wuhan Three Towns</t>
   </si>
   <si>
+    <t>Sichuan Jiuniu</t>
+  </si>
+  <si>
+    <t>Dalian Zhixing</t>
+  </si>
+  <si>
+    <t>Henan Jianye</t>
+  </si>
+  <si>
     <t>Changchun Yatai</t>
   </si>
   <si>
     <t>Beijing Guoan</t>
   </si>
   <si>
-    <t>Dalian Zhixing</t>
-  </si>
-  <si>
-    <t>Henan Jianye</t>
-  </si>
-  <si>
-    <t>Sichuan Jiuniu</t>
-  </si>
-  <si>
     <t>['59']</t>
   </si>
   <si>
@@ -316,6 +316,18 @@
     <t>['4', '80']</t>
   </si>
   <si>
+    <t>['9', '19', '45+1']</t>
+  </si>
+  <si>
+    <t>['33', '47', '84']</t>
+  </si>
+  <si>
+    <t>['31', '69']</t>
+  </si>
+  <si>
+    <t>['17']</t>
+  </si>
+  <si>
     <t>['42']</t>
   </si>
   <si>
@@ -347,6 +359,18 @@
   </si>
   <si>
     <t>['12', '59']</t>
+  </si>
+  <si>
+    <t>['25', '56', '83']</t>
+  </si>
+  <si>
+    <t>['4', '25', '35', '45+1']</t>
+  </si>
+  <si>
+    <t>['13', '24', '51', '81']</t>
+  </si>
+  <si>
+    <t>['67', '74', '90+5']</t>
   </si>
 </sst>
 </file>
@@ -708,7 +732,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP17"/>
+  <dimension ref="A1:BP23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1146,7 +1170,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -1170,7 +1194,7 @@
         <v>87</v>
       </c>
       <c r="P3" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="Q3">
         <v>1.7</v>
@@ -1352,7 +1376,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1376,7 +1400,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -1582,7 +1606,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="Q5">
         <v>2.85</v>
@@ -1764,7 +1788,7 @@
         <v>74</v>
       </c>
       <c r="H6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -1788,7 +1812,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="Q6">
         <v>2.2</v>
@@ -1970,7 +1994,7 @@
         <v>75</v>
       </c>
       <c r="H7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -2200,7 +2224,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="Q8">
         <v>2.04</v>
@@ -2278,7 +2302,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ8">
         <v>1</v>
@@ -2382,7 +2406,7 @@
         <v>77</v>
       </c>
       <c r="H9" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="I9">
         <v>1</v>
@@ -2406,7 +2430,7 @@
         <v>92</v>
       </c>
       <c r="P9" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="Q9">
         <v>1.5</v>
@@ -2588,7 +2612,7 @@
         <v>75</v>
       </c>
       <c r="H10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I10">
         <v>1</v>
@@ -2612,7 +2636,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="Q10">
         <v>2.1</v>
@@ -2794,7 +2818,7 @@
         <v>77</v>
       </c>
       <c r="H11" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -3000,7 +3024,7 @@
         <v>73</v>
       </c>
       <c r="H12" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -3024,7 +3048,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="Q12">
         <v>3.1</v>
@@ -3206,7 +3230,7 @@
         <v>78</v>
       </c>
       <c r="H13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I13">
         <v>1</v>
@@ -3230,7 +3254,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -3412,7 +3436,7 @@
         <v>71</v>
       </c>
       <c r="H14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="I14">
         <v>2</v>
@@ -3436,7 +3460,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="Q14">
         <v>2.13</v>
@@ -3642,7 +3666,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="Q15">
         <v>3.2</v>
@@ -3723,7 +3747,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR15">
         <v>1.22</v>
@@ -3848,7 +3872,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="Q16">
         <v>1.78</v>
@@ -4132,7 +4156,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ17">
         <v>0</v>
@@ -4211,6 +4235,1242 @@
       </c>
       <c r="BP17">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:68">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>7825208</v>
+      </c>
+      <c r="C18" t="s">
+        <v>68</v>
+      </c>
+      <c r="D18" t="s">
+        <v>69</v>
+      </c>
+      <c r="E18" s="2">
+        <v>45744.33333333334</v>
+      </c>
+      <c r="F18">
+        <v>3</v>
+      </c>
+      <c r="G18" t="s">
+        <v>79</v>
+      </c>
+      <c r="H18" t="s">
+        <v>77</v>
+      </c>
+      <c r="I18">
+        <v>3</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="K18">
+        <v>4</v>
+      </c>
+      <c r="L18">
+        <v>3</v>
+      </c>
+      <c r="M18">
+        <v>3</v>
+      </c>
+      <c r="N18">
+        <v>6</v>
+      </c>
+      <c r="O18" t="s">
+        <v>100</v>
+      </c>
+      <c r="P18" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q18">
+        <v>5.5</v>
+      </c>
+      <c r="R18">
+        <v>2.6</v>
+      </c>
+      <c r="S18">
+        <v>1.91</v>
+      </c>
+      <c r="T18">
+        <v>1.25</v>
+      </c>
+      <c r="U18">
+        <v>3.75</v>
+      </c>
+      <c r="V18">
+        <v>2.2</v>
+      </c>
+      <c r="W18">
+        <v>1.62</v>
+      </c>
+      <c r="X18">
+        <v>5</v>
+      </c>
+      <c r="Y18">
+        <v>1.17</v>
+      </c>
+      <c r="Z18">
+        <v>6.5</v>
+      </c>
+      <c r="AA18">
+        <v>5.4</v>
+      </c>
+      <c r="AB18">
+        <v>1.37</v>
+      </c>
+      <c r="AC18">
+        <v>1.01</v>
+      </c>
+      <c r="AD18">
+        <v>16.5</v>
+      </c>
+      <c r="AE18">
+        <v>1.14</v>
+      </c>
+      <c r="AF18">
+        <v>5.36</v>
+      </c>
+      <c r="AG18">
+        <v>1.38</v>
+      </c>
+      <c r="AH18">
+        <v>2.9</v>
+      </c>
+      <c r="AI18">
+        <v>1.62</v>
+      </c>
+      <c r="AJ18">
+        <v>2.2</v>
+      </c>
+      <c r="AK18">
+        <v>2.62</v>
+      </c>
+      <c r="AL18">
+        <v>1.13</v>
+      </c>
+      <c r="AM18">
+        <v>1.1</v>
+      </c>
+      <c r="AN18">
+        <v>3</v>
+      </c>
+      <c r="AO18">
+        <v>0</v>
+      </c>
+      <c r="AP18">
+        <v>2</v>
+      </c>
+      <c r="AQ18">
+        <v>1</v>
+      </c>
+      <c r="AR18">
+        <v>0.8</v>
+      </c>
+      <c r="AS18">
+        <v>0</v>
+      </c>
+      <c r="AT18">
+        <v>0.8</v>
+      </c>
+      <c r="AU18">
+        <v>5</v>
+      </c>
+      <c r="AV18">
+        <v>4</v>
+      </c>
+      <c r="AW18">
+        <v>6</v>
+      </c>
+      <c r="AX18">
+        <v>14</v>
+      </c>
+      <c r="AY18">
+        <v>14</v>
+      </c>
+      <c r="AZ18">
+        <v>23</v>
+      </c>
+      <c r="BA18">
+        <v>1</v>
+      </c>
+      <c r="BB18">
+        <v>8</v>
+      </c>
+      <c r="BC18">
+        <v>9</v>
+      </c>
+      <c r="BD18">
+        <v>3.3</v>
+      </c>
+      <c r="BE18">
+        <v>6.75</v>
+      </c>
+      <c r="BF18">
+        <v>1.42</v>
+      </c>
+      <c r="BG18">
+        <v>1.27</v>
+      </c>
+      <c r="BH18">
+        <v>3.3</v>
+      </c>
+      <c r="BI18">
+        <v>1.47</v>
+      </c>
+      <c r="BJ18">
+        <v>2.48</v>
+      </c>
+      <c r="BK18">
+        <v>1.75</v>
+      </c>
+      <c r="BL18">
+        <v>1.95</v>
+      </c>
+      <c r="BM18">
+        <v>2.18</v>
+      </c>
+      <c r="BN18">
+        <v>1.58</v>
+      </c>
+      <c r="BO18">
+        <v>2.8</v>
+      </c>
+      <c r="BP18">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:68">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>7825209</v>
+      </c>
+      <c r="C19" t="s">
+        <v>68</v>
+      </c>
+      <c r="D19" t="s">
+        <v>69</v>
+      </c>
+      <c r="E19" s="2">
+        <v>45744.35763888889</v>
+      </c>
+      <c r="F19">
+        <v>3</v>
+      </c>
+      <c r="G19" t="s">
+        <v>80</v>
+      </c>
+      <c r="H19" t="s">
+        <v>74</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>4</v>
+      </c>
+      <c r="K19">
+        <v>4</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>4</v>
+      </c>
+      <c r="N19">
+        <v>4</v>
+      </c>
+      <c r="O19" t="s">
+        <v>88</v>
+      </c>
+      <c r="P19" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q19">
+        <v>3.75</v>
+      </c>
+      <c r="R19">
+        <v>2.1</v>
+      </c>
+      <c r="S19">
+        <v>3.1</v>
+      </c>
+      <c r="T19">
+        <v>1.44</v>
+      </c>
+      <c r="U19">
+        <v>2.63</v>
+      </c>
+      <c r="V19">
+        <v>3.25</v>
+      </c>
+      <c r="W19">
+        <v>1.33</v>
+      </c>
+      <c r="X19">
+        <v>9</v>
+      </c>
+      <c r="Y19">
+        <v>1.07</v>
+      </c>
+      <c r="Z19">
+        <v>3.4</v>
+      </c>
+      <c r="AA19">
+        <v>3.15</v>
+      </c>
+      <c r="AB19">
+        <v>2.15</v>
+      </c>
+      <c r="AC19">
+        <v>1</v>
+      </c>
+      <c r="AD19">
+        <v>9</v>
+      </c>
+      <c r="AE19">
+        <v>1.32</v>
+      </c>
+      <c r="AF19">
+        <v>3.2</v>
+      </c>
+      <c r="AG19">
+        <v>1.96</v>
+      </c>
+      <c r="AH19">
+        <v>1.82</v>
+      </c>
+      <c r="AI19">
+        <v>1.8</v>
+      </c>
+      <c r="AJ19">
+        <v>1.95</v>
+      </c>
+      <c r="AK19">
+        <v>1.57</v>
+      </c>
+      <c r="AL19">
+        <v>1.28</v>
+      </c>
+      <c r="AM19">
+        <v>1.38</v>
+      </c>
+      <c r="AN19">
+        <v>0</v>
+      </c>
+      <c r="AO19">
+        <v>1</v>
+      </c>
+      <c r="AP19">
+        <v>0</v>
+      </c>
+      <c r="AQ19">
+        <v>2</v>
+      </c>
+      <c r="AR19">
+        <v>0</v>
+      </c>
+      <c r="AS19">
+        <v>1.38</v>
+      </c>
+      <c r="AT19">
+        <v>1.38</v>
+      </c>
+      <c r="AU19">
+        <v>5</v>
+      </c>
+      <c r="AV19">
+        <v>7</v>
+      </c>
+      <c r="AW19">
+        <v>10</v>
+      </c>
+      <c r="AX19">
+        <v>10</v>
+      </c>
+      <c r="AY19">
+        <v>20</v>
+      </c>
+      <c r="AZ19">
+        <v>20</v>
+      </c>
+      <c r="BA19">
+        <v>5</v>
+      </c>
+      <c r="BB19">
+        <v>2</v>
+      </c>
+      <c r="BC19">
+        <v>7</v>
+      </c>
+      <c r="BD19">
+        <v>2.08</v>
+      </c>
+      <c r="BE19">
+        <v>6.4</v>
+      </c>
+      <c r="BF19">
+        <v>1.9</v>
+      </c>
+      <c r="BG19">
+        <v>1.43</v>
+      </c>
+      <c r="BH19">
+        <v>2.55</v>
+      </c>
+      <c r="BI19">
+        <v>1.73</v>
+      </c>
+      <c r="BJ19">
+        <v>1.96</v>
+      </c>
+      <c r="BK19">
+        <v>2.17</v>
+      </c>
+      <c r="BL19">
+        <v>1.6</v>
+      </c>
+      <c r="BM19">
+        <v>2.8</v>
+      </c>
+      <c r="BN19">
+        <v>1.37</v>
+      </c>
+      <c r="BO19">
+        <v>3.7</v>
+      </c>
+      <c r="BP19">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:68">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>7825210</v>
+      </c>
+      <c r="C20" t="s">
+        <v>68</v>
+      </c>
+      <c r="D20" t="s">
+        <v>69</v>
+      </c>
+      <c r="E20" s="2">
+        <v>45744.375</v>
+      </c>
+      <c r="F20">
+        <v>3</v>
+      </c>
+      <c r="G20" t="s">
+        <v>81</v>
+      </c>
+      <c r="H20" t="s">
+        <v>72</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+      <c r="J20">
+        <v>2</v>
+      </c>
+      <c r="K20">
+        <v>3</v>
+      </c>
+      <c r="L20">
+        <v>3</v>
+      </c>
+      <c r="M20">
+        <v>4</v>
+      </c>
+      <c r="N20">
+        <v>7</v>
+      </c>
+      <c r="O20" t="s">
+        <v>101</v>
+      </c>
+      <c r="P20" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q20">
+        <v>3.25</v>
+      </c>
+      <c r="R20">
+        <v>2</v>
+      </c>
+      <c r="S20">
+        <v>3.6</v>
+      </c>
+      <c r="T20">
+        <v>1.5</v>
+      </c>
+      <c r="U20">
+        <v>2.5</v>
+      </c>
+      <c r="V20">
+        <v>3.4</v>
+      </c>
+      <c r="W20">
+        <v>1.3</v>
+      </c>
+      <c r="X20">
+        <v>10</v>
+      </c>
+      <c r="Y20">
+        <v>1.06</v>
+      </c>
+      <c r="Z20">
+        <v>2.45</v>
+      </c>
+      <c r="AA20">
+        <v>3.2</v>
+      </c>
+      <c r="AB20">
+        <v>2.88</v>
+      </c>
+      <c r="AC20">
+        <v>1</v>
+      </c>
+      <c r="AD20">
+        <v>9.1</v>
+      </c>
+      <c r="AE20">
+        <v>1.34</v>
+      </c>
+      <c r="AF20">
+        <v>3.02</v>
+      </c>
+      <c r="AG20">
+        <v>2.15</v>
+      </c>
+      <c r="AH20">
+        <v>1.67</v>
+      </c>
+      <c r="AI20">
+        <v>1.95</v>
+      </c>
+      <c r="AJ20">
+        <v>1.8</v>
+      </c>
+      <c r="AK20">
+        <v>1.4</v>
+      </c>
+      <c r="AL20">
+        <v>1.3</v>
+      </c>
+      <c r="AM20">
+        <v>1.5</v>
+      </c>
+      <c r="AN20">
+        <v>0</v>
+      </c>
+      <c r="AO20">
+        <v>0</v>
+      </c>
+      <c r="AP20">
+        <v>0</v>
+      </c>
+      <c r="AQ20">
+        <v>3</v>
+      </c>
+      <c r="AR20">
+        <v>0</v>
+      </c>
+      <c r="AS20">
+        <v>0</v>
+      </c>
+      <c r="AT20">
+        <v>0</v>
+      </c>
+      <c r="AU20">
+        <v>9</v>
+      </c>
+      <c r="AV20">
+        <v>6</v>
+      </c>
+      <c r="AW20">
+        <v>10</v>
+      </c>
+      <c r="AX20">
+        <v>4</v>
+      </c>
+      <c r="AY20">
+        <v>19</v>
+      </c>
+      <c r="AZ20">
+        <v>10</v>
+      </c>
+      <c r="BA20">
+        <v>10</v>
+      </c>
+      <c r="BB20">
+        <v>2</v>
+      </c>
+      <c r="BC20">
+        <v>12</v>
+      </c>
+      <c r="BD20">
+        <v>1.94</v>
+      </c>
+      <c r="BE20">
+        <v>6.25</v>
+      </c>
+      <c r="BF20">
+        <v>2.08</v>
+      </c>
+      <c r="BG20">
+        <v>1.47</v>
+      </c>
+      <c r="BH20">
+        <v>2.48</v>
+      </c>
+      <c r="BI20">
+        <v>1.77</v>
+      </c>
+      <c r="BJ20">
+        <v>1.91</v>
+      </c>
+      <c r="BK20">
+        <v>2.23</v>
+      </c>
+      <c r="BL20">
+        <v>1.56</v>
+      </c>
+      <c r="BM20">
+        <v>2.9</v>
+      </c>
+      <c r="BN20">
+        <v>1.34</v>
+      </c>
+      <c r="BO20">
+        <v>3.95</v>
+      </c>
+      <c r="BP20">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:68">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>7825211</v>
+      </c>
+      <c r="C21" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" t="s">
+        <v>69</v>
+      </c>
+      <c r="E21" s="2">
+        <v>45745.1875</v>
+      </c>
+      <c r="F21">
+        <v>3</v>
+      </c>
+      <c r="G21" t="s">
+        <v>82</v>
+      </c>
+      <c r="H21" t="s">
+        <v>84</v>
+      </c>
+      <c r="I21">
+        <v>1</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>1</v>
+      </c>
+      <c r="L21">
+        <v>2</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>2</v>
+      </c>
+      <c r="O21" t="s">
+        <v>102</v>
+      </c>
+      <c r="P21" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q21">
+        <v>3.25</v>
+      </c>
+      <c r="R21">
+        <v>2.2</v>
+      </c>
+      <c r="S21">
+        <v>3.25</v>
+      </c>
+      <c r="T21">
+        <v>1.4</v>
+      </c>
+      <c r="U21">
+        <v>2.75</v>
+      </c>
+      <c r="V21">
+        <v>2.75</v>
+      </c>
+      <c r="W21">
+        <v>1.4</v>
+      </c>
+      <c r="X21">
+        <v>8</v>
+      </c>
+      <c r="Y21">
+        <v>1.08</v>
+      </c>
+      <c r="Z21">
+        <v>2.89</v>
+      </c>
+      <c r="AA21">
+        <v>3.53</v>
+      </c>
+      <c r="AB21">
+        <v>2.27</v>
+      </c>
+      <c r="AC21">
+        <v>1</v>
+      </c>
+      <c r="AD21">
+        <v>9</v>
+      </c>
+      <c r="AE21">
+        <v>1.24</v>
+      </c>
+      <c r="AF21">
+        <v>3.36</v>
+      </c>
+      <c r="AG21">
+        <v>1.92</v>
+      </c>
+      <c r="AH21">
+        <v>1.82</v>
+      </c>
+      <c r="AI21">
+        <v>1.7</v>
+      </c>
+      <c r="AJ21">
+        <v>2.05</v>
+      </c>
+      <c r="AK21">
+        <v>1.44</v>
+      </c>
+      <c r="AL21">
+        <v>1.33</v>
+      </c>
+      <c r="AM21">
+        <v>1.44</v>
+      </c>
+      <c r="AN21">
+        <v>0</v>
+      </c>
+      <c r="AO21">
+        <v>0</v>
+      </c>
+      <c r="AP21">
+        <v>3</v>
+      </c>
+      <c r="AQ21">
+        <v>0</v>
+      </c>
+      <c r="AR21">
+        <v>0</v>
+      </c>
+      <c r="AS21">
+        <v>0.88</v>
+      </c>
+      <c r="AT21">
+        <v>0.88</v>
+      </c>
+      <c r="AU21">
+        <v>7</v>
+      </c>
+      <c r="AV21">
+        <v>2</v>
+      </c>
+      <c r="AW21">
+        <v>14</v>
+      </c>
+      <c r="AX21">
+        <v>4</v>
+      </c>
+      <c r="AY21">
+        <v>25</v>
+      </c>
+      <c r="AZ21">
+        <v>7</v>
+      </c>
+      <c r="BA21">
+        <v>9</v>
+      </c>
+      <c r="BB21">
+        <v>2</v>
+      </c>
+      <c r="BC21">
+        <v>11</v>
+      </c>
+      <c r="BD21">
+        <v>2</v>
+      </c>
+      <c r="BE21">
+        <v>6.4</v>
+      </c>
+      <c r="BF21">
+        <v>1.98</v>
+      </c>
+      <c r="BG21">
+        <v>1.3</v>
+      </c>
+      <c r="BH21">
+        <v>3.1</v>
+      </c>
+      <c r="BI21">
+        <v>1.53</v>
+      </c>
+      <c r="BJ21">
+        <v>2.32</v>
+      </c>
+      <c r="BK21">
+        <v>1.86</v>
+      </c>
+      <c r="BL21">
+        <v>1.82</v>
+      </c>
+      <c r="BM21">
+        <v>2.35</v>
+      </c>
+      <c r="BN21">
+        <v>1.5</v>
+      </c>
+      <c r="BO21">
+        <v>3.05</v>
+      </c>
+      <c r="BP21">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="22" spans="1:68">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>7825212</v>
+      </c>
+      <c r="C22" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E22" s="2">
+        <v>45745.1875</v>
+      </c>
+      <c r="F22">
+        <v>3</v>
+      </c>
+      <c r="G22" t="s">
+        <v>76</v>
+      </c>
+      <c r="H22" t="s">
+        <v>73</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>1</v>
+      </c>
+      <c r="L22">
+        <v>1</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>1</v>
+      </c>
+      <c r="O22" t="s">
+        <v>103</v>
+      </c>
+      <c r="P22" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q22">
+        <v>2.2</v>
+      </c>
+      <c r="R22">
+        <v>2.25</v>
+      </c>
+      <c r="S22">
+        <v>5.5</v>
+      </c>
+      <c r="T22">
+        <v>1.36</v>
+      </c>
+      <c r="U22">
+        <v>3</v>
+      </c>
+      <c r="V22">
+        <v>2.75</v>
+      </c>
+      <c r="W22">
+        <v>1.4</v>
+      </c>
+      <c r="X22">
+        <v>7</v>
+      </c>
+      <c r="Y22">
+        <v>1.1</v>
+      </c>
+      <c r="Z22">
+        <v>1.57</v>
+      </c>
+      <c r="AA22">
+        <v>3.7</v>
+      </c>
+      <c r="AB22">
+        <v>6.25</v>
+      </c>
+      <c r="AC22">
+        <v>1.01</v>
+      </c>
+      <c r="AD22">
+        <v>8.4</v>
+      </c>
+      <c r="AE22">
+        <v>1.23</v>
+      </c>
+      <c r="AF22">
+        <v>3.44</v>
+      </c>
+      <c r="AG22">
+        <v>1.85</v>
+      </c>
+      <c r="AH22">
+        <v>1.95</v>
+      </c>
+      <c r="AI22">
+        <v>1.91</v>
+      </c>
+      <c r="AJ22">
+        <v>1.91</v>
+      </c>
+      <c r="AK22">
+        <v>1.15</v>
+      </c>
+      <c r="AL22">
+        <v>1.29</v>
+      </c>
+      <c r="AM22">
+        <v>2.2</v>
+      </c>
+      <c r="AN22">
+        <v>1</v>
+      </c>
+      <c r="AO22">
+        <v>0</v>
+      </c>
+      <c r="AP22">
+        <v>2</v>
+      </c>
+      <c r="AQ22">
+        <v>0</v>
+      </c>
+      <c r="AR22">
+        <v>3.42</v>
+      </c>
+      <c r="AS22">
+        <v>0</v>
+      </c>
+      <c r="AT22">
+        <v>3.42</v>
+      </c>
+      <c r="AU22">
+        <v>11</v>
+      </c>
+      <c r="AV22">
+        <v>2</v>
+      </c>
+      <c r="AW22">
+        <v>15</v>
+      </c>
+      <c r="AX22">
+        <v>6</v>
+      </c>
+      <c r="AY22">
+        <v>31</v>
+      </c>
+      <c r="AZ22">
+        <v>8</v>
+      </c>
+      <c r="BA22">
+        <v>10</v>
+      </c>
+      <c r="BB22">
+        <v>3</v>
+      </c>
+      <c r="BC22">
+        <v>13</v>
+      </c>
+      <c r="BD22">
+        <v>1.43</v>
+      </c>
+      <c r="BE22">
+        <v>7</v>
+      </c>
+      <c r="BF22">
+        <v>3.15</v>
+      </c>
+      <c r="BG22">
+        <v>1.25</v>
+      </c>
+      <c r="BH22">
+        <v>3.45</v>
+      </c>
+      <c r="BI22">
+        <v>1.44</v>
+      </c>
+      <c r="BJ22">
+        <v>2.55</v>
+      </c>
+      <c r="BK22">
+        <v>1.7</v>
+      </c>
+      <c r="BL22">
+        <v>2.02</v>
+      </c>
+      <c r="BM22">
+        <v>2.08</v>
+      </c>
+      <c r="BN22">
+        <v>1.65</v>
+      </c>
+      <c r="BO22">
+        <v>2.63</v>
+      </c>
+      <c r="BP22">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:68">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>7825213</v>
+      </c>
+      <c r="C23" t="s">
+        <v>68</v>
+      </c>
+      <c r="D23" t="s">
+        <v>69</v>
+      </c>
+      <c r="E23" s="2">
+        <v>45745.29166666666</v>
+      </c>
+      <c r="F23">
+        <v>3</v>
+      </c>
+      <c r="G23" t="s">
+        <v>83</v>
+      </c>
+      <c r="H23" t="s">
+        <v>71</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>1</v>
+      </c>
+      <c r="L23">
+        <v>1</v>
+      </c>
+      <c r="M23">
+        <v>3</v>
+      </c>
+      <c r="N23">
+        <v>4</v>
+      </c>
+      <c r="O23" t="s">
+        <v>104</v>
+      </c>
+      <c r="P23" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q23">
+        <v>4</v>
+      </c>
+      <c r="R23">
+        <v>2.2</v>
+      </c>
+      <c r="S23">
+        <v>2.6</v>
+      </c>
+      <c r="T23">
+        <v>1.36</v>
+      </c>
+      <c r="U23">
+        <v>3</v>
+      </c>
+      <c r="V23">
+        <v>2.75</v>
+      </c>
+      <c r="W23">
+        <v>1.4</v>
+      </c>
+      <c r="X23">
+        <v>7</v>
+      </c>
+      <c r="Y23">
+        <v>1.1</v>
+      </c>
+      <c r="Z23">
+        <v>3.75</v>
+      </c>
+      <c r="AA23">
+        <v>3.7</v>
+      </c>
+      <c r="AB23">
+        <v>1.88</v>
+      </c>
+      <c r="AC23">
+        <v>1</v>
+      </c>
+      <c r="AD23">
+        <v>9</v>
+      </c>
+      <c r="AE23">
+        <v>1.22</v>
+      </c>
+      <c r="AF23">
+        <v>3.52</v>
+      </c>
+      <c r="AG23">
+        <v>1.77</v>
+      </c>
+      <c r="AH23">
+        <v>1.98</v>
+      </c>
+      <c r="AI23">
+        <v>1.7</v>
+      </c>
+      <c r="AJ23">
+        <v>2.05</v>
+      </c>
+      <c r="AK23">
+        <v>1.8</v>
+      </c>
+      <c r="AL23">
+        <v>1.33</v>
+      </c>
+      <c r="AM23">
+        <v>1.25</v>
+      </c>
+      <c r="AN23">
+        <v>0</v>
+      </c>
+      <c r="AO23">
+        <v>0</v>
+      </c>
+      <c r="AP23">
+        <v>0</v>
+      </c>
+      <c r="AQ23">
+        <v>3</v>
+      </c>
+      <c r="AR23">
+        <v>0</v>
+      </c>
+      <c r="AS23">
+        <v>0</v>
+      </c>
+      <c r="AT23">
+        <v>0</v>
+      </c>
+      <c r="AU23">
+        <v>5</v>
+      </c>
+      <c r="AV23">
+        <v>8</v>
+      </c>
+      <c r="AW23">
+        <v>3</v>
+      </c>
+      <c r="AX23">
+        <v>9</v>
+      </c>
+      <c r="AY23">
+        <v>8</v>
+      </c>
+      <c r="AZ23">
+        <v>18</v>
+      </c>
+      <c r="BA23">
+        <v>2</v>
+      </c>
+      <c r="BB23">
+        <v>9</v>
+      </c>
+      <c r="BC23">
+        <v>11</v>
+      </c>
+      <c r="BD23">
+        <v>2.33</v>
+      </c>
+      <c r="BE23">
+        <v>6.75</v>
+      </c>
+      <c r="BF23">
+        <v>1.72</v>
+      </c>
+      <c r="BG23">
+        <v>1.18</v>
+      </c>
+      <c r="BH23">
+        <v>4.1</v>
+      </c>
+      <c r="BI23">
+        <v>1.32</v>
+      </c>
+      <c r="BJ23">
+        <v>3.05</v>
+      </c>
+      <c r="BK23">
+        <v>1.53</v>
+      </c>
+      <c r="BL23">
+        <v>2.32</v>
+      </c>
+      <c r="BM23">
+        <v>1.84</v>
+      </c>
+      <c r="BN23">
+        <v>1.84</v>
+      </c>
+      <c r="BO23">
+        <v>2.28</v>
+      </c>
+      <c r="BP23">
+        <v>1.54</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="123">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -268,12 +268,12 @@
     <t>Henan Jianye</t>
   </si>
   <si>
+    <t>Beijing Guoan</t>
+  </si>
+  <si>
     <t>Changchun Yatai</t>
   </si>
   <si>
-    <t>Beijing Guoan</t>
-  </si>
-  <si>
     <t>['59']</t>
   </si>
   <si>
@@ -331,6 +331,12 @@
     <t>['42']</t>
   </si>
   <si>
+    <t>['2', '20', '34']</t>
+  </si>
+  <si>
+    <t>['18']</t>
+  </si>
+  <si>
     <t>['53', '79']</t>
   </si>
   <si>
@@ -371,6 +377,12 @@
   </si>
   <si>
     <t>['67', '74', '90+5']</t>
+  </si>
+  <si>
+    <t>['45+10', '54', '88', '90+9']</t>
+  </si>
+  <si>
+    <t>['78']</t>
   </si>
 </sst>
 </file>
@@ -732,7 +744,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP23"/>
+  <dimension ref="A1:BP25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1170,7 +1182,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -1376,7 +1388,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1400,7 +1412,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -1606,7 +1618,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="Q5">
         <v>2.85</v>
@@ -1812,7 +1824,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="Q6">
         <v>2.2</v>
@@ -2224,7 +2236,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="Q8">
         <v>2.04</v>
@@ -2430,7 +2442,7 @@
         <v>92</v>
       </c>
       <c r="P9" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="Q9">
         <v>1.5</v>
@@ -2636,7 +2648,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="Q10">
         <v>2.1</v>
@@ -2818,7 +2830,7 @@
         <v>77</v>
       </c>
       <c r="H11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -3048,7 +3060,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="Q12">
         <v>3.1</v>
@@ -3254,7 +3266,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -3332,7 +3344,7 @@
         <v>1</v>
       </c>
       <c r="AP13">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AQ13">
         <v>0.5</v>
@@ -3436,7 +3448,7 @@
         <v>71</v>
       </c>
       <c r="H14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I14">
         <v>2</v>
@@ -3460,7 +3472,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="Q14">
         <v>2.13</v>
@@ -3666,7 +3678,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="Q15">
         <v>3.2</v>
@@ -3872,7 +3884,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="Q16">
         <v>1.78</v>
@@ -4284,7 +4296,7 @@
         <v>100</v>
       </c>
       <c r="P18" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="Q18">
         <v>5.5</v>
@@ -4490,7 +4502,7 @@
         <v>88</v>
       </c>
       <c r="P19" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="Q19">
         <v>3.75</v>
@@ -4696,7 +4708,7 @@
         <v>101</v>
       </c>
       <c r="P20" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="Q20">
         <v>3.25</v>
@@ -4878,7 +4890,7 @@
         <v>82</v>
       </c>
       <c r="H21" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I21">
         <v>1</v>
@@ -5314,7 +5326,7 @@
         <v>104</v>
       </c>
       <c r="P23" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="Q23">
         <v>4</v>
@@ -5471,6 +5483,418 @@
       </c>
       <c r="BP23">
         <v>1.54</v>
+      </c>
+    </row>
+    <row r="24" spans="1:68">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>7825214</v>
+      </c>
+      <c r="C24" t="s">
+        <v>68</v>
+      </c>
+      <c r="D24" t="s">
+        <v>69</v>
+      </c>
+      <c r="E24" s="2">
+        <v>45745.33333333334</v>
+      </c>
+      <c r="F24">
+        <v>3</v>
+      </c>
+      <c r="G24" t="s">
+        <v>78</v>
+      </c>
+      <c r="H24" t="s">
+        <v>75</v>
+      </c>
+      <c r="I24">
+        <v>3</v>
+      </c>
+      <c r="J24">
+        <v>1</v>
+      </c>
+      <c r="K24">
+        <v>4</v>
+      </c>
+      <c r="L24">
+        <v>3</v>
+      </c>
+      <c r="M24">
+        <v>4</v>
+      </c>
+      <c r="N24">
+        <v>7</v>
+      </c>
+      <c r="O24" t="s">
+        <v>105</v>
+      </c>
+      <c r="P24" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q24">
+        <v>4.75</v>
+      </c>
+      <c r="R24">
+        <v>2.4</v>
+      </c>
+      <c r="S24">
+        <v>2.2</v>
+      </c>
+      <c r="T24">
+        <v>1.29</v>
+      </c>
+      <c r="U24">
+        <v>3.5</v>
+      </c>
+      <c r="V24">
+        <v>2.38</v>
+      </c>
+      <c r="W24">
+        <v>1.53</v>
+      </c>
+      <c r="X24">
+        <v>5.5</v>
+      </c>
+      <c r="Y24">
+        <v>1.14</v>
+      </c>
+      <c r="Z24">
+        <v>4.6</v>
+      </c>
+      <c r="AA24">
+        <v>4.2</v>
+      </c>
+      <c r="AB24">
+        <v>1.63</v>
+      </c>
+      <c r="AC24">
+        <v>1.01</v>
+      </c>
+      <c r="AD24">
+        <v>13</v>
+      </c>
+      <c r="AE24">
+        <v>1.13</v>
+      </c>
+      <c r="AF24">
+        <v>4.6</v>
+      </c>
+      <c r="AG24">
+        <v>1.53</v>
+      </c>
+      <c r="AH24">
+        <v>2.25</v>
+      </c>
+      <c r="AI24">
+        <v>1.62</v>
+      </c>
+      <c r="AJ24">
+        <v>2.2</v>
+      </c>
+      <c r="AK24">
+        <v>2.2</v>
+      </c>
+      <c r="AL24">
+        <v>1.25</v>
+      </c>
+      <c r="AM24">
+        <v>1.18</v>
+      </c>
+      <c r="AN24">
+        <v>3</v>
+      </c>
+      <c r="AO24">
+        <v>0</v>
+      </c>
+      <c r="AP24">
+        <v>1.5</v>
+      </c>
+      <c r="AQ24">
+        <v>3</v>
+      </c>
+      <c r="AR24">
+        <v>1.93</v>
+      </c>
+      <c r="AS24">
+        <v>0</v>
+      </c>
+      <c r="AT24">
+        <v>1.93</v>
+      </c>
+      <c r="AU24">
+        <v>7</v>
+      </c>
+      <c r="AV24">
+        <v>8</v>
+      </c>
+      <c r="AW24">
+        <v>0</v>
+      </c>
+      <c r="AX24">
+        <v>13</v>
+      </c>
+      <c r="AY24">
+        <v>8</v>
+      </c>
+      <c r="AZ24">
+        <v>24</v>
+      </c>
+      <c r="BA24">
+        <v>2</v>
+      </c>
+      <c r="BB24">
+        <v>7</v>
+      </c>
+      <c r="BC24">
+        <v>9</v>
+      </c>
+      <c r="BD24">
+        <v>2.7</v>
+      </c>
+      <c r="BE24">
+        <v>6.75</v>
+      </c>
+      <c r="BF24">
+        <v>1.54</v>
+      </c>
+      <c r="BG24">
+        <v>1.23</v>
+      </c>
+      <c r="BH24">
+        <v>3.65</v>
+      </c>
+      <c r="BI24">
+        <v>1.41</v>
+      </c>
+      <c r="BJ24">
+        <v>2.65</v>
+      </c>
+      <c r="BK24">
+        <v>1.66</v>
+      </c>
+      <c r="BL24">
+        <v>2.07</v>
+      </c>
+      <c r="BM24">
+        <v>2.04</v>
+      </c>
+      <c r="BN24">
+        <v>1.67</v>
+      </c>
+      <c r="BO24">
+        <v>2.55</v>
+      </c>
+      <c r="BP24">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:68">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>7825215</v>
+      </c>
+      <c r="C25" t="s">
+        <v>68</v>
+      </c>
+      <c r="D25" t="s">
+        <v>69</v>
+      </c>
+      <c r="E25" s="2">
+        <v>45745.35763888889</v>
+      </c>
+      <c r="F25">
+        <v>3</v>
+      </c>
+      <c r="G25" t="s">
+        <v>84</v>
+      </c>
+      <c r="H25" t="s">
+        <v>70</v>
+      </c>
+      <c r="I25">
+        <v>1</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>1</v>
+      </c>
+      <c r="L25">
+        <v>1</v>
+      </c>
+      <c r="M25">
+        <v>1</v>
+      </c>
+      <c r="N25">
+        <v>2</v>
+      </c>
+      <c r="O25" t="s">
+        <v>106</v>
+      </c>
+      <c r="P25" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q25">
+        <v>2.88</v>
+      </c>
+      <c r="R25">
+        <v>2.2</v>
+      </c>
+      <c r="S25">
+        <v>3.6</v>
+      </c>
+      <c r="T25">
+        <v>1.36</v>
+      </c>
+      <c r="U25">
+        <v>3</v>
+      </c>
+      <c r="V25">
+        <v>2.75</v>
+      </c>
+      <c r="W25">
+        <v>1.4</v>
+      </c>
+      <c r="X25">
+        <v>7</v>
+      </c>
+      <c r="Y25">
+        <v>1.1</v>
+      </c>
+      <c r="Z25">
+        <v>2.27</v>
+      </c>
+      <c r="AA25">
+        <v>3.63</v>
+      </c>
+      <c r="AB25">
+        <v>2.83</v>
+      </c>
+      <c r="AC25">
+        <v>1</v>
+      </c>
+      <c r="AD25">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AE25">
+        <v>1.2</v>
+      </c>
+      <c r="AF25">
+        <v>3.72</v>
+      </c>
+      <c r="AG25">
+        <v>1.77</v>
+      </c>
+      <c r="AH25">
+        <v>1.98</v>
+      </c>
+      <c r="AI25">
+        <v>1.67</v>
+      </c>
+      <c r="AJ25">
+        <v>2.1</v>
+      </c>
+      <c r="AK25">
+        <v>1.36</v>
+      </c>
+      <c r="AL25">
+        <v>1.33</v>
+      </c>
+      <c r="AM25">
+        <v>1.6</v>
+      </c>
+      <c r="AN25">
+        <v>0</v>
+      </c>
+      <c r="AO25">
+        <v>0</v>
+      </c>
+      <c r="AP25">
+        <v>1</v>
+      </c>
+      <c r="AQ25">
+        <v>1</v>
+      </c>
+      <c r="AR25">
+        <v>0</v>
+      </c>
+      <c r="AS25">
+        <v>0</v>
+      </c>
+      <c r="AT25">
+        <v>0</v>
+      </c>
+      <c r="AU25">
+        <v>3</v>
+      </c>
+      <c r="AV25">
+        <v>10</v>
+      </c>
+      <c r="AW25">
+        <v>3</v>
+      </c>
+      <c r="AX25">
+        <v>6</v>
+      </c>
+      <c r="AY25">
+        <v>8</v>
+      </c>
+      <c r="AZ25">
+        <v>17</v>
+      </c>
+      <c r="BA25">
+        <v>3</v>
+      </c>
+      <c r="BB25">
+        <v>7</v>
+      </c>
+      <c r="BC25">
+        <v>10</v>
+      </c>
+      <c r="BD25">
+        <v>1.83</v>
+      </c>
+      <c r="BE25">
+        <v>6.5</v>
+      </c>
+      <c r="BF25">
+        <v>2.18</v>
+      </c>
+      <c r="BG25">
+        <v>1.3</v>
+      </c>
+      <c r="BH25">
+        <v>3.15</v>
+      </c>
+      <c r="BI25">
+        <v>1.52</v>
+      </c>
+      <c r="BJ25">
+        <v>2.32</v>
+      </c>
+      <c r="BK25">
+        <v>1.85</v>
+      </c>
+      <c r="BL25">
+        <v>1.83</v>
+      </c>
+      <c r="BM25">
+        <v>2.33</v>
+      </c>
+      <c r="BN25">
+        <v>1.52</v>
+      </c>
+      <c r="BO25">
+        <v>3</v>
+      </c>
+      <c r="BP25">
+        <v>1.32</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="126">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -337,6 +337,12 @@
     <t>['18']</t>
   </si>
   <si>
+    <t>['16', '63']</t>
+  </si>
+  <si>
+    <t>['13', '90+2', '90+5']</t>
+  </si>
+  <si>
     <t>['53', '79']</t>
   </si>
   <si>
@@ -383,6 +389,9 @@
   </si>
   <si>
     <t>['78']</t>
+  </si>
+  <si>
+    <t>['47', '90+2', '90+3']</t>
   </si>
 </sst>
 </file>
@@ -744,7 +753,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP25"/>
+  <dimension ref="A1:BP27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1412,7 +1421,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -1618,7 +1627,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="Q5">
         <v>2.85</v>
@@ -1699,7 +1708,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -1824,7 +1833,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="Q6">
         <v>2.2</v>
@@ -1902,7 +1911,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ6">
         <v>0.5</v>
@@ -2236,7 +2245,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="Q8">
         <v>2.04</v>
@@ -2442,7 +2451,7 @@
         <v>92</v>
       </c>
       <c r="P9" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="Q9">
         <v>1.5</v>
@@ -2523,7 +2532,7 @@
         <v>3</v>
       </c>
       <c r="AQ9">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -2648,7 +2657,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="Q10">
         <v>2.1</v>
@@ -3060,7 +3069,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="Q12">
         <v>3.1</v>
@@ -3141,7 +3150,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ12">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR12">
         <v>1.44</v>
@@ -3266,7 +3275,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -3472,7 +3481,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="Q14">
         <v>2.13</v>
@@ -3678,7 +3687,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="Q15">
         <v>3.2</v>
@@ -3884,7 +3893,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="Q16">
         <v>1.78</v>
@@ -4296,7 +4305,7 @@
         <v>100</v>
       </c>
       <c r="P18" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="Q18">
         <v>5.5</v>
@@ -4502,7 +4511,7 @@
         <v>88</v>
       </c>
       <c r="P19" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="Q19">
         <v>3.75</v>
@@ -4708,7 +4717,7 @@
         <v>101</v>
       </c>
       <c r="P20" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="Q20">
         <v>3.25</v>
@@ -5326,7 +5335,7 @@
         <v>104</v>
       </c>
       <c r="P23" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="Q23">
         <v>4</v>
@@ -5532,7 +5541,7 @@
         <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="Q24">
         <v>4.75</v>
@@ -5738,7 +5747,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -5895,6 +5904,418 @@
       </c>
       <c r="BP25">
         <v>1.32</v>
+      </c>
+    </row>
+    <row r="26" spans="1:68">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>7825216</v>
+      </c>
+      <c r="C26" t="s">
+        <v>68</v>
+      </c>
+      <c r="D26" t="s">
+        <v>69</v>
+      </c>
+      <c r="E26" s="2">
+        <v>45748.33333333334</v>
+      </c>
+      <c r="F26">
+        <v>4</v>
+      </c>
+      <c r="G26" t="s">
+        <v>83</v>
+      </c>
+      <c r="H26" t="s">
+        <v>79</v>
+      </c>
+      <c r="I26">
+        <v>1</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>1</v>
+      </c>
+      <c r="L26">
+        <v>2</v>
+      </c>
+      <c r="M26">
+        <v>3</v>
+      </c>
+      <c r="N26">
+        <v>5</v>
+      </c>
+      <c r="O26" t="s">
+        <v>107</v>
+      </c>
+      <c r="P26" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q26">
+        <v>2.88</v>
+      </c>
+      <c r="R26">
+        <v>2.2</v>
+      </c>
+      <c r="S26">
+        <v>3.6</v>
+      </c>
+      <c r="T26">
+        <v>1.36</v>
+      </c>
+      <c r="U26">
+        <v>3</v>
+      </c>
+      <c r="V26">
+        <v>2.63</v>
+      </c>
+      <c r="W26">
+        <v>1.44</v>
+      </c>
+      <c r="X26">
+        <v>7</v>
+      </c>
+      <c r="Y26">
+        <v>1.1</v>
+      </c>
+      <c r="Z26">
+        <v>2.2</v>
+      </c>
+      <c r="AA26">
+        <v>3.4</v>
+      </c>
+      <c r="AB26">
+        <v>3.2</v>
+      </c>
+      <c r="AC26">
+        <v>1.04</v>
+      </c>
+      <c r="AD26">
+        <v>9</v>
+      </c>
+      <c r="AE26">
+        <v>1.25</v>
+      </c>
+      <c r="AF26">
+        <v>3.7</v>
+      </c>
+      <c r="AG26">
+        <v>1.8</v>
+      </c>
+      <c r="AH26">
+        <v>2</v>
+      </c>
+      <c r="AI26">
+        <v>1.62</v>
+      </c>
+      <c r="AJ26">
+        <v>2.2</v>
+      </c>
+      <c r="AK26">
+        <v>1.34</v>
+      </c>
+      <c r="AL26">
+        <v>1.28</v>
+      </c>
+      <c r="AM26">
+        <v>1.68</v>
+      </c>
+      <c r="AN26">
+        <v>0</v>
+      </c>
+      <c r="AO26">
+        <v>1</v>
+      </c>
+      <c r="AP26">
+        <v>0</v>
+      </c>
+      <c r="AQ26">
+        <v>2</v>
+      </c>
+      <c r="AR26">
+        <v>1.09</v>
+      </c>
+      <c r="AS26">
+        <v>1.65</v>
+      </c>
+      <c r="AT26">
+        <v>2.74</v>
+      </c>
+      <c r="AU26">
+        <v>6</v>
+      </c>
+      <c r="AV26">
+        <v>5</v>
+      </c>
+      <c r="AW26">
+        <v>2</v>
+      </c>
+      <c r="AX26">
+        <v>8</v>
+      </c>
+      <c r="AY26">
+        <v>8</v>
+      </c>
+      <c r="AZ26">
+        <v>15</v>
+      </c>
+      <c r="BA26">
+        <v>2</v>
+      </c>
+      <c r="BB26">
+        <v>4</v>
+      </c>
+      <c r="BC26">
+        <v>6</v>
+      </c>
+      <c r="BD26">
+        <v>1.79</v>
+      </c>
+      <c r="BE26">
+        <v>6.4</v>
+      </c>
+      <c r="BF26">
+        <v>2.23</v>
+      </c>
+      <c r="BG26">
+        <v>1.29</v>
+      </c>
+      <c r="BH26">
+        <v>3.15</v>
+      </c>
+      <c r="BI26">
+        <v>1.5</v>
+      </c>
+      <c r="BJ26">
+        <v>2.35</v>
+      </c>
+      <c r="BK26">
+        <v>1.82</v>
+      </c>
+      <c r="BL26">
+        <v>1.86</v>
+      </c>
+      <c r="BM26">
+        <v>2.3</v>
+      </c>
+      <c r="BN26">
+        <v>1.54</v>
+      </c>
+      <c r="BO26">
+        <v>2.9</v>
+      </c>
+      <c r="BP26">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="27" spans="1:68">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>7825217</v>
+      </c>
+      <c r="C27" t="s">
+        <v>68</v>
+      </c>
+      <c r="D27" t="s">
+        <v>69</v>
+      </c>
+      <c r="E27" s="2">
+        <v>45748.35763888889</v>
+      </c>
+      <c r="F27">
+        <v>4</v>
+      </c>
+      <c r="G27" t="s">
+        <v>74</v>
+      </c>
+      <c r="H27" t="s">
+        <v>81</v>
+      </c>
+      <c r="I27">
+        <v>1</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>1</v>
+      </c>
+      <c r="L27">
+        <v>3</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>3</v>
+      </c>
+      <c r="O27" t="s">
+        <v>108</v>
+      </c>
+      <c r="P27" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q27">
+        <v>2.3</v>
+      </c>
+      <c r="R27">
+        <v>2.38</v>
+      </c>
+      <c r="S27">
+        <v>4.5</v>
+      </c>
+      <c r="T27">
+        <v>1.3</v>
+      </c>
+      <c r="U27">
+        <v>3.4</v>
+      </c>
+      <c r="V27">
+        <v>2.5</v>
+      </c>
+      <c r="W27">
+        <v>1.5</v>
+      </c>
+      <c r="X27">
+        <v>6</v>
+      </c>
+      <c r="Y27">
+        <v>1.13</v>
+      </c>
+      <c r="Z27">
+        <v>1.73</v>
+      </c>
+      <c r="AA27">
+        <v>3.6</v>
+      </c>
+      <c r="AB27">
+        <v>4.75</v>
+      </c>
+      <c r="AC27">
+        <v>1.04</v>
+      </c>
+      <c r="AD27">
+        <v>9</v>
+      </c>
+      <c r="AE27">
+        <v>1.2</v>
+      </c>
+      <c r="AF27">
+        <v>4.2</v>
+      </c>
+      <c r="AG27">
+        <v>1.65</v>
+      </c>
+      <c r="AH27">
+        <v>2.2</v>
+      </c>
+      <c r="AI27">
+        <v>1.62</v>
+      </c>
+      <c r="AJ27">
+        <v>2.2</v>
+      </c>
+      <c r="AK27">
+        <v>1.2</v>
+      </c>
+      <c r="AL27">
+        <v>1.24</v>
+      </c>
+      <c r="AM27">
+        <v>2.1</v>
+      </c>
+      <c r="AN27">
+        <v>1</v>
+      </c>
+      <c r="AO27">
+        <v>1.5</v>
+      </c>
+      <c r="AP27">
+        <v>2</v>
+      </c>
+      <c r="AQ27">
+        <v>1</v>
+      </c>
+      <c r="AR27">
+        <v>1.37</v>
+      </c>
+      <c r="AS27">
+        <v>1.47</v>
+      </c>
+      <c r="AT27">
+        <v>2.84</v>
+      </c>
+      <c r="AU27">
+        <v>7</v>
+      </c>
+      <c r="AV27">
+        <v>2</v>
+      </c>
+      <c r="AW27">
+        <v>6</v>
+      </c>
+      <c r="AX27">
+        <v>8</v>
+      </c>
+      <c r="AY27">
+        <v>13</v>
+      </c>
+      <c r="AZ27">
+        <v>10</v>
+      </c>
+      <c r="BA27">
+        <v>1</v>
+      </c>
+      <c r="BB27">
+        <v>2</v>
+      </c>
+      <c r="BC27">
+        <v>3</v>
+      </c>
+      <c r="BD27">
+        <v>1.61</v>
+      </c>
+      <c r="BE27">
+        <v>6.75</v>
+      </c>
+      <c r="BF27">
+        <v>2.55</v>
+      </c>
+      <c r="BG27">
+        <v>1.35</v>
+      </c>
+      <c r="BH27">
+        <v>2.9</v>
+      </c>
+      <c r="BI27">
+        <v>1.58</v>
+      </c>
+      <c r="BJ27">
+        <v>2.18</v>
+      </c>
+      <c r="BK27">
+        <v>1.96</v>
+      </c>
+      <c r="BL27">
+        <v>1.74</v>
+      </c>
+      <c r="BM27">
+        <v>2.48</v>
+      </c>
+      <c r="BN27">
+        <v>1.47</v>
+      </c>
+      <c r="BO27">
+        <v>3.25</v>
+      </c>
+      <c r="BP27">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="136">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -343,6 +343,21 @@
     <t>['13', '90+2', '90+5']</t>
   </si>
   <si>
+    <t>['32']</t>
+  </si>
+  <si>
+    <t>['63', '85', '90+1']</t>
+  </si>
+  <si>
+    <t>['64']</t>
+  </si>
+  <si>
+    <t>['71', '78']</t>
+  </si>
+  <si>
+    <t>['6', '44']</t>
+  </si>
+  <si>
     <t>['53', '79']</t>
   </si>
   <si>
@@ -392,6 +407,21 @@
   </si>
   <si>
     <t>['47', '90+2', '90+3']</t>
+  </si>
+  <si>
+    <t>['40']</t>
+  </si>
+  <si>
+    <t>['23']</t>
+  </si>
+  <si>
+    <t>['27', '90+1']</t>
+  </si>
+  <si>
+    <t>['5', '45+3', '68']</t>
+  </si>
+  <si>
+    <t>['90+10']</t>
   </si>
 </sst>
 </file>
@@ -753,7 +783,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP27"/>
+  <dimension ref="A1:BP33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1090,7 +1120,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1293,7 +1323,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ3">
         <v>0</v>
@@ -1421,7 +1451,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -1502,7 +1532,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ4">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1627,7 +1657,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="Q5">
         <v>2.85</v>
@@ -1705,7 +1735,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AQ5">
         <v>2</v>
@@ -1833,7 +1863,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="Q6">
         <v>2.2</v>
@@ -1914,7 +1944,7 @@
         <v>2</v>
       </c>
       <c r="AQ6">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2117,7 +2147,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AQ7">
         <v>0.5</v>
@@ -2245,7 +2275,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="Q8">
         <v>2.04</v>
@@ -2323,10 +2353,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2451,7 +2481,7 @@
         <v>92</v>
       </c>
       <c r="P9" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="Q9">
         <v>1.5</v>
@@ -2657,7 +2687,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="Q10">
         <v>2.1</v>
@@ -2735,10 +2765,10 @@
         <v>1</v>
       </c>
       <c r="AP10">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AQ10">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR10">
         <v>2.21</v>
@@ -3069,7 +3099,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="Q12">
         <v>3.1</v>
@@ -3147,7 +3177,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AQ12">
         <v>1</v>
@@ -3275,7 +3305,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -3481,7 +3511,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="Q14">
         <v>2.13</v>
@@ -3559,10 +3589,10 @@
         <v>3</v>
       </c>
       <c r="AP14">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ14">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AR14">
         <v>2.29</v>
@@ -3687,7 +3717,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="Q15">
         <v>3.2</v>
@@ -3893,7 +3923,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="Q16">
         <v>1.78</v>
@@ -4180,7 +4210,7 @@
         <v>2</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4305,7 +4335,7 @@
         <v>100</v>
       </c>
       <c r="P18" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="Q18">
         <v>5.5</v>
@@ -4511,7 +4541,7 @@
         <v>88</v>
       </c>
       <c r="P19" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="Q19">
         <v>3.75</v>
@@ -4717,7 +4747,7 @@
         <v>101</v>
       </c>
       <c r="P20" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="Q20">
         <v>3.25</v>
@@ -4798,7 +4828,7 @@
         <v>0</v>
       </c>
       <c r="AQ20">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -5207,7 +5237,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ22">
         <v>0</v>
@@ -5335,7 +5365,7 @@
         <v>104</v>
       </c>
       <c r="P23" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="Q23">
         <v>4</v>
@@ -5541,7 +5571,7 @@
         <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="Q24">
         <v>4.75</v>
@@ -5747,7 +5777,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -5828,7 +5858,7 @@
         <v>1</v>
       </c>
       <c r="AQ25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR25">
         <v>0</v>
@@ -5953,7 +5983,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="Q26">
         <v>2.88</v>
@@ -6316,6 +6346,1242 @@
       </c>
       <c r="BP27">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="28" spans="1:68">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>7825218</v>
+      </c>
+      <c r="C28" t="s">
+        <v>68</v>
+      </c>
+      <c r="D28" t="s">
+        <v>69</v>
+      </c>
+      <c r="E28" s="2">
+        <v>45749.1875</v>
+      </c>
+      <c r="F28">
+        <v>4</v>
+      </c>
+      <c r="G28" t="s">
+        <v>85</v>
+      </c>
+      <c r="H28" t="s">
+        <v>80</v>
+      </c>
+      <c r="I28">
+        <v>1</v>
+      </c>
+      <c r="J28">
+        <v>1</v>
+      </c>
+      <c r="K28">
+        <v>2</v>
+      </c>
+      <c r="L28">
+        <v>1</v>
+      </c>
+      <c r="M28">
+        <v>1</v>
+      </c>
+      <c r="N28">
+        <v>2</v>
+      </c>
+      <c r="O28" t="s">
+        <v>109</v>
+      </c>
+      <c r="P28" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q28">
+        <v>2.88</v>
+      </c>
+      <c r="R28">
+        <v>2.1</v>
+      </c>
+      <c r="S28">
+        <v>3.75</v>
+      </c>
+      <c r="T28">
+        <v>1.4</v>
+      </c>
+      <c r="U28">
+        <v>2.75</v>
+      </c>
+      <c r="V28">
+        <v>3</v>
+      </c>
+      <c r="W28">
+        <v>1.36</v>
+      </c>
+      <c r="X28">
+        <v>8</v>
+      </c>
+      <c r="Y28">
+        <v>1.08</v>
+      </c>
+      <c r="Z28">
+        <v>2.13</v>
+      </c>
+      <c r="AA28">
+        <v>3.51</v>
+      </c>
+      <c r="AB28">
+        <v>3.17</v>
+      </c>
+      <c r="AC28">
+        <v>1.05</v>
+      </c>
+      <c r="AD28">
+        <v>8.5</v>
+      </c>
+      <c r="AE28">
+        <v>1.28</v>
+      </c>
+      <c r="AF28">
+        <v>3.4</v>
+      </c>
+      <c r="AG28">
+        <v>1.91</v>
+      </c>
+      <c r="AH28">
+        <v>1.83</v>
+      </c>
+      <c r="AI28">
+        <v>1.75</v>
+      </c>
+      <c r="AJ28">
+        <v>2</v>
+      </c>
+      <c r="AK28">
+        <v>1.36</v>
+      </c>
+      <c r="AL28">
+        <v>1.29</v>
+      </c>
+      <c r="AM28">
+        <v>1.63</v>
+      </c>
+      <c r="AN28">
+        <v>0</v>
+      </c>
+      <c r="AO28">
+        <v>0</v>
+      </c>
+      <c r="AP28">
+        <v>1</v>
+      </c>
+      <c r="AQ28">
+        <v>0.33</v>
+      </c>
+      <c r="AR28">
+        <v>0</v>
+      </c>
+      <c r="AS28">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AT28">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AU28">
+        <v>4</v>
+      </c>
+      <c r="AV28">
+        <v>3</v>
+      </c>
+      <c r="AW28">
+        <v>4</v>
+      </c>
+      <c r="AX28">
+        <v>13</v>
+      </c>
+      <c r="AY28">
+        <v>9</v>
+      </c>
+      <c r="AZ28">
+        <v>19</v>
+      </c>
+      <c r="BA28">
+        <v>3</v>
+      </c>
+      <c r="BB28">
+        <v>7</v>
+      </c>
+      <c r="BC28">
+        <v>10</v>
+      </c>
+      <c r="BD28">
+        <v>1.79</v>
+      </c>
+      <c r="BE28">
+        <v>6.4</v>
+      </c>
+      <c r="BF28">
+        <v>2.23</v>
+      </c>
+      <c r="BG28">
+        <v>1.4</v>
+      </c>
+      <c r="BH28">
+        <v>2.7</v>
+      </c>
+      <c r="BI28">
+        <v>1.65</v>
+      </c>
+      <c r="BJ28">
+        <v>2.07</v>
+      </c>
+      <c r="BK28">
+        <v>2.06</v>
+      </c>
+      <c r="BL28">
+        <v>1.66</v>
+      </c>
+      <c r="BM28">
+        <v>2.65</v>
+      </c>
+      <c r="BN28">
+        <v>1.41</v>
+      </c>
+      <c r="BO28">
+        <v>3.55</v>
+      </c>
+      <c r="BP28">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:68">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>7825219</v>
+      </c>
+      <c r="C29" t="s">
+        <v>68</v>
+      </c>
+      <c r="D29" t="s">
+        <v>69</v>
+      </c>
+      <c r="E29" s="2">
+        <v>45749.29166666666</v>
+      </c>
+      <c r="F29">
+        <v>4</v>
+      </c>
+      <c r="G29" t="s">
+        <v>71</v>
+      </c>
+      <c r="H29" t="s">
+        <v>72</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>1</v>
+      </c>
+      <c r="K29">
+        <v>1</v>
+      </c>
+      <c r="L29">
+        <v>3</v>
+      </c>
+      <c r="M29">
+        <v>1</v>
+      </c>
+      <c r="N29">
+        <v>4</v>
+      </c>
+      <c r="O29" t="s">
+        <v>110</v>
+      </c>
+      <c r="P29" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q29">
+        <v>1.83</v>
+      </c>
+      <c r="R29">
+        <v>2.5</v>
+      </c>
+      <c r="S29">
+        <v>7</v>
+      </c>
+      <c r="T29">
+        <v>1.3</v>
+      </c>
+      <c r="U29">
+        <v>3.4</v>
+      </c>
+      <c r="V29">
+        <v>2.38</v>
+      </c>
+      <c r="W29">
+        <v>1.53</v>
+      </c>
+      <c r="X29">
+        <v>6</v>
+      </c>
+      <c r="Y29">
+        <v>1.13</v>
+      </c>
+      <c r="Z29">
+        <v>1.36</v>
+      </c>
+      <c r="AA29">
+        <v>5.1</v>
+      </c>
+      <c r="AB29">
+        <v>7.2</v>
+      </c>
+      <c r="AC29">
+        <v>1.03</v>
+      </c>
+      <c r="AD29">
+        <v>10</v>
+      </c>
+      <c r="AE29">
+        <v>1.18</v>
+      </c>
+      <c r="AF29">
+        <v>4.5</v>
+      </c>
+      <c r="AG29">
+        <v>1.6</v>
+      </c>
+      <c r="AH29">
+        <v>2.1</v>
+      </c>
+      <c r="AI29">
+        <v>1.91</v>
+      </c>
+      <c r="AJ29">
+        <v>1.91</v>
+      </c>
+      <c r="AK29">
+        <v>1.09</v>
+      </c>
+      <c r="AL29">
+        <v>1.17</v>
+      </c>
+      <c r="AM29">
+        <v>2.95</v>
+      </c>
+      <c r="AN29">
+        <v>2</v>
+      </c>
+      <c r="AO29">
+        <v>3</v>
+      </c>
+      <c r="AP29">
+        <v>2.33</v>
+      </c>
+      <c r="AQ29">
+        <v>1.5</v>
+      </c>
+      <c r="AR29">
+        <v>1.91</v>
+      </c>
+      <c r="AS29">
+        <v>1.21</v>
+      </c>
+      <c r="AT29">
+        <v>3.12</v>
+      </c>
+      <c r="AU29">
+        <v>11</v>
+      </c>
+      <c r="AV29">
+        <v>4</v>
+      </c>
+      <c r="AW29">
+        <v>27</v>
+      </c>
+      <c r="AX29">
+        <v>5</v>
+      </c>
+      <c r="AY29">
+        <v>52</v>
+      </c>
+      <c r="AZ29">
+        <v>10</v>
+      </c>
+      <c r="BA29">
+        <v>16</v>
+      </c>
+      <c r="BB29">
+        <v>1</v>
+      </c>
+      <c r="BC29">
+        <v>17</v>
+      </c>
+      <c r="BD29">
+        <v>1.3</v>
+      </c>
+      <c r="BE29">
+        <v>7.5</v>
+      </c>
+      <c r="BF29">
+        <v>3.9</v>
+      </c>
+      <c r="BG29">
+        <v>1.29</v>
+      </c>
+      <c r="BH29">
+        <v>3.15</v>
+      </c>
+      <c r="BI29">
+        <v>1.5</v>
+      </c>
+      <c r="BJ29">
+        <v>2.35</v>
+      </c>
+      <c r="BK29">
+        <v>1.8</v>
+      </c>
+      <c r="BL29">
+        <v>1.89</v>
+      </c>
+      <c r="BM29">
+        <v>2.25</v>
+      </c>
+      <c r="BN29">
+        <v>1.55</v>
+      </c>
+      <c r="BO29">
+        <v>2.9</v>
+      </c>
+      <c r="BP29">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="30" spans="1:68">
+      <c r="A30" s="1">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>7825220</v>
+      </c>
+      <c r="C30" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30" t="s">
+        <v>69</v>
+      </c>
+      <c r="E30" s="2">
+        <v>45749.33333333334</v>
+      </c>
+      <c r="F30">
+        <v>4</v>
+      </c>
+      <c r="G30" t="s">
+        <v>73</v>
+      </c>
+      <c r="H30" t="s">
+        <v>82</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>1</v>
+      </c>
+      <c r="K30">
+        <v>1</v>
+      </c>
+      <c r="L30">
+        <v>1</v>
+      </c>
+      <c r="M30">
+        <v>1</v>
+      </c>
+      <c r="N30">
+        <v>2</v>
+      </c>
+      <c r="O30" t="s">
+        <v>111</v>
+      </c>
+      <c r="P30" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q30">
+        <v>3.75</v>
+      </c>
+      <c r="R30">
+        <v>2.05</v>
+      </c>
+      <c r="S30">
+        <v>3</v>
+      </c>
+      <c r="T30">
+        <v>1.44</v>
+      </c>
+      <c r="U30">
+        <v>2.63</v>
+      </c>
+      <c r="V30">
+        <v>3.25</v>
+      </c>
+      <c r="W30">
+        <v>1.33</v>
+      </c>
+      <c r="X30">
+        <v>9</v>
+      </c>
+      <c r="Y30">
+        <v>1.07</v>
+      </c>
+      <c r="Z30">
+        <v>3.1</v>
+      </c>
+      <c r="AA30">
+        <v>3.5</v>
+      </c>
+      <c r="AB30">
+        <v>2.25</v>
+      </c>
+      <c r="AC30">
+        <v>1.05</v>
+      </c>
+      <c r="AD30">
+        <v>8.5</v>
+      </c>
+      <c r="AE30">
+        <v>1.3</v>
+      </c>
+      <c r="AF30">
+        <v>3.25</v>
+      </c>
+      <c r="AG30">
+        <v>2.08</v>
+      </c>
+      <c r="AH30">
+        <v>1.73</v>
+      </c>
+      <c r="AI30">
+        <v>1.91</v>
+      </c>
+      <c r="AJ30">
+        <v>1.91</v>
+      </c>
+      <c r="AK30">
+        <v>1.65</v>
+      </c>
+      <c r="AL30">
+        <v>1.3</v>
+      </c>
+      <c r="AM30">
+        <v>1.33</v>
+      </c>
+      <c r="AN30">
+        <v>0.5</v>
+      </c>
+      <c r="AO30">
+        <v>0.5</v>
+      </c>
+      <c r="AP30">
+        <v>0.67</v>
+      </c>
+      <c r="AQ30">
+        <v>0.67</v>
+      </c>
+      <c r="AR30">
+        <v>1.32</v>
+      </c>
+      <c r="AS30">
+        <v>1.25</v>
+      </c>
+      <c r="AT30">
+        <v>2.57</v>
+      </c>
+      <c r="AU30">
+        <v>6</v>
+      </c>
+      <c r="AV30">
+        <v>4</v>
+      </c>
+      <c r="AW30">
+        <v>7</v>
+      </c>
+      <c r="AX30">
+        <v>11</v>
+      </c>
+      <c r="AY30">
+        <v>14</v>
+      </c>
+      <c r="AZ30">
+        <v>16</v>
+      </c>
+      <c r="BA30">
+        <v>3</v>
+      </c>
+      <c r="BB30">
+        <v>9</v>
+      </c>
+      <c r="BC30">
+        <v>12</v>
+      </c>
+      <c r="BD30">
+        <v>2.17</v>
+      </c>
+      <c r="BE30">
+        <v>6.4</v>
+      </c>
+      <c r="BF30">
+        <v>1.84</v>
+      </c>
+      <c r="BG30">
+        <v>1.32</v>
+      </c>
+      <c r="BH30">
+        <v>3.05</v>
+      </c>
+      <c r="BI30">
+        <v>1.55</v>
+      </c>
+      <c r="BJ30">
+        <v>2.28</v>
+      </c>
+      <c r="BK30">
+        <v>1.88</v>
+      </c>
+      <c r="BL30">
+        <v>1.8</v>
+      </c>
+      <c r="BM30">
+        <v>2.4</v>
+      </c>
+      <c r="BN30">
+        <v>1.5</v>
+      </c>
+      <c r="BO30">
+        <v>3.05</v>
+      </c>
+      <c r="BP30">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:68">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>7825222</v>
+      </c>
+      <c r="C31" t="s">
+        <v>68</v>
+      </c>
+      <c r="D31" t="s">
+        <v>69</v>
+      </c>
+      <c r="E31" s="2">
+        <v>45749.35763888889</v>
+      </c>
+      <c r="F31">
+        <v>4</v>
+      </c>
+      <c r="G31" t="s">
+        <v>76</v>
+      </c>
+      <c r="H31" t="s">
+        <v>84</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>1</v>
+      </c>
+      <c r="K31">
+        <v>1</v>
+      </c>
+      <c r="L31">
+        <v>2</v>
+      </c>
+      <c r="M31">
+        <v>2</v>
+      </c>
+      <c r="N31">
+        <v>4</v>
+      </c>
+      <c r="O31" t="s">
+        <v>112</v>
+      </c>
+      <c r="P31" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q31">
+        <v>3.42</v>
+      </c>
+      <c r="R31">
+        <v>2.03</v>
+      </c>
+      <c r="S31">
+        <v>3.12</v>
+      </c>
+      <c r="T31">
+        <v>1.39</v>
+      </c>
+      <c r="U31">
+        <v>2.77</v>
+      </c>
+      <c r="V31">
+        <v>2.65</v>
+      </c>
+      <c r="W31">
+        <v>1.42</v>
+      </c>
+      <c r="X31">
+        <v>6.4</v>
+      </c>
+      <c r="Y31">
+        <v>1.05</v>
+      </c>
+      <c r="Z31">
+        <v>2.78</v>
+      </c>
+      <c r="AA31">
+        <v>3.47</v>
+      </c>
+      <c r="AB31">
+        <v>2.37</v>
+      </c>
+      <c r="AC31">
+        <v>1</v>
+      </c>
+      <c r="AD31">
+        <v>9</v>
+      </c>
+      <c r="AE31">
+        <v>1.24</v>
+      </c>
+      <c r="AF31">
+        <v>3.69</v>
+      </c>
+      <c r="AG31">
+        <v>1.87</v>
+      </c>
+      <c r="AH31">
+        <v>1.87</v>
+      </c>
+      <c r="AI31">
+        <v>1.63</v>
+      </c>
+      <c r="AJ31">
+        <v>2.14</v>
+      </c>
+      <c r="AK31">
+        <v>1.5</v>
+      </c>
+      <c r="AL31">
+        <v>1.33</v>
+      </c>
+      <c r="AM31">
+        <v>1.42</v>
+      </c>
+      <c r="AN31">
+        <v>2</v>
+      </c>
+      <c r="AO31">
+        <v>2</v>
+      </c>
+      <c r="AP31">
+        <v>1.67</v>
+      </c>
+      <c r="AQ31">
+        <v>1.67</v>
+      </c>
+      <c r="AR31">
+        <v>3.11</v>
+      </c>
+      <c r="AS31">
+        <v>1.2</v>
+      </c>
+      <c r="AT31">
+        <v>4.31</v>
+      </c>
+      <c r="AU31">
+        <v>10</v>
+      </c>
+      <c r="AV31">
+        <v>6</v>
+      </c>
+      <c r="AW31">
+        <v>11</v>
+      </c>
+      <c r="AX31">
+        <v>10</v>
+      </c>
+      <c r="AY31">
+        <v>25</v>
+      </c>
+      <c r="AZ31">
+        <v>17</v>
+      </c>
+      <c r="BA31">
+        <v>8</v>
+      </c>
+      <c r="BB31">
+        <v>4</v>
+      </c>
+      <c r="BC31">
+        <v>12</v>
+      </c>
+      <c r="BD31">
+        <v>2.07</v>
+      </c>
+      <c r="BE31">
+        <v>6.4</v>
+      </c>
+      <c r="BF31">
+        <v>1.94</v>
+      </c>
+      <c r="BG31">
+        <v>1.4</v>
+      </c>
+      <c r="BH31">
+        <v>2.7</v>
+      </c>
+      <c r="BI31">
+        <v>1.67</v>
+      </c>
+      <c r="BJ31">
+        <v>2.05</v>
+      </c>
+      <c r="BK31">
+        <v>2.07</v>
+      </c>
+      <c r="BL31">
+        <v>1.66</v>
+      </c>
+      <c r="BM31">
+        <v>2.65</v>
+      </c>
+      <c r="BN31">
+        <v>1.41</v>
+      </c>
+      <c r="BO31">
+        <v>3.45</v>
+      </c>
+      <c r="BP31">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:68">
+      <c r="A32" s="1">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>7825221</v>
+      </c>
+      <c r="C32" t="s">
+        <v>68</v>
+      </c>
+      <c r="D32" t="s">
+        <v>69</v>
+      </c>
+      <c r="E32" s="2">
+        <v>45749.35763888889</v>
+      </c>
+      <c r="F32">
+        <v>4</v>
+      </c>
+      <c r="G32" t="s">
+        <v>75</v>
+      </c>
+      <c r="H32" t="s">
+        <v>70</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>2</v>
+      </c>
+      <c r="K32">
+        <v>2</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>3</v>
+      </c>
+      <c r="N32">
+        <v>3</v>
+      </c>
+      <c r="O32" t="s">
+        <v>88</v>
+      </c>
+      <c r="P32" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q32">
+        <v>2.9</v>
+      </c>
+      <c r="R32">
+        <v>2.19</v>
+      </c>
+      <c r="S32">
+        <v>3.3</v>
+      </c>
+      <c r="T32">
+        <v>1.32</v>
+      </c>
+      <c r="U32">
+        <v>3.1</v>
+      </c>
+      <c r="V32">
+        <v>2.57</v>
+      </c>
+      <c r="W32">
+        <v>1.44</v>
+      </c>
+      <c r="X32">
+        <v>6.25</v>
+      </c>
+      <c r="Y32">
+        <v>1.06</v>
+      </c>
+      <c r="Z32">
+        <v>2.41</v>
+      </c>
+      <c r="AA32">
+        <v>3.43</v>
+      </c>
+      <c r="AB32">
+        <v>2.79</v>
+      </c>
+      <c r="AC32">
+        <v>1.02</v>
+      </c>
+      <c r="AD32">
+        <v>12</v>
+      </c>
+      <c r="AE32">
+        <v>1.22</v>
+      </c>
+      <c r="AF32">
+        <v>3.93</v>
+      </c>
+      <c r="AG32">
+        <v>1.74</v>
+      </c>
+      <c r="AH32">
+        <v>2.03</v>
+      </c>
+      <c r="AI32">
+        <v>1.6</v>
+      </c>
+      <c r="AJ32">
+        <v>2.19</v>
+      </c>
+      <c r="AK32">
+        <v>1.43</v>
+      </c>
+      <c r="AL32">
+        <v>1.28</v>
+      </c>
+      <c r="AM32">
+        <v>1.56</v>
+      </c>
+      <c r="AN32">
+        <v>2</v>
+      </c>
+      <c r="AO32">
+        <v>1</v>
+      </c>
+      <c r="AP32">
+        <v>1.33</v>
+      </c>
+      <c r="AQ32">
+        <v>2</v>
+      </c>
+      <c r="AR32">
+        <v>2.46</v>
+      </c>
+      <c r="AS32">
+        <v>2.14</v>
+      </c>
+      <c r="AT32">
+        <v>4.6</v>
+      </c>
+      <c r="AU32">
+        <v>3</v>
+      </c>
+      <c r="AV32">
+        <v>9</v>
+      </c>
+      <c r="AW32">
+        <v>8</v>
+      </c>
+      <c r="AX32">
+        <v>8</v>
+      </c>
+      <c r="AY32">
+        <v>14</v>
+      </c>
+      <c r="AZ32">
+        <v>20</v>
+      </c>
+      <c r="BA32">
+        <v>6</v>
+      </c>
+      <c r="BB32">
+        <v>11</v>
+      </c>
+      <c r="BC32">
+        <v>17</v>
+      </c>
+      <c r="BD32">
+        <v>1.86</v>
+      </c>
+      <c r="BE32">
+        <v>6.4</v>
+      </c>
+      <c r="BF32">
+        <v>2.15</v>
+      </c>
+      <c r="BG32">
+        <v>1.36</v>
+      </c>
+      <c r="BH32">
+        <v>2.8</v>
+      </c>
+      <c r="BI32">
+        <v>1.61</v>
+      </c>
+      <c r="BJ32">
+        <v>2.15</v>
+      </c>
+      <c r="BK32">
+        <v>1.98</v>
+      </c>
+      <c r="BL32">
+        <v>1.72</v>
+      </c>
+      <c r="BM32">
+        <v>2.55</v>
+      </c>
+      <c r="BN32">
+        <v>1.44</v>
+      </c>
+      <c r="BO32">
+        <v>3.3</v>
+      </c>
+      <c r="BP32">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="33" spans="1:68">
+      <c r="A33" s="1">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>7825223</v>
+      </c>
+      <c r="C33" t="s">
+        <v>68</v>
+      </c>
+      <c r="D33" t="s">
+        <v>69</v>
+      </c>
+      <c r="E33" s="2">
+        <v>45749.375</v>
+      </c>
+      <c r="F33">
+        <v>4</v>
+      </c>
+      <c r="G33" t="s">
+        <v>77</v>
+      </c>
+      <c r="H33" t="s">
+        <v>78</v>
+      </c>
+      <c r="I33">
+        <v>2</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>2</v>
+      </c>
+      <c r="L33">
+        <v>2</v>
+      </c>
+      <c r="M33">
+        <v>1</v>
+      </c>
+      <c r="N33">
+        <v>3</v>
+      </c>
+      <c r="O33" t="s">
+        <v>113</v>
+      </c>
+      <c r="P33" t="s">
+        <v>135</v>
+      </c>
+      <c r="Q33">
+        <v>1.56</v>
+      </c>
+      <c r="R33">
+        <v>3.02</v>
+      </c>
+      <c r="S33">
+        <v>7.5</v>
+      </c>
+      <c r="T33">
+        <v>1.15</v>
+      </c>
+      <c r="U33">
+        <v>4.5</v>
+      </c>
+      <c r="V33">
+        <v>1.88</v>
+      </c>
+      <c r="W33">
+        <v>1.86</v>
+      </c>
+      <c r="X33">
+        <v>3.66</v>
+      </c>
+      <c r="Y33">
+        <v>1.22</v>
+      </c>
+      <c r="Z33">
+        <v>1.21</v>
+      </c>
+      <c r="AA33">
+        <v>7</v>
+      </c>
+      <c r="AB33">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="AC33">
+        <v>1.01</v>
+      </c>
+      <c r="AD33">
+        <v>29</v>
+      </c>
+      <c r="AE33">
+        <v>1.04</v>
+      </c>
+      <c r="AF33">
+        <v>7</v>
+      </c>
+      <c r="AG33">
+        <v>1.28</v>
+      </c>
+      <c r="AH33">
+        <v>3.34</v>
+      </c>
+      <c r="AI33">
+        <v>1.65</v>
+      </c>
+      <c r="AJ33">
+        <v>2.11</v>
+      </c>
+      <c r="AK33">
+        <v>1.03</v>
+      </c>
+      <c r="AL33">
+        <v>1.1</v>
+      </c>
+      <c r="AM33">
+        <v>4.1</v>
+      </c>
+      <c r="AN33">
+        <v>3</v>
+      </c>
+      <c r="AO33">
+        <v>1</v>
+      </c>
+      <c r="AP33">
+        <v>3</v>
+      </c>
+      <c r="AQ33">
+        <v>0.5</v>
+      </c>
+      <c r="AR33">
+        <v>2.3</v>
+      </c>
+      <c r="AS33">
+        <v>1.39</v>
+      </c>
+      <c r="AT33">
+        <v>3.69</v>
+      </c>
+      <c r="AU33">
+        <v>12</v>
+      </c>
+      <c r="AV33">
+        <v>4</v>
+      </c>
+      <c r="AW33">
+        <v>9</v>
+      </c>
+      <c r="AX33">
+        <v>7</v>
+      </c>
+      <c r="AY33">
+        <v>26</v>
+      </c>
+      <c r="AZ33">
+        <v>13</v>
+      </c>
+      <c r="BA33">
+        <v>2</v>
+      </c>
+      <c r="BB33">
+        <v>4</v>
+      </c>
+      <c r="BC33">
+        <v>6</v>
+      </c>
+      <c r="BD33">
+        <v>1.23</v>
+      </c>
+      <c r="BE33">
+        <v>8</v>
+      </c>
+      <c r="BF33">
+        <v>4.4</v>
+      </c>
+      <c r="BG33">
+        <v>1.25</v>
+      </c>
+      <c r="BH33">
+        <v>3.4</v>
+      </c>
+      <c r="BI33">
+        <v>1.44</v>
+      </c>
+      <c r="BJ33">
+        <v>2.55</v>
+      </c>
+      <c r="BK33">
+        <v>1.72</v>
+      </c>
+      <c r="BL33">
+        <v>1.98</v>
+      </c>
+      <c r="BM33">
+        <v>2.12</v>
+      </c>
+      <c r="BN33">
+        <v>1.62</v>
+      </c>
+      <c r="BO33">
+        <v>2.65</v>
+      </c>
+      <c r="BP33">
+        <v>1.41</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="138">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -358,6 +358,9 @@
     <t>['6', '44']</t>
   </si>
   <si>
+    <t>['85']</t>
+  </si>
+  <si>
     <t>['53', '79']</t>
   </si>
   <si>
@@ -422,6 +425,9 @@
   </si>
   <si>
     <t>['90+10']</t>
+  </si>
+  <si>
+    <t>['42', '59', '74']</t>
   </si>
 </sst>
 </file>
@@ -783,7 +789,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP33"/>
+  <dimension ref="A1:BP34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1451,7 +1457,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -1657,7 +1663,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q5">
         <v>2.85</v>
@@ -1863,7 +1869,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q6">
         <v>2.2</v>
@@ -2150,7 +2156,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ7">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2275,7 +2281,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q8">
         <v>2.04</v>
@@ -2481,7 +2487,7 @@
         <v>92</v>
       </c>
       <c r="P9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q9">
         <v>1.5</v>
@@ -2687,7 +2693,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q10">
         <v>2.1</v>
@@ -3099,7 +3105,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q12">
         <v>3.1</v>
@@ -3305,7 +3311,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -3386,7 +3392,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ13">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3511,7 +3517,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q14">
         <v>2.13</v>
@@ -3717,7 +3723,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q15">
         <v>3.2</v>
@@ -3923,7 +3929,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q16">
         <v>1.78</v>
@@ -4335,7 +4341,7 @@
         <v>100</v>
       </c>
       <c r="P18" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q18">
         <v>5.5</v>
@@ -4541,7 +4547,7 @@
         <v>88</v>
       </c>
       <c r="P19" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q19">
         <v>3.75</v>
@@ -4747,7 +4753,7 @@
         <v>101</v>
       </c>
       <c r="P20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q20">
         <v>3.25</v>
@@ -5365,7 +5371,7 @@
         <v>104</v>
       </c>
       <c r="P23" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q23">
         <v>4</v>
@@ -5571,7 +5577,7 @@
         <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q24">
         <v>4.75</v>
@@ -5777,7 +5783,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -5983,7 +5989,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q26">
         <v>2.88</v>
@@ -6395,7 +6401,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -6601,7 +6607,7 @@
         <v>110</v>
       </c>
       <c r="P29" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q29">
         <v>1.83</v>
@@ -7013,7 +7019,7 @@
         <v>112</v>
       </c>
       <c r="P31" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q31">
         <v>3.42</v>
@@ -7219,7 +7225,7 @@
         <v>88</v>
       </c>
       <c r="P32" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q32">
         <v>2.9</v>
@@ -7425,7 +7431,7 @@
         <v>113</v>
       </c>
       <c r="P33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q33">
         <v>1.56</v>
@@ -7582,6 +7588,212 @@
       </c>
       <c r="BP33">
         <v>1.41</v>
+      </c>
+    </row>
+    <row r="34" spans="1:68">
+      <c r="A34" s="1">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>7825224</v>
+      </c>
+      <c r="C34" t="s">
+        <v>68</v>
+      </c>
+      <c r="D34" t="s">
+        <v>69</v>
+      </c>
+      <c r="E34" s="2">
+        <v>45752.35763888889</v>
+      </c>
+      <c r="F34">
+        <v>5</v>
+      </c>
+      <c r="G34" t="s">
+        <v>81</v>
+      </c>
+      <c r="H34" t="s">
+        <v>83</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>1</v>
+      </c>
+      <c r="K34">
+        <v>1</v>
+      </c>
+      <c r="L34">
+        <v>1</v>
+      </c>
+      <c r="M34">
+        <v>3</v>
+      </c>
+      <c r="N34">
+        <v>4</v>
+      </c>
+      <c r="O34" t="s">
+        <v>114</v>
+      </c>
+      <c r="P34" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q34">
+        <v>3.25</v>
+      </c>
+      <c r="R34">
+        <v>2.1</v>
+      </c>
+      <c r="S34">
+        <v>3.25</v>
+      </c>
+      <c r="T34">
+        <v>1.4</v>
+      </c>
+      <c r="U34">
+        <v>2.75</v>
+      </c>
+      <c r="V34">
+        <v>3</v>
+      </c>
+      <c r="W34">
+        <v>1.36</v>
+      </c>
+      <c r="X34">
+        <v>9</v>
+      </c>
+      <c r="Y34">
+        <v>1.07</v>
+      </c>
+      <c r="Z34">
+        <v>2.6</v>
+      </c>
+      <c r="AA34">
+        <v>3.4</v>
+      </c>
+      <c r="AB34">
+        <v>2.6</v>
+      </c>
+      <c r="AC34">
+        <v>1.05</v>
+      </c>
+      <c r="AD34">
+        <v>8.5</v>
+      </c>
+      <c r="AE34">
+        <v>1.33</v>
+      </c>
+      <c r="AF34">
+        <v>3.2</v>
+      </c>
+      <c r="AG34">
+        <v>2</v>
+      </c>
+      <c r="AH34">
+        <v>1.8</v>
+      </c>
+      <c r="AI34">
+        <v>1.8</v>
+      </c>
+      <c r="AJ34">
+        <v>1.95</v>
+      </c>
+      <c r="AK34">
+        <v>1.44</v>
+      </c>
+      <c r="AL34">
+        <v>1.32</v>
+      </c>
+      <c r="AM34">
+        <v>1.49</v>
+      </c>
+      <c r="AN34">
+        <v>0</v>
+      </c>
+      <c r="AO34">
+        <v>0.5</v>
+      </c>
+      <c r="AP34">
+        <v>0</v>
+      </c>
+      <c r="AQ34">
+        <v>1.33</v>
+      </c>
+      <c r="AR34">
+        <v>2.26</v>
+      </c>
+      <c r="AS34">
+        <v>1.53</v>
+      </c>
+      <c r="AT34">
+        <v>3.79</v>
+      </c>
+      <c r="AU34">
+        <v>3</v>
+      </c>
+      <c r="AV34">
+        <v>10</v>
+      </c>
+      <c r="AW34">
+        <v>10</v>
+      </c>
+      <c r="AX34">
+        <v>9</v>
+      </c>
+      <c r="AY34">
+        <v>15</v>
+      </c>
+      <c r="AZ34">
+        <v>20</v>
+      </c>
+      <c r="BA34">
+        <v>6</v>
+      </c>
+      <c r="BB34">
+        <v>5</v>
+      </c>
+      <c r="BC34">
+        <v>11</v>
+      </c>
+      <c r="BD34">
+        <v>2.16</v>
+      </c>
+      <c r="BE34">
+        <v>8.6</v>
+      </c>
+      <c r="BF34">
+        <v>1.9</v>
+      </c>
+      <c r="BG34">
+        <v>1.14</v>
+      </c>
+      <c r="BH34">
+        <v>4.33</v>
+      </c>
+      <c r="BI34">
+        <v>1.3</v>
+      </c>
+      <c r="BJ34">
+        <v>2.97</v>
+      </c>
+      <c r="BK34">
+        <v>1.7</v>
+      </c>
+      <c r="BL34">
+        <v>2.05</v>
+      </c>
+      <c r="BM34">
+        <v>1.93</v>
+      </c>
+      <c r="BN34">
+        <v>1.77</v>
+      </c>
+      <c r="BO34">
+        <v>2.51</v>
+      </c>
+      <c r="BP34">
+        <v>1.44</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="148">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -361,6 +361,27 @@
     <t>['85']</t>
   </si>
   <si>
+    <t>['47']</t>
+  </si>
+  <si>
+    <t>['33', '72']</t>
+  </si>
+  <si>
+    <t>['69', '73', '82']</t>
+  </si>
+  <si>
+    <t>['39', '57']</t>
+  </si>
+  <si>
+    <t>['5']</t>
+  </si>
+  <si>
+    <t>['21', '56']</t>
+  </si>
+  <si>
+    <t>['86']</t>
+  </si>
+  <si>
     <t>['53', '79']</t>
   </si>
   <si>
@@ -428,6 +449,15 @@
   </si>
   <si>
     <t>['42', '59', '74']</t>
+  </si>
+  <si>
+    <t>['34', '76']</t>
+  </si>
+  <si>
+    <t>['27', '37']</t>
+  </si>
+  <si>
+    <t>['82']</t>
   </si>
 </sst>
 </file>
@@ -789,7 +819,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP34"/>
+  <dimension ref="A1:BP41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1123,10 +1153,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AQ2">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1457,7 +1487,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -1535,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ4">
         <v>1.67</v>
@@ -1663,7 +1693,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="Q5">
         <v>2.85</v>
@@ -1869,7 +1899,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="Q6">
         <v>2.2</v>
@@ -1950,7 +1980,7 @@
         <v>2</v>
       </c>
       <c r="AQ6">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2281,7 +2311,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="Q8">
         <v>2.04</v>
@@ -2487,7 +2517,7 @@
         <v>92</v>
       </c>
       <c r="P9" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="Q9">
         <v>1.5</v>
@@ -2565,7 +2595,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AQ9">
         <v>1</v>
@@ -2693,7 +2723,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="Q10">
         <v>2.1</v>
@@ -2774,7 +2804,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ10">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AR10">
         <v>2.21</v>
@@ -2977,7 +3007,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AQ11">
         <v>0</v>
@@ -3105,7 +3135,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="Q12">
         <v>3.1</v>
@@ -3311,7 +3341,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -3389,7 +3419,7 @@
         <v>1</v>
       </c>
       <c r="AP13">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AQ13">
         <v>1.33</v>
@@ -3517,7 +3547,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="Q14">
         <v>2.13</v>
@@ -3723,7 +3753,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="Q15">
         <v>3.2</v>
@@ -3801,10 +3831,10 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ15">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AR15">
         <v>1.22</v>
@@ -3929,7 +3959,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="Q16">
         <v>1.78</v>
@@ -4007,10 +4037,10 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AQ16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR16">
         <v>2.91</v>
@@ -4213,10 +4243,10 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ17">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4341,7 +4371,7 @@
         <v>100</v>
       </c>
       <c r="P18" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="Q18">
         <v>5.5</v>
@@ -4419,7 +4449,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ18">
         <v>1</v>
@@ -4547,7 +4577,7 @@
         <v>88</v>
       </c>
       <c r="P19" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="Q19">
         <v>3.75</v>
@@ -4628,7 +4658,7 @@
         <v>0</v>
       </c>
       <c r="AQ19">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -4753,7 +4783,7 @@
         <v>101</v>
       </c>
       <c r="P20" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="Q20">
         <v>3.25</v>
@@ -5371,7 +5401,7 @@
         <v>104</v>
       </c>
       <c r="P23" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="Q23">
         <v>4</v>
@@ -5452,7 +5482,7 @@
         <v>0</v>
       </c>
       <c r="AQ23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR23">
         <v>0</v>
@@ -5577,7 +5607,7 @@
         <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="Q24">
         <v>4.75</v>
@@ -5655,7 +5685,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AQ24">
         <v>3</v>
@@ -5783,7 +5813,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -5861,7 +5891,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ25">
         <v>2</v>
@@ -5989,7 +6019,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="Q26">
         <v>2.88</v>
@@ -6401,7 +6431,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -6479,10 +6509,10 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AQ28">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR28">
         <v>0</v>
@@ -6607,7 +6637,7 @@
         <v>110</v>
       </c>
       <c r="P29" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="Q29">
         <v>1.83</v>
@@ -6894,7 +6924,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ30">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AR30">
         <v>1.32</v>
@@ -7019,7 +7049,7 @@
         <v>112</v>
       </c>
       <c r="P31" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="Q31">
         <v>3.42</v>
@@ -7225,7 +7255,7 @@
         <v>88</v>
       </c>
       <c r="P32" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="Q32">
         <v>2.9</v>
@@ -7431,7 +7461,7 @@
         <v>113</v>
       </c>
       <c r="P33" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="Q33">
         <v>1.56</v>
@@ -7509,7 +7539,7 @@
         <v>1</v>
       </c>
       <c r="AP33">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AQ33">
         <v>0.5</v>
@@ -7637,7 +7667,7 @@
         <v>114</v>
       </c>
       <c r="P34" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="Q34">
         <v>3.25</v>
@@ -7794,6 +7824,1448 @@
       </c>
       <c r="BP34">
         <v>1.44</v>
+      </c>
+    </row>
+    <row r="35" spans="1:68">
+      <c r="A35" s="1">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>7825225</v>
+      </c>
+      <c r="C35" t="s">
+        <v>68</v>
+      </c>
+      <c r="D35" t="s">
+        <v>69</v>
+      </c>
+      <c r="E35" s="2">
+        <v>45753.1875</v>
+      </c>
+      <c r="F35">
+        <v>5</v>
+      </c>
+      <c r="G35" t="s">
+        <v>85</v>
+      </c>
+      <c r="H35" t="s">
+        <v>75</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>1</v>
+      </c>
+      <c r="K35">
+        <v>1</v>
+      </c>
+      <c r="L35">
+        <v>1</v>
+      </c>
+      <c r="M35">
+        <v>2</v>
+      </c>
+      <c r="N35">
+        <v>3</v>
+      </c>
+      <c r="O35" t="s">
+        <v>115</v>
+      </c>
+      <c r="P35" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q35">
+        <v>4.25</v>
+      </c>
+      <c r="R35">
+        <v>2.31</v>
+      </c>
+      <c r="S35">
+        <v>2.29</v>
+      </c>
+      <c r="T35">
+        <v>1.29</v>
+      </c>
+      <c r="U35">
+        <v>3.28</v>
+      </c>
+      <c r="V35">
+        <v>2.39</v>
+      </c>
+      <c r="W35">
+        <v>1.51</v>
+      </c>
+      <c r="X35">
+        <v>5.25</v>
+      </c>
+      <c r="Y35">
+        <v>1.09</v>
+      </c>
+      <c r="Z35">
+        <v>4.4</v>
+      </c>
+      <c r="AA35">
+        <v>3.7</v>
+      </c>
+      <c r="AB35">
+        <v>1.77</v>
+      </c>
+      <c r="AC35">
+        <v>1.01</v>
+      </c>
+      <c r="AD35">
+        <v>11</v>
+      </c>
+      <c r="AE35">
+        <v>1.16</v>
+      </c>
+      <c r="AF35">
+        <v>4.1</v>
+      </c>
+      <c r="AG35">
+        <v>1.57</v>
+      </c>
+      <c r="AH35">
+        <v>2.15</v>
+      </c>
+      <c r="AI35">
+        <v>1.6</v>
+      </c>
+      <c r="AJ35">
+        <v>2.19</v>
+      </c>
+      <c r="AK35">
+        <v>2</v>
+      </c>
+      <c r="AL35">
+        <v>1.24</v>
+      </c>
+      <c r="AM35">
+        <v>1.23</v>
+      </c>
+      <c r="AN35">
+        <v>1</v>
+      </c>
+      <c r="AO35">
+        <v>3</v>
+      </c>
+      <c r="AP35">
+        <v>0.5</v>
+      </c>
+      <c r="AQ35">
+        <v>3</v>
+      </c>
+      <c r="AR35">
+        <v>1.08</v>
+      </c>
+      <c r="AS35">
+        <v>2.1</v>
+      </c>
+      <c r="AT35">
+        <v>3.18</v>
+      </c>
+      <c r="AU35">
+        <v>6</v>
+      </c>
+      <c r="AV35">
+        <v>7</v>
+      </c>
+      <c r="AW35">
+        <v>10</v>
+      </c>
+      <c r="AX35">
+        <v>17</v>
+      </c>
+      <c r="AY35">
+        <v>18</v>
+      </c>
+      <c r="AZ35">
+        <v>27</v>
+      </c>
+      <c r="BA35">
+        <v>5</v>
+      </c>
+      <c r="BB35">
+        <v>7</v>
+      </c>
+      <c r="BC35">
+        <v>12</v>
+      </c>
+      <c r="BD35">
+        <v>2.95</v>
+      </c>
+      <c r="BE35">
+        <v>6.75</v>
+      </c>
+      <c r="BF35">
+        <v>1.48</v>
+      </c>
+      <c r="BG35">
+        <v>1.34</v>
+      </c>
+      <c r="BH35">
+        <v>2.9</v>
+      </c>
+      <c r="BI35">
+        <v>1.58</v>
+      </c>
+      <c r="BJ35">
+        <v>2.18</v>
+      </c>
+      <c r="BK35">
+        <v>1.94</v>
+      </c>
+      <c r="BL35">
+        <v>1.76</v>
+      </c>
+      <c r="BM35">
+        <v>2.43</v>
+      </c>
+      <c r="BN35">
+        <v>1.48</v>
+      </c>
+      <c r="BO35">
+        <v>3.15</v>
+      </c>
+      <c r="BP35">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:68">
+      <c r="A36" s="1">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>7825226</v>
+      </c>
+      <c r="C36" t="s">
+        <v>68</v>
+      </c>
+      <c r="D36" t="s">
+        <v>69</v>
+      </c>
+      <c r="E36" s="2">
+        <v>45753.3125</v>
+      </c>
+      <c r="F36">
+        <v>5</v>
+      </c>
+      <c r="G36" t="s">
+        <v>79</v>
+      </c>
+      <c r="H36" t="s">
+        <v>76</v>
+      </c>
+      <c r="I36">
+        <v>1</v>
+      </c>
+      <c r="J36">
+        <v>2</v>
+      </c>
+      <c r="K36">
+        <v>3</v>
+      </c>
+      <c r="L36">
+        <v>2</v>
+      </c>
+      <c r="M36">
+        <v>2</v>
+      </c>
+      <c r="N36">
+        <v>4</v>
+      </c>
+      <c r="O36" t="s">
+        <v>116</v>
+      </c>
+      <c r="P36" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q36">
+        <v>3.15</v>
+      </c>
+      <c r="R36">
+        <v>2.17</v>
+      </c>
+      <c r="S36">
+        <v>3.06</v>
+      </c>
+      <c r="T36">
+        <v>1.33</v>
+      </c>
+      <c r="U36">
+        <v>3.04</v>
+      </c>
+      <c r="V36">
+        <v>2.62</v>
+      </c>
+      <c r="W36">
+        <v>1.43</v>
+      </c>
+      <c r="X36">
+        <v>6.15</v>
+      </c>
+      <c r="Y36">
+        <v>1.06</v>
+      </c>
+      <c r="Z36">
+        <v>2.5</v>
+      </c>
+      <c r="AA36">
+        <v>3.4</v>
+      </c>
+      <c r="AB36">
+        <v>2.7</v>
+      </c>
+      <c r="AC36">
+        <v>1.02</v>
+      </c>
+      <c r="AD36">
+        <v>10</v>
+      </c>
+      <c r="AE36">
+        <v>1.21</v>
+      </c>
+      <c r="AF36">
+        <v>3.6</v>
+      </c>
+      <c r="AG36">
+        <v>1.8</v>
+      </c>
+      <c r="AH36">
+        <v>2</v>
+      </c>
+      <c r="AI36">
+        <v>1.62</v>
+      </c>
+      <c r="AJ36">
+        <v>2.16</v>
+      </c>
+      <c r="AK36">
+        <v>1.49</v>
+      </c>
+      <c r="AL36">
+        <v>1.28</v>
+      </c>
+      <c r="AM36">
+        <v>1.48</v>
+      </c>
+      <c r="AN36">
+        <v>2</v>
+      </c>
+      <c r="AO36">
+        <v>3</v>
+      </c>
+      <c r="AP36">
+        <v>1.67</v>
+      </c>
+      <c r="AQ36">
+        <v>2</v>
+      </c>
+      <c r="AR36">
+        <v>1.07</v>
+      </c>
+      <c r="AS36">
+        <v>1.28</v>
+      </c>
+      <c r="AT36">
+        <v>2.35</v>
+      </c>
+      <c r="AU36">
+        <v>4</v>
+      </c>
+      <c r="AV36">
+        <v>5</v>
+      </c>
+      <c r="AW36">
+        <v>6</v>
+      </c>
+      <c r="AX36">
+        <v>3</v>
+      </c>
+      <c r="AY36">
+        <v>13</v>
+      </c>
+      <c r="AZ36">
+        <v>9</v>
+      </c>
+      <c r="BA36">
+        <v>4</v>
+      </c>
+      <c r="BB36">
+        <v>3</v>
+      </c>
+      <c r="BC36">
+        <v>7</v>
+      </c>
+      <c r="BD36">
+        <v>1.84</v>
+      </c>
+      <c r="BE36">
+        <v>6.4</v>
+      </c>
+      <c r="BF36">
+        <v>2.18</v>
+      </c>
+      <c r="BG36">
+        <v>1.34</v>
+      </c>
+      <c r="BH36">
+        <v>2.9</v>
+      </c>
+      <c r="BI36">
+        <v>1.58</v>
+      </c>
+      <c r="BJ36">
+        <v>2.18</v>
+      </c>
+      <c r="BK36">
+        <v>1.95</v>
+      </c>
+      <c r="BL36">
+        <v>1.75</v>
+      </c>
+      <c r="BM36">
+        <v>2.48</v>
+      </c>
+      <c r="BN36">
+        <v>1.46</v>
+      </c>
+      <c r="BO36">
+        <v>3.2</v>
+      </c>
+      <c r="BP36">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="37" spans="1:68">
+      <c r="A37" s="1">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>7825227</v>
+      </c>
+      <c r="C37" t="s">
+        <v>68</v>
+      </c>
+      <c r="D37" t="s">
+        <v>69</v>
+      </c>
+      <c r="E37" s="2">
+        <v>45753.33333333334</v>
+      </c>
+      <c r="F37">
+        <v>5</v>
+      </c>
+      <c r="G37" t="s">
+        <v>78</v>
+      </c>
+      <c r="H37" t="s">
+        <v>80</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>1</v>
+      </c>
+      <c r="K37">
+        <v>1</v>
+      </c>
+      <c r="L37">
+        <v>3</v>
+      </c>
+      <c r="M37">
+        <v>1</v>
+      </c>
+      <c r="N37">
+        <v>4</v>
+      </c>
+      <c r="O37" t="s">
+        <v>117</v>
+      </c>
+      <c r="P37" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q37">
+        <v>2.75</v>
+      </c>
+      <c r="R37">
+        <v>2.15</v>
+      </c>
+      <c r="S37">
+        <v>3.62</v>
+      </c>
+      <c r="T37">
+        <v>1.33</v>
+      </c>
+      <c r="U37">
+        <v>3.04</v>
+      </c>
+      <c r="V37">
+        <v>2.69</v>
+      </c>
+      <c r="W37">
+        <v>1.41</v>
+      </c>
+      <c r="X37">
+        <v>6.95</v>
+      </c>
+      <c r="Y37">
+        <v>1.04</v>
+      </c>
+      <c r="Z37">
+        <v>2.2</v>
+      </c>
+      <c r="AA37">
+        <v>3.5</v>
+      </c>
+      <c r="AB37">
+        <v>3.2</v>
+      </c>
+      <c r="AC37">
+        <v>1.02</v>
+      </c>
+      <c r="AD37">
+        <v>10</v>
+      </c>
+      <c r="AE37">
+        <v>1.2</v>
+      </c>
+      <c r="AF37">
+        <v>3.72</v>
+      </c>
+      <c r="AG37">
+        <v>1.67</v>
+      </c>
+      <c r="AH37">
+        <v>2</v>
+      </c>
+      <c r="AI37">
+        <v>1.65</v>
+      </c>
+      <c r="AJ37">
+        <v>2.11</v>
+      </c>
+      <c r="AK37">
+        <v>1.35</v>
+      </c>
+      <c r="AL37">
+        <v>1.28</v>
+      </c>
+      <c r="AM37">
+        <v>1.66</v>
+      </c>
+      <c r="AN37">
+        <v>1.5</v>
+      </c>
+      <c r="AO37">
+        <v>0.33</v>
+      </c>
+      <c r="AP37">
+        <v>2</v>
+      </c>
+      <c r="AQ37">
+        <v>0.25</v>
+      </c>
+      <c r="AR37">
+        <v>1.61</v>
+      </c>
+      <c r="AS37">
+        <v>0.96</v>
+      </c>
+      <c r="AT37">
+        <v>2.57</v>
+      </c>
+      <c r="AU37">
+        <v>9</v>
+      </c>
+      <c r="AV37">
+        <v>3</v>
+      </c>
+      <c r="AW37">
+        <v>9</v>
+      </c>
+      <c r="AX37">
+        <v>4</v>
+      </c>
+      <c r="AY37">
+        <v>22</v>
+      </c>
+      <c r="AZ37">
+        <v>9</v>
+      </c>
+      <c r="BA37">
+        <v>6</v>
+      </c>
+      <c r="BB37">
+        <v>1</v>
+      </c>
+      <c r="BC37">
+        <v>7</v>
+      </c>
+      <c r="BD37">
+        <v>1.66</v>
+      </c>
+      <c r="BE37">
+        <v>6.75</v>
+      </c>
+      <c r="BF37">
+        <v>2.45</v>
+      </c>
+      <c r="BG37">
+        <v>1.35</v>
+      </c>
+      <c r="BH37">
+        <v>2.9</v>
+      </c>
+      <c r="BI37">
+        <v>1.6</v>
+      </c>
+      <c r="BJ37">
+        <v>2.17</v>
+      </c>
+      <c r="BK37">
+        <v>1.98</v>
+      </c>
+      <c r="BL37">
+        <v>1.72</v>
+      </c>
+      <c r="BM37">
+        <v>2.5</v>
+      </c>
+      <c r="BN37">
+        <v>1.46</v>
+      </c>
+      <c r="BO37">
+        <v>3.3</v>
+      </c>
+      <c r="BP37">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="38" spans="1:68">
+      <c r="A38" s="1">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>7825228</v>
+      </c>
+      <c r="C38" t="s">
+        <v>68</v>
+      </c>
+      <c r="D38" t="s">
+        <v>69</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45753.33333333334</v>
+      </c>
+      <c r="F38">
+        <v>5</v>
+      </c>
+      <c r="G38" t="s">
+        <v>70</v>
+      </c>
+      <c r="H38" t="s">
+        <v>82</v>
+      </c>
+      <c r="I38">
+        <v>1</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>1</v>
+      </c>
+      <c r="L38">
+        <v>2</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38">
+        <v>2</v>
+      </c>
+      <c r="O38" t="s">
+        <v>118</v>
+      </c>
+      <c r="P38" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q38">
+        <v>1.7</v>
+      </c>
+      <c r="R38">
+        <v>2.57</v>
+      </c>
+      <c r="S38">
+        <v>7.8</v>
+      </c>
+      <c r="T38">
+        <v>1.24</v>
+      </c>
+      <c r="U38">
+        <v>3.5</v>
+      </c>
+      <c r="V38">
+        <v>2.34</v>
+      </c>
+      <c r="W38">
+        <v>1.56</v>
+      </c>
+      <c r="X38">
+        <v>5.55</v>
+      </c>
+      <c r="Y38">
+        <v>1.1</v>
+      </c>
+      <c r="Z38">
+        <v>1.3</v>
+      </c>
+      <c r="AA38">
+        <v>5.5</v>
+      </c>
+      <c r="AB38">
+        <v>9</v>
+      </c>
+      <c r="AC38">
+        <v>1.01</v>
+      </c>
+      <c r="AD38">
+        <v>13</v>
+      </c>
+      <c r="AE38">
+        <v>1.12</v>
+      </c>
+      <c r="AF38">
+        <v>4.75</v>
+      </c>
+      <c r="AG38">
+        <v>1.57</v>
+      </c>
+      <c r="AH38">
+        <v>2.35</v>
+      </c>
+      <c r="AI38">
+        <v>1.93</v>
+      </c>
+      <c r="AJ38">
+        <v>1.78</v>
+      </c>
+      <c r="AK38">
+        <v>1.04</v>
+      </c>
+      <c r="AL38">
+        <v>1.13</v>
+      </c>
+      <c r="AM38">
+        <v>3.54</v>
+      </c>
+      <c r="AN38">
+        <v>1.5</v>
+      </c>
+      <c r="AO38">
+        <v>0.67</v>
+      </c>
+      <c r="AP38">
+        <v>2</v>
+      </c>
+      <c r="AQ38">
+        <v>0.5</v>
+      </c>
+      <c r="AR38">
+        <v>2.39</v>
+      </c>
+      <c r="AS38">
+        <v>1.36</v>
+      </c>
+      <c r="AT38">
+        <v>3.75</v>
+      </c>
+      <c r="AU38">
+        <v>9</v>
+      </c>
+      <c r="AV38">
+        <v>2</v>
+      </c>
+      <c r="AW38">
+        <v>9</v>
+      </c>
+      <c r="AX38">
+        <v>5</v>
+      </c>
+      <c r="AY38">
+        <v>19</v>
+      </c>
+      <c r="AZ38">
+        <v>8</v>
+      </c>
+      <c r="BA38">
+        <v>7</v>
+      </c>
+      <c r="BB38">
+        <v>3</v>
+      </c>
+      <c r="BC38">
+        <v>10</v>
+      </c>
+      <c r="BD38">
+        <v>1.24</v>
+      </c>
+      <c r="BE38">
+        <v>8.5</v>
+      </c>
+      <c r="BF38">
+        <v>4.35</v>
+      </c>
+      <c r="BG38">
+        <v>1.27</v>
+      </c>
+      <c r="BH38">
+        <v>3.3</v>
+      </c>
+      <c r="BI38">
+        <v>1.47</v>
+      </c>
+      <c r="BJ38">
+        <v>2.48</v>
+      </c>
+      <c r="BK38">
+        <v>1.74</v>
+      </c>
+      <c r="BL38">
+        <v>1.96</v>
+      </c>
+      <c r="BM38">
+        <v>2.15</v>
+      </c>
+      <c r="BN38">
+        <v>1.61</v>
+      </c>
+      <c r="BO38">
+        <v>2.7</v>
+      </c>
+      <c r="BP38">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="39" spans="1:68">
+      <c r="A39" s="1">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>7825229</v>
+      </c>
+      <c r="C39" t="s">
+        <v>68</v>
+      </c>
+      <c r="D39" t="s">
+        <v>69</v>
+      </c>
+      <c r="E39" s="2">
+        <v>45753.35763888889</v>
+      </c>
+      <c r="F39">
+        <v>5</v>
+      </c>
+      <c r="G39" t="s">
+        <v>77</v>
+      </c>
+      <c r="H39" t="s">
+        <v>71</v>
+      </c>
+      <c r="I39">
+        <v>1</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>1</v>
+      </c>
+      <c r="L39">
+        <v>1</v>
+      </c>
+      <c r="M39">
+        <v>1</v>
+      </c>
+      <c r="N39">
+        <v>2</v>
+      </c>
+      <c r="O39" t="s">
+        <v>119</v>
+      </c>
+      <c r="P39" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q39">
+        <v>2.88</v>
+      </c>
+      <c r="R39">
+        <v>2.23</v>
+      </c>
+      <c r="S39">
+        <v>3.24</v>
+      </c>
+      <c r="T39">
+        <v>1.25</v>
+      </c>
+      <c r="U39">
+        <v>3.42</v>
+      </c>
+      <c r="V39">
+        <v>2.23</v>
+      </c>
+      <c r="W39">
+        <v>1.61</v>
+      </c>
+      <c r="X39">
+        <v>5.15</v>
+      </c>
+      <c r="Y39">
+        <v>1.11</v>
+      </c>
+      <c r="Z39">
+        <v>2.4</v>
+      </c>
+      <c r="AA39">
+        <v>3.7</v>
+      </c>
+      <c r="AB39">
+        <v>2.75</v>
+      </c>
+      <c r="AC39">
+        <v>1.01</v>
+      </c>
+      <c r="AD39">
+        <v>13</v>
+      </c>
+      <c r="AE39">
+        <v>1.09</v>
+      </c>
+      <c r="AF39">
+        <v>5.25</v>
+      </c>
+      <c r="AG39">
+        <v>1.53</v>
+      </c>
+      <c r="AH39">
+        <v>2.2</v>
+      </c>
+      <c r="AI39">
+        <v>1.41</v>
+      </c>
+      <c r="AJ39">
+        <v>2.69</v>
+      </c>
+      <c r="AK39">
+        <v>1.43</v>
+      </c>
+      <c r="AL39">
+        <v>1.28</v>
+      </c>
+      <c r="AM39">
+        <v>1.56</v>
+      </c>
+      <c r="AN39">
+        <v>3</v>
+      </c>
+      <c r="AO39">
+        <v>3</v>
+      </c>
+      <c r="AP39">
+        <v>2.5</v>
+      </c>
+      <c r="AQ39">
+        <v>2</v>
+      </c>
+      <c r="AR39">
+        <v>2.38</v>
+      </c>
+      <c r="AS39">
+        <v>2.07</v>
+      </c>
+      <c r="AT39">
+        <v>4.45</v>
+      </c>
+      <c r="AU39">
+        <v>2</v>
+      </c>
+      <c r="AV39">
+        <v>6</v>
+      </c>
+      <c r="AW39">
+        <v>9</v>
+      </c>
+      <c r="AX39">
+        <v>12</v>
+      </c>
+      <c r="AY39">
+        <v>11</v>
+      </c>
+      <c r="AZ39">
+        <v>22</v>
+      </c>
+      <c r="BA39">
+        <v>8</v>
+      </c>
+      <c r="BB39">
+        <v>10</v>
+      </c>
+      <c r="BC39">
+        <v>18</v>
+      </c>
+      <c r="BD39">
+        <v>1.82</v>
+      </c>
+      <c r="BE39">
+        <v>6.75</v>
+      </c>
+      <c r="BF39">
+        <v>2.17</v>
+      </c>
+      <c r="BG39">
+        <v>1.18</v>
+      </c>
+      <c r="BH39">
+        <v>4.1</v>
+      </c>
+      <c r="BI39">
+        <v>1.34</v>
+      </c>
+      <c r="BJ39">
+        <v>2.9</v>
+      </c>
+      <c r="BK39">
+        <v>1.56</v>
+      </c>
+      <c r="BL39">
+        <v>2.23</v>
+      </c>
+      <c r="BM39">
+        <v>1.88</v>
+      </c>
+      <c r="BN39">
+        <v>1.81</v>
+      </c>
+      <c r="BO39">
+        <v>2.32</v>
+      </c>
+      <c r="BP39">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="40" spans="1:68">
+      <c r="A40" s="1">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>7825230</v>
+      </c>
+      <c r="C40" t="s">
+        <v>68</v>
+      </c>
+      <c r="D40" t="s">
+        <v>69</v>
+      </c>
+      <c r="E40" s="2">
+        <v>45753.35763888889</v>
+      </c>
+      <c r="F40">
+        <v>5</v>
+      </c>
+      <c r="G40" t="s">
+        <v>84</v>
+      </c>
+      <c r="H40" t="s">
+        <v>74</v>
+      </c>
+      <c r="I40">
+        <v>1</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>1</v>
+      </c>
+      <c r="L40">
+        <v>2</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40">
+        <v>2</v>
+      </c>
+      <c r="O40" t="s">
+        <v>120</v>
+      </c>
+      <c r="P40" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q40">
+        <v>2.19</v>
+      </c>
+      <c r="R40">
+        <v>2.24</v>
+      </c>
+      <c r="S40">
+        <v>4.95</v>
+      </c>
+      <c r="T40">
+        <v>1.3</v>
+      </c>
+      <c r="U40">
+        <v>3.22</v>
+      </c>
+      <c r="V40">
+        <v>2.32</v>
+      </c>
+      <c r="W40">
+        <v>1.54</v>
+      </c>
+      <c r="X40">
+        <v>5.3</v>
+      </c>
+      <c r="Y40">
+        <v>1.09</v>
+      </c>
+      <c r="Z40">
+        <v>1.65</v>
+      </c>
+      <c r="AA40">
+        <v>4</v>
+      </c>
+      <c r="AB40">
+        <v>4.9</v>
+      </c>
+      <c r="AC40">
+        <v>1.01</v>
+      </c>
+      <c r="AD40">
+        <v>13</v>
+      </c>
+      <c r="AE40">
+        <v>1.13</v>
+      </c>
+      <c r="AF40">
+        <v>4.6</v>
+      </c>
+      <c r="AG40">
+        <v>1.6</v>
+      </c>
+      <c r="AH40">
+        <v>2.1</v>
+      </c>
+      <c r="AI40">
+        <v>1.58</v>
+      </c>
+      <c r="AJ40">
+        <v>2.23</v>
+      </c>
+      <c r="AK40">
+        <v>1.16</v>
+      </c>
+      <c r="AL40">
+        <v>1.24</v>
+      </c>
+      <c r="AM40">
+        <v>2.19</v>
+      </c>
+      <c r="AN40">
+        <v>1</v>
+      </c>
+      <c r="AO40">
+        <v>2</v>
+      </c>
+      <c r="AP40">
+        <v>2</v>
+      </c>
+      <c r="AQ40">
+        <v>1.33</v>
+      </c>
+      <c r="AR40">
+        <v>0.75</v>
+      </c>
+      <c r="AS40">
+        <v>1.53</v>
+      </c>
+      <c r="AT40">
+        <v>2.28</v>
+      </c>
+      <c r="AU40">
+        <v>12</v>
+      </c>
+      <c r="AV40">
+        <v>5</v>
+      </c>
+      <c r="AW40">
+        <v>14</v>
+      </c>
+      <c r="AX40">
+        <v>6</v>
+      </c>
+      <c r="AY40">
+        <v>28</v>
+      </c>
+      <c r="AZ40">
+        <v>12</v>
+      </c>
+      <c r="BA40">
+        <v>10</v>
+      </c>
+      <c r="BB40">
+        <v>8</v>
+      </c>
+      <c r="BC40">
+        <v>18</v>
+      </c>
+      <c r="BD40">
+        <v>1.49</v>
+      </c>
+      <c r="BE40">
+        <v>6.75</v>
+      </c>
+      <c r="BF40">
+        <v>2.9</v>
+      </c>
+      <c r="BG40">
+        <v>1.25</v>
+      </c>
+      <c r="BH40">
+        <v>3.45</v>
+      </c>
+      <c r="BI40">
+        <v>1.44</v>
+      </c>
+      <c r="BJ40">
+        <v>2.55</v>
+      </c>
+      <c r="BK40">
+        <v>1.72</v>
+      </c>
+      <c r="BL40">
+        <v>1.98</v>
+      </c>
+      <c r="BM40">
+        <v>2.1</v>
+      </c>
+      <c r="BN40">
+        <v>1.64</v>
+      </c>
+      <c r="BO40">
+        <v>2.65</v>
+      </c>
+      <c r="BP40">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="41" spans="1:68">
+      <c r="A41" s="1">
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <v>7825231</v>
+      </c>
+      <c r="C41" t="s">
+        <v>68</v>
+      </c>
+      <c r="D41" t="s">
+        <v>69</v>
+      </c>
+      <c r="E41" s="2">
+        <v>45753.375</v>
+      </c>
+      <c r="F41">
+        <v>5</v>
+      </c>
+      <c r="G41" t="s">
+        <v>72</v>
+      </c>
+      <c r="H41" t="s">
+        <v>73</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>0</v>
+      </c>
+      <c r="L41">
+        <v>1</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41">
+        <v>1</v>
+      </c>
+      <c r="O41" t="s">
+        <v>121</v>
+      </c>
+      <c r="P41" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q41">
+        <v>2.23</v>
+      </c>
+      <c r="R41">
+        <v>2.22</v>
+      </c>
+      <c r="S41">
+        <v>4.85</v>
+      </c>
+      <c r="T41">
+        <v>1.33</v>
+      </c>
+      <c r="U41">
+        <v>3.04</v>
+      </c>
+      <c r="V41">
+        <v>2.65</v>
+      </c>
+      <c r="W41">
+        <v>1.42</v>
+      </c>
+      <c r="X41">
+        <v>6.5</v>
+      </c>
+      <c r="Y41">
+        <v>1.05</v>
+      </c>
+      <c r="Z41">
+        <v>2.1</v>
+      </c>
+      <c r="AA41">
+        <v>3.5</v>
+      </c>
+      <c r="AB41">
+        <v>3.5</v>
+      </c>
+      <c r="AC41">
+        <v>1</v>
+      </c>
+      <c r="AD41">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE41">
+        <v>1.21</v>
+      </c>
+      <c r="AF41">
+        <v>3.6</v>
+      </c>
+      <c r="AG41">
+        <v>1.79</v>
+      </c>
+      <c r="AH41">
+        <v>1.81</v>
+      </c>
+      <c r="AI41">
+        <v>1.74</v>
+      </c>
+      <c r="AJ41">
+        <v>1.98</v>
+      </c>
+      <c r="AK41">
+        <v>1.18</v>
+      </c>
+      <c r="AL41">
+        <v>1.25</v>
+      </c>
+      <c r="AM41">
+        <v>2.09</v>
+      </c>
+      <c r="AN41">
+        <v>0.5</v>
+      </c>
+      <c r="AO41">
+        <v>0</v>
+      </c>
+      <c r="AP41">
+        <v>1.33</v>
+      </c>
+      <c r="AQ41">
+        <v>0</v>
+      </c>
+      <c r="AR41">
+        <v>1.18</v>
+      </c>
+      <c r="AS41">
+        <v>0.8</v>
+      </c>
+      <c r="AT41">
+        <v>1.98</v>
+      </c>
+      <c r="AU41">
+        <v>6</v>
+      </c>
+      <c r="AV41">
+        <v>6</v>
+      </c>
+      <c r="AW41">
+        <v>15</v>
+      </c>
+      <c r="AX41">
+        <v>6</v>
+      </c>
+      <c r="AY41">
+        <v>26</v>
+      </c>
+      <c r="AZ41">
+        <v>15</v>
+      </c>
+      <c r="BA41">
+        <v>7</v>
+      </c>
+      <c r="BB41">
+        <v>4</v>
+      </c>
+      <c r="BC41">
+        <v>11</v>
+      </c>
+      <c r="BD41">
+        <v>1.5</v>
+      </c>
+      <c r="BE41">
+        <v>6.75</v>
+      </c>
+      <c r="BF41">
+        <v>2.8</v>
+      </c>
+      <c r="BG41">
+        <v>1.32</v>
+      </c>
+      <c r="BH41">
+        <v>3.05</v>
+      </c>
+      <c r="BI41">
+        <v>1.55</v>
+      </c>
+      <c r="BJ41">
+        <v>2.28</v>
+      </c>
+      <c r="BK41">
+        <v>1.89</v>
+      </c>
+      <c r="BL41">
+        <v>1.8</v>
+      </c>
+      <c r="BM41">
+        <v>2.4</v>
+      </c>
+      <c r="BN41">
+        <v>1.49</v>
+      </c>
+      <c r="BO41">
+        <v>3.05</v>
+      </c>
+      <c r="BP41">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
@@ -9220,13 +9220,13 @@
         <v>15</v>
       </c>
       <c r="BA41">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB41">
         <v>4</v>
       </c>
       <c r="BC41">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD41">
         <v>1.5</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="235">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -517,6 +517,15 @@
     <t>['15']</t>
   </si>
   <si>
+    <t>['12', '32']</t>
+  </si>
+  <si>
+    <t>['80', '9012']</t>
+  </si>
+  <si>
+    <t>['18', '25']</t>
+  </si>
+  <si>
     <t>['53', '79']</t>
   </si>
   <si>
@@ -704,6 +713,12 @@
   </si>
   <si>
     <t>['57']</t>
+  </si>
+  <si>
+    <t>['45', '51']</t>
+  </si>
+  <si>
+    <t>['88']</t>
   </si>
 </sst>
 </file>
@@ -1065,7 +1080,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP102"/>
+  <dimension ref="A1:BP107"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1608,7 +1623,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ3">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1733,7 +1748,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -1939,7 +1954,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="Q5">
         <v>2.85</v>
@@ -2145,7 +2160,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="Q6">
         <v>2.2</v>
@@ -2223,7 +2238,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ6">
         <v>0.57</v>
@@ -2557,7 +2572,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Q8">
         <v>2.04</v>
@@ -2638,7 +2653,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ8">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2763,7 +2778,7 @@
         <v>92</v>
       </c>
       <c r="P9" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="Q9">
         <v>1.5</v>
@@ -2969,7 +2984,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="Q10">
         <v>2.1</v>
@@ -3256,7 +3271,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ11">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AR11">
         <v>1.91</v>
@@ -3381,7 +3396,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="Q12">
         <v>3.1</v>
@@ -3587,7 +3602,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -3793,7 +3808,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Q14">
         <v>2.13</v>
@@ -3999,7 +4014,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Q15">
         <v>3.2</v>
@@ -4205,7 +4220,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q16">
         <v>1.78</v>
@@ -4489,7 +4504,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AQ17">
         <v>0.67</v>
@@ -4617,7 +4632,7 @@
         <v>100</v>
       </c>
       <c r="P18" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Q18">
         <v>5.5</v>
@@ -4695,10 +4710,10 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AQ18">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AR18">
         <v>0.8</v>
@@ -4823,7 +4838,7 @@
         <v>88</v>
       </c>
       <c r="P19" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Q19">
         <v>3.75</v>
@@ -4901,7 +4916,7 @@
         <v>1</v>
       </c>
       <c r="AP19">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ19">
         <v>0.57</v>
@@ -5029,7 +5044,7 @@
         <v>101</v>
       </c>
       <c r="P20" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="Q20">
         <v>3.25</v>
@@ -5110,7 +5125,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ20">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -5313,10 +5328,10 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ21">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AR21">
         <v>0</v>
@@ -5522,7 +5537,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ22">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AR22">
         <v>3.42</v>
@@ -5647,7 +5662,7 @@
         <v>104</v>
       </c>
       <c r="P23" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="Q23">
         <v>4</v>
@@ -5853,7 +5868,7 @@
         <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Q24">
         <v>4.75</v>
@@ -6059,7 +6074,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -6137,7 +6152,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AQ25">
         <v>2.67</v>
@@ -6265,7 +6280,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Q26">
         <v>2.88</v>
@@ -6549,7 +6564,7 @@
         <v>1.5</v>
       </c>
       <c r="AP27">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ27">
         <v>0.57</v>
@@ -6883,7 +6898,7 @@
         <v>110</v>
       </c>
       <c r="P29" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Q29">
         <v>1.83</v>
@@ -6964,7 +6979,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ29">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR29">
         <v>1.91</v>
@@ -7295,7 +7310,7 @@
         <v>88</v>
       </c>
       <c r="P31" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q31">
         <v>2.9</v>
@@ -7501,7 +7516,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q32">
         <v>3.42</v>
@@ -7707,7 +7722,7 @@
         <v>113</v>
       </c>
       <c r="P33" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q33">
         <v>1.56</v>
@@ -7788,7 +7803,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ33">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR33">
         <v>2.3</v>
@@ -7913,7 +7928,7 @@
         <v>114</v>
       </c>
       <c r="P34" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q34">
         <v>3.25</v>
@@ -8119,7 +8134,7 @@
         <v>115</v>
       </c>
       <c r="P35" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q35">
         <v>4.25</v>
@@ -8325,7 +8340,7 @@
         <v>116</v>
       </c>
       <c r="P36" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q36">
         <v>3.15</v>
@@ -8403,7 +8418,7 @@
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AQ36">
         <v>1.57</v>
@@ -8531,7 +8546,7 @@
         <v>117</v>
       </c>
       <c r="P37" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="Q37">
         <v>2.75</v>
@@ -8943,7 +8958,7 @@
         <v>119</v>
       </c>
       <c r="P39" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q39">
         <v>2.88</v>
@@ -9227,7 +9242,7 @@
         <v>2</v>
       </c>
       <c r="AP40">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AQ40">
         <v>0.57</v>
@@ -9436,7 +9451,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ41">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AR41">
         <v>1.18</v>
@@ -9767,7 +9782,7 @@
         <v>123</v>
       </c>
       <c r="P43" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q43">
         <v>3</v>
@@ -9848,7 +9863,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ43">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AR43">
         <v>1.8</v>
@@ -9973,7 +9988,7 @@
         <v>124</v>
       </c>
       <c r="P44" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q44">
         <v>3.2</v>
@@ -10051,7 +10066,7 @@
         <v>2</v>
       </c>
       <c r="AP44">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ44">
         <v>1.57</v>
@@ -10179,7 +10194,7 @@
         <v>88</v>
       </c>
       <c r="P45" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q45">
         <v>7.5</v>
@@ -10463,10 +10478,10 @@
         <v>1.5</v>
       </c>
       <c r="AP46">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ46">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR46">
         <v>1.82</v>
@@ -10591,7 +10606,7 @@
         <v>126</v>
       </c>
       <c r="P47" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q47">
         <v>1.95</v>
@@ -10797,7 +10812,7 @@
         <v>127</v>
       </c>
       <c r="P48" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q48">
         <v>3.7</v>
@@ -10875,7 +10890,7 @@
         <v>3</v>
       </c>
       <c r="AP48">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AQ48">
         <v>1.67</v>
@@ -11003,7 +11018,7 @@
         <v>128</v>
       </c>
       <c r="P49" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q49">
         <v>4.33</v>
@@ -11081,7 +11096,7 @@
         <v>1.67</v>
       </c>
       <c r="AP49">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ49">
         <v>1.86</v>
@@ -11209,7 +11224,7 @@
         <v>129</v>
       </c>
       <c r="P50" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="Q50">
         <v>2.65</v>
@@ -11290,7 +11305,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ50">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AR50">
         <v>1.81</v>
@@ -11415,7 +11430,7 @@
         <v>130</v>
       </c>
       <c r="P51" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q51">
         <v>4.15</v>
@@ -11496,7 +11511,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ51">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AR51">
         <v>2.87</v>
@@ -11699,7 +11714,7 @@
         <v>1.33</v>
       </c>
       <c r="AP52">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ52">
         <v>1.14</v>
@@ -11827,7 +11842,7 @@
         <v>132</v>
       </c>
       <c r="P53" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q53">
         <v>1.8</v>
@@ -11905,10 +11920,10 @@
         <v>0.5</v>
       </c>
       <c r="AP53">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ53">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR53">
         <v>1.5</v>
@@ -12033,7 +12048,7 @@
         <v>104</v>
       </c>
       <c r="P54" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q54">
         <v>1.71</v>
@@ -12114,7 +12129,7 @@
         <v>2</v>
       </c>
       <c r="AQ54">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR54">
         <v>2.36</v>
@@ -12239,7 +12254,7 @@
         <v>133</v>
       </c>
       <c r="P55" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q55">
         <v>1.45</v>
@@ -12320,7 +12335,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ55">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AR55">
         <v>2.44</v>
@@ -12651,7 +12666,7 @@
         <v>135</v>
       </c>
       <c r="P57" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -12729,7 +12744,7 @@
         <v>3</v>
       </c>
       <c r="AP57">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AQ57">
         <v>1.67</v>
@@ -12938,7 +12953,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ58">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR58">
         <v>1.38</v>
@@ -13141,7 +13156,7 @@
         <v>0.5</v>
       </c>
       <c r="AP59">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AQ59">
         <v>0.57</v>
@@ -13350,7 +13365,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ60">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AR60">
         <v>1.14</v>
@@ -13887,7 +13902,7 @@
         <v>140</v>
       </c>
       <c r="P63" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q63">
         <v>2.88</v>
@@ -14171,7 +14186,7 @@
         <v>1</v>
       </c>
       <c r="AP64">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AQ64">
         <v>1.14</v>
@@ -14299,7 +14314,7 @@
         <v>142</v>
       </c>
       <c r="P65" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q65">
         <v>4.5</v>
@@ -14380,7 +14395,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ65">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AR65">
         <v>1.5</v>
@@ -14505,7 +14520,7 @@
         <v>143</v>
       </c>
       <c r="P66" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q66">
         <v>5.2</v>
@@ -14711,7 +14726,7 @@
         <v>144</v>
       </c>
       <c r="P67" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q67">
         <v>3.22</v>
@@ -14917,7 +14932,7 @@
         <v>88</v>
       </c>
       <c r="P68" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q68">
         <v>3.24</v>
@@ -15123,7 +15138,7 @@
         <v>145</v>
       </c>
       <c r="P69" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q69">
         <v>3.18</v>
@@ -15201,7 +15216,7 @@
         <v>1.67</v>
       </c>
       <c r="AP69">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ69">
         <v>1.57</v>
@@ -15329,7 +15344,7 @@
         <v>124</v>
       </c>
       <c r="P70" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q70">
         <v>3.22</v>
@@ -15410,7 +15425,7 @@
         <v>1</v>
       </c>
       <c r="AQ70">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR70">
         <v>1.3</v>
@@ -15535,7 +15550,7 @@
         <v>146</v>
       </c>
       <c r="P71" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q71">
         <v>2.1</v>
@@ -15613,7 +15628,7 @@
         <v>2</v>
       </c>
       <c r="AP71">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ71">
         <v>1</v>
@@ -15741,7 +15756,7 @@
         <v>147</v>
       </c>
       <c r="P72" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q72">
         <v>2.75</v>
@@ -15819,10 +15834,10 @@
         <v>1</v>
       </c>
       <c r="AP72">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ72">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR72">
         <v>1.95</v>
@@ -16153,7 +16168,7 @@
         <v>148</v>
       </c>
       <c r="P74" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q74">
         <v>2.2</v>
@@ -16231,10 +16246,10 @@
         <v>0.6</v>
       </c>
       <c r="AP74">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ74">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AR74">
         <v>1.47</v>
@@ -16359,7 +16374,7 @@
         <v>149</v>
       </c>
       <c r="P75" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -16565,7 +16580,7 @@
         <v>150</v>
       </c>
       <c r="P76" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q76">
         <v>1.57</v>
@@ -16646,7 +16661,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ76">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AR76">
         <v>1.89</v>
@@ -16771,7 +16786,7 @@
         <v>151</v>
       </c>
       <c r="P77" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q77">
         <v>2.63</v>
@@ -17055,10 +17070,10 @@
         <v>0.75</v>
       </c>
       <c r="AP78">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AQ78">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR78">
         <v>1.12</v>
@@ -17389,7 +17404,7 @@
         <v>88</v>
       </c>
       <c r="P80" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q80">
         <v>3.6</v>
@@ -17467,7 +17482,7 @@
         <v>1.8</v>
       </c>
       <c r="AP80">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ80">
         <v>1.86</v>
@@ -17595,7 +17610,7 @@
         <v>154</v>
       </c>
       <c r="P81" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q81">
         <v>2.6</v>
@@ -17801,7 +17816,7 @@
         <v>88</v>
       </c>
       <c r="P82" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q82">
         <v>4.5</v>
@@ -17879,10 +17894,10 @@
         <v>2.33</v>
       </c>
       <c r="AP82">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ82">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AR82">
         <v>2.09</v>
@@ -18088,7 +18103,7 @@
         <v>1</v>
       </c>
       <c r="AQ83">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AR83">
         <v>1.41</v>
@@ -18419,7 +18434,7 @@
         <v>157</v>
       </c>
       <c r="P85" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q85">
         <v>4</v>
@@ -18625,7 +18640,7 @@
         <v>114</v>
       </c>
       <c r="P86" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q86">
         <v>5.5</v>
@@ -18909,7 +18924,7 @@
         <v>0.6</v>
       </c>
       <c r="AP87">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AQ87">
         <v>0.57</v>
@@ -19037,7 +19052,7 @@
         <v>158</v>
       </c>
       <c r="P88" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q88">
         <v>1.53</v>
@@ -19118,7 +19133,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ88">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AR88">
         <v>2.08</v>
@@ -19449,7 +19464,7 @@
         <v>88</v>
       </c>
       <c r="P90" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q90">
         <v>6</v>
@@ -19655,7 +19670,7 @@
         <v>160</v>
       </c>
       <c r="P91" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q91">
         <v>2.2</v>
@@ -19861,7 +19876,7 @@
         <v>161</v>
       </c>
       <c r="P92" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q92">
         <v>1.8</v>
@@ -19939,7 +19954,7 @@
         <v>0.67</v>
       </c>
       <c r="AP92">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AQ92">
         <v>0.57</v>
@@ -20067,7 +20082,7 @@
         <v>88</v>
       </c>
       <c r="P93" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="Q93">
         <v>3.5</v>
@@ -20354,7 +20369,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ94">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR94">
         <v>2.25</v>
@@ -20479,7 +20494,7 @@
         <v>162</v>
       </c>
       <c r="P95" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q95">
         <v>2.88</v>
@@ -20557,7 +20572,7 @@
         <v>0.5</v>
       </c>
       <c r="AP95">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ95">
         <v>0.57</v>
@@ -20685,7 +20700,7 @@
         <v>163</v>
       </c>
       <c r="P96" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q96">
         <v>2.38</v>
@@ -20763,7 +20778,7 @@
         <v>1.17</v>
       </c>
       <c r="AP96">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ96">
         <v>1.14</v>
@@ -20972,7 +20987,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ97">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR97">
         <v>1.63</v>
@@ -21097,7 +21112,7 @@
         <v>88</v>
       </c>
       <c r="P98" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q98">
         <v>5.25</v>
@@ -21175,7 +21190,7 @@
         <v>2</v>
       </c>
       <c r="AP98">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ98">
         <v>2.17</v>
@@ -21303,7 +21318,7 @@
         <v>165</v>
       </c>
       <c r="P99" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q99">
         <v>3.52</v>
@@ -21509,7 +21524,7 @@
         <v>166</v>
       </c>
       <c r="P100" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Q100">
         <v>1.79</v>
@@ -21715,7 +21730,7 @@
         <v>127</v>
       </c>
       <c r="P101" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q101">
         <v>5.55</v>
@@ -21921,7 +21936,7 @@
         <v>114</v>
       </c>
       <c r="P102" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q102">
         <v>2.3</v>
@@ -22078,6 +22093,1036 @@
       </c>
       <c r="BP102">
         <v>1.53</v>
+      </c>
+    </row>
+    <row r="103" spans="1:68">
+      <c r="A103" s="1">
+        <v>102</v>
+      </c>
+      <c r="B103">
+        <v>7825296</v>
+      </c>
+      <c r="C103" t="s">
+        <v>68</v>
+      </c>
+      <c r="D103" t="s">
+        <v>69</v>
+      </c>
+      <c r="E103" s="2">
+        <v>45821.35763888889</v>
+      </c>
+      <c r="F103">
+        <v>14</v>
+      </c>
+      <c r="G103" t="s">
+        <v>82</v>
+      </c>
+      <c r="H103" t="s">
+        <v>78</v>
+      </c>
+      <c r="I103">
+        <v>0</v>
+      </c>
+      <c r="J103">
+        <v>0</v>
+      </c>
+      <c r="K103">
+        <v>0</v>
+      </c>
+      <c r="L103">
+        <v>1</v>
+      </c>
+      <c r="M103">
+        <v>0</v>
+      </c>
+      <c r="N103">
+        <v>1</v>
+      </c>
+      <c r="O103" t="s">
+        <v>143</v>
+      </c>
+      <c r="P103" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q103">
+        <v>2.06</v>
+      </c>
+      <c r="R103">
+        <v>2.34</v>
+      </c>
+      <c r="S103">
+        <v>5.2</v>
+      </c>
+      <c r="T103">
+        <v>1.28</v>
+      </c>
+      <c r="U103">
+        <v>3.34</v>
+      </c>
+      <c r="V103">
+        <v>2.44</v>
+      </c>
+      <c r="W103">
+        <v>1.49</v>
+      </c>
+      <c r="X103">
+        <v>5.95</v>
+      </c>
+      <c r="Y103">
+        <v>1.07</v>
+      </c>
+      <c r="Z103">
+        <v>1.63</v>
+      </c>
+      <c r="AA103">
+        <v>3.92</v>
+      </c>
+      <c r="AB103">
+        <v>4.3</v>
+      </c>
+      <c r="AC103">
+        <v>1.01</v>
+      </c>
+      <c r="AD103">
+        <v>13</v>
+      </c>
+      <c r="AE103">
+        <v>1.15</v>
+      </c>
+      <c r="AF103">
+        <v>4.3</v>
+      </c>
+      <c r="AG103">
+        <v>1.61</v>
+      </c>
+      <c r="AH103">
+        <v>2.1</v>
+      </c>
+      <c r="AI103">
+        <v>1.69</v>
+      </c>
+      <c r="AJ103">
+        <v>2.04</v>
+      </c>
+      <c r="AK103">
+        <v>1.14</v>
+      </c>
+      <c r="AL103">
+        <v>1.21</v>
+      </c>
+      <c r="AM103">
+        <v>2.38</v>
+      </c>
+      <c r="AN103">
+        <v>1.67</v>
+      </c>
+      <c r="AO103">
+        <v>0.5</v>
+      </c>
+      <c r="AP103">
+        <v>1.86</v>
+      </c>
+      <c r="AQ103">
+        <v>0.43</v>
+      </c>
+      <c r="AR103">
+        <v>1.84</v>
+      </c>
+      <c r="AS103">
+        <v>1.31</v>
+      </c>
+      <c r="AT103">
+        <v>3.15</v>
+      </c>
+      <c r="AU103">
+        <v>2</v>
+      </c>
+      <c r="AV103">
+        <v>2</v>
+      </c>
+      <c r="AW103">
+        <v>11</v>
+      </c>
+      <c r="AX103">
+        <v>3</v>
+      </c>
+      <c r="AY103">
+        <v>13</v>
+      </c>
+      <c r="AZ103">
+        <v>5</v>
+      </c>
+      <c r="BA103">
+        <v>6</v>
+      </c>
+      <c r="BB103">
+        <v>3</v>
+      </c>
+      <c r="BC103">
+        <v>9</v>
+      </c>
+      <c r="BD103">
+        <v>1.44</v>
+      </c>
+      <c r="BE103">
+        <v>7</v>
+      </c>
+      <c r="BF103">
+        <v>3.05</v>
+      </c>
+      <c r="BG103">
+        <v>1.19</v>
+      </c>
+      <c r="BH103">
+        <v>3.9</v>
+      </c>
+      <c r="BI103">
+        <v>1.36</v>
+      </c>
+      <c r="BJ103">
+        <v>2.85</v>
+      </c>
+      <c r="BK103">
+        <v>1.58</v>
+      </c>
+      <c r="BL103">
+        <v>2.17</v>
+      </c>
+      <c r="BM103">
+        <v>1.93</v>
+      </c>
+      <c r="BN103">
+        <v>1.76</v>
+      </c>
+      <c r="BO103">
+        <v>2.4</v>
+      </c>
+      <c r="BP103">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="104" spans="1:68">
+      <c r="A104" s="1">
+        <v>103</v>
+      </c>
+      <c r="B104">
+        <v>7825297</v>
+      </c>
+      <c r="C104" t="s">
+        <v>68</v>
+      </c>
+      <c r="D104" t="s">
+        <v>69</v>
+      </c>
+      <c r="E104" s="2">
+        <v>45821.375</v>
+      </c>
+      <c r="F104">
+        <v>14</v>
+      </c>
+      <c r="G104" t="s">
+        <v>80</v>
+      </c>
+      <c r="H104" t="s">
+        <v>73</v>
+      </c>
+      <c r="I104">
+        <v>2</v>
+      </c>
+      <c r="J104">
+        <v>0</v>
+      </c>
+      <c r="K104">
+        <v>2</v>
+      </c>
+      <c r="L104">
+        <v>2</v>
+      </c>
+      <c r="M104">
+        <v>0</v>
+      </c>
+      <c r="N104">
+        <v>2</v>
+      </c>
+      <c r="O104" t="s">
+        <v>167</v>
+      </c>
+      <c r="P104" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q104">
+        <v>2.34</v>
+      </c>
+      <c r="R104">
+        <v>2.25</v>
+      </c>
+      <c r="S104">
+        <v>4.3</v>
+      </c>
+      <c r="T104">
+        <v>1.31</v>
+      </c>
+      <c r="U104">
+        <v>3.15</v>
+      </c>
+      <c r="V104">
+        <v>2.5</v>
+      </c>
+      <c r="W104">
+        <v>1.47</v>
+      </c>
+      <c r="X104">
+        <v>5.8</v>
+      </c>
+      <c r="Y104">
+        <v>1.07</v>
+      </c>
+      <c r="Z104">
+        <v>1.86</v>
+      </c>
+      <c r="AA104">
+        <v>3.69</v>
+      </c>
+      <c r="AB104">
+        <v>3.45</v>
+      </c>
+      <c r="AC104">
+        <v>1.01</v>
+      </c>
+      <c r="AD104">
+        <v>11</v>
+      </c>
+      <c r="AE104">
+        <v>1.18</v>
+      </c>
+      <c r="AF104">
+        <v>3.88</v>
+      </c>
+      <c r="AG104">
+        <v>1.76</v>
+      </c>
+      <c r="AH104">
+        <v>1.94</v>
+      </c>
+      <c r="AI104">
+        <v>1.64</v>
+      </c>
+      <c r="AJ104">
+        <v>2.12</v>
+      </c>
+      <c r="AK104">
+        <v>1.24</v>
+      </c>
+      <c r="AL104">
+        <v>1.25</v>
+      </c>
+      <c r="AM104">
+        <v>1.94</v>
+      </c>
+      <c r="AN104">
+        <v>1.33</v>
+      </c>
+      <c r="AO104">
+        <v>0.17</v>
+      </c>
+      <c r="AP104">
+        <v>1.57</v>
+      </c>
+      <c r="AQ104">
+        <v>0.14</v>
+      </c>
+      <c r="AR104">
+        <v>2.06</v>
+      </c>
+      <c r="AS104">
+        <v>1.14</v>
+      </c>
+      <c r="AT104">
+        <v>3.2</v>
+      </c>
+      <c r="AU104">
+        <v>6</v>
+      </c>
+      <c r="AV104">
+        <v>4</v>
+      </c>
+      <c r="AW104">
+        <v>7</v>
+      </c>
+      <c r="AX104">
+        <v>10</v>
+      </c>
+      <c r="AY104">
+        <v>13</v>
+      </c>
+      <c r="AZ104">
+        <v>14</v>
+      </c>
+      <c r="BA104">
+        <v>3</v>
+      </c>
+      <c r="BB104">
+        <v>4</v>
+      </c>
+      <c r="BC104">
+        <v>7</v>
+      </c>
+      <c r="BD104">
+        <v>1.49</v>
+      </c>
+      <c r="BE104">
+        <v>7</v>
+      </c>
+      <c r="BF104">
+        <v>2.9</v>
+      </c>
+      <c r="BG104">
+        <v>1.28</v>
+      </c>
+      <c r="BH104">
+        <v>3.2</v>
+      </c>
+      <c r="BI104">
+        <v>1.49</v>
+      </c>
+      <c r="BJ104">
+        <v>2.4</v>
+      </c>
+      <c r="BK104">
+        <v>1.8</v>
+      </c>
+      <c r="BL104">
+        <v>1.89</v>
+      </c>
+      <c r="BM104">
+        <v>2.23</v>
+      </c>
+      <c r="BN104">
+        <v>1.56</v>
+      </c>
+      <c r="BO104">
+        <v>2.9</v>
+      </c>
+      <c r="BP104">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="105" spans="1:68">
+      <c r="A105" s="1">
+        <v>104</v>
+      </c>
+      <c r="B105">
+        <v>7825298</v>
+      </c>
+      <c r="C105" t="s">
+        <v>68</v>
+      </c>
+      <c r="D105" t="s">
+        <v>69</v>
+      </c>
+      <c r="E105" s="2">
+        <v>45822.1875</v>
+      </c>
+      <c r="F105">
+        <v>14</v>
+      </c>
+      <c r="G105" t="s">
+        <v>74</v>
+      </c>
+      <c r="H105" t="s">
+        <v>77</v>
+      </c>
+      <c r="I105">
+        <v>0</v>
+      </c>
+      <c r="J105">
+        <v>1</v>
+      </c>
+      <c r="K105">
+        <v>1</v>
+      </c>
+      <c r="L105">
+        <v>2</v>
+      </c>
+      <c r="M105">
+        <v>2</v>
+      </c>
+      <c r="N105">
+        <v>4</v>
+      </c>
+      <c r="O105" t="s">
+        <v>168</v>
+      </c>
+      <c r="P105" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q105">
+        <v>3.54</v>
+      </c>
+      <c r="R105">
+        <v>2.46</v>
+      </c>
+      <c r="S105">
+        <v>2.4</v>
+      </c>
+      <c r="T105">
+        <v>1.19</v>
+      </c>
+      <c r="U105">
+        <v>3.98</v>
+      </c>
+      <c r="V105">
+        <v>2.08</v>
+      </c>
+      <c r="W105">
+        <v>1.7</v>
+      </c>
+      <c r="X105">
+        <v>4.45</v>
+      </c>
+      <c r="Y105">
+        <v>1.15</v>
+      </c>
+      <c r="Z105">
+        <v>3.32</v>
+      </c>
+      <c r="AA105">
+        <v>3.97</v>
+      </c>
+      <c r="AB105">
+        <v>1.83</v>
+      </c>
+      <c r="AC105">
+        <v>1.02</v>
+      </c>
+      <c r="AD105">
+        <v>19</v>
+      </c>
+      <c r="AE105">
+        <v>1.07</v>
+      </c>
+      <c r="AF105">
+        <v>5.8</v>
+      </c>
+      <c r="AG105">
+        <v>1.42</v>
+      </c>
+      <c r="AH105">
+        <v>2.65</v>
+      </c>
+      <c r="AI105">
+        <v>1.39</v>
+      </c>
+      <c r="AJ105">
+        <v>2.76</v>
+      </c>
+      <c r="AK105">
+        <v>1.82</v>
+      </c>
+      <c r="AL105">
+        <v>1.23</v>
+      </c>
+      <c r="AM105">
+        <v>1.32</v>
+      </c>
+      <c r="AN105">
+        <v>2</v>
+      </c>
+      <c r="AO105">
+        <v>2.5</v>
+      </c>
+      <c r="AP105">
+        <v>1.86</v>
+      </c>
+      <c r="AQ105">
+        <v>2.2</v>
+      </c>
+      <c r="AR105">
+        <v>1.56</v>
+      </c>
+      <c r="AS105">
+        <v>1.67</v>
+      </c>
+      <c r="AT105">
+        <v>3.23</v>
+      </c>
+      <c r="AU105">
+        <v>8</v>
+      </c>
+      <c r="AV105">
+        <v>6</v>
+      </c>
+      <c r="AW105">
+        <v>6</v>
+      </c>
+      <c r="AX105">
+        <v>5</v>
+      </c>
+      <c r="AY105">
+        <v>14</v>
+      </c>
+      <c r="AZ105">
+        <v>11</v>
+      </c>
+      <c r="BA105">
+        <v>5</v>
+      </c>
+      <c r="BB105">
+        <v>5</v>
+      </c>
+      <c r="BC105">
+        <v>10</v>
+      </c>
+      <c r="BD105">
+        <v>2.17</v>
+      </c>
+      <c r="BE105">
+        <v>6.75</v>
+      </c>
+      <c r="BF105">
+        <v>1.84</v>
+      </c>
+      <c r="BG105">
+        <v>1.2</v>
+      </c>
+      <c r="BH105">
+        <v>3.95</v>
+      </c>
+      <c r="BI105">
+        <v>1.36</v>
+      </c>
+      <c r="BJ105">
+        <v>2.8</v>
+      </c>
+      <c r="BK105">
+        <v>1.58</v>
+      </c>
+      <c r="BL105">
+        <v>2.18</v>
+      </c>
+      <c r="BM105">
+        <v>1.94</v>
+      </c>
+      <c r="BN105">
+        <v>1.76</v>
+      </c>
+      <c r="BO105">
+        <v>2.4</v>
+      </c>
+      <c r="BP105">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="106" spans="1:68">
+      <c r="A106" s="1">
+        <v>105</v>
+      </c>
+      <c r="B106">
+        <v>7825299</v>
+      </c>
+      <c r="C106" t="s">
+        <v>68</v>
+      </c>
+      <c r="D106" t="s">
+        <v>69</v>
+      </c>
+      <c r="E106" s="2">
+        <v>45822.33333333334</v>
+      </c>
+      <c r="F106">
+        <v>14</v>
+      </c>
+      <c r="G106" t="s">
+        <v>79</v>
+      </c>
+      <c r="H106" t="s">
+        <v>72</v>
+      </c>
+      <c r="I106">
+        <v>0</v>
+      </c>
+      <c r="J106">
+        <v>0</v>
+      </c>
+      <c r="K106">
+        <v>0</v>
+      </c>
+      <c r="L106">
+        <v>0</v>
+      </c>
+      <c r="M106">
+        <v>0</v>
+      </c>
+      <c r="N106">
+        <v>0</v>
+      </c>
+      <c r="O106" t="s">
+        <v>88</v>
+      </c>
+      <c r="P106" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q106">
+        <v>2.74</v>
+      </c>
+      <c r="R106">
+        <v>2.27</v>
+      </c>
+      <c r="S106">
+        <v>3.34</v>
+      </c>
+      <c r="T106">
+        <v>1.29</v>
+      </c>
+      <c r="U106">
+        <v>3.28</v>
+      </c>
+      <c r="V106">
+        <v>2.39</v>
+      </c>
+      <c r="W106">
+        <v>1.51</v>
+      </c>
+      <c r="X106">
+        <v>5.25</v>
+      </c>
+      <c r="Y106">
+        <v>1.09</v>
+      </c>
+      <c r="Z106">
+        <v>2.11</v>
+      </c>
+      <c r="AA106">
+        <v>3.58</v>
+      </c>
+      <c r="AB106">
+        <v>2.89</v>
+      </c>
+      <c r="AC106">
+        <v>1.01</v>
+      </c>
+      <c r="AD106">
+        <v>13</v>
+      </c>
+      <c r="AE106">
+        <v>1.16</v>
+      </c>
+      <c r="AF106">
+        <v>4.1</v>
+      </c>
+      <c r="AG106">
+        <v>1.61</v>
+      </c>
+      <c r="AH106">
+        <v>2.05</v>
+      </c>
+      <c r="AI106">
+        <v>1.53</v>
+      </c>
+      <c r="AJ106">
+        <v>2.33</v>
+      </c>
+      <c r="AK106">
+        <v>1.41</v>
+      </c>
+      <c r="AL106">
+        <v>1.27</v>
+      </c>
+      <c r="AM106">
+        <v>1.6</v>
+      </c>
+      <c r="AN106">
+        <v>1.71</v>
+      </c>
+      <c r="AO106">
+        <v>1.14</v>
+      </c>
+      <c r="AP106">
+        <v>1.63</v>
+      </c>
+      <c r="AQ106">
+        <v>1.13</v>
+      </c>
+      <c r="AR106">
+        <v>1.24</v>
+      </c>
+      <c r="AS106">
+        <v>1.36</v>
+      </c>
+      <c r="AT106">
+        <v>2.6</v>
+      </c>
+      <c r="AU106">
+        <v>2</v>
+      </c>
+      <c r="AV106">
+        <v>6</v>
+      </c>
+      <c r="AW106">
+        <v>8</v>
+      </c>
+      <c r="AX106">
+        <v>7</v>
+      </c>
+      <c r="AY106">
+        <v>10</v>
+      </c>
+      <c r="AZ106">
+        <v>13</v>
+      </c>
+      <c r="BA106">
+        <v>8</v>
+      </c>
+      <c r="BB106">
+        <v>9</v>
+      </c>
+      <c r="BC106">
+        <v>17</v>
+      </c>
+      <c r="BD106">
+        <v>1.74</v>
+      </c>
+      <c r="BE106">
+        <v>6.4</v>
+      </c>
+      <c r="BF106">
+        <v>2.32</v>
+      </c>
+      <c r="BG106">
+        <v>1.29</v>
+      </c>
+      <c r="BH106">
+        <v>3.15</v>
+      </c>
+      <c r="BI106">
+        <v>1.5</v>
+      </c>
+      <c r="BJ106">
+        <v>2.35</v>
+      </c>
+      <c r="BK106">
+        <v>1.82</v>
+      </c>
+      <c r="BL106">
+        <v>1.86</v>
+      </c>
+      <c r="BM106">
+        <v>2.3</v>
+      </c>
+      <c r="BN106">
+        <v>1.54</v>
+      </c>
+      <c r="BO106">
+        <v>2.9</v>
+      </c>
+      <c r="BP106">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="107" spans="1:68">
+      <c r="A107" s="1">
+        <v>106</v>
+      </c>
+      <c r="B107">
+        <v>7825300</v>
+      </c>
+      <c r="C107" t="s">
+        <v>68</v>
+      </c>
+      <c r="D107" t="s">
+        <v>69</v>
+      </c>
+      <c r="E107" s="2">
+        <v>45822.33333333334</v>
+      </c>
+      <c r="F107">
+        <v>14</v>
+      </c>
+      <c r="G107" t="s">
+        <v>84</v>
+      </c>
+      <c r="H107" t="s">
+        <v>85</v>
+      </c>
+      <c r="I107">
+        <v>2</v>
+      </c>
+      <c r="J107">
+        <v>0</v>
+      </c>
+      <c r="K107">
+        <v>2</v>
+      </c>
+      <c r="L107">
+        <v>2</v>
+      </c>
+      <c r="M107">
+        <v>1</v>
+      </c>
+      <c r="N107">
+        <v>3</v>
+      </c>
+      <c r="O107" t="s">
+        <v>169</v>
+      </c>
+      <c r="P107" t="s">
+        <v>234</v>
+      </c>
+      <c r="Q107">
+        <v>1.49</v>
+      </c>
+      <c r="R107">
+        <v>3.12</v>
+      </c>
+      <c r="S107">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="T107">
+        <v>1.14</v>
+      </c>
+      <c r="U107">
+        <v>4.55</v>
+      </c>
+      <c r="V107">
+        <v>1.86</v>
+      </c>
+      <c r="W107">
+        <v>1.88</v>
+      </c>
+      <c r="X107">
+        <v>3.58</v>
+      </c>
+      <c r="Y107">
+        <v>1.23</v>
+      </c>
+      <c r="Z107">
+        <v>1.15</v>
+      </c>
+      <c r="AA107">
+        <v>7</v>
+      </c>
+      <c r="AB107">
+        <v>11</v>
+      </c>
+      <c r="AC107">
+        <v>1.01</v>
+      </c>
+      <c r="AD107">
+        <v>29</v>
+      </c>
+      <c r="AE107">
+        <v>1.03</v>
+      </c>
+      <c r="AF107">
+        <v>7.2</v>
+      </c>
+      <c r="AG107">
+        <v>1.28</v>
+      </c>
+      <c r="AH107">
+        <v>3.34</v>
+      </c>
+      <c r="AI107">
+        <v>1.75</v>
+      </c>
+      <c r="AJ107">
+        <v>1.96</v>
+      </c>
+      <c r="AK107">
+        <v>1.01</v>
+      </c>
+      <c r="AL107">
+        <v>1.08</v>
+      </c>
+      <c r="AM107">
+        <v>4.8</v>
+      </c>
+      <c r="AN107">
+        <v>2.6</v>
+      </c>
+      <c r="AO107">
+        <v>0.43</v>
+      </c>
+      <c r="AP107">
+        <v>2.67</v>
+      </c>
+      <c r="AQ107">
+        <v>0.38</v>
+      </c>
+      <c r="AR107">
+        <v>2</v>
+      </c>
+      <c r="AS107">
+        <v>1.28</v>
+      </c>
+      <c r="AT107">
+        <v>3.28</v>
+      </c>
+      <c r="AU107">
+        <v>6</v>
+      </c>
+      <c r="AV107">
+        <v>3</v>
+      </c>
+      <c r="AW107">
+        <v>8</v>
+      </c>
+      <c r="AX107">
+        <v>2</v>
+      </c>
+      <c r="AY107">
+        <v>14</v>
+      </c>
+      <c r="AZ107">
+        <v>5</v>
+      </c>
+      <c r="BA107">
+        <v>4</v>
+      </c>
+      <c r="BB107">
+        <v>2</v>
+      </c>
+      <c r="BC107">
+        <v>6</v>
+      </c>
+      <c r="BD107">
+        <v>1.19</v>
+      </c>
+      <c r="BE107">
+        <v>9</v>
+      </c>
+      <c r="BF107">
+        <v>5.1</v>
+      </c>
+      <c r="BG107">
+        <v>1.21</v>
+      </c>
+      <c r="BH107">
+        <v>3.8</v>
+      </c>
+      <c r="BI107">
+        <v>1.37</v>
+      </c>
+      <c r="BJ107">
+        <v>2.8</v>
+      </c>
+      <c r="BK107">
+        <v>1.58</v>
+      </c>
+      <c r="BL107">
+        <v>2.18</v>
+      </c>
+      <c r="BM107">
+        <v>1.92</v>
+      </c>
+      <c r="BN107">
+        <v>1.77</v>
+      </c>
+      <c r="BO107">
+        <v>2.4</v>
+      </c>
+      <c r="BP107">
+        <v>1.49</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="239">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -526,6 +526,15 @@
     <t>['18', '25']</t>
   </si>
   <si>
+    <t>['36', '50', '9004']</t>
+  </si>
+  <si>
+    <t>['15', '27', '69']</t>
+  </si>
+  <si>
+    <t>['44']</t>
+  </si>
+  <si>
     <t>['53', '79']</t>
   </si>
   <si>
@@ -719,6 +728,9 @@
   </si>
   <si>
     <t>['88']</t>
+  </si>
+  <si>
+    <t>['8', '21']</t>
   </si>
 </sst>
 </file>
@@ -1080,7 +1092,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP107"/>
+  <dimension ref="A1:BP110"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1748,7 +1760,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -1954,7 +1966,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="Q5">
         <v>2.85</v>
@@ -2160,7 +2172,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="Q6">
         <v>2.2</v>
@@ -2572,7 +2584,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="Q8">
         <v>2.04</v>
@@ -2650,7 +2662,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ8">
         <v>0.43</v>
@@ -2778,7 +2790,7 @@
         <v>92</v>
       </c>
       <c r="P9" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Q9">
         <v>1.5</v>
@@ -2984,7 +2996,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Q10">
         <v>2.1</v>
@@ -3396,7 +3408,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="Q12">
         <v>3.1</v>
@@ -3602,7 +3614,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -3808,7 +3820,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Q14">
         <v>2.13</v>
@@ -4014,7 +4026,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Q15">
         <v>3.2</v>
@@ -4220,7 +4232,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="Q16">
         <v>1.78</v>
@@ -4632,7 +4644,7 @@
         <v>100</v>
       </c>
       <c r="P18" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="Q18">
         <v>5.5</v>
@@ -4838,7 +4850,7 @@
         <v>88</v>
       </c>
       <c r="P19" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Q19">
         <v>3.75</v>
@@ -5044,7 +5056,7 @@
         <v>101</v>
       </c>
       <c r="P20" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q20">
         <v>3.25</v>
@@ -5122,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AQ20">
         <v>1.13</v>
@@ -5534,7 +5546,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ22">
         <v>0.14</v>
@@ -5662,7 +5674,7 @@
         <v>104</v>
       </c>
       <c r="P23" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Q23">
         <v>4</v>
@@ -5740,10 +5752,10 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AQ23">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AR23">
         <v>0</v>
@@ -5868,7 +5880,7 @@
         <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Q24">
         <v>4.75</v>
@@ -5949,7 +5961,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ24">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR24">
         <v>1.93</v>
@@ -6074,7 +6086,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -6155,7 +6167,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ25">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
       <c r="AR25">
         <v>0</v>
@@ -6280,7 +6292,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q26">
         <v>2.88</v>
@@ -6358,7 +6370,7 @@
         <v>1</v>
       </c>
       <c r="AP26">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AQ26">
         <v>1</v>
@@ -6898,7 +6910,7 @@
         <v>110</v>
       </c>
       <c r="P29" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q29">
         <v>1.83</v>
@@ -7310,7 +7322,7 @@
         <v>88</v>
       </c>
       <c r="P31" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q31">
         <v>2.9</v>
@@ -7391,7 +7403,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ31">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
       <c r="AR31">
         <v>2.46</v>
@@ -7516,7 +7528,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q32">
         <v>3.42</v>
@@ -7594,7 +7606,7 @@
         <v>2</v>
       </c>
       <c r="AP32">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ32">
         <v>1.86</v>
@@ -7722,7 +7734,7 @@
         <v>113</v>
       </c>
       <c r="P33" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q33">
         <v>1.56</v>
@@ -7928,7 +7940,7 @@
         <v>114</v>
       </c>
       <c r="P34" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q34">
         <v>3.25</v>
@@ -8006,7 +8018,7 @@
         <v>0.5</v>
       </c>
       <c r="AP34">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AQ34">
         <v>1.14</v>
@@ -8134,7 +8146,7 @@
         <v>115</v>
       </c>
       <c r="P35" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q35">
         <v>4.25</v>
@@ -8215,7 +8227,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ35">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR35">
         <v>1.08</v>
@@ -8340,7 +8352,7 @@
         <v>116</v>
       </c>
       <c r="P36" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q36">
         <v>3.15</v>
@@ -8546,7 +8558,7 @@
         <v>117</v>
       </c>
       <c r="P37" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Q37">
         <v>2.75</v>
@@ -8958,7 +8970,7 @@
         <v>119</v>
       </c>
       <c r="P39" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q39">
         <v>2.88</v>
@@ -9039,7 +9051,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ39">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AR39">
         <v>2.38</v>
@@ -9782,7 +9794,7 @@
         <v>123</v>
       </c>
       <c r="P43" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q43">
         <v>3</v>
@@ -9988,7 +10000,7 @@
         <v>124</v>
       </c>
       <c r="P44" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q44">
         <v>3.2</v>
@@ -10194,7 +10206,7 @@
         <v>88</v>
       </c>
       <c r="P45" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q45">
         <v>7.5</v>
@@ -10275,7 +10287,7 @@
         <v>1</v>
       </c>
       <c r="AQ45">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
       <c r="AR45">
         <v>1.43</v>
@@ -10606,7 +10618,7 @@
         <v>126</v>
       </c>
       <c r="P47" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q47">
         <v>1.95</v>
@@ -10812,7 +10824,7 @@
         <v>127</v>
       </c>
       <c r="P48" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q48">
         <v>3.7</v>
@@ -10893,7 +10905,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ48">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR48">
         <v>1.15</v>
@@ -11018,7 +11030,7 @@
         <v>128</v>
       </c>
       <c r="P49" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q49">
         <v>4.33</v>
@@ -11224,7 +11236,7 @@
         <v>129</v>
       </c>
       <c r="P50" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Q50">
         <v>2.65</v>
@@ -11302,7 +11314,7 @@
         <v>0.75</v>
       </c>
       <c r="AP50">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AQ50">
         <v>0.38</v>
@@ -11430,7 +11442,7 @@
         <v>130</v>
       </c>
       <c r="P51" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q51">
         <v>4.15</v>
@@ -11508,7 +11520,7 @@
         <v>1</v>
       </c>
       <c r="AP51">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ51">
         <v>2.2</v>
@@ -11842,7 +11854,7 @@
         <v>132</v>
       </c>
       <c r="P53" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q53">
         <v>1.8</v>
@@ -12048,7 +12060,7 @@
         <v>104</v>
       </c>
       <c r="P54" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q54">
         <v>1.71</v>
@@ -12254,7 +12266,7 @@
         <v>133</v>
       </c>
       <c r="P55" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q55">
         <v>1.45</v>
@@ -12666,7 +12678,7 @@
         <v>135</v>
       </c>
       <c r="P57" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -12747,7 +12759,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ57">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR57">
         <v>1.81</v>
@@ -13362,7 +13374,7 @@
         <v>0</v>
       </c>
       <c r="AP60">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AQ60">
         <v>0.14</v>
@@ -13774,7 +13786,7 @@
         <v>1</v>
       </c>
       <c r="AP62">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ62">
         <v>0.57</v>
@@ -13902,7 +13914,7 @@
         <v>140</v>
       </c>
       <c r="P63" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q63">
         <v>2.88</v>
@@ -13983,7 +13995,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ63">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
       <c r="AR63">
         <v>2.06</v>
@@ -14314,7 +14326,7 @@
         <v>142</v>
       </c>
       <c r="P65" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q65">
         <v>4.5</v>
@@ -14520,7 +14532,7 @@
         <v>143</v>
       </c>
       <c r="P66" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q66">
         <v>5.2</v>
@@ -14601,7 +14613,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ66">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
       <c r="AR66">
         <v>1.35</v>
@@ -14726,7 +14738,7 @@
         <v>144</v>
       </c>
       <c r="P67" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q67">
         <v>3.22</v>
@@ -14804,7 +14816,7 @@
         <v>0.4</v>
       </c>
       <c r="AP67">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AQ67">
         <v>0.57</v>
@@ -14932,7 +14944,7 @@
         <v>88</v>
       </c>
       <c r="P68" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q68">
         <v>3.24</v>
@@ -15013,7 +15025,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ68">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AR68">
         <v>2.12</v>
@@ -15138,7 +15150,7 @@
         <v>145</v>
       </c>
       <c r="P69" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q69">
         <v>3.18</v>
@@ -15344,7 +15356,7 @@
         <v>124</v>
       </c>
       <c r="P70" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q70">
         <v>3.22</v>
@@ -15550,7 +15562,7 @@
         <v>146</v>
       </c>
       <c r="P71" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q71">
         <v>2.1</v>
@@ -15756,7 +15768,7 @@
         <v>147</v>
       </c>
       <c r="P72" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q72">
         <v>2.75</v>
@@ -16040,7 +16052,7 @@
         <v>1.25</v>
       </c>
       <c r="AP73">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AQ73">
         <v>1.57</v>
@@ -16168,7 +16180,7 @@
         <v>148</v>
       </c>
       <c r="P74" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q74">
         <v>2.2</v>
@@ -16374,7 +16386,7 @@
         <v>149</v>
       </c>
       <c r="P75" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -16452,7 +16464,7 @@
         <v>0.2</v>
       </c>
       <c r="AP75">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AQ75">
         <v>0.67</v>
@@ -16580,7 +16592,7 @@
         <v>150</v>
       </c>
       <c r="P76" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q76">
         <v>1.57</v>
@@ -16786,7 +16798,7 @@
         <v>151</v>
       </c>
       <c r="P77" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q77">
         <v>2.63</v>
@@ -17279,7 +17291,7 @@
         <v>2</v>
       </c>
       <c r="AQ79">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AR79">
         <v>2.28</v>
@@ -17404,7 +17416,7 @@
         <v>88</v>
       </c>
       <c r="P80" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q80">
         <v>3.6</v>
@@ -17610,7 +17622,7 @@
         <v>154</v>
       </c>
       <c r="P81" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q81">
         <v>2.6</v>
@@ -17688,7 +17700,7 @@
         <v>1</v>
       </c>
       <c r="AP81">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AQ81">
         <v>1.57</v>
@@ -17816,7 +17828,7 @@
         <v>88</v>
       </c>
       <c r="P82" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q82">
         <v>4.5</v>
@@ -18434,7 +18446,7 @@
         <v>157</v>
       </c>
       <c r="P85" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q85">
         <v>4</v>
@@ -18515,7 +18527,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ85">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR85">
         <v>1.6</v>
@@ -18640,7 +18652,7 @@
         <v>114</v>
       </c>
       <c r="P86" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q86">
         <v>5.5</v>
@@ -18721,7 +18733,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ86">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AR86">
         <v>2.02</v>
@@ -19052,7 +19064,7 @@
         <v>158</v>
       </c>
       <c r="P88" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q88">
         <v>1.53</v>
@@ -19464,7 +19476,7 @@
         <v>88</v>
       </c>
       <c r="P90" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q90">
         <v>6</v>
@@ -19545,7 +19557,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ90">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
       <c r="AR90">
         <v>1.96</v>
@@ -19670,7 +19682,7 @@
         <v>160</v>
       </c>
       <c r="P91" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q91">
         <v>2.2</v>
@@ -19876,7 +19888,7 @@
         <v>161</v>
       </c>
       <c r="P92" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q92">
         <v>1.8</v>
@@ -20082,7 +20094,7 @@
         <v>88</v>
       </c>
       <c r="P93" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q93">
         <v>3.5</v>
@@ -20366,7 +20378,7 @@
         <v>0.83</v>
       </c>
       <c r="AP94">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ94">
         <v>1.13</v>
@@ -20494,7 +20506,7 @@
         <v>162</v>
       </c>
       <c r="P95" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q95">
         <v>2.88</v>
@@ -20700,7 +20712,7 @@
         <v>163</v>
       </c>
       <c r="P96" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q96">
         <v>2.38</v>
@@ -21112,7 +21124,7 @@
         <v>88</v>
       </c>
       <c r="P98" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q98">
         <v>5.25</v>
@@ -21193,7 +21205,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ98">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AR98">
         <v>1.87</v>
@@ -21318,7 +21330,7 @@
         <v>165</v>
       </c>
       <c r="P99" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q99">
         <v>3.52</v>
@@ -21524,7 +21536,7 @@
         <v>166</v>
       </c>
       <c r="P100" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q100">
         <v>1.79</v>
@@ -21730,7 +21742,7 @@
         <v>127</v>
       </c>
       <c r="P101" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q101">
         <v>5.55</v>
@@ -21936,7 +21948,7 @@
         <v>114</v>
       </c>
       <c r="P102" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q102">
         <v>2.3</v>
@@ -22017,7 +22029,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ102">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR102">
         <v>2.21</v>
@@ -22554,7 +22566,7 @@
         <v>168</v>
       </c>
       <c r="P105" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q105">
         <v>3.54</v>
@@ -22853,22 +22865,22 @@
         <v>2.6</v>
       </c>
       <c r="AU106">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV106">
+        <v>5</v>
+      </c>
+      <c r="AW106">
+        <v>10</v>
+      </c>
+      <c r="AX106">
         <v>6</v>
       </c>
-      <c r="AW106">
-        <v>8</v>
-      </c>
-      <c r="AX106">
-        <v>7</v>
-      </c>
       <c r="AY106">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AZ106">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA106">
         <v>8</v>
@@ -22966,7 +22978,7 @@
         <v>169</v>
       </c>
       <c r="P107" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q107">
         <v>1.49</v>
@@ -23062,19 +23074,19 @@
         <v>6</v>
       </c>
       <c r="AV107">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW107">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX107">
         <v>2</v>
       </c>
       <c r="AY107">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ107">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA107">
         <v>4</v>
@@ -23123,6 +23135,624 @@
       </c>
       <c r="BP107">
         <v>1.49</v>
+      </c>
+    </row>
+    <row r="108" spans="1:68">
+      <c r="A108" s="1">
+        <v>107</v>
+      </c>
+      <c r="B108">
+        <v>7825301</v>
+      </c>
+      <c r="C108" t="s">
+        <v>68</v>
+      </c>
+      <c r="D108" t="s">
+        <v>69</v>
+      </c>
+      <c r="E108" s="2">
+        <v>45822.35763888889</v>
+      </c>
+      <c r="F108">
+        <v>14</v>
+      </c>
+      <c r="G108" t="s">
+        <v>81</v>
+      </c>
+      <c r="H108" t="s">
+        <v>71</v>
+      </c>
+      <c r="I108">
+        <v>1</v>
+      </c>
+      <c r="J108">
+        <v>1</v>
+      </c>
+      <c r="K108">
+        <v>2</v>
+      </c>
+      <c r="L108">
+        <v>3</v>
+      </c>
+      <c r="M108">
+        <v>1</v>
+      </c>
+      <c r="N108">
+        <v>4</v>
+      </c>
+      <c r="O108" t="s">
+        <v>170</v>
+      </c>
+      <c r="P108" t="s">
+        <v>141</v>
+      </c>
+      <c r="Q108">
+        <v>7</v>
+      </c>
+      <c r="R108">
+        <v>2.5</v>
+      </c>
+      <c r="S108">
+        <v>1.83</v>
+      </c>
+      <c r="T108">
+        <v>1.29</v>
+      </c>
+      <c r="U108">
+        <v>3.5</v>
+      </c>
+      <c r="V108">
+        <v>2.38</v>
+      </c>
+      <c r="W108">
+        <v>1.53</v>
+      </c>
+      <c r="X108">
+        <v>5.5</v>
+      </c>
+      <c r="Y108">
+        <v>1.14</v>
+      </c>
+      <c r="Z108">
+        <v>6.83</v>
+      </c>
+      <c r="AA108">
+        <v>4.6</v>
+      </c>
+      <c r="AB108">
+        <v>1.43</v>
+      </c>
+      <c r="AC108">
+        <v>0</v>
+      </c>
+      <c r="AD108">
+        <v>0</v>
+      </c>
+      <c r="AE108">
+        <v>0</v>
+      </c>
+      <c r="AF108">
+        <v>0</v>
+      </c>
+      <c r="AG108">
+        <v>1.65</v>
+      </c>
+      <c r="AH108">
+        <v>2.2</v>
+      </c>
+      <c r="AI108">
+        <v>1.91</v>
+      </c>
+      <c r="AJ108">
+        <v>1.91</v>
+      </c>
+      <c r="AK108">
+        <v>0</v>
+      </c>
+      <c r="AL108">
+        <v>0</v>
+      </c>
+      <c r="AM108">
+        <v>0</v>
+      </c>
+      <c r="AN108">
+        <v>1.4</v>
+      </c>
+      <c r="AO108">
+        <v>2.17</v>
+      </c>
+      <c r="AP108">
+        <v>1.67</v>
+      </c>
+      <c r="AQ108">
+        <v>1.86</v>
+      </c>
+      <c r="AR108">
+        <v>1.54</v>
+      </c>
+      <c r="AS108">
+        <v>1.81</v>
+      </c>
+      <c r="AT108">
+        <v>3.35</v>
+      </c>
+      <c r="AU108">
+        <v>5</v>
+      </c>
+      <c r="AV108">
+        <v>7</v>
+      </c>
+      <c r="AW108">
+        <v>5</v>
+      </c>
+      <c r="AX108">
+        <v>12</v>
+      </c>
+      <c r="AY108">
+        <v>10</v>
+      </c>
+      <c r="AZ108">
+        <v>19</v>
+      </c>
+      <c r="BA108">
+        <v>3</v>
+      </c>
+      <c r="BB108">
+        <v>8</v>
+      </c>
+      <c r="BC108">
+        <v>11</v>
+      </c>
+      <c r="BD108">
+        <v>0</v>
+      </c>
+      <c r="BE108">
+        <v>0</v>
+      </c>
+      <c r="BF108">
+        <v>0</v>
+      </c>
+      <c r="BG108">
+        <v>0</v>
+      </c>
+      <c r="BH108">
+        <v>0</v>
+      </c>
+      <c r="BI108">
+        <v>0</v>
+      </c>
+      <c r="BJ108">
+        <v>0</v>
+      </c>
+      <c r="BK108">
+        <v>0</v>
+      </c>
+      <c r="BL108">
+        <v>0</v>
+      </c>
+      <c r="BM108">
+        <v>0</v>
+      </c>
+      <c r="BN108">
+        <v>0</v>
+      </c>
+      <c r="BO108">
+        <v>0</v>
+      </c>
+      <c r="BP108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:68">
+      <c r="A109" s="1">
+        <v>108</v>
+      </c>
+      <c r="B109">
+        <v>7825302</v>
+      </c>
+      <c r="C109" t="s">
+        <v>68</v>
+      </c>
+      <c r="D109" t="s">
+        <v>69</v>
+      </c>
+      <c r="E109" s="2">
+        <v>45822.35763888889</v>
+      </c>
+      <c r="F109">
+        <v>14</v>
+      </c>
+      <c r="G109" t="s">
+        <v>83</v>
+      </c>
+      <c r="H109" t="s">
+        <v>70</v>
+      </c>
+      <c r="I109">
+        <v>2</v>
+      </c>
+      <c r="J109">
+        <v>2</v>
+      </c>
+      <c r="K109">
+        <v>4</v>
+      </c>
+      <c r="L109">
+        <v>3</v>
+      </c>
+      <c r="M109">
+        <v>2</v>
+      </c>
+      <c r="N109">
+        <v>5</v>
+      </c>
+      <c r="O109" t="s">
+        <v>171</v>
+      </c>
+      <c r="P109" t="s">
+        <v>238</v>
+      </c>
+      <c r="Q109">
+        <v>5.2</v>
+      </c>
+      <c r="R109">
+        <v>2.38</v>
+      </c>
+      <c r="S109">
+        <v>2.03</v>
+      </c>
+      <c r="T109">
+        <v>1.28</v>
+      </c>
+      <c r="U109">
+        <v>3.34</v>
+      </c>
+      <c r="V109">
+        <v>2.34</v>
+      </c>
+      <c r="W109">
+        <v>1.53</v>
+      </c>
+      <c r="X109">
+        <v>5.3</v>
+      </c>
+      <c r="Y109">
+        <v>1.09</v>
+      </c>
+      <c r="Z109">
+        <v>5.45</v>
+      </c>
+      <c r="AA109">
+        <v>4.3</v>
+      </c>
+      <c r="AB109">
+        <v>1.54</v>
+      </c>
+      <c r="AC109">
+        <v>1.01</v>
+      </c>
+      <c r="AD109">
+        <v>13</v>
+      </c>
+      <c r="AE109">
+        <v>1.15</v>
+      </c>
+      <c r="AF109">
+        <v>4.3</v>
+      </c>
+      <c r="AG109">
+        <v>1.62</v>
+      </c>
+      <c r="AH109">
+        <v>2.25</v>
+      </c>
+      <c r="AI109">
+        <v>1.68</v>
+      </c>
+      <c r="AJ109">
+        <v>2.06</v>
+      </c>
+      <c r="AK109">
+        <v>2.42</v>
+      </c>
+      <c r="AL109">
+        <v>1.21</v>
+      </c>
+      <c r="AM109">
+        <v>1.14</v>
+      </c>
+      <c r="AN109">
+        <v>0.6</v>
+      </c>
+      <c r="AO109">
+        <v>2.67</v>
+      </c>
+      <c r="AP109">
+        <v>1</v>
+      </c>
+      <c r="AQ109">
+        <v>2.29</v>
+      </c>
+      <c r="AR109">
+        <v>1.49</v>
+      </c>
+      <c r="AS109">
+        <v>2.04</v>
+      </c>
+      <c r="AT109">
+        <v>3.53</v>
+      </c>
+      <c r="AU109">
+        <v>9</v>
+      </c>
+      <c r="AV109">
+        <v>7</v>
+      </c>
+      <c r="AW109">
+        <v>8</v>
+      </c>
+      <c r="AX109">
+        <v>9</v>
+      </c>
+      <c r="AY109">
+        <v>17</v>
+      </c>
+      <c r="AZ109">
+        <v>16</v>
+      </c>
+      <c r="BA109">
+        <v>8</v>
+      </c>
+      <c r="BB109">
+        <v>6</v>
+      </c>
+      <c r="BC109">
+        <v>14</v>
+      </c>
+      <c r="BD109">
+        <v>2.6</v>
+      </c>
+      <c r="BE109">
+        <v>6.75</v>
+      </c>
+      <c r="BF109">
+        <v>1.58</v>
+      </c>
+      <c r="BG109">
+        <v>1.24</v>
+      </c>
+      <c r="BH109">
+        <v>3.55</v>
+      </c>
+      <c r="BI109">
+        <v>1.43</v>
+      </c>
+      <c r="BJ109">
+        <v>2.55</v>
+      </c>
+      <c r="BK109">
+        <v>1.72</v>
+      </c>
+      <c r="BL109">
+        <v>1.98</v>
+      </c>
+      <c r="BM109">
+        <v>2.08</v>
+      </c>
+      <c r="BN109">
+        <v>1.65</v>
+      </c>
+      <c r="BO109">
+        <v>2.65</v>
+      </c>
+      <c r="BP109">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="110" spans="1:68">
+      <c r="A110" s="1">
+        <v>109</v>
+      </c>
+      <c r="B110">
+        <v>7825303</v>
+      </c>
+      <c r="C110" t="s">
+        <v>68</v>
+      </c>
+      <c r="D110" t="s">
+        <v>69</v>
+      </c>
+      <c r="E110" s="2">
+        <v>45822.375</v>
+      </c>
+      <c r="F110">
+        <v>14</v>
+      </c>
+      <c r="G110" t="s">
+        <v>76</v>
+      </c>
+      <c r="H110" t="s">
+        <v>75</v>
+      </c>
+      <c r="I110">
+        <v>1</v>
+      </c>
+      <c r="J110">
+        <v>0</v>
+      </c>
+      <c r="K110">
+        <v>1</v>
+      </c>
+      <c r="L110">
+        <v>1</v>
+      </c>
+      <c r="M110">
+        <v>0</v>
+      </c>
+      <c r="N110">
+        <v>1</v>
+      </c>
+      <c r="O110" t="s">
+        <v>172</v>
+      </c>
+      <c r="P110" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q110">
+        <v>3.83</v>
+      </c>
+      <c r="R110">
+        <v>2.58</v>
+      </c>
+      <c r="S110">
+        <v>2.43</v>
+      </c>
+      <c r="T110">
+        <v>1.22</v>
+      </c>
+      <c r="U110">
+        <v>3.64</v>
+      </c>
+      <c r="V110">
+        <v>2.17</v>
+      </c>
+      <c r="W110">
+        <v>1.66</v>
+      </c>
+      <c r="X110">
+        <v>4.5</v>
+      </c>
+      <c r="Y110">
+        <v>1.15</v>
+      </c>
+      <c r="Z110">
+        <v>3.07</v>
+      </c>
+      <c r="AA110">
+        <v>3.75</v>
+      </c>
+      <c r="AB110">
+        <v>1.97</v>
+      </c>
+      <c r="AC110">
+        <v>1.02</v>
+      </c>
+      <c r="AD110">
+        <v>10</v>
+      </c>
+      <c r="AE110">
+        <v>1.13</v>
+      </c>
+      <c r="AF110">
+        <v>5</v>
+      </c>
+      <c r="AG110">
+        <v>1.55</v>
+      </c>
+      <c r="AH110">
+        <v>2.29</v>
+      </c>
+      <c r="AI110">
+        <v>1.42</v>
+      </c>
+      <c r="AJ110">
+        <v>2.77</v>
+      </c>
+      <c r="AK110">
+        <v>1.83</v>
+      </c>
+      <c r="AL110">
+        <v>1.25</v>
+      </c>
+      <c r="AM110">
+        <v>1.3</v>
+      </c>
+      <c r="AN110">
+        <v>1.33</v>
+      </c>
+      <c r="AO110">
+        <v>1.67</v>
+      </c>
+      <c r="AP110">
+        <v>1.57</v>
+      </c>
+      <c r="AQ110">
+        <v>1.43</v>
+      </c>
+      <c r="AR110">
+        <v>2.32</v>
+      </c>
+      <c r="AS110">
+        <v>2</v>
+      </c>
+      <c r="AT110">
+        <v>4.32</v>
+      </c>
+      <c r="AU110">
+        <v>5</v>
+      </c>
+      <c r="AV110">
+        <v>3</v>
+      </c>
+      <c r="AW110">
+        <v>9</v>
+      </c>
+      <c r="AX110">
+        <v>8</v>
+      </c>
+      <c r="AY110">
+        <v>14</v>
+      </c>
+      <c r="AZ110">
+        <v>11</v>
+      </c>
+      <c r="BA110">
+        <v>2</v>
+      </c>
+      <c r="BB110">
+        <v>4</v>
+      </c>
+      <c r="BC110">
+        <v>6</v>
+      </c>
+      <c r="BD110">
+        <v>2.38</v>
+      </c>
+      <c r="BE110">
+        <v>6.75</v>
+      </c>
+      <c r="BF110">
+        <v>1.7</v>
+      </c>
+      <c r="BG110">
+        <v>1.17</v>
+      </c>
+      <c r="BH110">
+        <v>4.3</v>
+      </c>
+      <c r="BI110">
+        <v>1.3</v>
+      </c>
+      <c r="BJ110">
+        <v>3.05</v>
+      </c>
+      <c r="BK110">
+        <v>1.52</v>
+      </c>
+      <c r="BL110">
+        <v>2.33</v>
+      </c>
+      <c r="BM110">
+        <v>1.82</v>
+      </c>
+      <c r="BN110">
+        <v>1.86</v>
+      </c>
+      <c r="BO110">
+        <v>2.23</v>
+      </c>
+      <c r="BP110">
+        <v>1.56</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="240">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -533,6 +533,9 @@
   </si>
   <si>
     <t>['44']</t>
+  </si>
+  <si>
+    <t>['-1']</t>
   </si>
   <si>
     <t>['53', '79']</t>
@@ -1092,7 +1095,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP110"/>
+  <dimension ref="A1:BP111"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1760,7 +1763,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -1966,7 +1969,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q5">
         <v>2.85</v>
@@ -2047,7 +2050,7 @@
         <v>1</v>
       </c>
       <c r="AQ5">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2172,7 +2175,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q6">
         <v>2.2</v>
@@ -2584,7 +2587,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q8">
         <v>2.04</v>
@@ -2790,7 +2793,7 @@
         <v>92</v>
       </c>
       <c r="P9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q9">
         <v>1.5</v>
@@ -2996,7 +2999,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q10">
         <v>2.1</v>
@@ -3408,7 +3411,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q12">
         <v>3.1</v>
@@ -3614,7 +3617,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -3820,7 +3823,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q14">
         <v>2.13</v>
@@ -4026,7 +4029,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q15">
         <v>3.2</v>
@@ -4232,7 +4235,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q16">
         <v>1.78</v>
@@ -4644,7 +4647,7 @@
         <v>100</v>
       </c>
       <c r="P18" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q18">
         <v>5.5</v>
@@ -4850,7 +4853,7 @@
         <v>88</v>
       </c>
       <c r="P19" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q19">
         <v>3.75</v>
@@ -5056,7 +5059,7 @@
         <v>101</v>
       </c>
       <c r="P20" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q20">
         <v>3.25</v>
@@ -5674,7 +5677,7 @@
         <v>104</v>
       </c>
       <c r="P23" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q23">
         <v>4</v>
@@ -5880,7 +5883,7 @@
         <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q24">
         <v>4.75</v>
@@ -6086,7 +6089,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -6164,7 +6167,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AQ25">
         <v>2.29</v>
@@ -6292,7 +6295,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q26">
         <v>2.88</v>
@@ -6373,7 +6376,7 @@
         <v>1</v>
       </c>
       <c r="AQ26">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AR26">
         <v>1.09</v>
@@ -6910,7 +6913,7 @@
         <v>110</v>
       </c>
       <c r="P29" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q29">
         <v>1.83</v>
@@ -7322,7 +7325,7 @@
         <v>88</v>
       </c>
       <c r="P31" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q31">
         <v>2.9</v>
@@ -7528,7 +7531,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q32">
         <v>3.42</v>
@@ -7734,7 +7737,7 @@
         <v>113</v>
       </c>
       <c r="P33" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q33">
         <v>1.56</v>
@@ -7940,7 +7943,7 @@
         <v>114</v>
       </c>
       <c r="P34" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q34">
         <v>3.25</v>
@@ -8146,7 +8149,7 @@
         <v>115</v>
       </c>
       <c r="P35" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q35">
         <v>4.25</v>
@@ -8352,7 +8355,7 @@
         <v>116</v>
       </c>
       <c r="P36" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q36">
         <v>3.15</v>
@@ -8558,7 +8561,7 @@
         <v>117</v>
       </c>
       <c r="P37" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q37">
         <v>2.75</v>
@@ -8970,7 +8973,7 @@
         <v>119</v>
       </c>
       <c r="P39" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q39">
         <v>2.88</v>
@@ -9254,7 +9257,7 @@
         <v>2</v>
       </c>
       <c r="AP40">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AQ40">
         <v>0.57</v>
@@ -9794,7 +9797,7 @@
         <v>123</v>
       </c>
       <c r="P43" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q43">
         <v>3</v>
@@ -10000,7 +10003,7 @@
         <v>124</v>
       </c>
       <c r="P44" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q44">
         <v>3.2</v>
@@ -10206,7 +10209,7 @@
         <v>88</v>
       </c>
       <c r="P45" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q45">
         <v>7.5</v>
@@ -10618,7 +10621,7 @@
         <v>126</v>
       </c>
       <c r="P47" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q47">
         <v>1.95</v>
@@ -10824,7 +10827,7 @@
         <v>127</v>
       </c>
       <c r="P48" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q48">
         <v>3.7</v>
@@ -11030,7 +11033,7 @@
         <v>128</v>
       </c>
       <c r="P49" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q49">
         <v>4.33</v>
@@ -11236,7 +11239,7 @@
         <v>129</v>
       </c>
       <c r="P50" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q50">
         <v>2.65</v>
@@ -11442,7 +11445,7 @@
         <v>130</v>
       </c>
       <c r="P51" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q51">
         <v>4.15</v>
@@ -11854,7 +11857,7 @@
         <v>132</v>
       </c>
       <c r="P53" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q53">
         <v>1.8</v>
@@ -12060,7 +12063,7 @@
         <v>104</v>
       </c>
       <c r="P54" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q54">
         <v>1.71</v>
@@ -12266,7 +12269,7 @@
         <v>133</v>
       </c>
       <c r="P55" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q55">
         <v>1.45</v>
@@ -12678,7 +12681,7 @@
         <v>135</v>
       </c>
       <c r="P57" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -12756,7 +12759,7 @@
         <v>3</v>
       </c>
       <c r="AP57">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AQ57">
         <v>1.43</v>
@@ -13914,7 +13917,7 @@
         <v>140</v>
       </c>
       <c r="P63" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q63">
         <v>2.88</v>
@@ -14198,7 +14201,7 @@
         <v>1</v>
       </c>
       <c r="AP64">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AQ64">
         <v>1.14</v>
@@ -14326,7 +14329,7 @@
         <v>142</v>
       </c>
       <c r="P65" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q65">
         <v>4.5</v>
@@ -14532,7 +14535,7 @@
         <v>143</v>
       </c>
       <c r="P66" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q66">
         <v>5.2</v>
@@ -14738,7 +14741,7 @@
         <v>144</v>
       </c>
       <c r="P67" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q67">
         <v>3.22</v>
@@ -14944,7 +14947,7 @@
         <v>88</v>
       </c>
       <c r="P68" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q68">
         <v>3.24</v>
@@ -15150,7 +15153,7 @@
         <v>145</v>
       </c>
       <c r="P69" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q69">
         <v>3.18</v>
@@ -15356,7 +15359,7 @@
         <v>124</v>
       </c>
       <c r="P70" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q70">
         <v>3.22</v>
@@ -15562,7 +15565,7 @@
         <v>146</v>
       </c>
       <c r="P71" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q71">
         <v>2.1</v>
@@ -15643,7 +15646,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ71">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AR71">
         <v>1.62</v>
@@ -15768,7 +15771,7 @@
         <v>147</v>
       </c>
       <c r="P72" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q72">
         <v>2.75</v>
@@ -16180,7 +16183,7 @@
         <v>148</v>
       </c>
       <c r="P74" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q74">
         <v>2.2</v>
@@ -16386,7 +16389,7 @@
         <v>149</v>
       </c>
       <c r="P75" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -16592,7 +16595,7 @@
         <v>150</v>
       </c>
       <c r="P76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q76">
         <v>1.57</v>
@@ -16798,7 +16801,7 @@
         <v>151</v>
       </c>
       <c r="P77" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q77">
         <v>2.63</v>
@@ -17416,7 +17419,7 @@
         <v>88</v>
       </c>
       <c r="P80" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q80">
         <v>3.6</v>
@@ -17622,7 +17625,7 @@
         <v>154</v>
       </c>
       <c r="P81" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q81">
         <v>2.6</v>
@@ -17828,7 +17831,7 @@
         <v>88</v>
       </c>
       <c r="P82" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q82">
         <v>4.5</v>
@@ -18446,7 +18449,7 @@
         <v>157</v>
       </c>
       <c r="P85" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q85">
         <v>4</v>
@@ -18652,7 +18655,7 @@
         <v>114</v>
       </c>
       <c r="P86" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q86">
         <v>5.5</v>
@@ -19064,7 +19067,7 @@
         <v>158</v>
       </c>
       <c r="P88" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q88">
         <v>1.53</v>
@@ -19351,7 +19354,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ89">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AR89">
         <v>2.4</v>
@@ -19476,7 +19479,7 @@
         <v>88</v>
       </c>
       <c r="P90" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q90">
         <v>6</v>
@@ -19682,7 +19685,7 @@
         <v>160</v>
       </c>
       <c r="P91" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q91">
         <v>2.2</v>
@@ -19888,7 +19891,7 @@
         <v>161</v>
       </c>
       <c r="P92" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q92">
         <v>1.8</v>
@@ -19966,7 +19969,7 @@
         <v>0.67</v>
       </c>
       <c r="AP92">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AQ92">
         <v>0.57</v>
@@ -20094,7 +20097,7 @@
         <v>88</v>
       </c>
       <c r="P93" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q93">
         <v>3.5</v>
@@ -20506,7 +20509,7 @@
         <v>162</v>
       </c>
       <c r="P95" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q95">
         <v>2.88</v>
@@ -20712,7 +20715,7 @@
         <v>163</v>
       </c>
       <c r="P96" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q96">
         <v>2.38</v>
@@ -21124,7 +21127,7 @@
         <v>88</v>
       </c>
       <c r="P98" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q98">
         <v>5.25</v>
@@ -21330,7 +21333,7 @@
         <v>165</v>
       </c>
       <c r="P99" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q99">
         <v>3.52</v>
@@ -21536,7 +21539,7 @@
         <v>166</v>
       </c>
       <c r="P100" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q100">
         <v>1.79</v>
@@ -21617,7 +21620,7 @@
         <v>2</v>
       </c>
       <c r="AQ100">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AR100">
         <v>2.09</v>
@@ -21742,7 +21745,7 @@
         <v>127</v>
       </c>
       <c r="P101" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q101">
         <v>5.55</v>
@@ -21948,7 +21951,7 @@
         <v>114</v>
       </c>
       <c r="P102" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q102">
         <v>2.3</v>
@@ -22566,7 +22569,7 @@
         <v>168</v>
       </c>
       <c r="P105" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q105">
         <v>3.54</v>
@@ -22978,7 +22981,7 @@
         <v>169</v>
       </c>
       <c r="P107" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q107">
         <v>1.49</v>
@@ -23056,7 +23059,7 @@
         <v>0.43</v>
       </c>
       <c r="AP107">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AQ107">
         <v>0.38</v>
@@ -23390,7 +23393,7 @@
         <v>171</v>
       </c>
       <c r="P109" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q109">
         <v>5.2</v>
@@ -23753,6 +23756,212 @@
       </c>
       <c r="BP110">
         <v>1.56</v>
+      </c>
+    </row>
+    <row r="111" spans="1:68">
+      <c r="A111" s="1">
+        <v>110</v>
+      </c>
+      <c r="B111">
+        <v>7825234</v>
+      </c>
+      <c r="C111" t="s">
+        <v>68</v>
+      </c>
+      <c r="D111" t="s">
+        <v>69</v>
+      </c>
+      <c r="E111" s="2">
+        <v>45825.35763888889</v>
+      </c>
+      <c r="F111">
+        <v>6</v>
+      </c>
+      <c r="G111" t="s">
+        <v>84</v>
+      </c>
+      <c r="H111" t="s">
+        <v>79</v>
+      </c>
+      <c r="I111">
+        <v>0</v>
+      </c>
+      <c r="J111">
+        <v>0</v>
+      </c>
+      <c r="K111">
+        <v>0</v>
+      </c>
+      <c r="L111">
+        <v>1</v>
+      </c>
+      <c r="M111">
+        <v>0</v>
+      </c>
+      <c r="N111">
+        <v>1</v>
+      </c>
+      <c r="O111" t="s">
+        <v>173</v>
+      </c>
+      <c r="P111" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q111">
+        <v>1.91</v>
+      </c>
+      <c r="R111">
+        <v>2.5</v>
+      </c>
+      <c r="S111">
+        <v>6</v>
+      </c>
+      <c r="T111">
+        <v>1.29</v>
+      </c>
+      <c r="U111">
+        <v>3.5</v>
+      </c>
+      <c r="V111">
+        <v>2.25</v>
+      </c>
+      <c r="W111">
+        <v>1.57</v>
+      </c>
+      <c r="X111">
+        <v>5.5</v>
+      </c>
+      <c r="Y111">
+        <v>1.14</v>
+      </c>
+      <c r="Z111">
+        <v>1.32</v>
+      </c>
+      <c r="AA111">
+        <v>5.1</v>
+      </c>
+      <c r="AB111">
+        <v>7</v>
+      </c>
+      <c r="AC111">
+        <v>1.03</v>
+      </c>
+      <c r="AD111">
+        <v>10</v>
+      </c>
+      <c r="AE111">
+        <v>1.17</v>
+      </c>
+      <c r="AF111">
+        <v>4.75</v>
+      </c>
+      <c r="AG111">
+        <v>1.36</v>
+      </c>
+      <c r="AH111">
+        <v>2.9</v>
+      </c>
+      <c r="AI111">
+        <v>1.7</v>
+      </c>
+      <c r="AJ111">
+        <v>2.05</v>
+      </c>
+      <c r="AK111">
+        <v>1.08</v>
+      </c>
+      <c r="AL111">
+        <v>1.14</v>
+      </c>
+      <c r="AM111">
+        <v>2.7</v>
+      </c>
+      <c r="AN111">
+        <v>2.67</v>
+      </c>
+      <c r="AO111">
+        <v>1</v>
+      </c>
+      <c r="AP111">
+        <v>2.71</v>
+      </c>
+      <c r="AQ111">
+        <v>0.83</v>
+      </c>
+      <c r="AR111">
+        <v>1.97</v>
+      </c>
+      <c r="AS111">
+        <v>1.22</v>
+      </c>
+      <c r="AT111">
+        <v>3.19</v>
+      </c>
+      <c r="AU111">
+        <v>4</v>
+      </c>
+      <c r="AV111">
+        <v>4</v>
+      </c>
+      <c r="AW111">
+        <v>9</v>
+      </c>
+      <c r="AX111">
+        <v>10</v>
+      </c>
+      <c r="AY111">
+        <v>13</v>
+      </c>
+      <c r="AZ111">
+        <v>14</v>
+      </c>
+      <c r="BA111">
+        <v>6</v>
+      </c>
+      <c r="BB111">
+        <v>6</v>
+      </c>
+      <c r="BC111">
+        <v>12</v>
+      </c>
+      <c r="BD111">
+        <v>1.42</v>
+      </c>
+      <c r="BE111">
+        <v>7</v>
+      </c>
+      <c r="BF111">
+        <v>3.2</v>
+      </c>
+      <c r="BG111">
+        <v>1.26</v>
+      </c>
+      <c r="BH111">
+        <v>3.4</v>
+      </c>
+      <c r="BI111">
+        <v>1.46</v>
+      </c>
+      <c r="BJ111">
+        <v>2.5</v>
+      </c>
+      <c r="BK111">
+        <v>1.72</v>
+      </c>
+      <c r="BL111">
+        <v>1.97</v>
+      </c>
+      <c r="BM111">
+        <v>2.12</v>
+      </c>
+      <c r="BN111">
+        <v>1.63</v>
+      </c>
+      <c r="BO111">
+        <v>2.65</v>
+      </c>
+      <c r="BP111">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="243">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -535,7 +535,13 @@
     <t>['44']</t>
   </si>
   <si>
-    <t>['-1']</t>
+    <t>['24']</t>
+  </si>
+  <si>
+    <t>['70']</t>
+  </si>
+  <si>
+    <t>['49']</t>
   </si>
   <si>
     <t>['53', '79']</t>
@@ -706,9 +712,6 @@
     <t>['3', '69']</t>
   </si>
   <si>
-    <t>['49']</t>
-  </si>
-  <si>
     <t>['14', '34']</t>
   </si>
   <si>
@@ -734,6 +737,12 @@
   </si>
   <si>
     <t>['8', '21']</t>
+  </si>
+  <si>
+    <t>['32', '44', '4501']</t>
+  </si>
+  <si>
+    <t>['63', '75']</t>
   </si>
 </sst>
 </file>
@@ -1095,7 +1104,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP111"/>
+  <dimension ref="A1:BP113"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1432,7 +1441,7 @@
         <v>2</v>
       </c>
       <c r="AQ2">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1763,7 +1772,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -1969,7 +1978,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q5">
         <v>2.85</v>
@@ -2175,7 +2184,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q6">
         <v>2.2</v>
@@ -2587,7 +2596,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q8">
         <v>2.04</v>
@@ -2793,7 +2802,7 @@
         <v>92</v>
       </c>
       <c r="P9" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q9">
         <v>1.5</v>
@@ -2999,7 +3008,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q10">
         <v>2.1</v>
@@ -3411,7 +3420,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q12">
         <v>3.1</v>
@@ -3617,7 +3626,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -3823,7 +3832,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q14">
         <v>2.13</v>
@@ -4029,7 +4038,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q15">
         <v>3.2</v>
@@ -4235,7 +4244,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q16">
         <v>1.78</v>
@@ -4522,7 +4531,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ17">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4647,7 +4656,7 @@
         <v>100</v>
       </c>
       <c r="P18" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q18">
         <v>5.5</v>
@@ -4728,7 +4737,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ18">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AR18">
         <v>0.8</v>
@@ -4853,7 +4862,7 @@
         <v>88</v>
       </c>
       <c r="P19" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q19">
         <v>3.75</v>
@@ -5059,7 +5068,7 @@
         <v>101</v>
       </c>
       <c r="P20" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q20">
         <v>3.25</v>
@@ -5137,7 +5146,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AQ20">
         <v>1.13</v>
@@ -5677,7 +5686,7 @@
         <v>104</v>
       </c>
       <c r="P23" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q23">
         <v>4</v>
@@ -5755,7 +5764,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AQ23">
         <v>1.86</v>
@@ -5883,7 +5892,7 @@
         <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q24">
         <v>4.75</v>
@@ -6089,7 +6098,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -6295,7 +6304,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q26">
         <v>2.88</v>
@@ -6373,7 +6382,7 @@
         <v>1</v>
       </c>
       <c r="AP26">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AQ26">
         <v>0.83</v>
@@ -6788,7 +6797,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ28">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AR28">
         <v>0</v>
@@ -6913,7 +6922,7 @@
         <v>110</v>
       </c>
       <c r="P29" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q29">
         <v>1.83</v>
@@ -7325,7 +7334,7 @@
         <v>88</v>
       </c>
       <c r="P31" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q31">
         <v>2.9</v>
@@ -7531,7 +7540,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q32">
         <v>3.42</v>
@@ -7737,7 +7746,7 @@
         <v>113</v>
       </c>
       <c r="P33" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q33">
         <v>1.56</v>
@@ -7943,7 +7952,7 @@
         <v>114</v>
       </c>
       <c r="P34" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q34">
         <v>3.25</v>
@@ -8021,7 +8030,7 @@
         <v>0.5</v>
       </c>
       <c r="AP34">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AQ34">
         <v>1.14</v>
@@ -8149,7 +8158,7 @@
         <v>115</v>
       </c>
       <c r="P35" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q35">
         <v>4.25</v>
@@ -8355,7 +8364,7 @@
         <v>116</v>
       </c>
       <c r="P36" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q36">
         <v>3.15</v>
@@ -8561,7 +8570,7 @@
         <v>117</v>
       </c>
       <c r="P37" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q37">
         <v>2.75</v>
@@ -8642,7 +8651,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ37">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AR37">
         <v>1.61</v>
@@ -8973,7 +8982,7 @@
         <v>119</v>
       </c>
       <c r="P39" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q39">
         <v>2.88</v>
@@ -9797,7 +9806,7 @@
         <v>123</v>
       </c>
       <c r="P43" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q43">
         <v>3</v>
@@ -10003,7 +10012,7 @@
         <v>124</v>
       </c>
       <c r="P44" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q44">
         <v>3.2</v>
@@ -10209,7 +10218,7 @@
         <v>88</v>
       </c>
       <c r="P45" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q45">
         <v>7.5</v>
@@ -10621,7 +10630,7 @@
         <v>126</v>
       </c>
       <c r="P47" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q47">
         <v>1.95</v>
@@ -10827,7 +10836,7 @@
         <v>127</v>
       </c>
       <c r="P48" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q48">
         <v>3.7</v>
@@ -11033,7 +11042,7 @@
         <v>128</v>
       </c>
       <c r="P49" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q49">
         <v>4.33</v>
@@ -11239,7 +11248,7 @@
         <v>129</v>
       </c>
       <c r="P50" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q50">
         <v>2.65</v>
@@ -11317,7 +11326,7 @@
         <v>0.75</v>
       </c>
       <c r="AP50">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AQ50">
         <v>0.38</v>
@@ -11445,7 +11454,7 @@
         <v>130</v>
       </c>
       <c r="P51" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q51">
         <v>4.15</v>
@@ -11526,7 +11535,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ51">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AR51">
         <v>2.87</v>
@@ -11857,7 +11866,7 @@
         <v>132</v>
       </c>
       <c r="P53" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q53">
         <v>1.8</v>
@@ -12063,7 +12072,7 @@
         <v>104</v>
       </c>
       <c r="P54" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q54">
         <v>1.71</v>
@@ -12269,7 +12278,7 @@
         <v>133</v>
       </c>
       <c r="P55" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q55">
         <v>1.45</v>
@@ -12556,7 +12565,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ56">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AR56">
         <v>2.49</v>
@@ -12681,7 +12690,7 @@
         <v>135</v>
       </c>
       <c r="P57" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -13377,7 +13386,7 @@
         <v>0</v>
       </c>
       <c r="AP60">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AQ60">
         <v>0.14</v>
@@ -13917,7 +13926,7 @@
         <v>140</v>
       </c>
       <c r="P63" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q63">
         <v>2.88</v>
@@ -14329,7 +14338,7 @@
         <v>142</v>
       </c>
       <c r="P65" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q65">
         <v>4.5</v>
@@ -14410,7 +14419,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ65">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AR65">
         <v>1.5</v>
@@ -14535,7 +14544,7 @@
         <v>143</v>
       </c>
       <c r="P66" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q66">
         <v>5.2</v>
@@ -14741,7 +14750,7 @@
         <v>144</v>
       </c>
       <c r="P67" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q67">
         <v>3.22</v>
@@ -14819,7 +14828,7 @@
         <v>0.4</v>
       </c>
       <c r="AP67">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AQ67">
         <v>0.57</v>
@@ -14947,7 +14956,7 @@
         <v>88</v>
       </c>
       <c r="P68" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q68">
         <v>3.24</v>
@@ -15153,7 +15162,7 @@
         <v>145</v>
       </c>
       <c r="P69" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q69">
         <v>3.18</v>
@@ -15359,7 +15368,7 @@
         <v>124</v>
       </c>
       <c r="P70" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q70">
         <v>3.22</v>
@@ -15565,7 +15574,7 @@
         <v>146</v>
       </c>
       <c r="P71" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q71">
         <v>2.1</v>
@@ -15771,7 +15780,7 @@
         <v>147</v>
       </c>
       <c r="P72" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q72">
         <v>2.75</v>
@@ -16055,7 +16064,7 @@
         <v>1.25</v>
       </c>
       <c r="AP73">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AQ73">
         <v>1.57</v>
@@ -16183,7 +16192,7 @@
         <v>148</v>
       </c>
       <c r="P74" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q74">
         <v>2.2</v>
@@ -16389,7 +16398,7 @@
         <v>149</v>
       </c>
       <c r="P75" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -16467,10 +16476,10 @@
         <v>0.2</v>
       </c>
       <c r="AP75">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AQ75">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AR75">
         <v>1.26</v>
@@ -16595,7 +16604,7 @@
         <v>150</v>
       </c>
       <c r="P76" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q76">
         <v>1.57</v>
@@ -16801,7 +16810,7 @@
         <v>151</v>
       </c>
       <c r="P77" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q77">
         <v>2.63</v>
@@ -17419,7 +17428,7 @@
         <v>88</v>
       </c>
       <c r="P80" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q80">
         <v>3.6</v>
@@ -17625,7 +17634,7 @@
         <v>154</v>
       </c>
       <c r="P81" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q81">
         <v>2.6</v>
@@ -17703,7 +17712,7 @@
         <v>1</v>
       </c>
       <c r="AP81">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AQ81">
         <v>1.57</v>
@@ -17831,7 +17840,7 @@
         <v>88</v>
       </c>
       <c r="P82" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q82">
         <v>4.5</v>
@@ -17912,7 +17921,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ82">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AR82">
         <v>2.09</v>
@@ -18449,7 +18458,7 @@
         <v>157</v>
       </c>
       <c r="P85" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q85">
         <v>4</v>
@@ -18655,7 +18664,7 @@
         <v>114</v>
       </c>
       <c r="P86" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q86">
         <v>5.5</v>
@@ -19067,7 +19076,7 @@
         <v>158</v>
       </c>
       <c r="P88" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q88">
         <v>1.53</v>
@@ -19479,7 +19488,7 @@
         <v>88</v>
       </c>
       <c r="P90" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q90">
         <v>6</v>
@@ -19685,7 +19694,7 @@
         <v>160</v>
       </c>
       <c r="P91" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q91">
         <v>2.2</v>
@@ -19891,7 +19900,7 @@
         <v>161</v>
       </c>
       <c r="P92" t="s">
-        <v>230</v>
+        <v>175</v>
       </c>
       <c r="Q92">
         <v>1.8</v>
@@ -20097,7 +20106,7 @@
         <v>88</v>
       </c>
       <c r="P93" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q93">
         <v>3.5</v>
@@ -20509,7 +20518,7 @@
         <v>162</v>
       </c>
       <c r="P95" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q95">
         <v>2.88</v>
@@ -20715,7 +20724,7 @@
         <v>163</v>
       </c>
       <c r="P96" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q96">
         <v>2.38</v>
@@ -21127,7 +21136,7 @@
         <v>88</v>
       </c>
       <c r="P98" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q98">
         <v>5.25</v>
@@ -21333,7 +21342,7 @@
         <v>165</v>
       </c>
       <c r="P99" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q99">
         <v>3.52</v>
@@ -21539,7 +21548,7 @@
         <v>166</v>
       </c>
       <c r="P100" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q100">
         <v>1.79</v>
@@ -21745,7 +21754,7 @@
         <v>127</v>
       </c>
       <c r="P101" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q101">
         <v>5.55</v>
@@ -21951,7 +21960,7 @@
         <v>114</v>
       </c>
       <c r="P102" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q102">
         <v>2.3</v>
@@ -22569,7 +22578,7 @@
         <v>168</v>
       </c>
       <c r="P105" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q105">
         <v>3.54</v>
@@ -22650,7 +22659,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ105">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AR105">
         <v>1.56</v>
@@ -22981,7 +22990,7 @@
         <v>169</v>
       </c>
       <c r="P107" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q107">
         <v>1.49</v>
@@ -23265,7 +23274,7 @@
         <v>2.17</v>
       </c>
       <c r="AP108">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AQ108">
         <v>1.86</v>
@@ -23393,7 +23402,7 @@
         <v>171</v>
       </c>
       <c r="P109" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q109">
         <v>5.2</v>
@@ -23471,7 +23480,7 @@
         <v>2.67</v>
       </c>
       <c r="AP109">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AQ109">
         <v>2.29</v>
@@ -23784,13 +23793,13 @@
         <v>79</v>
       </c>
       <c r="I111">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J111">
         <v>0</v>
       </c>
       <c r="K111">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L111">
         <v>1</v>
@@ -23898,22 +23907,22 @@
         <v>3.19</v>
       </c>
       <c r="AU111">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV111">
         <v>4</v>
       </c>
       <c r="AW111">
+        <v>3</v>
+      </c>
+      <c r="AX111">
+        <v>5</v>
+      </c>
+      <c r="AY111">
+        <v>8</v>
+      </c>
+      <c r="AZ111">
         <v>9</v>
-      </c>
-      <c r="AX111">
-        <v>10</v>
-      </c>
-      <c r="AY111">
-        <v>13</v>
-      </c>
-      <c r="AZ111">
-        <v>14</v>
       </c>
       <c r="BA111">
         <v>6</v>
@@ -23962,6 +23971,418 @@
       </c>
       <c r="BP111">
         <v>1.4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:68">
+      <c r="A112" s="1">
+        <v>111</v>
+      </c>
+      <c r="B112">
+        <v>7825236</v>
+      </c>
+      <c r="C112" t="s">
+        <v>68</v>
+      </c>
+      <c r="D112" t="s">
+        <v>69</v>
+      </c>
+      <c r="E112" s="2">
+        <v>45826.35763888889</v>
+      </c>
+      <c r="F112">
+        <v>6</v>
+      </c>
+      <c r="G112" t="s">
+        <v>83</v>
+      </c>
+      <c r="H112" t="s">
+        <v>77</v>
+      </c>
+      <c r="I112">
+        <v>0</v>
+      </c>
+      <c r="J112">
+        <v>3</v>
+      </c>
+      <c r="K112">
+        <v>3</v>
+      </c>
+      <c r="L112">
+        <v>1</v>
+      </c>
+      <c r="M112">
+        <v>3</v>
+      </c>
+      <c r="N112">
+        <v>4</v>
+      </c>
+      <c r="O112" t="s">
+        <v>174</v>
+      </c>
+      <c r="P112" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q112">
+        <v>4</v>
+      </c>
+      <c r="R112">
+        <v>2.4</v>
+      </c>
+      <c r="S112">
+        <v>2.38</v>
+      </c>
+      <c r="T112">
+        <v>1.29</v>
+      </c>
+      <c r="U112">
+        <v>3.5</v>
+      </c>
+      <c r="V112">
+        <v>2.25</v>
+      </c>
+      <c r="W112">
+        <v>1.57</v>
+      </c>
+      <c r="X112">
+        <v>5.5</v>
+      </c>
+      <c r="Y112">
+        <v>1.14</v>
+      </c>
+      <c r="Z112">
+        <v>2.7</v>
+      </c>
+      <c r="AA112">
+        <v>3.93</v>
+      </c>
+      <c r="AB112">
+        <v>2.11</v>
+      </c>
+      <c r="AC112">
+        <v>1.01</v>
+      </c>
+      <c r="AD112">
+        <v>13</v>
+      </c>
+      <c r="AE112">
+        <v>1.11</v>
+      </c>
+      <c r="AF112">
+        <v>4.9</v>
+      </c>
+      <c r="AG112">
+        <v>1.42</v>
+      </c>
+      <c r="AH112">
+        <v>2.65</v>
+      </c>
+      <c r="AI112">
+        <v>1.5</v>
+      </c>
+      <c r="AJ112">
+        <v>2.5</v>
+      </c>
+      <c r="AK112">
+        <v>1.97</v>
+      </c>
+      <c r="AL112">
+        <v>1.28</v>
+      </c>
+      <c r="AM112">
+        <v>1.2</v>
+      </c>
+      <c r="AN112">
+        <v>1</v>
+      </c>
+      <c r="AO112">
+        <v>2.2</v>
+      </c>
+      <c r="AP112">
+        <v>0.86</v>
+      </c>
+      <c r="AQ112">
+        <v>2.33</v>
+      </c>
+      <c r="AR112">
+        <v>1.59</v>
+      </c>
+      <c r="AS112">
+        <v>1.64</v>
+      </c>
+      <c r="AT112">
+        <v>3.23</v>
+      </c>
+      <c r="AU112">
+        <v>4</v>
+      </c>
+      <c r="AV112">
+        <v>8</v>
+      </c>
+      <c r="AW112">
+        <v>12</v>
+      </c>
+      <c r="AX112">
+        <v>3</v>
+      </c>
+      <c r="AY112">
+        <v>16</v>
+      </c>
+      <c r="AZ112">
+        <v>11</v>
+      </c>
+      <c r="BA112">
+        <v>6</v>
+      </c>
+      <c r="BB112">
+        <v>4</v>
+      </c>
+      <c r="BC112">
+        <v>10</v>
+      </c>
+      <c r="BD112">
+        <v>2.4</v>
+      </c>
+      <c r="BE112">
+        <v>6.75</v>
+      </c>
+      <c r="BF112">
+        <v>1.68</v>
+      </c>
+      <c r="BG112">
+        <v>1.17</v>
+      </c>
+      <c r="BH112">
+        <v>4.35</v>
+      </c>
+      <c r="BI112">
+        <v>1.3</v>
+      </c>
+      <c r="BJ112">
+        <v>3.15</v>
+      </c>
+      <c r="BK112">
+        <v>1.49</v>
+      </c>
+      <c r="BL112">
+        <v>2.4</v>
+      </c>
+      <c r="BM112">
+        <v>1.77</v>
+      </c>
+      <c r="BN112">
+        <v>1.91</v>
+      </c>
+      <c r="BO112">
+        <v>2.17</v>
+      </c>
+      <c r="BP112">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="113" spans="1:68">
+      <c r="A113" s="1">
+        <v>112</v>
+      </c>
+      <c r="B113">
+        <v>7825291</v>
+      </c>
+      <c r="C113" t="s">
+        <v>68</v>
+      </c>
+      <c r="D113" t="s">
+        <v>69</v>
+      </c>
+      <c r="E113" s="2">
+        <v>45826.375</v>
+      </c>
+      <c r="F113">
+        <v>13</v>
+      </c>
+      <c r="G113" t="s">
+        <v>81</v>
+      </c>
+      <c r="H113" t="s">
+        <v>80</v>
+      </c>
+      <c r="I113">
+        <v>0</v>
+      </c>
+      <c r="J113">
+        <v>0</v>
+      </c>
+      <c r="K113">
+        <v>0</v>
+      </c>
+      <c r="L113">
+        <v>1</v>
+      </c>
+      <c r="M113">
+        <v>2</v>
+      </c>
+      <c r="N113">
+        <v>3</v>
+      </c>
+      <c r="O113" t="s">
+        <v>175</v>
+      </c>
+      <c r="P113" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q113">
+        <v>3.04</v>
+      </c>
+      <c r="R113">
+        <v>2.16</v>
+      </c>
+      <c r="S113">
+        <v>3.2</v>
+      </c>
+      <c r="T113">
+        <v>1.33</v>
+      </c>
+      <c r="U113">
+        <v>3.02</v>
+      </c>
+      <c r="V113">
+        <v>2.62</v>
+      </c>
+      <c r="W113">
+        <v>1.43</v>
+      </c>
+      <c r="X113">
+        <v>6.25</v>
+      </c>
+      <c r="Y113">
+        <v>1.06</v>
+      </c>
+      <c r="Z113">
+        <v>2.51</v>
+      </c>
+      <c r="AA113">
+        <v>3.5</v>
+      </c>
+      <c r="AB113">
+        <v>2.62</v>
+      </c>
+      <c r="AC113">
+        <v>1.02</v>
+      </c>
+      <c r="AD113">
+        <v>10</v>
+      </c>
+      <c r="AE113">
+        <v>1.21</v>
+      </c>
+      <c r="AF113">
+        <v>3.6</v>
+      </c>
+      <c r="AG113">
+        <v>1.81</v>
+      </c>
+      <c r="AH113">
+        <v>1.96</v>
+      </c>
+      <c r="AI113">
+        <v>1.63</v>
+      </c>
+      <c r="AJ113">
+        <v>2.14</v>
+      </c>
+      <c r="AK113">
+        <v>1.47</v>
+      </c>
+      <c r="AL113">
+        <v>1.28</v>
+      </c>
+      <c r="AM113">
+        <v>1.51</v>
+      </c>
+      <c r="AN113">
+        <v>1.67</v>
+      </c>
+      <c r="AO113">
+        <v>0.67</v>
+      </c>
+      <c r="AP113">
+        <v>1.43</v>
+      </c>
+      <c r="AQ113">
+        <v>1</v>
+      </c>
+      <c r="AR113">
+        <v>1.49</v>
+      </c>
+      <c r="AS113">
+        <v>1.01</v>
+      </c>
+      <c r="AT113">
+        <v>2.5</v>
+      </c>
+      <c r="AU113">
+        <v>4</v>
+      </c>
+      <c r="AV113">
+        <v>9</v>
+      </c>
+      <c r="AW113">
+        <v>5</v>
+      </c>
+      <c r="AX113">
+        <v>4</v>
+      </c>
+      <c r="AY113">
+        <v>9</v>
+      </c>
+      <c r="AZ113">
+        <v>13</v>
+      </c>
+      <c r="BA113">
+        <v>4</v>
+      </c>
+      <c r="BB113">
+        <v>2</v>
+      </c>
+      <c r="BC113">
+        <v>6</v>
+      </c>
+      <c r="BD113">
+        <v>2</v>
+      </c>
+      <c r="BE113">
+        <v>6.5</v>
+      </c>
+      <c r="BF113">
+        <v>1.98</v>
+      </c>
+      <c r="BG113">
+        <v>1.3</v>
+      </c>
+      <c r="BH113">
+        <v>3.15</v>
+      </c>
+      <c r="BI113">
+        <v>1.52</v>
+      </c>
+      <c r="BJ113">
+        <v>2.33</v>
+      </c>
+      <c r="BK113">
+        <v>1.84</v>
+      </c>
+      <c r="BL113">
+        <v>1.84</v>
+      </c>
+      <c r="BM113">
+        <v>2.32</v>
+      </c>
+      <c r="BN113">
+        <v>1.53</v>
+      </c>
+      <c r="BO113">
+        <v>2.95</v>
+      </c>
+      <c r="BP113">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
@@ -23907,22 +23907,22 @@
         <v>3.19</v>
       </c>
       <c r="AU111">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV111">
         <v>4</v>
       </c>
       <c r="AW111">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AX111">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AY111">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AZ111">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="BA111">
         <v>6</v>
@@ -24113,22 +24113,22 @@
         <v>3.23</v>
       </c>
       <c r="AU112">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AV112">
         <v>8</v>
       </c>
       <c r="AW112">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AX112">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AY112">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="AZ112">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="BA112">
         <v>6</v>
@@ -24319,22 +24319,22 @@
         <v>2.5</v>
       </c>
       <c r="AU113">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV113">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW113">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX113">
         <v>4</v>
       </c>
       <c r="AY113">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AZ113">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA113">
         <v>4</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
@@ -23907,22 +23907,22 @@
         <v>3.19</v>
       </c>
       <c r="AU111">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV111">
         <v>4</v>
       </c>
       <c r="AW111">
+        <v>3</v>
+      </c>
+      <c r="AX111">
+        <v>5</v>
+      </c>
+      <c r="AY111">
+        <v>8</v>
+      </c>
+      <c r="AZ111">
         <v>9</v>
-      </c>
-      <c r="AX111">
-        <v>10</v>
-      </c>
-      <c r="AY111">
-        <v>13</v>
-      </c>
-      <c r="AZ111">
-        <v>14</v>
       </c>
       <c r="BA111">
         <v>6</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="250">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -544,6 +544,18 @@
     <t>['49']</t>
   </si>
   <si>
+    <t>['42', '4504', '9005']</t>
+  </si>
+  <si>
+    <t>['77']</t>
+  </si>
+  <si>
+    <t>['26', '70', '9005']</t>
+  </si>
+  <si>
+    <t>['9', '16', '62', '75', '83']</t>
+  </si>
+  <si>
     <t>['53', '79']</t>
   </si>
   <si>
@@ -743,6 +755,15 @@
   </si>
   <si>
     <t>['63', '75']</t>
+  </si>
+  <si>
+    <t>['47', '69', '9004']</t>
+  </si>
+  <si>
+    <t>['9002']</t>
+  </si>
+  <si>
+    <t>['21', '45', '55', '69']</t>
   </si>
 </sst>
 </file>
@@ -1104,7 +1125,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP113"/>
+  <dimension ref="A1:BP119"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1438,10 +1459,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ2">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1644,7 +1665,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AQ3">
         <v>0.38</v>
@@ -1772,7 +1793,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -1853,7 +1874,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ4">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1978,7 +1999,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="Q5">
         <v>2.85</v>
@@ -2056,10 +2077,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ5">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2184,7 +2205,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="Q6">
         <v>2.2</v>
@@ -2468,7 +2489,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AQ7">
         <v>1.14</v>
@@ -2596,7 +2617,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="Q8">
         <v>2.04</v>
@@ -2802,7 +2823,7 @@
         <v>92</v>
       </c>
       <c r="P9" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="Q9">
         <v>1.5</v>
@@ -2883,7 +2904,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ9">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3008,7 +3029,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="Q10">
         <v>2.1</v>
@@ -3086,7 +3107,7 @@
         <v>1</v>
       </c>
       <c r="AP10">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AQ10">
         <v>0.57</v>
@@ -3420,7 +3441,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="Q12">
         <v>3.1</v>
@@ -3498,10 +3519,10 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ12">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR12">
         <v>1.44</v>
@@ -3626,7 +3647,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -3704,7 +3725,7 @@
         <v>1</v>
       </c>
       <c r="AP13">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ13">
         <v>1.14</v>
@@ -3832,7 +3853,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="Q14">
         <v>2.13</v>
@@ -3910,10 +3931,10 @@
         <v>3</v>
       </c>
       <c r="AP14">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AQ14">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AR14">
         <v>2.29</v>
@@ -4038,7 +4059,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="Q15">
         <v>3.2</v>
@@ -4119,7 +4140,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ15">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AR15">
         <v>1.22</v>
@@ -4244,7 +4265,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="Q16">
         <v>1.78</v>
@@ -4322,10 +4343,10 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ16">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AR16">
         <v>2.91</v>
@@ -4531,7 +4552,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ17">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4656,7 +4677,7 @@
         <v>100</v>
       </c>
       <c r="P18" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="Q18">
         <v>5.5</v>
@@ -4862,7 +4883,7 @@
         <v>88</v>
       </c>
       <c r="P19" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="Q19">
         <v>3.75</v>
@@ -4943,7 +4964,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ19">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5068,7 +5089,7 @@
         <v>101</v>
       </c>
       <c r="P20" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="Q20">
         <v>3.25</v>
@@ -5686,7 +5707,7 @@
         <v>104</v>
       </c>
       <c r="P23" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="Q23">
         <v>4</v>
@@ -5892,7 +5913,7 @@
         <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="Q24">
         <v>4.75</v>
@@ -5970,7 +5991,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ24">
         <v>1.43</v>
@@ -6098,7 +6119,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -6304,7 +6325,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="Q26">
         <v>2.88</v>
@@ -6385,7 +6406,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ26">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR26">
         <v>1.09</v>
@@ -6591,7 +6612,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ27">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR27">
         <v>1.37</v>
@@ -6794,10 +6815,10 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="AQ28">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR28">
         <v>0</v>
@@ -6922,7 +6943,7 @@
         <v>110</v>
       </c>
       <c r="P29" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="Q29">
         <v>1.83</v>
@@ -7000,7 +7021,7 @@
         <v>3</v>
       </c>
       <c r="AP29">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AQ29">
         <v>1.13</v>
@@ -7206,7 +7227,7 @@
         <v>0.5</v>
       </c>
       <c r="AP30">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ30">
         <v>0.57</v>
@@ -7334,7 +7355,7 @@
         <v>88</v>
       </c>
       <c r="P31" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="Q31">
         <v>2.9</v>
@@ -7412,7 +7433,7 @@
         <v>1</v>
       </c>
       <c r="AP31">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AQ31">
         <v>2.29</v>
@@ -7540,7 +7561,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="Q32">
         <v>3.42</v>
@@ -7621,7 +7642,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ32">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AR32">
         <v>3.11</v>
@@ -7746,7 +7767,7 @@
         <v>113</v>
       </c>
       <c r="P33" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="Q33">
         <v>1.56</v>
@@ -7952,7 +7973,7 @@
         <v>114</v>
       </c>
       <c r="P34" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="Q34">
         <v>3.25</v>
@@ -8158,7 +8179,7 @@
         <v>115</v>
       </c>
       <c r="P35" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="Q35">
         <v>4.25</v>
@@ -8236,7 +8257,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="AQ35">
         <v>1.43</v>
@@ -8364,7 +8385,7 @@
         <v>116</v>
       </c>
       <c r="P36" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="Q36">
         <v>3.15</v>
@@ -8445,7 +8466,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ36">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AR36">
         <v>1.07</v>
@@ -8570,7 +8591,7 @@
         <v>117</v>
       </c>
       <c r="P37" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="Q37">
         <v>2.75</v>
@@ -8648,10 +8669,10 @@
         <v>0.33</v>
       </c>
       <c r="AP37">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ37">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR37">
         <v>1.61</v>
@@ -8854,7 +8875,7 @@
         <v>0.67</v>
       </c>
       <c r="AP38">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ38">
         <v>0.57</v>
@@ -8982,7 +9003,7 @@
         <v>119</v>
       </c>
       <c r="P39" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="Q39">
         <v>2.88</v>
@@ -9269,7 +9290,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ40">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AR40">
         <v>0.75</v>
@@ -9678,10 +9699,10 @@
         <v>1</v>
       </c>
       <c r="AP42">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AQ42">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR42">
         <v>2.03</v>
@@ -9806,7 +9827,7 @@
         <v>123</v>
       </c>
       <c r="P43" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="Q43">
         <v>3</v>
@@ -9884,7 +9905,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ43">
         <v>0.38</v>
@@ -10012,7 +10033,7 @@
         <v>124</v>
       </c>
       <c r="P44" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="Q44">
         <v>3.2</v>
@@ -10093,7 +10114,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ44">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AR44">
         <v>2.26</v>
@@ -10218,7 +10239,7 @@
         <v>88</v>
       </c>
       <c r="P45" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="Q45">
         <v>7.5</v>
@@ -10296,7 +10317,7 @@
         <v>2</v>
       </c>
       <c r="AP45">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ45">
         <v>2.29</v>
@@ -10630,7 +10651,7 @@
         <v>126</v>
       </c>
       <c r="P47" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="Q47">
         <v>1.95</v>
@@ -10708,10 +10729,10 @@
         <v>1.33</v>
       </c>
       <c r="AP47">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AQ47">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AR47">
         <v>2.72</v>
@@ -10836,7 +10857,7 @@
         <v>127</v>
       </c>
       <c r="P48" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="Q48">
         <v>3.7</v>
@@ -11042,7 +11063,7 @@
         <v>128</v>
       </c>
       <c r="P49" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="Q49">
         <v>4.33</v>
@@ -11123,7 +11144,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ49">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AR49">
         <v>1.83</v>
@@ -11248,7 +11269,7 @@
         <v>129</v>
       </c>
       <c r="P50" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="Q50">
         <v>2.65</v>
@@ -11454,7 +11475,7 @@
         <v>130</v>
       </c>
       <c r="P51" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="Q51">
         <v>4.15</v>
@@ -11866,7 +11887,7 @@
         <v>132</v>
       </c>
       <c r="P53" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="Q53">
         <v>1.8</v>
@@ -12072,7 +12093,7 @@
         <v>104</v>
       </c>
       <c r="P54" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="Q54">
         <v>1.71</v>
@@ -12150,7 +12171,7 @@
         <v>1</v>
       </c>
       <c r="AP54">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ54">
         <v>1.13</v>
@@ -12278,7 +12299,7 @@
         <v>133</v>
       </c>
       <c r="P55" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="Q55">
         <v>1.45</v>
@@ -12356,7 +12377,7 @@
         <v>0</v>
       </c>
       <c r="AP55">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AQ55">
         <v>0.14</v>
@@ -12562,10 +12583,10 @@
         <v>0.25</v>
       </c>
       <c r="AP56">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AQ56">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR56">
         <v>2.49</v>
@@ -12690,7 +12711,7 @@
         <v>135</v>
       </c>
       <c r="P57" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -12974,7 +12995,7 @@
         <v>1</v>
       </c>
       <c r="AP58">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="AQ58">
         <v>1.13</v>
@@ -13592,10 +13613,10 @@
         <v>0.75</v>
       </c>
       <c r="AP61">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ61">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR61">
         <v>2.04</v>
@@ -13801,7 +13822,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ62">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AR62">
         <v>2.42</v>
@@ -13926,7 +13947,7 @@
         <v>140</v>
       </c>
       <c r="P63" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="Q63">
         <v>2.88</v>
@@ -14338,7 +14359,7 @@
         <v>142</v>
       </c>
       <c r="P65" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="Q65">
         <v>4.5</v>
@@ -14544,7 +14565,7 @@
         <v>143</v>
       </c>
       <c r="P66" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="Q66">
         <v>5.2</v>
@@ -14622,7 +14643,7 @@
         <v>2.5</v>
       </c>
       <c r="AP66">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="AQ66">
         <v>2.29</v>
@@ -14750,7 +14771,7 @@
         <v>144</v>
       </c>
       <c r="P67" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="Q67">
         <v>3.22</v>
@@ -14956,7 +14977,7 @@
         <v>88</v>
       </c>
       <c r="P68" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="Q68">
         <v>3.24</v>
@@ -15034,7 +15055,7 @@
         <v>2</v>
       </c>
       <c r="AP68">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AQ68">
         <v>1.86</v>
@@ -15162,7 +15183,7 @@
         <v>145</v>
       </c>
       <c r="P69" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="Q69">
         <v>3.18</v>
@@ -15243,7 +15264,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ69">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AR69">
         <v>2.08</v>
@@ -15368,7 +15389,7 @@
         <v>124</v>
       </c>
       <c r="P70" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="Q70">
         <v>3.22</v>
@@ -15446,7 +15467,7 @@
         <v>0.67</v>
       </c>
       <c r="AP70">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ70">
         <v>0.43</v>
@@ -15574,7 +15595,7 @@
         <v>146</v>
       </c>
       <c r="P71" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="Q71">
         <v>2.1</v>
@@ -15655,7 +15676,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ71">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR71">
         <v>1.62</v>
@@ -15780,7 +15801,7 @@
         <v>147</v>
       </c>
       <c r="P72" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="Q72">
         <v>2.75</v>
@@ -16067,7 +16088,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ73">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AR73">
         <v>1.59</v>
@@ -16192,7 +16213,7 @@
         <v>148</v>
       </c>
       <c r="P74" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="Q74">
         <v>2.2</v>
@@ -16398,7 +16419,7 @@
         <v>149</v>
       </c>
       <c r="P75" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -16479,7 +16500,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ75">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR75">
         <v>1.26</v>
@@ -16604,7 +16625,7 @@
         <v>150</v>
       </c>
       <c r="P76" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="Q76">
         <v>1.57</v>
@@ -16682,7 +16703,7 @@
         <v>0</v>
       </c>
       <c r="AP76">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AQ76">
         <v>0.14</v>
@@ -16810,7 +16831,7 @@
         <v>151</v>
       </c>
       <c r="P77" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Q77">
         <v>2.63</v>
@@ -16891,7 +16912,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ77">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AR77">
         <v>2</v>
@@ -17300,7 +17321,7 @@
         <v>2.33</v>
       </c>
       <c r="AP79">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ79">
         <v>1.86</v>
@@ -17428,7 +17449,7 @@
         <v>88</v>
       </c>
       <c r="P80" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="Q80">
         <v>3.6</v>
@@ -17509,7 +17530,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ80">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AR80">
         <v>2.04</v>
@@ -17634,7 +17655,7 @@
         <v>154</v>
       </c>
       <c r="P81" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="Q81">
         <v>2.6</v>
@@ -17715,7 +17736,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ81">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AR81">
         <v>1.41</v>
@@ -17840,7 +17861,7 @@
         <v>88</v>
       </c>
       <c r="P82" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="Q82">
         <v>4.5</v>
@@ -18124,7 +18145,7 @@
         <v>0.5</v>
       </c>
       <c r="AP83">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ83">
         <v>0.38</v>
@@ -18330,10 +18351,10 @@
         <v>0.8</v>
       </c>
       <c r="AP84">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ84">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AR84">
         <v>2.13</v>
@@ -18458,7 +18479,7 @@
         <v>157</v>
       </c>
       <c r="P85" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="Q85">
         <v>4</v>
@@ -18664,7 +18685,7 @@
         <v>114</v>
       </c>
       <c r="P86" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="Q86">
         <v>5.5</v>
@@ -18742,7 +18763,7 @@
         <v>1.75</v>
       </c>
       <c r="AP86">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ86">
         <v>1.86</v>
@@ -18951,7 +18972,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ87">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR87">
         <v>1.17</v>
@@ -19076,7 +19097,7 @@
         <v>158</v>
       </c>
       <c r="P88" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="Q88">
         <v>1.53</v>
@@ -19360,10 +19381,10 @@
         <v>1.33</v>
       </c>
       <c r="AP89">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AQ89">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR89">
         <v>2.4</v>
@@ -19488,7 +19509,7 @@
         <v>88</v>
       </c>
       <c r="P90" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Q90">
         <v>6</v>
@@ -19566,7 +19587,7 @@
         <v>2.6</v>
       </c>
       <c r="AP90">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ90">
         <v>2.29</v>
@@ -19694,7 +19715,7 @@
         <v>160</v>
       </c>
       <c r="P91" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="Q91">
         <v>2.2</v>
@@ -19772,10 +19793,10 @@
         <v>0.67</v>
       </c>
       <c r="AP91">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AQ91">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AR91">
         <v>1.93</v>
@@ -19981,7 +20002,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ92">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR92">
         <v>1.9</v>
@@ -20106,7 +20127,7 @@
         <v>88</v>
       </c>
       <c r="P93" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="Q93">
         <v>3.5</v>
@@ -20184,7 +20205,7 @@
         <v>0.8</v>
       </c>
       <c r="AP93">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="AQ93">
         <v>1.14</v>
@@ -20518,7 +20539,7 @@
         <v>162</v>
       </c>
       <c r="P95" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="Q95">
         <v>2.88</v>
@@ -20724,7 +20745,7 @@
         <v>163</v>
       </c>
       <c r="P96" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="Q96">
         <v>2.38</v>
@@ -21136,7 +21157,7 @@
         <v>88</v>
       </c>
       <c r="P98" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="Q98">
         <v>5.25</v>
@@ -21342,7 +21363,7 @@
         <v>165</v>
       </c>
       <c r="P99" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q99">
         <v>3.52</v>
@@ -21420,10 +21441,10 @@
         <v>1.33</v>
       </c>
       <c r="AP99">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="AQ99">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AR99">
         <v>1.19</v>
@@ -21548,7 +21569,7 @@
         <v>166</v>
       </c>
       <c r="P100" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="Q100">
         <v>1.79</v>
@@ -21626,10 +21647,10 @@
         <v>1</v>
       </c>
       <c r="AP100">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ100">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR100">
         <v>2.09</v>
@@ -21754,7 +21775,7 @@
         <v>127</v>
       </c>
       <c r="P101" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="Q101">
         <v>5.55</v>
@@ -21832,10 +21853,10 @@
         <v>2</v>
       </c>
       <c r="AP101">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ101">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AR101">
         <v>1.51</v>
@@ -21960,7 +21981,7 @@
         <v>114</v>
       </c>
       <c r="P102" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="Q102">
         <v>2.3</v>
@@ -22578,7 +22599,7 @@
         <v>168</v>
       </c>
       <c r="P105" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="Q105">
         <v>3.54</v>
@@ -22990,7 +23011,7 @@
         <v>169</v>
       </c>
       <c r="P107" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="Q107">
         <v>1.49</v>
@@ -23402,7 +23423,7 @@
         <v>171</v>
       </c>
       <c r="P109" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="Q109">
         <v>5.2</v>
@@ -23895,7 +23916,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ111">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR111">
         <v>1.97</v>
@@ -24020,7 +24041,7 @@
         <v>174</v>
       </c>
       <c r="P112" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24226,7 +24247,7 @@
         <v>175</v>
       </c>
       <c r="P113" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="Q113">
         <v>3.04</v>
@@ -24307,7 +24328,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ113">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR113">
         <v>1.49</v>
@@ -24383,6 +24404,1242 @@
       </c>
       <c r="BP113">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="114" spans="1:68">
+      <c r="A114" s="1">
+        <v>113</v>
+      </c>
+      <c r="B114">
+        <v>7825304</v>
+      </c>
+      <c r="C114" t="s">
+        <v>68</v>
+      </c>
+      <c r="D114" t="s">
+        <v>69</v>
+      </c>
+      <c r="E114" s="2">
+        <v>45833.33333333334</v>
+      </c>
+      <c r="F114">
+        <v>15</v>
+      </c>
+      <c r="G114" t="s">
+        <v>71</v>
+      </c>
+      <c r="H114" t="s">
+        <v>76</v>
+      </c>
+      <c r="I114">
+        <v>2</v>
+      </c>
+      <c r="J114">
+        <v>0</v>
+      </c>
+      <c r="K114">
+        <v>2</v>
+      </c>
+      <c r="L114">
+        <v>3</v>
+      </c>
+      <c r="M114">
+        <v>0</v>
+      </c>
+      <c r="N114">
+        <v>3</v>
+      </c>
+      <c r="O114" t="s">
+        <v>176</v>
+      </c>
+      <c r="P114" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q114">
+        <v>1.8</v>
+      </c>
+      <c r="R114">
+        <v>2.75</v>
+      </c>
+      <c r="S114">
+        <v>6</v>
+      </c>
+      <c r="T114">
+        <v>1.22</v>
+      </c>
+      <c r="U114">
+        <v>4</v>
+      </c>
+      <c r="V114">
+        <v>2</v>
+      </c>
+      <c r="W114">
+        <v>1.73</v>
+      </c>
+      <c r="X114">
+        <v>4.33</v>
+      </c>
+      <c r="Y114">
+        <v>1.2</v>
+      </c>
+      <c r="Z114">
+        <v>1.32</v>
+      </c>
+      <c r="AA114">
+        <v>5.1</v>
+      </c>
+      <c r="AB114">
+        <v>6.7</v>
+      </c>
+      <c r="AC114">
+        <v>1.01</v>
+      </c>
+      <c r="AD114">
+        <v>17</v>
+      </c>
+      <c r="AE114">
+        <v>1.1</v>
+      </c>
+      <c r="AF114">
+        <v>5.2</v>
+      </c>
+      <c r="AG114">
+        <v>1.43</v>
+      </c>
+      <c r="AH114">
+        <v>2.62</v>
+      </c>
+      <c r="AI114">
+        <v>1.62</v>
+      </c>
+      <c r="AJ114">
+        <v>2.2</v>
+      </c>
+      <c r="AK114">
+        <v>1.08</v>
+      </c>
+      <c r="AL114">
+        <v>1.15</v>
+      </c>
+      <c r="AM114">
+        <v>3.05</v>
+      </c>
+      <c r="AN114">
+        <v>2.71</v>
+      </c>
+      <c r="AO114">
+        <v>1.57</v>
+      </c>
+      <c r="AP114">
+        <v>2.75</v>
+      </c>
+      <c r="AQ114">
+        <v>1.38</v>
+      </c>
+      <c r="AR114">
+        <v>2.36</v>
+      </c>
+      <c r="AS114">
+        <v>1.18</v>
+      </c>
+      <c r="AT114">
+        <v>3.54</v>
+      </c>
+      <c r="AU114">
+        <v>7</v>
+      </c>
+      <c r="AV114">
+        <v>7</v>
+      </c>
+      <c r="AW114">
+        <v>12</v>
+      </c>
+      <c r="AX114">
+        <v>5</v>
+      </c>
+      <c r="AY114">
+        <v>19</v>
+      </c>
+      <c r="AZ114">
+        <v>12</v>
+      </c>
+      <c r="BA114">
+        <v>10</v>
+      </c>
+      <c r="BB114">
+        <v>6</v>
+      </c>
+      <c r="BC114">
+        <v>16</v>
+      </c>
+      <c r="BD114">
+        <v>1.26</v>
+      </c>
+      <c r="BE114">
+        <v>8.5</v>
+      </c>
+      <c r="BF114">
+        <v>4.1</v>
+      </c>
+      <c r="BG114">
+        <v>1.19</v>
+      </c>
+      <c r="BH114">
+        <v>4.1</v>
+      </c>
+      <c r="BI114">
+        <v>1.33</v>
+      </c>
+      <c r="BJ114">
+        <v>2.95</v>
+      </c>
+      <c r="BK114">
+        <v>1.55</v>
+      </c>
+      <c r="BL114">
+        <v>2.25</v>
+      </c>
+      <c r="BM114">
+        <v>1.86</v>
+      </c>
+      <c r="BN114">
+        <v>1.82</v>
+      </c>
+      <c r="BO114">
+        <v>2.32</v>
+      </c>
+      <c r="BP114">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="115" spans="1:68">
+      <c r="A115" s="1">
+        <v>114</v>
+      </c>
+      <c r="B115">
+        <v>7825305</v>
+      </c>
+      <c r="C115" t="s">
+        <v>68</v>
+      </c>
+      <c r="D115" t="s">
+        <v>69</v>
+      </c>
+      <c r="E115" s="2">
+        <v>45833.33333333334</v>
+      </c>
+      <c r="F115">
+        <v>15</v>
+      </c>
+      <c r="G115" t="s">
+        <v>73</v>
+      </c>
+      <c r="H115" t="s">
+        <v>74</v>
+      </c>
+      <c r="I115">
+        <v>0</v>
+      </c>
+      <c r="J115">
+        <v>0</v>
+      </c>
+      <c r="K115">
+        <v>0</v>
+      </c>
+      <c r="L115">
+        <v>0</v>
+      </c>
+      <c r="M115">
+        <v>3</v>
+      </c>
+      <c r="N115">
+        <v>3</v>
+      </c>
+      <c r="O115" t="s">
+        <v>88</v>
+      </c>
+      <c r="P115" t="s">
+        <v>247</v>
+      </c>
+      <c r="Q115">
+        <v>3.5</v>
+      </c>
+      <c r="R115">
+        <v>2.4</v>
+      </c>
+      <c r="S115">
+        <v>2.63</v>
+      </c>
+      <c r="T115">
+        <v>1.29</v>
+      </c>
+      <c r="U115">
+        <v>3.5</v>
+      </c>
+      <c r="V115">
+        <v>2.25</v>
+      </c>
+      <c r="W115">
+        <v>1.57</v>
+      </c>
+      <c r="X115">
+        <v>5.5</v>
+      </c>
+      <c r="Y115">
+        <v>1.14</v>
+      </c>
+      <c r="Z115">
+        <v>2.83</v>
+      </c>
+      <c r="AA115">
+        <v>3.62</v>
+      </c>
+      <c r="AB115">
+        <v>2.13</v>
+      </c>
+      <c r="AC115">
+        <v>1.01</v>
+      </c>
+      <c r="AD115">
+        <v>13</v>
+      </c>
+      <c r="AE115">
+        <v>1.12</v>
+      </c>
+      <c r="AF115">
+        <v>4.8</v>
+      </c>
+      <c r="AG115">
+        <v>1.6</v>
+      </c>
+      <c r="AH115">
+        <v>2.1</v>
+      </c>
+      <c r="AI115">
+        <v>1.5</v>
+      </c>
+      <c r="AJ115">
+        <v>2.5</v>
+      </c>
+      <c r="AK115">
+        <v>1.73</v>
+      </c>
+      <c r="AL115">
+        <v>1.25</v>
+      </c>
+      <c r="AM115">
+        <v>1.34</v>
+      </c>
+      <c r="AN115">
+        <v>1</v>
+      </c>
+      <c r="AO115">
+        <v>0.57</v>
+      </c>
+      <c r="AP115">
+        <v>0.88</v>
+      </c>
+      <c r="AQ115">
+        <v>0.88</v>
+      </c>
+      <c r="AR115">
+        <v>1.48</v>
+      </c>
+      <c r="AS115">
+        <v>1.31</v>
+      </c>
+      <c r="AT115">
+        <v>2.79</v>
+      </c>
+      <c r="AU115">
+        <v>4</v>
+      </c>
+      <c r="AV115">
+        <v>8</v>
+      </c>
+      <c r="AW115">
+        <v>5</v>
+      </c>
+      <c r="AX115">
+        <v>4</v>
+      </c>
+      <c r="AY115">
+        <v>9</v>
+      </c>
+      <c r="AZ115">
+        <v>12</v>
+      </c>
+      <c r="BA115">
+        <v>1</v>
+      </c>
+      <c r="BB115">
+        <v>6</v>
+      </c>
+      <c r="BC115">
+        <v>7</v>
+      </c>
+      <c r="BD115">
+        <v>2.33</v>
+      </c>
+      <c r="BE115">
+        <v>6.5</v>
+      </c>
+      <c r="BF115">
+        <v>1.72</v>
+      </c>
+      <c r="BG115">
+        <v>1.26</v>
+      </c>
+      <c r="BH115">
+        <v>3.4</v>
+      </c>
+      <c r="BI115">
+        <v>1.44</v>
+      </c>
+      <c r="BJ115">
+        <v>2.55</v>
+      </c>
+      <c r="BK115">
+        <v>1.72</v>
+      </c>
+      <c r="BL115">
+        <v>1.98</v>
+      </c>
+      <c r="BM115">
+        <v>2.12</v>
+      </c>
+      <c r="BN115">
+        <v>1.62</v>
+      </c>
+      <c r="BO115">
+        <v>2.65</v>
+      </c>
+      <c r="BP115">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="116" spans="1:68">
+      <c r="A116" s="1">
+        <v>115</v>
+      </c>
+      <c r="B116">
+        <v>7825307</v>
+      </c>
+      <c r="C116" t="s">
+        <v>68</v>
+      </c>
+      <c r="D116" t="s">
+        <v>69</v>
+      </c>
+      <c r="E116" s="2">
+        <v>45833.35763888889</v>
+      </c>
+      <c r="F116">
+        <v>15</v>
+      </c>
+      <c r="G116" t="s">
+        <v>85</v>
+      </c>
+      <c r="H116" t="s">
+        <v>79</v>
+      </c>
+      <c r="I116">
+        <v>0</v>
+      </c>
+      <c r="J116">
+        <v>0</v>
+      </c>
+      <c r="K116">
+        <v>0</v>
+      </c>
+      <c r="L116">
+        <v>1</v>
+      </c>
+      <c r="M116">
+        <v>0</v>
+      </c>
+      <c r="N116">
+        <v>1</v>
+      </c>
+      <c r="O116" t="s">
+        <v>177</v>
+      </c>
+      <c r="P116" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q116">
+        <v>3.5</v>
+      </c>
+      <c r="R116">
+        <v>2.25</v>
+      </c>
+      <c r="S116">
+        <v>2.88</v>
+      </c>
+      <c r="T116">
+        <v>1.33</v>
+      </c>
+      <c r="U116">
+        <v>3.25</v>
+      </c>
+      <c r="V116">
+        <v>2.63</v>
+      </c>
+      <c r="W116">
+        <v>1.44</v>
+      </c>
+      <c r="X116">
+        <v>6.5</v>
+      </c>
+      <c r="Y116">
+        <v>1.11</v>
+      </c>
+      <c r="Z116">
+        <v>2.9</v>
+      </c>
+      <c r="AA116">
+        <v>3.53</v>
+      </c>
+      <c r="AB116">
+        <v>2.12</v>
+      </c>
+      <c r="AC116">
+        <v>1</v>
+      </c>
+      <c r="AD116">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AE116">
+        <v>1.21</v>
+      </c>
+      <c r="AF116">
+        <v>3.6</v>
+      </c>
+      <c r="AG116">
+        <v>1.76</v>
+      </c>
+      <c r="AH116">
+        <v>1.94</v>
+      </c>
+      <c r="AI116">
+        <v>1.62</v>
+      </c>
+      <c r="AJ116">
+        <v>2.2</v>
+      </c>
+      <c r="AK116">
+        <v>1.62</v>
+      </c>
+      <c r="AL116">
+        <v>1.28</v>
+      </c>
+      <c r="AM116">
+        <v>1.38</v>
+      </c>
+      <c r="AN116">
+        <v>0.33</v>
+      </c>
+      <c r="AO116">
+        <v>0.83</v>
+      </c>
+      <c r="AP116">
+        <v>0.71</v>
+      </c>
+      <c r="AQ116">
+        <v>0.71</v>
+      </c>
+      <c r="AR116">
+        <v>1.24</v>
+      </c>
+      <c r="AS116">
+        <v>1.2</v>
+      </c>
+      <c r="AT116">
+        <v>2.44</v>
+      </c>
+      <c r="AU116">
+        <v>6</v>
+      </c>
+      <c r="AV116">
+        <v>5</v>
+      </c>
+      <c r="AW116">
+        <v>5</v>
+      </c>
+      <c r="AX116">
+        <v>7</v>
+      </c>
+      <c r="AY116">
+        <v>11</v>
+      </c>
+      <c r="AZ116">
+        <v>12</v>
+      </c>
+      <c r="BA116">
+        <v>6</v>
+      </c>
+      <c r="BB116">
+        <v>4</v>
+      </c>
+      <c r="BC116">
+        <v>10</v>
+      </c>
+      <c r="BD116">
+        <v>2.12</v>
+      </c>
+      <c r="BE116">
+        <v>6.4</v>
+      </c>
+      <c r="BF116">
+        <v>1.86</v>
+      </c>
+      <c r="BG116">
+        <v>1.34</v>
+      </c>
+      <c r="BH116">
+        <v>2.9</v>
+      </c>
+      <c r="BI116">
+        <v>1.58</v>
+      </c>
+      <c r="BJ116">
+        <v>2.18</v>
+      </c>
+      <c r="BK116">
+        <v>1.96</v>
+      </c>
+      <c r="BL116">
+        <v>1.74</v>
+      </c>
+      <c r="BM116">
+        <v>2.45</v>
+      </c>
+      <c r="BN116">
+        <v>1.48</v>
+      </c>
+      <c r="BO116">
+        <v>3.15</v>
+      </c>
+      <c r="BP116">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="117" spans="1:68">
+      <c r="A117" s="1">
+        <v>116</v>
+      </c>
+      <c r="B117">
+        <v>7825306</v>
+      </c>
+      <c r="C117" t="s">
+        <v>68</v>
+      </c>
+      <c r="D117" t="s">
+        <v>69</v>
+      </c>
+      <c r="E117" s="2">
+        <v>45833.35763888889</v>
+      </c>
+      <c r="F117">
+        <v>15</v>
+      </c>
+      <c r="G117" t="s">
+        <v>75</v>
+      </c>
+      <c r="H117" t="s">
+        <v>80</v>
+      </c>
+      <c r="I117">
+        <v>1</v>
+      </c>
+      <c r="J117">
+        <v>0</v>
+      </c>
+      <c r="K117">
+        <v>1</v>
+      </c>
+      <c r="L117">
+        <v>3</v>
+      </c>
+      <c r="M117">
+        <v>1</v>
+      </c>
+      <c r="N117">
+        <v>4</v>
+      </c>
+      <c r="O117" t="s">
+        <v>178</v>
+      </c>
+      <c r="P117" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q117">
+        <v>1.95</v>
+      </c>
+      <c r="R117">
+        <v>2.75</v>
+      </c>
+      <c r="S117">
+        <v>5</v>
+      </c>
+      <c r="T117">
+        <v>1.2</v>
+      </c>
+      <c r="U117">
+        <v>4.33</v>
+      </c>
+      <c r="V117">
+        <v>2</v>
+      </c>
+      <c r="W117">
+        <v>1.73</v>
+      </c>
+      <c r="X117">
+        <v>4.33</v>
+      </c>
+      <c r="Y117">
+        <v>1.2</v>
+      </c>
+      <c r="Z117">
+        <v>1.56</v>
+      </c>
+      <c r="AA117">
+        <v>4.3</v>
+      </c>
+      <c r="AB117">
+        <v>4.4</v>
+      </c>
+      <c r="AC117">
+        <v>1.01</v>
+      </c>
+      <c r="AD117">
+        <v>23</v>
+      </c>
+      <c r="AE117">
+        <v>1.07</v>
+      </c>
+      <c r="AF117">
+        <v>5.9</v>
+      </c>
+      <c r="AG117">
+        <v>1.4</v>
+      </c>
+      <c r="AH117">
+        <v>2.73</v>
+      </c>
+      <c r="AI117">
+        <v>1.53</v>
+      </c>
+      <c r="AJ117">
+        <v>2.38</v>
+      </c>
+      <c r="AK117">
+        <v>1.14</v>
+      </c>
+      <c r="AL117">
+        <v>1.17</v>
+      </c>
+      <c r="AM117">
+        <v>2.55</v>
+      </c>
+      <c r="AN117">
+        <v>1.57</v>
+      </c>
+      <c r="AO117">
+        <v>1</v>
+      </c>
+      <c r="AP117">
+        <v>1.75</v>
+      </c>
+      <c r="AQ117">
+        <v>0.88</v>
+      </c>
+      <c r="AR117">
+        <v>1.9</v>
+      </c>
+      <c r="AS117">
+        <v>1.09</v>
+      </c>
+      <c r="AT117">
+        <v>2.99</v>
+      </c>
+      <c r="AU117">
+        <v>18</v>
+      </c>
+      <c r="AV117">
+        <v>6</v>
+      </c>
+      <c r="AW117">
+        <v>16</v>
+      </c>
+      <c r="AX117">
+        <v>6</v>
+      </c>
+      <c r="AY117">
+        <v>34</v>
+      </c>
+      <c r="AZ117">
+        <v>12</v>
+      </c>
+      <c r="BA117">
+        <v>7</v>
+      </c>
+      <c r="BB117">
+        <v>4</v>
+      </c>
+      <c r="BC117">
+        <v>11</v>
+      </c>
+      <c r="BD117">
+        <v>1.4</v>
+      </c>
+      <c r="BE117">
+        <v>7.5</v>
+      </c>
+      <c r="BF117">
+        <v>3.2</v>
+      </c>
+      <c r="BG117">
+        <v>1.19</v>
+      </c>
+      <c r="BH117">
+        <v>4.1</v>
+      </c>
+      <c r="BI117">
+        <v>1.34</v>
+      </c>
+      <c r="BJ117">
+        <v>2.9</v>
+      </c>
+      <c r="BK117">
+        <v>1.58</v>
+      </c>
+      <c r="BL117">
+        <v>2.18</v>
+      </c>
+      <c r="BM117">
+        <v>1.94</v>
+      </c>
+      <c r="BN117">
+        <v>1.76</v>
+      </c>
+      <c r="BO117">
+        <v>2.4</v>
+      </c>
+      <c r="BP117">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="118" spans="1:68">
+      <c r="A118" s="1">
+        <v>117</v>
+      </c>
+      <c r="B118">
+        <v>7825308</v>
+      </c>
+      <c r="C118" t="s">
+        <v>68</v>
+      </c>
+      <c r="D118" t="s">
+        <v>69</v>
+      </c>
+      <c r="E118" s="2">
+        <v>45833.35763888889</v>
+      </c>
+      <c r="F118">
+        <v>15</v>
+      </c>
+      <c r="G118" t="s">
+        <v>78</v>
+      </c>
+      <c r="H118" t="s">
+        <v>84</v>
+      </c>
+      <c r="I118">
+        <v>0</v>
+      </c>
+      <c r="J118">
+        <v>2</v>
+      </c>
+      <c r="K118">
+        <v>2</v>
+      </c>
+      <c r="L118">
+        <v>0</v>
+      </c>
+      <c r="M118">
+        <v>4</v>
+      </c>
+      <c r="N118">
+        <v>4</v>
+      </c>
+      <c r="O118" t="s">
+        <v>88</v>
+      </c>
+      <c r="P118" t="s">
+        <v>249</v>
+      </c>
+      <c r="Q118">
+        <v>5.5</v>
+      </c>
+      <c r="R118">
+        <v>2.63</v>
+      </c>
+      <c r="S118">
+        <v>1.95</v>
+      </c>
+      <c r="T118">
+        <v>1.22</v>
+      </c>
+      <c r="U118">
+        <v>4</v>
+      </c>
+      <c r="V118">
+        <v>2.1</v>
+      </c>
+      <c r="W118">
+        <v>1.67</v>
+      </c>
+      <c r="X118">
+        <v>4.5</v>
+      </c>
+      <c r="Y118">
+        <v>1.18</v>
+      </c>
+      <c r="Z118">
+        <v>5.4</v>
+      </c>
+      <c r="AA118">
+        <v>4.7</v>
+      </c>
+      <c r="AB118">
+        <v>1.43</v>
+      </c>
+      <c r="AC118">
+        <v>1.01</v>
+      </c>
+      <c r="AD118">
+        <v>17</v>
+      </c>
+      <c r="AE118">
+        <v>1.09</v>
+      </c>
+      <c r="AF118">
+        <v>5.4</v>
+      </c>
+      <c r="AG118">
+        <v>1.43</v>
+      </c>
+      <c r="AH118">
+        <v>2.62</v>
+      </c>
+      <c r="AI118">
+        <v>1.57</v>
+      </c>
+      <c r="AJ118">
+        <v>2.25</v>
+      </c>
+      <c r="AK118">
+        <v>2.61</v>
+      </c>
+      <c r="AL118">
+        <v>1.18</v>
+      </c>
+      <c r="AM118">
+        <v>1.12</v>
+      </c>
+      <c r="AN118">
+        <v>1.29</v>
+      </c>
+      <c r="AO118">
+        <v>1.86</v>
+      </c>
+      <c r="AP118">
+        <v>1.13</v>
+      </c>
+      <c r="AQ118">
+        <v>2</v>
+      </c>
+      <c r="AR118">
+        <v>1.81</v>
+      </c>
+      <c r="AS118">
+        <v>1.46</v>
+      </c>
+      <c r="AT118">
+        <v>3.27</v>
+      </c>
+      <c r="AU118">
+        <v>5</v>
+      </c>
+      <c r="AV118">
+        <v>8</v>
+      </c>
+      <c r="AW118">
+        <v>4</v>
+      </c>
+      <c r="AX118">
+        <v>4</v>
+      </c>
+      <c r="AY118">
+        <v>9</v>
+      </c>
+      <c r="AZ118">
+        <v>12</v>
+      </c>
+      <c r="BA118">
+        <v>5</v>
+      </c>
+      <c r="BB118">
+        <v>6</v>
+      </c>
+      <c r="BC118">
+        <v>11</v>
+      </c>
+      <c r="BD118">
+        <v>3.15</v>
+      </c>
+      <c r="BE118">
+        <v>7</v>
+      </c>
+      <c r="BF118">
+        <v>1.43</v>
+      </c>
+      <c r="BG118">
+        <v>1.19</v>
+      </c>
+      <c r="BH118">
+        <v>4.1</v>
+      </c>
+      <c r="BI118">
+        <v>1.33</v>
+      </c>
+      <c r="BJ118">
+        <v>2.95</v>
+      </c>
+      <c r="BK118">
+        <v>1.53</v>
+      </c>
+      <c r="BL118">
+        <v>2.3</v>
+      </c>
+      <c r="BM118">
+        <v>1.84</v>
+      </c>
+      <c r="BN118">
+        <v>1.84</v>
+      </c>
+      <c r="BO118">
+        <v>2.3</v>
+      </c>
+      <c r="BP118">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="119" spans="1:68">
+      <c r="A119" s="1">
+        <v>118</v>
+      </c>
+      <c r="B119">
+        <v>7825309</v>
+      </c>
+      <c r="C119" t="s">
+        <v>68</v>
+      </c>
+      <c r="D119" t="s">
+        <v>69</v>
+      </c>
+      <c r="E119" s="2">
+        <v>45833.375</v>
+      </c>
+      <c r="F119">
+        <v>15</v>
+      </c>
+      <c r="G119" t="s">
+        <v>70</v>
+      </c>
+      <c r="H119" t="s">
+        <v>81</v>
+      </c>
+      <c r="I119">
+        <v>2</v>
+      </c>
+      <c r="J119">
+        <v>0</v>
+      </c>
+      <c r="K119">
+        <v>2</v>
+      </c>
+      <c r="L119">
+        <v>5</v>
+      </c>
+      <c r="M119">
+        <v>0</v>
+      </c>
+      <c r="N119">
+        <v>5</v>
+      </c>
+      <c r="O119" t="s">
+        <v>179</v>
+      </c>
+      <c r="P119" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q119">
+        <v>1.53</v>
+      </c>
+      <c r="R119">
+        <v>3</v>
+      </c>
+      <c r="S119">
+        <v>10</v>
+      </c>
+      <c r="T119">
+        <v>1.22</v>
+      </c>
+      <c r="U119">
+        <v>4</v>
+      </c>
+      <c r="V119">
+        <v>2</v>
+      </c>
+      <c r="W119">
+        <v>1.73</v>
+      </c>
+      <c r="X119">
+        <v>4.33</v>
+      </c>
+      <c r="Y119">
+        <v>1.2</v>
+      </c>
+      <c r="Z119">
+        <v>1.18</v>
+      </c>
+      <c r="AA119">
+        <v>7.06</v>
+      </c>
+      <c r="AB119">
+        <v>12.52</v>
+      </c>
+      <c r="AC119">
+        <v>1.01</v>
+      </c>
+      <c r="AD119">
+        <v>17.5</v>
+      </c>
+      <c r="AE119">
+        <v>1.08</v>
+      </c>
+      <c r="AF119">
+        <v>5.65</v>
+      </c>
+      <c r="AG119">
+        <v>1.4</v>
+      </c>
+      <c r="AH119">
+        <v>2.88</v>
+      </c>
+      <c r="AI119">
+        <v>2</v>
+      </c>
+      <c r="AJ119">
+        <v>1.75</v>
+      </c>
+      <c r="AK119">
+        <v>1.01</v>
+      </c>
+      <c r="AL119">
+        <v>1.08</v>
+      </c>
+      <c r="AM119">
+        <v>4.7</v>
+      </c>
+      <c r="AN119">
+        <v>2</v>
+      </c>
+      <c r="AO119">
+        <v>0.57</v>
+      </c>
+      <c r="AP119">
+        <v>2.13</v>
+      </c>
+      <c r="AQ119">
+        <v>0.5</v>
+      </c>
+      <c r="AR119">
+        <v>2.15</v>
+      </c>
+      <c r="AS119">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AT119">
+        <v>3.09</v>
+      </c>
+      <c r="AU119">
+        <v>9</v>
+      </c>
+      <c r="AV119">
+        <v>2</v>
+      </c>
+      <c r="AW119">
+        <v>1</v>
+      </c>
+      <c r="AX119">
+        <v>1</v>
+      </c>
+      <c r="AY119">
+        <v>10</v>
+      </c>
+      <c r="AZ119">
+        <v>3</v>
+      </c>
+      <c r="BA119">
+        <v>8</v>
+      </c>
+      <c r="BB119">
+        <v>2</v>
+      </c>
+      <c r="BC119">
+        <v>10</v>
+      </c>
+      <c r="BD119">
+        <v>1.16</v>
+      </c>
+      <c r="BE119">
+        <v>10</v>
+      </c>
+      <c r="BF119">
+        <v>5.4</v>
+      </c>
+      <c r="BG119">
+        <v>1.21</v>
+      </c>
+      <c r="BH119">
+        <v>3.8</v>
+      </c>
+      <c r="BI119">
+        <v>1.38</v>
+      </c>
+      <c r="BJ119">
+        <v>2.75</v>
+      </c>
+      <c r="BK119">
+        <v>1.63</v>
+      </c>
+      <c r="BL119">
+        <v>2.12</v>
+      </c>
+      <c r="BM119">
+        <v>1.96</v>
+      </c>
+      <c r="BN119">
+        <v>1.73</v>
+      </c>
+      <c r="BO119">
+        <v>2.43</v>
+      </c>
+      <c r="BP119">
+        <v>1.48</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="253">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -541,7 +541,7 @@
     <t>['70']</t>
   </si>
   <si>
-    <t>['49']</t>
+    <t>['50']</t>
   </si>
   <si>
     <t>['42', '4504', '9005']</t>
@@ -554,6 +554,9 @@
   </si>
   <si>
     <t>['9', '16', '62', '75', '83']</t>
+  </si>
+  <si>
+    <t>['18', '4501', '9004']</t>
   </si>
   <si>
     <t>['53', '79']</t>
@@ -724,6 +727,9 @@
     <t>['3', '69']</t>
   </si>
   <si>
+    <t>['49']</t>
+  </si>
+  <si>
     <t>['14', '34']</t>
   </si>
   <si>
@@ -764,6 +770,9 @@
   </si>
   <si>
     <t>['21', '45', '55', '69']</t>
+  </si>
+  <si>
+    <t>['29']</t>
   </si>
 </sst>
 </file>
@@ -1125,7 +1134,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP119"/>
+  <dimension ref="A1:BP121"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1793,7 +1802,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -1871,7 +1880,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AQ4">
         <v>2</v>
@@ -1999,7 +2008,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q5">
         <v>2.85</v>
@@ -2205,7 +2214,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q6">
         <v>2.2</v>
@@ -2286,7 +2295,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ6">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2492,7 +2501,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ7">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2617,7 +2626,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q8">
         <v>2.04</v>
@@ -2823,7 +2832,7 @@
         <v>92</v>
       </c>
       <c r="P9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q9">
         <v>1.5</v>
@@ -2901,7 +2910,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ9">
         <v>0.5</v>
@@ -3029,7 +3038,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q10">
         <v>2.1</v>
@@ -3110,7 +3119,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ10">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR10">
         <v>2.21</v>
@@ -3313,7 +3322,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ11">
         <v>0.38</v>
@@ -3441,7 +3450,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q12">
         <v>3.1</v>
@@ -3647,7 +3656,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -3728,7 +3737,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ13">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3853,7 +3862,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q14">
         <v>2.13</v>
@@ -4059,7 +4068,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q15">
         <v>3.2</v>
@@ -4137,7 +4146,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AQ15">
         <v>0.88</v>
@@ -4265,7 +4274,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q16">
         <v>1.78</v>
@@ -4677,7 +4686,7 @@
         <v>100</v>
       </c>
       <c r="P18" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q18">
         <v>5.5</v>
@@ -4883,7 +4892,7 @@
         <v>88</v>
       </c>
       <c r="P19" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q19">
         <v>3.75</v>
@@ -5089,7 +5098,7 @@
         <v>101</v>
       </c>
       <c r="P20" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q20">
         <v>3.25</v>
@@ -5707,7 +5716,7 @@
         <v>104</v>
       </c>
       <c r="P23" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q23">
         <v>4</v>
@@ -5913,7 +5922,7 @@
         <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q24">
         <v>4.75</v>
@@ -6119,7 +6128,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -6325,7 +6334,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q26">
         <v>2.88</v>
@@ -6943,7 +6952,7 @@
         <v>110</v>
       </c>
       <c r="P29" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q29">
         <v>1.83</v>
@@ -7230,7 +7239,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ30">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR30">
         <v>1.32</v>
@@ -7355,7 +7364,7 @@
         <v>88</v>
       </c>
       <c r="P31" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q31">
         <v>2.9</v>
@@ -7561,7 +7570,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q32">
         <v>3.42</v>
@@ -7767,7 +7776,7 @@
         <v>113</v>
       </c>
       <c r="P33" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q33">
         <v>1.56</v>
@@ -7845,7 +7854,7 @@
         <v>1</v>
       </c>
       <c r="AP33">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ33">
         <v>0.43</v>
@@ -7973,7 +7982,7 @@
         <v>114</v>
       </c>
       <c r="P34" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q34">
         <v>3.25</v>
@@ -8054,7 +8063,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ34">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR34">
         <v>2.26</v>
@@ -8179,7 +8188,7 @@
         <v>115</v>
       </c>
       <c r="P35" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q35">
         <v>4.25</v>
@@ -8385,7 +8394,7 @@
         <v>116</v>
       </c>
       <c r="P36" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q36">
         <v>3.15</v>
@@ -8591,7 +8600,7 @@
         <v>117</v>
       </c>
       <c r="P37" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q37">
         <v>2.75</v>
@@ -8878,7 +8887,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ38">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR38">
         <v>2.39</v>
@@ -9003,7 +9012,7 @@
         <v>119</v>
       </c>
       <c r="P39" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q39">
         <v>2.88</v>
@@ -9081,7 +9090,7 @@
         <v>3</v>
       </c>
       <c r="AP39">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ39">
         <v>1.86</v>
@@ -9493,7 +9502,7 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AQ41">
         <v>0.14</v>
@@ -9827,7 +9836,7 @@
         <v>123</v>
       </c>
       <c r="P43" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q43">
         <v>3</v>
@@ -10033,7 +10042,7 @@
         <v>124</v>
       </c>
       <c r="P44" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q44">
         <v>3.2</v>
@@ -10239,7 +10248,7 @@
         <v>88</v>
       </c>
       <c r="P45" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q45">
         <v>7.5</v>
@@ -10651,7 +10660,7 @@
         <v>126</v>
       </c>
       <c r="P47" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q47">
         <v>1.95</v>
@@ -10857,7 +10866,7 @@
         <v>127</v>
       </c>
       <c r="P48" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q48">
         <v>3.7</v>
@@ -11063,7 +11072,7 @@
         <v>128</v>
       </c>
       <c r="P49" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q49">
         <v>4.33</v>
@@ -11269,7 +11278,7 @@
         <v>129</v>
       </c>
       <c r="P50" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q50">
         <v>2.65</v>
@@ -11475,7 +11484,7 @@
         <v>130</v>
       </c>
       <c r="P51" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q51">
         <v>4.15</v>
@@ -11762,7 +11771,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ52">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR52">
         <v>2.18</v>
@@ -11887,7 +11896,7 @@
         <v>132</v>
       </c>
       <c r="P53" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q53">
         <v>1.8</v>
@@ -12093,7 +12102,7 @@
         <v>104</v>
       </c>
       <c r="P54" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q54">
         <v>1.71</v>
@@ -12299,7 +12308,7 @@
         <v>133</v>
       </c>
       <c r="P55" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q55">
         <v>1.45</v>
@@ -12711,7 +12720,7 @@
         <v>135</v>
       </c>
       <c r="P57" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -13204,7 +13213,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ59">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR59">
         <v>1.22</v>
@@ -13947,7 +13956,7 @@
         <v>140</v>
       </c>
       <c r="P63" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q63">
         <v>2.88</v>
@@ -14025,7 +14034,7 @@
         <v>2.33</v>
       </c>
       <c r="AP63">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ63">
         <v>2.29</v>
@@ -14234,7 +14243,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ64">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR64">
         <v>2.07</v>
@@ -14359,7 +14368,7 @@
         <v>142</v>
       </c>
       <c r="P65" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q65">
         <v>4.5</v>
@@ -14437,7 +14446,7 @@
         <v>2</v>
       </c>
       <c r="AP65">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AQ65">
         <v>2.33</v>
@@ -14565,7 +14574,7 @@
         <v>143</v>
       </c>
       <c r="P66" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q66">
         <v>5.2</v>
@@ -14771,7 +14780,7 @@
         <v>144</v>
       </c>
       <c r="P67" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q67">
         <v>3.22</v>
@@ -14852,7 +14861,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ67">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR67">
         <v>1.64</v>
@@ -14977,7 +14986,7 @@
         <v>88</v>
       </c>
       <c r="P68" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q68">
         <v>3.24</v>
@@ -15183,7 +15192,7 @@
         <v>145</v>
       </c>
       <c r="P69" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q69">
         <v>3.18</v>
@@ -15389,7 +15398,7 @@
         <v>124</v>
       </c>
       <c r="P70" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q70">
         <v>3.22</v>
@@ -15595,7 +15604,7 @@
         <v>146</v>
       </c>
       <c r="P71" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q71">
         <v>2.1</v>
@@ -15801,7 +15810,7 @@
         <v>147</v>
       </c>
       <c r="P72" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q72">
         <v>2.75</v>
@@ -16213,7 +16222,7 @@
         <v>148</v>
       </c>
       <c r="P74" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q74">
         <v>2.2</v>
@@ -16419,7 +16428,7 @@
         <v>149</v>
       </c>
       <c r="P75" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -16625,7 +16634,7 @@
         <v>150</v>
       </c>
       <c r="P76" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q76">
         <v>1.57</v>
@@ -16831,7 +16840,7 @@
         <v>151</v>
       </c>
       <c r="P77" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q77">
         <v>2.63</v>
@@ -16909,7 +16918,7 @@
         <v>1.5</v>
       </c>
       <c r="AP77">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ77">
         <v>2</v>
@@ -17449,7 +17458,7 @@
         <v>88</v>
       </c>
       <c r="P80" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q80">
         <v>3.6</v>
@@ -17655,7 +17664,7 @@
         <v>154</v>
       </c>
       <c r="P81" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q81">
         <v>2.6</v>
@@ -17861,7 +17870,7 @@
         <v>88</v>
       </c>
       <c r="P82" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q82">
         <v>4.5</v>
@@ -18479,7 +18488,7 @@
         <v>157</v>
       </c>
       <c r="P85" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q85">
         <v>4</v>
@@ -18557,7 +18566,7 @@
         <v>2.25</v>
       </c>
       <c r="AP85">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AQ85">
         <v>1.43</v>
@@ -18685,7 +18694,7 @@
         <v>114</v>
       </c>
       <c r="P86" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q86">
         <v>5.5</v>
@@ -19097,7 +19106,7 @@
         <v>158</v>
       </c>
       <c r="P88" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q88">
         <v>1.53</v>
@@ -19175,7 +19184,7 @@
         <v>0.2</v>
       </c>
       <c r="AP88">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ88">
         <v>0.14</v>
@@ -19509,7 +19518,7 @@
         <v>88</v>
       </c>
       <c r="P90" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q90">
         <v>6</v>
@@ -19715,7 +19724,7 @@
         <v>160</v>
       </c>
       <c r="P91" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q91">
         <v>2.2</v>
@@ -19921,7 +19930,7 @@
         <v>161</v>
       </c>
       <c r="P92" t="s">
-        <v>175</v>
+        <v>237</v>
       </c>
       <c r="Q92">
         <v>1.8</v>
@@ -20127,7 +20136,7 @@
         <v>88</v>
       </c>
       <c r="P93" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q93">
         <v>3.5</v>
@@ -20208,7 +20217,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ93">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR93">
         <v>1.27</v>
@@ -20539,7 +20548,7 @@
         <v>162</v>
       </c>
       <c r="P95" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q95">
         <v>2.88</v>
@@ -20620,7 +20629,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ95">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR95">
         <v>2.07</v>
@@ -20745,7 +20754,7 @@
         <v>163</v>
       </c>
       <c r="P96" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q96">
         <v>2.38</v>
@@ -20826,7 +20835,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ96">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR96">
         <v>1.59</v>
@@ -21029,7 +21038,7 @@
         <v>0.6</v>
       </c>
       <c r="AP97">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AQ97">
         <v>0.43</v>
@@ -21157,7 +21166,7 @@
         <v>88</v>
       </c>
       <c r="P98" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q98">
         <v>5.25</v>
@@ -21363,7 +21372,7 @@
         <v>165</v>
       </c>
       <c r="P99" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q99">
         <v>3.52</v>
@@ -21569,7 +21578,7 @@
         <v>166</v>
       </c>
       <c r="P100" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q100">
         <v>1.79</v>
@@ -21775,7 +21784,7 @@
         <v>127</v>
       </c>
       <c r="P101" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q101">
         <v>5.55</v>
@@ -21981,7 +21990,7 @@
         <v>114</v>
       </c>
       <c r="P102" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q102">
         <v>2.3</v>
@@ -22059,7 +22068,7 @@
         <v>1.8</v>
       </c>
       <c r="AP102">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ102">
         <v>1.43</v>
@@ -22599,7 +22608,7 @@
         <v>168</v>
       </c>
       <c r="P105" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q105">
         <v>3.54</v>
@@ -23011,7 +23020,7 @@
         <v>169</v>
       </c>
       <c r="P107" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q107">
         <v>1.49</v>
@@ -23423,7 +23432,7 @@
         <v>171</v>
       </c>
       <c r="P109" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q109">
         <v>5.2</v>
@@ -24041,7 +24050,7 @@
         <v>174</v>
       </c>
       <c r="P112" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24247,7 +24256,7 @@
         <v>175</v>
       </c>
       <c r="P113" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q113">
         <v>3.04</v>
@@ -24659,7 +24668,7 @@
         <v>88</v>
       </c>
       <c r="P115" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q115">
         <v>3.5</v>
@@ -25071,7 +25080,7 @@
         <v>178</v>
       </c>
       <c r="P117" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q117">
         <v>1.95</v>
@@ -25277,7 +25286,7 @@
         <v>88</v>
       </c>
       <c r="P118" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q118">
         <v>5.5</v>
@@ -25640,6 +25649,418 @@
       </c>
       <c r="BP119">
         <v>1.48</v>
+      </c>
+    </row>
+    <row r="120" spans="1:68">
+      <c r="A120" s="1">
+        <v>119</v>
+      </c>
+      <c r="B120">
+        <v>7825310</v>
+      </c>
+      <c r="C120" t="s">
+        <v>68</v>
+      </c>
+      <c r="D120" t="s">
+        <v>69</v>
+      </c>
+      <c r="E120" s="2">
+        <v>45834.35763888889</v>
+      </c>
+      <c r="F120">
+        <v>15</v>
+      </c>
+      <c r="G120" t="s">
+        <v>77</v>
+      </c>
+      <c r="H120" t="s">
+        <v>82</v>
+      </c>
+      <c r="I120">
+        <v>2</v>
+      </c>
+      <c r="J120">
+        <v>0</v>
+      </c>
+      <c r="K120">
+        <v>2</v>
+      </c>
+      <c r="L120">
+        <v>3</v>
+      </c>
+      <c r="M120">
+        <v>0</v>
+      </c>
+      <c r="N120">
+        <v>3</v>
+      </c>
+      <c r="O120" t="s">
+        <v>180</v>
+      </c>
+      <c r="P120" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q120">
+        <v>1.73</v>
+      </c>
+      <c r="R120">
+        <v>2.88</v>
+      </c>
+      <c r="S120">
+        <v>7</v>
+      </c>
+      <c r="T120">
+        <v>1.22</v>
+      </c>
+      <c r="U120">
+        <v>4</v>
+      </c>
+      <c r="V120">
+        <v>2</v>
+      </c>
+      <c r="W120">
+        <v>1.73</v>
+      </c>
+      <c r="X120">
+        <v>4.33</v>
+      </c>
+      <c r="Y120">
+        <v>1.2</v>
+      </c>
+      <c r="Z120">
+        <v>1.3</v>
+      </c>
+      <c r="AA120">
+        <v>5.2</v>
+      </c>
+      <c r="AB120">
+        <v>7.1</v>
+      </c>
+      <c r="AC120">
+        <v>1.01</v>
+      </c>
+      <c r="AD120">
+        <v>17</v>
+      </c>
+      <c r="AE120">
+        <v>1.09</v>
+      </c>
+      <c r="AF120">
+        <v>5.25</v>
+      </c>
+      <c r="AG120">
+        <v>1.44</v>
+      </c>
+      <c r="AH120">
+        <v>2.59</v>
+      </c>
+      <c r="AI120">
+        <v>1.7</v>
+      </c>
+      <c r="AJ120">
+        <v>2.05</v>
+      </c>
+      <c r="AK120">
+        <v>1.08</v>
+      </c>
+      <c r="AL120">
+        <v>1.17</v>
+      </c>
+      <c r="AM120">
+        <v>3.2</v>
+      </c>
+      <c r="AN120">
+        <v>1.75</v>
+      </c>
+      <c r="AO120">
+        <v>0.57</v>
+      </c>
+      <c r="AP120">
+        <v>1.89</v>
+      </c>
+      <c r="AQ120">
+        <v>0.5</v>
+      </c>
+      <c r="AR120">
+        <v>2.09</v>
+      </c>
+      <c r="AS120">
+        <v>1.27</v>
+      </c>
+      <c r="AT120">
+        <v>3.36</v>
+      </c>
+      <c r="AU120">
+        <v>4</v>
+      </c>
+      <c r="AV120">
+        <v>3</v>
+      </c>
+      <c r="AW120">
+        <v>6</v>
+      </c>
+      <c r="AX120">
+        <v>8</v>
+      </c>
+      <c r="AY120">
+        <v>10</v>
+      </c>
+      <c r="AZ120">
+        <v>11</v>
+      </c>
+      <c r="BA120">
+        <v>7</v>
+      </c>
+      <c r="BB120">
+        <v>3</v>
+      </c>
+      <c r="BC120">
+        <v>10</v>
+      </c>
+      <c r="BD120">
+        <v>1.32</v>
+      </c>
+      <c r="BE120">
+        <v>7.5</v>
+      </c>
+      <c r="BF120">
+        <v>3.65</v>
+      </c>
+      <c r="BG120">
+        <v>1.22</v>
+      </c>
+      <c r="BH120">
+        <v>3.7</v>
+      </c>
+      <c r="BI120">
+        <v>1.4</v>
+      </c>
+      <c r="BJ120">
+        <v>2.7</v>
+      </c>
+      <c r="BK120">
+        <v>1.65</v>
+      </c>
+      <c r="BL120">
+        <v>2.08</v>
+      </c>
+      <c r="BM120">
+        <v>2</v>
+      </c>
+      <c r="BN120">
+        <v>1.71</v>
+      </c>
+      <c r="BO120">
+        <v>2.5</v>
+      </c>
+      <c r="BP120">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="121" spans="1:68">
+      <c r="A121" s="1">
+        <v>120</v>
+      </c>
+      <c r="B121">
+        <v>7825311</v>
+      </c>
+      <c r="C121" t="s">
+        <v>68</v>
+      </c>
+      <c r="D121" t="s">
+        <v>69</v>
+      </c>
+      <c r="E121" s="2">
+        <v>45834.375</v>
+      </c>
+      <c r="F121">
+        <v>15</v>
+      </c>
+      <c r="G121" t="s">
+        <v>72</v>
+      </c>
+      <c r="H121" t="s">
+        <v>83</v>
+      </c>
+      <c r="I121">
+        <v>0</v>
+      </c>
+      <c r="J121">
+        <v>1</v>
+      </c>
+      <c r="K121">
+        <v>1</v>
+      </c>
+      <c r="L121">
+        <v>1</v>
+      </c>
+      <c r="M121">
+        <v>1</v>
+      </c>
+      <c r="N121">
+        <v>2</v>
+      </c>
+      <c r="O121" t="s">
+        <v>144</v>
+      </c>
+      <c r="P121" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q121">
+        <v>3</v>
+      </c>
+      <c r="R121">
+        <v>2.38</v>
+      </c>
+      <c r="S121">
+        <v>3.1</v>
+      </c>
+      <c r="T121">
+        <v>1.29</v>
+      </c>
+      <c r="U121">
+        <v>3.5</v>
+      </c>
+      <c r="V121">
+        <v>2.38</v>
+      </c>
+      <c r="W121">
+        <v>1.53</v>
+      </c>
+      <c r="X121">
+        <v>5.5</v>
+      </c>
+      <c r="Y121">
+        <v>1.14</v>
+      </c>
+      <c r="Z121">
+        <v>2.23</v>
+      </c>
+      <c r="AA121">
+        <v>3.6</v>
+      </c>
+      <c r="AB121">
+        <v>2.68</v>
+      </c>
+      <c r="AC121">
+        <v>1.01</v>
+      </c>
+      <c r="AD121">
+        <v>13</v>
+      </c>
+      <c r="AE121">
+        <v>1.14</v>
+      </c>
+      <c r="AF121">
+        <v>4.4</v>
+      </c>
+      <c r="AG121">
+        <v>1.61</v>
+      </c>
+      <c r="AH121">
+        <v>2.05</v>
+      </c>
+      <c r="AI121">
+        <v>1.53</v>
+      </c>
+      <c r="AJ121">
+        <v>2.38</v>
+      </c>
+      <c r="AK121">
+        <v>1.44</v>
+      </c>
+      <c r="AL121">
+        <v>1.29</v>
+      </c>
+      <c r="AM121">
+        <v>1.57</v>
+      </c>
+      <c r="AN121">
+        <v>1.67</v>
+      </c>
+      <c r="AO121">
+        <v>1.14</v>
+      </c>
+      <c r="AP121">
+        <v>1.57</v>
+      </c>
+      <c r="AQ121">
+        <v>1.13</v>
+      </c>
+      <c r="AR121">
+        <v>1.59</v>
+      </c>
+      <c r="AS121">
+        <v>1.57</v>
+      </c>
+      <c r="AT121">
+        <v>3.16</v>
+      </c>
+      <c r="AU121">
+        <v>5</v>
+      </c>
+      <c r="AV121">
+        <v>8</v>
+      </c>
+      <c r="AW121">
+        <v>5</v>
+      </c>
+      <c r="AX121">
+        <v>9</v>
+      </c>
+      <c r="AY121">
+        <v>10</v>
+      </c>
+      <c r="AZ121">
+        <v>17</v>
+      </c>
+      <c r="BA121">
+        <v>2</v>
+      </c>
+      <c r="BB121">
+        <v>6</v>
+      </c>
+      <c r="BC121">
+        <v>8</v>
+      </c>
+      <c r="BD121">
+        <v>2.07</v>
+      </c>
+      <c r="BE121">
+        <v>6.75</v>
+      </c>
+      <c r="BF121">
+        <v>1.9</v>
+      </c>
+      <c r="BG121">
+        <v>1.23</v>
+      </c>
+      <c r="BH121">
+        <v>3.65</v>
+      </c>
+      <c r="BI121">
+        <v>1.41</v>
+      </c>
+      <c r="BJ121">
+        <v>2.65</v>
+      </c>
+      <c r="BK121">
+        <v>1.68</v>
+      </c>
+      <c r="BL121">
+        <v>2.04</v>
+      </c>
+      <c r="BM121">
+        <v>2.06</v>
+      </c>
+      <c r="BN121">
+        <v>1.66</v>
+      </c>
+      <c r="BO121">
+        <v>2.55</v>
+      </c>
+      <c r="BP121">
+        <v>1.43</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
@@ -1468,10 +1468,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AQ2">
-        <v>0.88</v>
+        <v>1.2</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1674,10 +1674,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>2.75</v>
+        <v>2.33</v>
       </c>
       <c r="AQ3">
-        <v>0.38</v>
+        <v>0.53</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1880,10 +1880,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AQ4">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2086,10 +2086,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0.88</v>
+        <v>0.53</v>
       </c>
       <c r="AQ5">
-        <v>0.71</v>
+        <v>1.2</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2292,10 +2292,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.86</v>
+        <v>1.33</v>
       </c>
       <c r="AQ6">
-        <v>0.5</v>
+        <v>1.13</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2498,10 +2498,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AQ7">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2704,10 +2704,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ8">
-        <v>0.43</v>
+        <v>0.8</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2910,10 +2910,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.89</v>
+        <v>2.07</v>
       </c>
       <c r="AQ9">
-        <v>0.5</v>
+        <v>0.93</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3116,10 +3116,10 @@
         <v>1</v>
       </c>
       <c r="AP10">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AQ10">
-        <v>0.5</v>
+        <v>1.13</v>
       </c>
       <c r="AR10">
         <v>2.21</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.89</v>
+        <v>2.07</v>
       </c>
       <c r="AQ11">
-        <v>0.38</v>
+        <v>0.53</v>
       </c>
       <c r="AR11">
         <v>1.91</v>
@@ -3528,10 +3528,10 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>0.88</v>
+        <v>0.53</v>
       </c>
       <c r="AQ12">
-        <v>0.5</v>
+        <v>0.93</v>
       </c>
       <c r="AR12">
         <v>1.44</v>
@@ -3728,25 +3728,25 @@
         <v>1.35</v>
       </c>
       <c r="AN13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO13">
         <v>1</v>
       </c>
       <c r="AP13">
-        <v>1.13</v>
+        <v>0.8</v>
       </c>
       <c r="AQ13">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AS13">
         <v>1.57</v>
       </c>
       <c r="AT13">
-        <v>1.57</v>
+        <v>2.96</v>
       </c>
       <c r="AU13">
         <v>8</v>
@@ -3940,10 +3940,10 @@
         <v>3</v>
       </c>
       <c r="AP14">
-        <v>2.75</v>
+        <v>2.33</v>
       </c>
       <c r="AQ14">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AR14">
         <v>2.29</v>
@@ -4143,22 +4143,22 @@
         <v>0</v>
       </c>
       <c r="AO15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP15">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AQ15">
-        <v>0.88</v>
+        <v>1.33</v>
       </c>
       <c r="AR15">
         <v>1.22</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AT15">
-        <v>1.22</v>
+        <v>2.59</v>
       </c>
       <c r="AU15">
         <v>4</v>
@@ -4349,22 +4349,22 @@
         <v>3</v>
       </c>
       <c r="AO16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP16">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AQ16">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AR16">
         <v>2.91</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AT16">
-        <v>2.91</v>
+        <v>6.33</v>
       </c>
       <c r="AU16">
         <v>5</v>
@@ -4552,25 +4552,25 @@
         <v>1.6</v>
       </c>
       <c r="AN17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO17">
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.63</v>
+        <v>1.2</v>
       </c>
       <c r="AQ17">
-        <v>0.88</v>
+        <v>1.2</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS17">
         <v>0.95</v>
       </c>
       <c r="AT17">
-        <v>0.95</v>
+        <v>2.6</v>
       </c>
       <c r="AU17">
         <v>3</v>
@@ -4758,25 +4758,25 @@
         <v>1.1</v>
       </c>
       <c r="AN18">
+        <v>2</v>
+      </c>
+      <c r="AO18">
         <v>3</v>
       </c>
-      <c r="AO18">
-        <v>0</v>
-      </c>
       <c r="AP18">
-        <v>1.63</v>
+        <v>1.2</v>
       </c>
       <c r="AQ18">
-        <v>2.33</v>
+        <v>2.07</v>
       </c>
       <c r="AR18">
-        <v>0.8</v>
+        <v>1.22</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AT18">
-        <v>0.8</v>
+        <v>3.52</v>
       </c>
       <c r="AU18">
         <v>5</v>
@@ -4970,19 +4970,19 @@
         <v>1</v>
       </c>
       <c r="AP19">
-        <v>1.57</v>
+        <v>1.2</v>
       </c>
       <c r="AQ19">
-        <v>0.88</v>
+        <v>1.33</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AS19">
         <v>1.38</v>
       </c>
       <c r="AT19">
-        <v>1.38</v>
+        <v>1.94</v>
       </c>
       <c r="AU19">
         <v>5</v>
@@ -5170,25 +5170,25 @@
         <v>1.5</v>
       </c>
       <c r="AN20">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO20">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AP20">
-        <v>1.43</v>
+        <v>0.93</v>
       </c>
       <c r="AQ20">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR20">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AS20">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AT20">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AU20">
         <v>9</v>
@@ -5376,25 +5376,25 @@
         <v>1.44</v>
       </c>
       <c r="AN21">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AO21">
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.86</v>
+        <v>1.13</v>
       </c>
       <c r="AQ21">
-        <v>0.38</v>
+        <v>0.53</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AS21">
         <v>0.88</v>
       </c>
       <c r="AT21">
-        <v>0.88</v>
+        <v>2.13</v>
       </c>
       <c r="AU21">
         <v>7</v>
@@ -5582,25 +5582,25 @@
         <v>2.2</v>
       </c>
       <c r="AN22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO22">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AP22">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ22">
-        <v>0.14</v>
+        <v>0.53</v>
       </c>
       <c r="AR22">
-        <v>3.42</v>
+        <v>2.35</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AT22">
-        <v>3.42</v>
+        <v>3.67</v>
       </c>
       <c r="AU22">
         <v>11</v>
@@ -5788,25 +5788,25 @@
         <v>1.25</v>
       </c>
       <c r="AN23">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AO23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AP23">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AQ23">
-        <v>1.86</v>
+        <v>2.33</v>
       </c>
       <c r="AR23">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AS23">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AT23">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AU23">
         <v>5</v>
@@ -5994,25 +5994,25 @@
         <v>1.18</v>
       </c>
       <c r="AN24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AP24">
-        <v>1.13</v>
+        <v>0.8</v>
       </c>
       <c r="AQ24">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="AR24">
-        <v>1.93</v>
+        <v>1.66</v>
       </c>
       <c r="AS24">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AT24">
-        <v>1.93</v>
+        <v>4.12</v>
       </c>
       <c r="AU24">
         <v>7</v>
@@ -6200,25 +6200,25 @@
         <v>1.6</v>
       </c>
       <c r="AN25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO25">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AP25">
-        <v>2.71</v>
+        <v>2.33</v>
       </c>
       <c r="AQ25">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AR25">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AS25">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AT25">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="AU25">
         <v>3</v>
@@ -6406,25 +6406,25 @@
         <v>1.68</v>
       </c>
       <c r="AN26">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AO26">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AP26">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AQ26">
-        <v>0.71</v>
+        <v>1.2</v>
       </c>
       <c r="AR26">
-        <v>1.09</v>
+        <v>1.38</v>
       </c>
       <c r="AS26">
-        <v>1.65</v>
+        <v>1.26</v>
       </c>
       <c r="AT26">
-        <v>2.74</v>
+        <v>2.64</v>
       </c>
       <c r="AU26">
         <v>6</v>
@@ -6612,25 +6612,25 @@
         <v>2.1</v>
       </c>
       <c r="AN27">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AO27">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AP27">
-        <v>1.86</v>
+        <v>1.33</v>
       </c>
       <c r="AQ27">
-        <v>0.5</v>
+        <v>0.93</v>
       </c>
       <c r="AR27">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="AS27">
-        <v>1.47</v>
+        <v>1.73</v>
       </c>
       <c r="AT27">
-        <v>2.84</v>
+        <v>3.21</v>
       </c>
       <c r="AU27">
         <v>7</v>
@@ -6824,19 +6824,19 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>0.71</v>
+        <v>0.53</v>
       </c>
       <c r="AQ28">
-        <v>0.88</v>
+        <v>1.2</v>
       </c>
       <c r="AR28">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="AS28">
-        <v>0.5600000000000001</v>
+        <v>0.98</v>
       </c>
       <c r="AT28">
-        <v>0.5600000000000001</v>
+        <v>1.82</v>
       </c>
       <c r="AU28">
         <v>4</v>
@@ -7024,25 +7024,25 @@
         <v>2.95</v>
       </c>
       <c r="AN29">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AO29">
-        <v>3</v>
+        <v>1.33</v>
       </c>
       <c r="AP29">
-        <v>2.75</v>
+        <v>2.33</v>
       </c>
       <c r="AQ29">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR29">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="AS29">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AT29">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="AU29">
         <v>11</v>
@@ -7230,25 +7230,25 @@
         <v>1.33</v>
       </c>
       <c r="AN30">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AO30">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AP30">
-        <v>0.88</v>
+        <v>0.53</v>
       </c>
       <c r="AQ30">
-        <v>0.5</v>
+        <v>1.13</v>
       </c>
       <c r="AR30">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="AS30">
-        <v>1.25</v>
+        <v>1.59</v>
       </c>
       <c r="AT30">
-        <v>2.57</v>
+        <v>2.74</v>
       </c>
       <c r="AU30">
         <v>6</v>
@@ -7436,25 +7436,25 @@
         <v>1.56</v>
       </c>
       <c r="AN31">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AO31">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AP31">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AQ31">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AR31">
-        <v>2.46</v>
+        <v>2.34</v>
       </c>
       <c r="AS31">
-        <v>2.14</v>
+        <v>2.31</v>
       </c>
       <c r="AT31">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="AU31">
         <v>3</v>
@@ -7642,25 +7642,25 @@
         <v>1.42</v>
       </c>
       <c r="AN32">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AO32">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AP32">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ32">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AR32">
-        <v>3.11</v>
+        <v>2.5</v>
       </c>
       <c r="AS32">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="AT32">
-        <v>4.31</v>
+        <v>3.55</v>
       </c>
       <c r="AU32">
         <v>10</v>
@@ -7848,25 +7848,25 @@
         <v>4.1</v>
       </c>
       <c r="AN33">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AO33">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AP33">
-        <v>1.89</v>
+        <v>2.07</v>
       </c>
       <c r="AQ33">
-        <v>0.43</v>
+        <v>0.8</v>
       </c>
       <c r="AR33">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="AS33">
-        <v>1.39</v>
+        <v>1.54</v>
       </c>
       <c r="AT33">
-        <v>3.69</v>
+        <v>3.66</v>
       </c>
       <c r="AU33">
         <v>12</v>
@@ -8054,25 +8054,25 @@
         <v>1.49</v>
       </c>
       <c r="AN34">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AO34">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AP34">
-        <v>1.43</v>
+        <v>0.93</v>
       </c>
       <c r="AQ34">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR34">
-        <v>2.26</v>
+        <v>1.55</v>
       </c>
       <c r="AS34">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AT34">
-        <v>3.79</v>
+        <v>2.88</v>
       </c>
       <c r="AU34">
         <v>3</v>
@@ -8260,25 +8260,25 @@
         <v>1.23</v>
       </c>
       <c r="AN35">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="AO35">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="AP35">
-        <v>0.71</v>
+        <v>0.53</v>
       </c>
       <c r="AQ35">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="AR35">
-        <v>1.08</v>
+        <v>0.9</v>
       </c>
       <c r="AS35">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AT35">
-        <v>3.18</v>
+        <v>2.95</v>
       </c>
       <c r="AU35">
         <v>6</v>
@@ -8469,22 +8469,22 @@
         <v>2</v>
       </c>
       <c r="AO36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP36">
-        <v>1.63</v>
+        <v>1.2</v>
       </c>
       <c r="AQ36">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AR36">
-        <v>1.07</v>
+        <v>1.35</v>
       </c>
       <c r="AS36">
-        <v>1.28</v>
+        <v>2.47</v>
       </c>
       <c r="AT36">
-        <v>2.35</v>
+        <v>3.82</v>
       </c>
       <c r="AU36">
         <v>4</v>
@@ -8672,25 +8672,25 @@
         <v>1.66</v>
       </c>
       <c r="AN37">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AO37">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AP37">
-        <v>1.13</v>
+        <v>0.8</v>
       </c>
       <c r="AQ37">
-        <v>0.88</v>
+        <v>1.2</v>
       </c>
       <c r="AR37">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="AS37">
-        <v>0.96</v>
+        <v>1.17</v>
       </c>
       <c r="AT37">
-        <v>2.57</v>
+        <v>2.64</v>
       </c>
       <c r="AU37">
         <v>9</v>
@@ -8878,25 +8878,25 @@
         <v>3.54</v>
       </c>
       <c r="AN38">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AO38">
-        <v>0.67</v>
+        <v>1.25</v>
       </c>
       <c r="AP38">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AQ38">
-        <v>0.5</v>
+        <v>1.13</v>
       </c>
       <c r="AR38">
-        <v>2.39</v>
+        <v>2.27</v>
       </c>
       <c r="AS38">
-        <v>1.36</v>
+        <v>1.58</v>
       </c>
       <c r="AT38">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="AU38">
         <v>9</v>
@@ -9084,25 +9084,25 @@
         <v>1.56</v>
       </c>
       <c r="AN39">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AO39">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AP39">
-        <v>1.89</v>
+        <v>2.07</v>
       </c>
       <c r="AQ39">
-        <v>1.86</v>
+        <v>2.33</v>
       </c>
       <c r="AR39">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="AS39">
-        <v>2.07</v>
+        <v>2.55</v>
       </c>
       <c r="AT39">
-        <v>4.45</v>
+        <v>4.78</v>
       </c>
       <c r="AU39">
         <v>2</v>
@@ -9290,25 +9290,25 @@
         <v>2.19</v>
       </c>
       <c r="AN40">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AO40">
         <v>2</v>
       </c>
       <c r="AP40">
-        <v>2.71</v>
+        <v>2.33</v>
       </c>
       <c r="AQ40">
-        <v>0.88</v>
+        <v>1.33</v>
       </c>
       <c r="AR40">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="AS40">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AT40">
-        <v>2.28</v>
+        <v>2.77</v>
       </c>
       <c r="AU40">
         <v>12</v>
@@ -9496,25 +9496,25 @@
         <v>2.09</v>
       </c>
       <c r="AN41">
+        <v>1</v>
+      </c>
+      <c r="AO41">
         <v>0.5</v>
       </c>
-      <c r="AO41">
-        <v>0</v>
-      </c>
       <c r="AP41">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AQ41">
-        <v>0.14</v>
+        <v>0.53</v>
       </c>
       <c r="AR41">
         <v>1.18</v>
       </c>
       <c r="AS41">
-        <v>0.8</v>
+        <v>1.27</v>
       </c>
       <c r="AT41">
-        <v>1.98</v>
+        <v>2.45</v>
       </c>
       <c r="AU41">
         <v>6</v>
@@ -9702,25 +9702,25 @@
         <v>2.7</v>
       </c>
       <c r="AN42">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="AO42">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="AP42">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AQ42">
-        <v>0.5</v>
+        <v>0.93</v>
       </c>
       <c r="AR42">
-        <v>2.03</v>
+        <v>2.14</v>
       </c>
       <c r="AS42">
-        <v>1.31</v>
+        <v>1.51</v>
       </c>
       <c r="AT42">
-        <v>3.34</v>
+        <v>3.65</v>
       </c>
       <c r="AU42">
         <v>11</v>
@@ -9908,25 +9908,25 @@
         <v>1.53</v>
       </c>
       <c r="AN43">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AO43">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AP43">
-        <v>1.13</v>
+        <v>0.8</v>
       </c>
       <c r="AQ43">
-        <v>0.38</v>
+        <v>0.53</v>
       </c>
       <c r="AR43">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="AS43">
-        <v>0.84</v>
+        <v>1.06</v>
       </c>
       <c r="AT43">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AU43">
         <v>7</v>
@@ -10114,25 +10114,25 @@
         <v>1.44</v>
       </c>
       <c r="AN44">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AO44">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AP44">
-        <v>1.86</v>
+        <v>1.13</v>
       </c>
       <c r="AQ44">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AR44">
-        <v>2.26</v>
+        <v>1.42</v>
       </c>
       <c r="AS44">
-        <v>1.16</v>
+        <v>2.19</v>
       </c>
       <c r="AT44">
-        <v>3.42</v>
+        <v>3.61</v>
       </c>
       <c r="AU44">
         <v>7</v>
@@ -10320,25 +10320,25 @@
         <v>1.06</v>
       </c>
       <c r="AN45">
-        <v>0.67</v>
+        <v>0.4</v>
       </c>
       <c r="AO45">
         <v>2</v>
       </c>
       <c r="AP45">
-        <v>0.88</v>
+        <v>0.53</v>
       </c>
       <c r="AQ45">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AR45">
-        <v>1.43</v>
+        <v>1.31</v>
       </c>
       <c r="AS45">
-        <v>2.14</v>
+        <v>2.27</v>
       </c>
       <c r="AT45">
-        <v>3.57</v>
+        <v>3.58</v>
       </c>
       <c r="AU45">
         <v>4</v>
@@ -10526,25 +10526,25 @@
         <v>1.5</v>
       </c>
       <c r="AN46">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AO46">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AP46">
-        <v>1.57</v>
+        <v>1.2</v>
       </c>
       <c r="AQ46">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR46">
-        <v>1.82</v>
+        <v>1.12</v>
       </c>
       <c r="AS46">
-        <v>1.19</v>
+        <v>1.37</v>
       </c>
       <c r="AT46">
-        <v>3.01</v>
+        <v>2.49</v>
       </c>
       <c r="AU46">
         <v>9</v>
@@ -10732,25 +10732,25 @@
         <v>2.7</v>
       </c>
       <c r="AN47">
+        <v>2.2</v>
+      </c>
+      <c r="AO47">
+        <v>1.6</v>
+      </c>
+      <c r="AP47">
         <v>2.33</v>
       </c>
-      <c r="AO47">
+      <c r="AQ47">
         <v>1.33</v>
       </c>
-      <c r="AP47">
-        <v>2.75</v>
-      </c>
-      <c r="AQ47">
-        <v>0.88</v>
-      </c>
       <c r="AR47">
-        <v>2.72</v>
+        <v>2.44</v>
       </c>
       <c r="AS47">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AT47">
-        <v>4.18</v>
+        <v>3.92</v>
       </c>
       <c r="AU47">
         <v>7</v>
@@ -10938,25 +10938,25 @@
         <v>1.3</v>
       </c>
       <c r="AN48">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AO48">
-        <v>3</v>
+        <v>2.17</v>
       </c>
       <c r="AP48">
-        <v>1.63</v>
+        <v>1.2</v>
       </c>
       <c r="AQ48">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="AR48">
-        <v>1.15</v>
+        <v>1.34</v>
       </c>
       <c r="AS48">
-        <v>2.31</v>
+        <v>2.18</v>
       </c>
       <c r="AT48">
-        <v>3.46</v>
+        <v>3.52</v>
       </c>
       <c r="AU48">
         <v>4</v>
@@ -11144,25 +11144,25 @@
         <v>1.24</v>
       </c>
       <c r="AN49">
-        <v>1.5</v>
+        <v>0.67</v>
       </c>
       <c r="AO49">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AP49">
-        <v>1.57</v>
+        <v>1.2</v>
       </c>
       <c r="AQ49">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AR49">
-        <v>1.83</v>
+        <v>1.24</v>
       </c>
       <c r="AS49">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="AT49">
-        <v>3.25</v>
+        <v>2.82</v>
       </c>
       <c r="AU49">
         <v>14</v>
@@ -11350,25 +11350,25 @@
         <v>1.67</v>
       </c>
       <c r="AN50">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AO50">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AP50">
-        <v>1.43</v>
+        <v>0.93</v>
       </c>
       <c r="AQ50">
-        <v>0.38</v>
+        <v>0.53</v>
       </c>
       <c r="AR50">
-        <v>1.81</v>
+        <v>1.42</v>
       </c>
       <c r="AS50">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AT50">
-        <v>2.82</v>
+        <v>2.55</v>
       </c>
       <c r="AU50">
         <v>6</v>
@@ -11559,22 +11559,22 @@
         <v>1.67</v>
       </c>
       <c r="AO51">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="AP51">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ51">
-        <v>2.33</v>
+        <v>2.07</v>
       </c>
       <c r="AR51">
-        <v>2.87</v>
+        <v>1.97</v>
       </c>
       <c r="AS51">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="AT51">
-        <v>4.64</v>
+        <v>3.97</v>
       </c>
       <c r="AU51">
         <v>3</v>
@@ -11762,25 +11762,25 @@
         <v>1.52</v>
       </c>
       <c r="AN52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO52">
-        <v>1.33</v>
+        <v>0.8</v>
       </c>
       <c r="AP52">
-        <v>1.86</v>
+        <v>1.13</v>
       </c>
       <c r="AQ52">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR52">
-        <v>2.18</v>
+        <v>1.53</v>
       </c>
       <c r="AS52">
-        <v>1.73</v>
+        <v>1.49</v>
       </c>
       <c r="AT52">
-        <v>3.91</v>
+        <v>3.02</v>
       </c>
       <c r="AU52">
         <v>4</v>
@@ -11968,25 +11968,25 @@
         <v>2.75</v>
       </c>
       <c r="AN53">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AO53">
-        <v>0.5</v>
+        <v>1.17</v>
       </c>
       <c r="AP53">
-        <v>1.86</v>
+        <v>1.33</v>
       </c>
       <c r="AQ53">
-        <v>0.43</v>
+        <v>0.8</v>
       </c>
       <c r="AR53">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="AS53">
-        <v>1.33</v>
+        <v>1.8</v>
       </c>
       <c r="AT53">
-        <v>2.83</v>
+        <v>3.15</v>
       </c>
       <c r="AU53">
         <v>4</v>
@@ -12174,25 +12174,25 @@
         <v>3.4</v>
       </c>
       <c r="AN54">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AO54">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AP54">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AQ54">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR54">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AS54">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AT54">
-        <v>3.63</v>
+        <v>3.55</v>
       </c>
       <c r="AU54">
         <v>6</v>
@@ -12380,25 +12380,25 @@
         <v>5.65</v>
       </c>
       <c r="AN55">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AO55">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AP55">
-        <v>2.75</v>
+        <v>2.33</v>
       </c>
       <c r="AQ55">
-        <v>0.14</v>
+        <v>0.53</v>
       </c>
       <c r="AR55">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AS55">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AT55">
-        <v>3.57</v>
+        <v>3.54</v>
       </c>
       <c r="AU55">
         <v>10</v>
@@ -12586,25 +12586,25 @@
         <v>0</v>
       </c>
       <c r="AN56">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="AO56">
-        <v>0.25</v>
+        <v>0.71</v>
       </c>
       <c r="AP56">
-        <v>2.75</v>
+        <v>2.33</v>
       </c>
       <c r="AQ56">
-        <v>0.88</v>
+        <v>1.2</v>
       </c>
       <c r="AR56">
-        <v>2.49</v>
+        <v>2.35</v>
       </c>
       <c r="AS56">
-        <v>0.9399999999999999</v>
+        <v>1.43</v>
       </c>
       <c r="AT56">
-        <v>3.43</v>
+        <v>3.78</v>
       </c>
       <c r="AU56">
         <v>7</v>
@@ -12792,25 +12792,25 @@
         <v>0</v>
       </c>
       <c r="AN57">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AO57">
-        <v>3</v>
+        <v>2.29</v>
       </c>
       <c r="AP57">
-        <v>2.71</v>
+        <v>2.33</v>
       </c>
       <c r="AQ57">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="AR57">
-        <v>1.81</v>
+        <v>1.59</v>
       </c>
       <c r="AS57">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AT57">
-        <v>4</v>
+        <v>3.74</v>
       </c>
       <c r="AU57">
         <v>9</v>
@@ -12998,25 +12998,25 @@
         <v>1.48</v>
       </c>
       <c r="AN58">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AO58">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AP58">
-        <v>0.71</v>
+        <v>0.53</v>
       </c>
       <c r="AQ58">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR58">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AS58">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="AT58">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="AU58">
         <v>4</v>
@@ -13204,25 +13204,25 @@
         <v>1.6</v>
       </c>
       <c r="AN59">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AO59">
-        <v>0.5</v>
+        <v>1.29</v>
       </c>
       <c r="AP59">
-        <v>1.63</v>
+        <v>1.2</v>
       </c>
       <c r="AQ59">
-        <v>0.5</v>
+        <v>1.13</v>
       </c>
       <c r="AR59">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AS59">
-        <v>1.21</v>
+        <v>1.53</v>
       </c>
       <c r="AT59">
-        <v>2.43</v>
+        <v>2.88</v>
       </c>
       <c r="AU59">
         <v>3</v>
@@ -13410,25 +13410,25 @@
         <v>2.15</v>
       </c>
       <c r="AN60">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AO60">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="AP60">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AQ60">
-        <v>0.14</v>
+        <v>0.53</v>
       </c>
       <c r="AR60">
-        <v>1.14</v>
+        <v>1.49</v>
       </c>
       <c r="AS60">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AT60">
-        <v>2.27</v>
+        <v>2.72</v>
       </c>
       <c r="AU60">
         <v>4</v>
@@ -13616,25 +13616,25 @@
         <v>1.65</v>
       </c>
       <c r="AN61">
-        <v>1.5</v>
+        <v>1.14</v>
       </c>
       <c r="AO61">
-        <v>0.75</v>
+        <v>0.86</v>
       </c>
       <c r="AP61">
-        <v>1.13</v>
+        <v>0.8</v>
       </c>
       <c r="AQ61">
-        <v>0.5</v>
+        <v>0.93</v>
       </c>
       <c r="AR61">
-        <v>2.04</v>
+        <v>1.72</v>
       </c>
       <c r="AS61">
-        <v>1.23</v>
+        <v>1.41</v>
       </c>
       <c r="AT61">
-        <v>3.27</v>
+        <v>3.13</v>
       </c>
       <c r="AU61">
         <v>6</v>
@@ -13822,25 +13822,25 @@
         <v>1.8</v>
       </c>
       <c r="AN62">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AO62">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AP62">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ62">
-        <v>0.88</v>
+        <v>1.33</v>
       </c>
       <c r="AR62">
-        <v>2.42</v>
+        <v>1.85</v>
       </c>
       <c r="AS62">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="AT62">
-        <v>3.7</v>
+        <v>3.27</v>
       </c>
       <c r="AU62">
         <v>5</v>
@@ -14028,25 +14028,25 @@
         <v>1.65</v>
       </c>
       <c r="AN63">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AO63">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AP63">
-        <v>1.89</v>
+        <v>2.07</v>
       </c>
       <c r="AQ63">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AR63">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="AS63">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="AT63">
-        <v>4.04</v>
+        <v>4.16</v>
       </c>
       <c r="AU63">
         <v>7</v>
@@ -14234,25 +14234,25 @@
         <v>2.25</v>
       </c>
       <c r="AN64">
+        <v>1.86</v>
+      </c>
+      <c r="AO64">
+        <v>1</v>
+      </c>
+      <c r="AP64">
         <v>2.33</v>
       </c>
-      <c r="AO64">
-        <v>1</v>
-      </c>
-      <c r="AP64">
-        <v>2.71</v>
-      </c>
       <c r="AQ64">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR64">
-        <v>2.07</v>
+        <v>1.73</v>
       </c>
       <c r="AS64">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="AT64">
-        <v>3.74</v>
+        <v>3.22</v>
       </c>
       <c r="AU64">
         <v>4</v>
@@ -14440,25 +14440,25 @@
         <v>1.14</v>
       </c>
       <c r="AN65">
+        <v>1.13</v>
+      </c>
+      <c r="AO65">
+        <v>2</v>
+      </c>
+      <c r="AP65">
         <v>1.33</v>
       </c>
-      <c r="AO65">
-        <v>2</v>
-      </c>
-      <c r="AP65">
-        <v>1.57</v>
-      </c>
       <c r="AQ65">
-        <v>2.33</v>
+        <v>2.07</v>
       </c>
       <c r="AR65">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="AS65">
-        <v>1.89</v>
+        <v>1.97</v>
       </c>
       <c r="AT65">
-        <v>3.39</v>
+        <v>3.29</v>
       </c>
       <c r="AU65">
         <v>6</v>
@@ -14646,25 +14646,25 @@
         <v>1.13</v>
       </c>
       <c r="AN66">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="AO66">
-        <v>2.5</v>
+        <v>2.13</v>
       </c>
       <c r="AP66">
-        <v>0.71</v>
+        <v>0.53</v>
       </c>
       <c r="AQ66">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AR66">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="AS66">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AT66">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AU66">
         <v>4</v>
@@ -14852,25 +14852,25 @@
         <v>1.47</v>
       </c>
       <c r="AN67">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AO67">
-        <v>0.4</v>
+        <v>1.13</v>
       </c>
       <c r="AP67">
-        <v>1.43</v>
+        <v>0.93</v>
       </c>
       <c r="AQ67">
-        <v>0.5</v>
+        <v>1.13</v>
       </c>
       <c r="AR67">
-        <v>1.64</v>
+        <v>1.29</v>
       </c>
       <c r="AS67">
-        <v>1.31</v>
+        <v>1.55</v>
       </c>
       <c r="AT67">
-        <v>2.95</v>
+        <v>2.84</v>
       </c>
       <c r="AU67">
         <v>5</v>
@@ -15058,25 +15058,25 @@
         <v>1.43</v>
       </c>
       <c r="AN68">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AO68">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AP68">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AQ68">
-        <v>1.86</v>
+        <v>2.33</v>
       </c>
       <c r="AR68">
-        <v>2.12</v>
+        <v>2.01</v>
       </c>
       <c r="AS68">
-        <v>2.01</v>
+        <v>2.3</v>
       </c>
       <c r="AT68">
-        <v>4.13</v>
+        <v>4.31</v>
       </c>
       <c r="AU68">
         <v>2</v>
@@ -15264,25 +15264,25 @@
         <v>1.47</v>
       </c>
       <c r="AN69">
-        <v>1.33</v>
+        <v>0.63</v>
       </c>
       <c r="AO69">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AP69">
-        <v>1.57</v>
+        <v>1.2</v>
       </c>
       <c r="AQ69">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AR69">
-        <v>2.08</v>
+        <v>1.4</v>
       </c>
       <c r="AS69">
-        <v>1.07</v>
+        <v>1.81</v>
       </c>
       <c r="AT69">
-        <v>3.15</v>
+        <v>3.21</v>
       </c>
       <c r="AU69">
         <v>11</v>
@@ -15470,25 +15470,25 @@
         <v>1.46</v>
       </c>
       <c r="AN70">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AO70">
-        <v>0.67</v>
+        <v>1.38</v>
       </c>
       <c r="AP70">
-        <v>0.88</v>
+        <v>0.53</v>
       </c>
       <c r="AQ70">
-        <v>0.43</v>
+        <v>0.8</v>
       </c>
       <c r="AR70">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AS70">
-        <v>1.29</v>
+        <v>1.75</v>
       </c>
       <c r="AT70">
-        <v>2.59</v>
+        <v>2.93</v>
       </c>
       <c r="AU70">
         <v>3</v>
@@ -15676,25 +15676,25 @@
         <v>2.19</v>
       </c>
       <c r="AN71">
-        <v>1.67</v>
+        <v>1.13</v>
       </c>
       <c r="AO71">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AP71">
-        <v>1.86</v>
+        <v>1.33</v>
       </c>
       <c r="AQ71">
-        <v>0.71</v>
+        <v>1.2</v>
       </c>
       <c r="AR71">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AS71">
-        <v>1.63</v>
+        <v>1.26</v>
       </c>
       <c r="AT71">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="AU71">
         <v>3</v>
@@ -15882,25 +15882,25 @@
         <v>1.68</v>
       </c>
       <c r="AN72">
-        <v>2.33</v>
+        <v>1.11</v>
       </c>
       <c r="AO72">
         <v>1</v>
       </c>
       <c r="AP72">
-        <v>1.86</v>
+        <v>1.13</v>
       </c>
       <c r="AQ72">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR72">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="AS72">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="AT72">
-        <v>3.16</v>
+        <v>2.91</v>
       </c>
       <c r="AU72">
         <v>8</v>
@@ -16088,25 +16088,25 @@
         <v>1.36</v>
       </c>
       <c r="AN73">
-        <v>1</v>
+        <v>0.78</v>
       </c>
       <c r="AO73">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AP73">
-        <v>1.43</v>
+        <v>0.93</v>
       </c>
       <c r="AQ73">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AR73">
-        <v>1.59</v>
+        <v>1.3</v>
       </c>
       <c r="AS73">
-        <v>1.12</v>
+        <v>1.75</v>
       </c>
       <c r="AT73">
-        <v>2.71</v>
+        <v>3.05</v>
       </c>
       <c r="AU73">
         <v>4</v>
@@ -16294,25 +16294,25 @@
         <v>2.15</v>
       </c>
       <c r="AN74">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AO74">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP74">
-        <v>1.86</v>
+        <v>1.33</v>
       </c>
       <c r="AQ74">
-        <v>0.38</v>
+        <v>0.53</v>
       </c>
       <c r="AR74">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="AS74">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AT74">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="AU74">
         <v>8</v>
@@ -16500,25 +16500,25 @@
         <v>1.77</v>
       </c>
       <c r="AN75">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AO75">
-        <v>0.2</v>
+        <v>0.89</v>
       </c>
       <c r="AP75">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AQ75">
-        <v>0.88</v>
+        <v>1.2</v>
       </c>
       <c r="AR75">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="AS75">
-        <v>0.99</v>
+        <v>1.48</v>
       </c>
       <c r="AT75">
-        <v>2.25</v>
+        <v>2.87</v>
       </c>
       <c r="AU75">
         <v>6</v>
@@ -16706,25 +16706,25 @@
         <v>3.9</v>
       </c>
       <c r="AN76">
-        <v>1.4</v>
+        <v>1.78</v>
       </c>
       <c r="AO76">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AP76">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AQ76">
-        <v>0.14</v>
+        <v>0.53</v>
       </c>
       <c r="AR76">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AS76">
-        <v>1.07</v>
+        <v>1.26</v>
       </c>
       <c r="AT76">
-        <v>2.96</v>
+        <v>3.16</v>
       </c>
       <c r="AU76">
         <v>5</v>
@@ -16912,25 +16912,25 @@
         <v>1.67</v>
       </c>
       <c r="AN77">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AO77">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AP77">
-        <v>1.89</v>
+        <v>2.07</v>
       </c>
       <c r="AQ77">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AR77">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AS77">
-        <v>1.48</v>
+        <v>1.69</v>
       </c>
       <c r="AT77">
-        <v>3.48</v>
+        <v>3.53</v>
       </c>
       <c r="AU77">
         <v>8</v>
@@ -17118,25 +17118,25 @@
         <v>1.8</v>
       </c>
       <c r="AN78">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AO78">
-        <v>0.75</v>
+        <v>1.33</v>
       </c>
       <c r="AP78">
-        <v>1.63</v>
+        <v>1.2</v>
       </c>
       <c r="AQ78">
-        <v>0.43</v>
+        <v>0.8</v>
       </c>
       <c r="AR78">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AS78">
-        <v>1.26</v>
+        <v>1.68</v>
       </c>
       <c r="AT78">
-        <v>2.38</v>
+        <v>2.93</v>
       </c>
       <c r="AU78">
         <v>6</v>
@@ -17324,25 +17324,25 @@
         <v>1.65</v>
       </c>
       <c r="AN79">
-        <v>1.75</v>
+        <v>2.22</v>
       </c>
       <c r="AO79">
+        <v>2.56</v>
+      </c>
+      <c r="AP79">
+        <v>2.2</v>
+      </c>
+      <c r="AQ79">
         <v>2.33</v>
       </c>
-      <c r="AP79">
-        <v>2.13</v>
-      </c>
-      <c r="AQ79">
-        <v>1.86</v>
-      </c>
       <c r="AR79">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="AS79">
-        <v>1.71</v>
+        <v>2.17</v>
       </c>
       <c r="AT79">
-        <v>3.99</v>
+        <v>4.27</v>
       </c>
       <c r="AU79">
         <v>3</v>
@@ -17530,25 +17530,25 @@
         <v>0</v>
       </c>
       <c r="AN80">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="AO80">
-        <v>1.8</v>
+        <v>2.11</v>
       </c>
       <c r="AP80">
-        <v>1.86</v>
+        <v>1.13</v>
       </c>
       <c r="AQ80">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AR80">
-        <v>2.04</v>
+        <v>1.6</v>
       </c>
       <c r="AS80">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AT80">
-        <v>3.54</v>
+        <v>3.27</v>
       </c>
       <c r="AU80">
         <v>2</v>
@@ -17736,25 +17736,25 @@
         <v>0</v>
       </c>
       <c r="AN81">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AO81">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="AP81">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AQ81">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AR81">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AS81">
-        <v>1.14</v>
+        <v>1.69</v>
       </c>
       <c r="AT81">
-        <v>2.55</v>
+        <v>3.13</v>
       </c>
       <c r="AU81">
         <v>5</v>
@@ -17942,25 +17942,25 @@
         <v>0</v>
       </c>
       <c r="AN82">
-        <v>1.75</v>
+        <v>1.1</v>
       </c>
       <c r="AO82">
-        <v>2.33</v>
+        <v>1.89</v>
       </c>
       <c r="AP82">
-        <v>1.57</v>
+        <v>1.2</v>
       </c>
       <c r="AQ82">
-        <v>2.33</v>
+        <v>2.07</v>
       </c>
       <c r="AR82">
-        <v>2.09</v>
+        <v>1.44</v>
       </c>
       <c r="AS82">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AT82">
-        <v>3.66</v>
+        <v>3.35</v>
       </c>
       <c r="AU82">
         <v>7</v>
@@ -18148,25 +18148,25 @@
         <v>0</v>
       </c>
       <c r="AN83">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="AO83">
         <v>0.5</v>
       </c>
       <c r="AP83">
-        <v>0.88</v>
+        <v>0.53</v>
       </c>
       <c r="AQ83">
-        <v>0.38</v>
+        <v>0.53</v>
       </c>
       <c r="AR83">
-        <v>1.41</v>
+        <v>1.24</v>
       </c>
       <c r="AS83">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AT83">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="AU83">
         <v>7</v>
@@ -18354,25 +18354,25 @@
         <v>0</v>
       </c>
       <c r="AN84">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AO84">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="AP84">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AQ84">
-        <v>0.88</v>
+        <v>1.33</v>
       </c>
       <c r="AR84">
-        <v>2.13</v>
+        <v>2.04</v>
       </c>
       <c r="AS84">
-        <v>1.32</v>
+        <v>1.46</v>
       </c>
       <c r="AT84">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AU84">
         <v>6</v>
@@ -18560,25 +18560,25 @@
         <v>0</v>
       </c>
       <c r="AN85">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AO85">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="AP85">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AQ85">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="AR85">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AS85">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AT85">
-        <v>3.5</v>
+        <v>3.36</v>
       </c>
       <c r="AU85">
         <v>8</v>
@@ -18766,25 +18766,25 @@
         <v>0</v>
       </c>
       <c r="AN86">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="AO86">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="AP86">
-        <v>1.13</v>
+        <v>0.8</v>
       </c>
       <c r="AQ86">
-        <v>1.86</v>
+        <v>2.33</v>
       </c>
       <c r="AR86">
-        <v>2.02</v>
+        <v>1.67</v>
       </c>
       <c r="AS86">
-        <v>1.59</v>
+        <v>2.08</v>
       </c>
       <c r="AT86">
-        <v>3.61</v>
+        <v>3.75</v>
       </c>
       <c r="AU86">
         <v>3</v>
@@ -18972,25 +18972,25 @@
         <v>0</v>
       </c>
       <c r="AN87">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AO87">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AP87">
-        <v>1.63</v>
+        <v>1.2</v>
       </c>
       <c r="AQ87">
-        <v>0.5</v>
+        <v>0.93</v>
       </c>
       <c r="AR87">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AS87">
-        <v>1.07</v>
+        <v>1.3</v>
       </c>
       <c r="AT87">
-        <v>2.24</v>
+        <v>2.57</v>
       </c>
       <c r="AU87">
         <v>3</v>
@@ -19178,25 +19178,25 @@
         <v>0</v>
       </c>
       <c r="AN88">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AO88">
-        <v>0.2</v>
+        <v>0.64</v>
       </c>
       <c r="AP88">
-        <v>1.89</v>
+        <v>2.07</v>
       </c>
       <c r="AQ88">
-        <v>0.14</v>
+        <v>0.53</v>
       </c>
       <c r="AR88">
-        <v>2.08</v>
+        <v>1.91</v>
       </c>
       <c r="AS88">
-        <v>1.07</v>
+        <v>1.31</v>
       </c>
       <c r="AT88">
-        <v>3.15</v>
+        <v>3.22</v>
       </c>
       <c r="AU88">
         <v>8</v>
@@ -19384,25 +19384,25 @@
         <v>0</v>
       </c>
       <c r="AN89">
-        <v>2.67</v>
+        <v>2.36</v>
       </c>
       <c r="AO89">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="AP89">
-        <v>2.75</v>
+        <v>2.33</v>
       </c>
       <c r="AQ89">
-        <v>0.71</v>
+        <v>1.2</v>
       </c>
       <c r="AR89">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AS89">
-        <v>1.47</v>
+        <v>1.31</v>
       </c>
       <c r="AT89">
-        <v>3.87</v>
+        <v>3.41</v>
       </c>
       <c r="AU89">
         <v>10</v>
@@ -19590,25 +19590,25 @@
         <v>0</v>
       </c>
       <c r="AN90">
-        <v>1.5</v>
+        <v>1.09</v>
       </c>
       <c r="AO90">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="AP90">
-        <v>1.13</v>
+        <v>0.8</v>
       </c>
       <c r="AQ90">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AR90">
-        <v>1.96</v>
+        <v>1.67</v>
       </c>
       <c r="AS90">
-        <v>1.96</v>
+        <v>2.03</v>
       </c>
       <c r="AT90">
-        <v>3.92</v>
+        <v>3.7</v>
       </c>
       <c r="AU90">
         <v>0</v>
@@ -19796,25 +19796,25 @@
         <v>0</v>
       </c>
       <c r="AN91">
+        <v>1.55</v>
+      </c>
+      <c r="AO91">
+        <v>1.36</v>
+      </c>
+      <c r="AP91">
+        <v>1.6</v>
+      </c>
+      <c r="AQ91">
         <v>1.33</v>
       </c>
-      <c r="AO91">
-        <v>0.67</v>
-      </c>
-      <c r="AP91">
-        <v>1.75</v>
-      </c>
-      <c r="AQ91">
-        <v>0.88</v>
-      </c>
       <c r="AR91">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AS91">
-        <v>1.2</v>
+        <v>1.37</v>
       </c>
       <c r="AT91">
-        <v>3.13</v>
+        <v>3.31</v>
       </c>
       <c r="AU91">
         <v>9</v>
@@ -20002,25 +20002,25 @@
         <v>0</v>
       </c>
       <c r="AN92">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AO92">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AP92">
-        <v>2.71</v>
+        <v>2.33</v>
       </c>
       <c r="AQ92">
-        <v>0.5</v>
+        <v>0.93</v>
       </c>
       <c r="AR92">
-        <v>1.9</v>
+        <v>1.66</v>
       </c>
       <c r="AS92">
-        <v>0.96</v>
+        <v>1.22</v>
       </c>
       <c r="AT92">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="AU92">
         <v>7</v>
@@ -20208,25 +20208,25 @@
         <v>1.35</v>
       </c>
       <c r="AN93">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AO93">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="AP93">
-        <v>0.71</v>
+        <v>0.53</v>
       </c>
       <c r="AQ93">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR93">
         <v>1.27</v>
       </c>
       <c r="AS93">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AT93">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="AU93">
         <v>3</v>
@@ -20414,25 +20414,25 @@
         <v>1.83</v>
       </c>
       <c r="AN94">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AO94">
-        <v>0.83</v>
+        <v>1.09</v>
       </c>
       <c r="AP94">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ94">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR94">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="AS94">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AT94">
-        <v>3.58</v>
+        <v>3.13</v>
       </c>
       <c r="AU94">
         <v>8</v>
@@ -20620,25 +20620,25 @@
         <v>1.62</v>
       </c>
       <c r="AN95">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AO95">
-        <v>0.5</v>
+        <v>1.18</v>
       </c>
       <c r="AP95">
+        <v>1.2</v>
+      </c>
+      <c r="AQ95">
+        <v>1.13</v>
+      </c>
+      <c r="AR95">
+        <v>1.49</v>
+      </c>
+      <c r="AS95">
         <v>1.57</v>
       </c>
-      <c r="AQ95">
-        <v>0.5</v>
-      </c>
-      <c r="AR95">
-        <v>2.07</v>
-      </c>
-      <c r="AS95">
-        <v>1.32</v>
-      </c>
       <c r="AT95">
-        <v>3.39</v>
+        <v>3.06</v>
       </c>
       <c r="AU95">
         <v>5</v>
@@ -20826,25 +20826,25 @@
         <v>1.83</v>
       </c>
       <c r="AN96">
-        <v>2.2</v>
+        <v>1.25</v>
       </c>
       <c r="AO96">
-        <v>1.17</v>
+        <v>0.91</v>
       </c>
       <c r="AP96">
-        <v>1.86</v>
+        <v>1.33</v>
       </c>
       <c r="AQ96">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR96">
-        <v>1.59</v>
+        <v>1.43</v>
       </c>
       <c r="AS96">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AT96">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="AU96">
         <v>5</v>
@@ -21032,25 +21032,25 @@
         <v>1.83</v>
       </c>
       <c r="AN97">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AO97">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AP97">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AQ97">
-        <v>0.43</v>
+        <v>0.8</v>
       </c>
       <c r="AR97">
-        <v>1.63</v>
+        <v>1.47</v>
       </c>
       <c r="AS97">
-        <v>1.32</v>
+        <v>1.6</v>
       </c>
       <c r="AT97">
-        <v>2.95</v>
+        <v>3.07</v>
       </c>
       <c r="AU97">
         <v>5</v>
@@ -21238,25 +21238,25 @@
         <v>1.14</v>
       </c>
       <c r="AN98">
-        <v>2</v>
+        <v>1.17</v>
       </c>
       <c r="AO98">
-        <v>2</v>
+        <v>2.42</v>
       </c>
       <c r="AP98">
-        <v>1.86</v>
+        <v>1.13</v>
       </c>
       <c r="AQ98">
-        <v>1.86</v>
+        <v>2.33</v>
       </c>
       <c r="AR98">
-        <v>1.87</v>
+        <v>1.52</v>
       </c>
       <c r="AS98">
-        <v>1.74</v>
+        <v>2.1</v>
       </c>
       <c r="AT98">
-        <v>3.61</v>
+        <v>3.62</v>
       </c>
       <c r="AU98">
         <v>6</v>
@@ -21444,25 +21444,25 @@
         <v>1.36</v>
       </c>
       <c r="AN99">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="AO99">
         <v>1.33</v>
       </c>
       <c r="AP99">
-        <v>0.71</v>
+        <v>0.53</v>
       </c>
       <c r="AQ99">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AR99">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AS99">
-        <v>1.19</v>
+        <v>1.76</v>
       </c>
       <c r="AT99">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="AU99">
         <v>6</v>
@@ -21650,25 +21650,25 @@
         <v>3.05</v>
       </c>
       <c r="AN100">
-        <v>2.17</v>
+        <v>2.42</v>
       </c>
       <c r="AO100">
-        <v>1</v>
+        <v>1.45</v>
       </c>
       <c r="AP100">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AQ100">
-        <v>0.71</v>
+        <v>1.2</v>
       </c>
       <c r="AR100">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="AS100">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AT100">
-        <v>3.43</v>
+        <v>3.34</v>
       </c>
       <c r="AU100">
         <v>9</v>
@@ -21856,25 +21856,25 @@
         <v>1.11</v>
       </c>
       <c r="AN101">
-        <v>1</v>
+        <v>0.58</v>
       </c>
       <c r="AO101">
-        <v>2</v>
+        <v>2.27</v>
       </c>
       <c r="AP101">
-        <v>0.88</v>
+        <v>0.53</v>
       </c>
       <c r="AQ101">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AR101">
-        <v>1.51</v>
+        <v>1.32</v>
       </c>
       <c r="AS101">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AT101">
-        <v>3.01</v>
+        <v>3.05</v>
       </c>
       <c r="AU101">
         <v>3</v>
@@ -22062,25 +22062,25 @@
         <v>1.89</v>
       </c>
       <c r="AN102">
-        <v>1.86</v>
+        <v>2.09</v>
       </c>
       <c r="AO102">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AP102">
-        <v>1.89</v>
+        <v>2.07</v>
       </c>
       <c r="AQ102">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="AR102">
-        <v>2.21</v>
+        <v>2.01</v>
       </c>
       <c r="AS102">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AT102">
-        <v>4.15</v>
+        <v>3.93</v>
       </c>
       <c r="AU102">
         <v>3</v>
@@ -22268,25 +22268,25 @@
         <v>2.38</v>
       </c>
       <c r="AN103">
-        <v>1.67</v>
+        <v>1.08</v>
       </c>
       <c r="AO103">
-        <v>0.5</v>
+        <v>0.92</v>
       </c>
       <c r="AP103">
-        <v>1.86</v>
+        <v>1.13</v>
       </c>
       <c r="AQ103">
-        <v>0.43</v>
+        <v>0.8</v>
       </c>
       <c r="AR103">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="AS103">
-        <v>1.31</v>
+        <v>1.58</v>
       </c>
       <c r="AT103">
-        <v>3.15</v>
+        <v>3.11</v>
       </c>
       <c r="AU103">
         <v>2</v>
@@ -22474,25 +22474,25 @@
         <v>1.94</v>
       </c>
       <c r="AN104">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AO104">
-        <v>0.17</v>
+        <v>0.62</v>
       </c>
       <c r="AP104">
-        <v>1.57</v>
+        <v>1.2</v>
       </c>
       <c r="AQ104">
-        <v>0.14</v>
+        <v>0.53</v>
       </c>
       <c r="AR104">
-        <v>2.06</v>
+        <v>1.54</v>
       </c>
       <c r="AS104">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="AT104">
-        <v>3.2</v>
+        <v>2.86</v>
       </c>
       <c r="AU104">
         <v>6</v>
@@ -22680,25 +22680,25 @@
         <v>1.32</v>
       </c>
       <c r="AN105">
-        <v>2</v>
+        <v>1.23</v>
       </c>
       <c r="AO105">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AP105">
-        <v>1.86</v>
+        <v>1.33</v>
       </c>
       <c r="AQ105">
-        <v>2.33</v>
+        <v>2.07</v>
       </c>
       <c r="AR105">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="AS105">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AT105">
-        <v>3.23</v>
+        <v>3.37</v>
       </c>
       <c r="AU105">
         <v>8</v>
@@ -22886,25 +22886,25 @@
         <v>1.6</v>
       </c>
       <c r="AN106">
-        <v>1.71</v>
+        <v>1.42</v>
       </c>
       <c r="AO106">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AP106">
-        <v>1.63</v>
+        <v>1.2</v>
       </c>
       <c r="AQ106">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR106">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AS106">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AT106">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AU106">
         <v>3</v>
@@ -23092,25 +23092,25 @@
         <v>4.8</v>
       </c>
       <c r="AN107">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="AO107">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AP107">
-        <v>2.71</v>
+        <v>2.33</v>
       </c>
       <c r="AQ107">
-        <v>0.38</v>
+        <v>0.53</v>
       </c>
       <c r="AR107">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AS107">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AT107">
-        <v>3.28</v>
+        <v>2.94</v>
       </c>
       <c r="AU107">
         <v>6</v>
@@ -23298,25 +23298,25 @@
         <v>0</v>
       </c>
       <c r="AN108">
-        <v>1.4</v>
+        <v>0.92</v>
       </c>
       <c r="AO108">
-        <v>2.17</v>
+        <v>2.46</v>
       </c>
       <c r="AP108">
-        <v>1.43</v>
+        <v>0.93</v>
       </c>
       <c r="AQ108">
-        <v>1.86</v>
+        <v>2.33</v>
       </c>
       <c r="AR108">
-        <v>1.54</v>
+        <v>1.19</v>
       </c>
       <c r="AS108">
-        <v>1.81</v>
+        <v>2.11</v>
       </c>
       <c r="AT108">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AU108">
         <v>5</v>
@@ -23504,25 +23504,25 @@
         <v>1.14</v>
       </c>
       <c r="AN109">
-        <v>0.6</v>
+        <v>0.92</v>
       </c>
       <c r="AO109">
-        <v>2.67</v>
+        <v>2.31</v>
       </c>
       <c r="AP109">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AQ109">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AR109">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="AS109">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AT109">
-        <v>3.53</v>
+        <v>3.64</v>
       </c>
       <c r="AU109">
         <v>9</v>
@@ -23710,25 +23710,25 @@
         <v>1.3</v>
       </c>
       <c r="AN110">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AO110">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AP110">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ110">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="AR110">
-        <v>2.32</v>
+        <v>1.71</v>
       </c>
       <c r="AS110">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AT110">
-        <v>4.32</v>
+        <v>3.66</v>
       </c>
       <c r="AU110">
         <v>5</v>
@@ -23916,25 +23916,25 @@
         <v>2.7</v>
       </c>
       <c r="AN111">
-        <v>2.67</v>
+        <v>2.23</v>
       </c>
       <c r="AO111">
-        <v>1</v>
+        <v>1.38</v>
       </c>
       <c r="AP111">
-        <v>2.71</v>
+        <v>2.33</v>
       </c>
       <c r="AQ111">
-        <v>0.71</v>
+        <v>1.2</v>
       </c>
       <c r="AR111">
-        <v>1.97</v>
+        <v>1.69</v>
       </c>
       <c r="AS111">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AT111">
-        <v>3.19</v>
+        <v>2.94</v>
       </c>
       <c r="AU111">
         <v>5</v>
@@ -24122,25 +24122,25 @@
         <v>1.2</v>
       </c>
       <c r="AN112">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AO112">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="AP112">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AQ112">
-        <v>2.33</v>
+        <v>2.07</v>
       </c>
       <c r="AR112">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AS112">
-        <v>1.64</v>
+        <v>1.92</v>
       </c>
       <c r="AT112">
-        <v>3.23</v>
+        <v>3.5</v>
       </c>
       <c r="AU112">
         <v>7</v>
@@ -24328,25 +24328,25 @@
         <v>1.51</v>
       </c>
       <c r="AN113">
-        <v>1.67</v>
+        <v>1.08</v>
       </c>
       <c r="AO113">
-        <v>0.67</v>
+        <v>1.15</v>
       </c>
       <c r="AP113">
-        <v>1.43</v>
+        <v>0.93</v>
       </c>
       <c r="AQ113">
-        <v>0.88</v>
+        <v>1.2</v>
       </c>
       <c r="AR113">
-        <v>1.49</v>
+        <v>1.19</v>
       </c>
       <c r="AS113">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="AT113">
-        <v>2.5</v>
+        <v>2.72</v>
       </c>
       <c r="AU113">
         <v>5</v>
@@ -24534,25 +24534,25 @@
         <v>3.05</v>
       </c>
       <c r="AN114">
-        <v>2.71</v>
+        <v>2.29</v>
       </c>
       <c r="AO114">
         <v>1.57</v>
       </c>
       <c r="AP114">
-        <v>2.75</v>
+        <v>2.33</v>
       </c>
       <c r="AQ114">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AR114">
-        <v>2.36</v>
+        <v>2.1</v>
       </c>
       <c r="AS114">
-        <v>1.18</v>
+        <v>1.7</v>
       </c>
       <c r="AT114">
-        <v>3.54</v>
+        <v>3.8</v>
       </c>
       <c r="AU114">
         <v>7</v>
@@ -24740,25 +24740,25 @@
         <v>1.34</v>
       </c>
       <c r="AN115">
-        <v>1</v>
+        <v>0.57</v>
       </c>
       <c r="AO115">
-        <v>0.57</v>
+        <v>1.21</v>
       </c>
       <c r="AP115">
-        <v>0.88</v>
+        <v>0.53</v>
       </c>
       <c r="AQ115">
-        <v>0.88</v>
+        <v>1.33</v>
       </c>
       <c r="AR115">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="AS115">
-        <v>1.31</v>
+        <v>1.45</v>
       </c>
       <c r="AT115">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="AU115">
         <v>4</v>
@@ -24946,25 +24946,25 @@
         <v>1.38</v>
       </c>
       <c r="AN116">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="AO116">
-        <v>0.83</v>
+        <v>1.29</v>
       </c>
       <c r="AP116">
-        <v>0.71</v>
+        <v>0.53</v>
       </c>
       <c r="AQ116">
-        <v>0.71</v>
+        <v>1.2</v>
       </c>
       <c r="AR116">
         <v>1.24</v>
       </c>
       <c r="AS116">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AT116">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="AU116">
         <v>6</v>
@@ -25152,25 +25152,25 @@
         <v>2.55</v>
       </c>
       <c r="AN117">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AO117">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AP117">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AQ117">
-        <v>0.88</v>
+        <v>1.2</v>
       </c>
       <c r="AR117">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AS117">
-        <v>1.09</v>
+        <v>1.53</v>
       </c>
       <c r="AT117">
-        <v>2.99</v>
+        <v>3.42</v>
       </c>
       <c r="AU117">
         <v>18</v>
@@ -25358,25 +25358,25 @@
         <v>1.12</v>
       </c>
       <c r="AN118">
-        <v>1.29</v>
+        <v>0.86</v>
       </c>
       <c r="AO118">
-        <v>1.86</v>
+        <v>2.29</v>
       </c>
       <c r="AP118">
-        <v>1.13</v>
+        <v>0.8</v>
       </c>
       <c r="AQ118">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AR118">
-        <v>1.81</v>
+        <v>1.52</v>
       </c>
       <c r="AS118">
-        <v>1.46</v>
+        <v>1.65</v>
       </c>
       <c r="AT118">
-        <v>3.27</v>
+        <v>3.17</v>
       </c>
       <c r="AU118">
         <v>5</v>
@@ -25564,25 +25564,25 @@
         <v>4.7</v>
       </c>
       <c r="AN119">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AO119">
-        <v>0.57</v>
+        <v>1</v>
       </c>
       <c r="AP119">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AQ119">
-        <v>0.5</v>
+        <v>0.93</v>
       </c>
       <c r="AR119">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AS119">
-        <v>0.9399999999999999</v>
+        <v>1.21</v>
       </c>
       <c r="AT119">
-        <v>3.09</v>
+        <v>3.28</v>
       </c>
       <c r="AU119">
         <v>9</v>
@@ -25770,25 +25770,25 @@
         <v>3.2</v>
       </c>
       <c r="AN120">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AO120">
-        <v>0.57</v>
+        <v>1.21</v>
       </c>
       <c r="AP120">
-        <v>1.89</v>
+        <v>2.07</v>
       </c>
       <c r="AQ120">
-        <v>0.5</v>
+        <v>1.13</v>
       </c>
       <c r="AR120">
-        <v>2.09</v>
+        <v>1.91</v>
       </c>
       <c r="AS120">
-        <v>1.27</v>
+        <v>1.51</v>
       </c>
       <c r="AT120">
-        <v>3.36</v>
+        <v>3.42</v>
       </c>
       <c r="AU120">
         <v>4</v>
@@ -25976,25 +25976,25 @@
         <v>1.57</v>
       </c>
       <c r="AN121">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="AO121">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AP121">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AQ121">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR121">
-        <v>1.59</v>
+        <v>1.46</v>
       </c>
       <c r="AS121">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AT121">
-        <v>3.16</v>
+        <v>3.09</v>
       </c>
       <c r="AU121">
         <v>5</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="257">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -559,6 +559,18 @@
     <t>['18', '4501', '9004']</t>
   </si>
   <si>
+    <t>['53']</t>
+  </si>
+  <si>
+    <t>['33']</t>
+  </si>
+  <si>
+    <t>['76']</t>
+  </si>
+  <si>
+    <t>['15', '75']</t>
+  </si>
+  <si>
     <t>['53', '79']</t>
   </si>
   <si>
@@ -575,9 +587,6 @@
   </si>
   <si>
     <t>['20']</t>
-  </si>
-  <si>
-    <t>['76']</t>
   </si>
   <si>
     <t>['11', '90+3']</t>
@@ -742,9 +751,6 @@
     <t>['8', '67']</t>
   </si>
   <si>
-    <t>['53']</t>
-  </si>
-  <si>
     <t>['57']</t>
   </si>
   <si>
@@ -773,6 +779,12 @@
   </si>
   <si>
     <t>['29']</t>
+  </si>
+  <si>
+    <t>['32', '44']</t>
+  </si>
+  <si>
+    <t>['6', '10']</t>
   </si>
 </sst>
 </file>
@@ -1134,7 +1146,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP121"/>
+  <dimension ref="A1:BP125"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1468,10 +1480,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ2">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1674,10 +1686,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ3">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1802,7 +1814,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2008,7 +2020,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="Q5">
         <v>2.85</v>
@@ -2086,10 +2098,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AQ5">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2214,7 +2226,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="Q6">
         <v>2.2</v>
@@ -2626,7 +2638,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="Q8">
         <v>2.04</v>
@@ -2704,10 +2716,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ8">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2832,7 +2844,7 @@
         <v>92</v>
       </c>
       <c r="P9" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="Q9">
         <v>1.5</v>
@@ -3038,7 +3050,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="Q10">
         <v>2.1</v>
@@ -3325,7 +3337,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ11">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR11">
         <v>1.91</v>
@@ -3450,7 +3462,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="Q12">
         <v>3.1</v>
@@ -3528,7 +3540,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AQ12">
         <v>0.93</v>
@@ -3656,7 +3668,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -3734,7 +3746,7 @@
         <v>1</v>
       </c>
       <c r="AP13">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AQ13">
         <v>1</v>
@@ -3862,7 +3874,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q14">
         <v>2.13</v>
@@ -3940,7 +3952,7 @@
         <v>3</v>
       </c>
       <c r="AP14">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ14">
         <v>2.33</v>
@@ -4068,7 +4080,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q15">
         <v>3.2</v>
@@ -4274,7 +4286,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q16">
         <v>1.78</v>
@@ -4352,10 +4364,10 @@
         <v>1</v>
       </c>
       <c r="AP16">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ16">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AR16">
         <v>2.91</v>
@@ -4558,10 +4570,10 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ17">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR17">
         <v>1.65</v>
@@ -4686,7 +4698,7 @@
         <v>100</v>
       </c>
       <c r="P18" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q18">
         <v>5.5</v>
@@ -4764,7 +4776,7 @@
         <v>3</v>
       </c>
       <c r="AP18">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ18">
         <v>2.07</v>
@@ -4892,7 +4904,7 @@
         <v>88</v>
       </c>
       <c r="P19" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q19">
         <v>3.75</v>
@@ -4970,7 +4982,7 @@
         <v>1</v>
       </c>
       <c r="AP19">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ19">
         <v>1.33</v>
@@ -5098,7 +5110,7 @@
         <v>101</v>
       </c>
       <c r="P20" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q20">
         <v>3.25</v>
@@ -5385,7 +5397,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ21">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR21">
         <v>1.25</v>
@@ -5588,10 +5600,10 @@
         <v>0.5</v>
       </c>
       <c r="AP22">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ22">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR22">
         <v>2.35</v>
@@ -5716,7 +5728,7 @@
         <v>104</v>
       </c>
       <c r="P23" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q23">
         <v>4</v>
@@ -5797,7 +5809,7 @@
         <v>1</v>
       </c>
       <c r="AQ23">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AR23">
         <v>1.53</v>
@@ -5922,7 +5934,7 @@
         <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q24">
         <v>4.75</v>
@@ -6000,7 +6012,7 @@
         <v>2</v>
       </c>
       <c r="AP24">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AQ24">
         <v>1.6</v>
@@ -6128,7 +6140,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -6209,7 +6221,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ25">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AR25">
         <v>1.2</v>
@@ -6334,7 +6346,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q26">
         <v>2.88</v>
@@ -6415,7 +6427,7 @@
         <v>1</v>
       </c>
       <c r="AQ26">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR26">
         <v>1.38</v>
@@ -6824,10 +6836,10 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AQ28">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR28">
         <v>0.84</v>
@@ -6952,7 +6964,7 @@
         <v>110</v>
       </c>
       <c r="P29" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q29">
         <v>1.83</v>
@@ -7030,7 +7042,7 @@
         <v>1.33</v>
       </c>
       <c r="AP29">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ29">
         <v>1.33</v>
@@ -7236,7 +7248,7 @@
         <v>1.33</v>
       </c>
       <c r="AP30">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AQ30">
         <v>1.13</v>
@@ -7364,7 +7376,7 @@
         <v>88</v>
       </c>
       <c r="P31" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q31">
         <v>2.9</v>
@@ -7445,7 +7457,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ31">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AR31">
         <v>2.34</v>
@@ -7570,7 +7582,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q32">
         <v>3.42</v>
@@ -7648,7 +7660,7 @@
         <v>1.67</v>
       </c>
       <c r="AP32">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ32">
         <v>2.33</v>
@@ -7776,7 +7788,7 @@
         <v>113</v>
       </c>
       <c r="P33" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q33">
         <v>1.56</v>
@@ -7857,7 +7869,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ33">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR33">
         <v>2.12</v>
@@ -7982,7 +7994,7 @@
         <v>114</v>
       </c>
       <c r="P34" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q34">
         <v>3.25</v>
@@ -8188,7 +8200,7 @@
         <v>115</v>
       </c>
       <c r="P35" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q35">
         <v>4.25</v>
@@ -8266,7 +8278,7 @@
         <v>1.75</v>
       </c>
       <c r="AP35">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AQ35">
         <v>1.6</v>
@@ -8394,7 +8406,7 @@
         <v>116</v>
       </c>
       <c r="P36" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q36">
         <v>3.15</v>
@@ -8472,10 +8484,10 @@
         <v>2</v>
       </c>
       <c r="AP36">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ36">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AR36">
         <v>1.35</v>
@@ -8600,7 +8612,7 @@
         <v>117</v>
       </c>
       <c r="P37" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="Q37">
         <v>2.75</v>
@@ -8678,10 +8690,10 @@
         <v>0.25</v>
       </c>
       <c r="AP37">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AQ37">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR37">
         <v>1.47</v>
@@ -8884,7 +8896,7 @@
         <v>1.25</v>
       </c>
       <c r="AP38">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ38">
         <v>1.13</v>
@@ -9012,7 +9024,7 @@
         <v>119</v>
       </c>
       <c r="P39" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q39">
         <v>2.88</v>
@@ -9093,7 +9105,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ39">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AR39">
         <v>2.23</v>
@@ -9505,7 +9517,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ41">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR41">
         <v>1.18</v>
@@ -9836,7 +9848,7 @@
         <v>123</v>
       </c>
       <c r="P43" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q43">
         <v>3</v>
@@ -9914,10 +9926,10 @@
         <v>0.2</v>
       </c>
       <c r="AP43">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AQ43">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR43">
         <v>1.61</v>
@@ -10042,7 +10054,7 @@
         <v>124</v>
       </c>
       <c r="P44" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q44">
         <v>3.2</v>
@@ -10123,7 +10135,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ44">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AR44">
         <v>1.42</v>
@@ -10248,7 +10260,7 @@
         <v>88</v>
       </c>
       <c r="P45" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q45">
         <v>7.5</v>
@@ -10326,10 +10338,10 @@
         <v>2</v>
       </c>
       <c r="AP45">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AQ45">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AR45">
         <v>1.31</v>
@@ -10532,7 +10544,7 @@
         <v>1.4</v>
       </c>
       <c r="AP46">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ46">
         <v>1.33</v>
@@ -10660,7 +10672,7 @@
         <v>126</v>
       </c>
       <c r="P47" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q47">
         <v>1.95</v>
@@ -10738,7 +10750,7 @@
         <v>1.6</v>
       </c>
       <c r="AP47">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ47">
         <v>1.33</v>
@@ -10866,7 +10878,7 @@
         <v>127</v>
       </c>
       <c r="P48" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q48">
         <v>3.7</v>
@@ -10944,7 +10956,7 @@
         <v>2.17</v>
       </c>
       <c r="AP48">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ48">
         <v>1.6</v>
@@ -11072,7 +11084,7 @@
         <v>128</v>
       </c>
       <c r="P49" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q49">
         <v>4.33</v>
@@ -11150,7 +11162,7 @@
         <v>1.8</v>
       </c>
       <c r="AP49">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ49">
         <v>2.33</v>
@@ -11278,7 +11290,7 @@
         <v>129</v>
       </c>
       <c r="P50" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="Q50">
         <v>2.65</v>
@@ -11359,7 +11371,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ50">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR50">
         <v>1.42</v>
@@ -11484,7 +11496,7 @@
         <v>130</v>
       </c>
       <c r="P51" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q51">
         <v>4.15</v>
@@ -11562,7 +11574,7 @@
         <v>2.2</v>
       </c>
       <c r="AP51">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ51">
         <v>2.07</v>
@@ -11896,7 +11908,7 @@
         <v>132</v>
       </c>
       <c r="P53" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q53">
         <v>1.8</v>
@@ -11977,7 +11989,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ53">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR53">
         <v>1.35</v>
@@ -12102,7 +12114,7 @@
         <v>104</v>
       </c>
       <c r="P54" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q54">
         <v>1.71</v>
@@ -12180,7 +12192,7 @@
         <v>1.17</v>
       </c>
       <c r="AP54">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ54">
         <v>1.33</v>
@@ -12308,7 +12320,7 @@
         <v>133</v>
       </c>
       <c r="P55" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q55">
         <v>1.45</v>
@@ -12386,10 +12398,10 @@
         <v>0.33</v>
       </c>
       <c r="AP55">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ55">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR55">
         <v>2.3</v>
@@ -12592,10 +12604,10 @@
         <v>0.71</v>
       </c>
       <c r="AP56">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ56">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR56">
         <v>2.35</v>
@@ -12720,7 +12732,7 @@
         <v>135</v>
       </c>
       <c r="P57" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -13004,7 +13016,7 @@
         <v>1.14</v>
       </c>
       <c r="AP58">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AQ58">
         <v>1.33</v>
@@ -13210,7 +13222,7 @@
         <v>1.29</v>
       </c>
       <c r="AP59">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ59">
         <v>1.13</v>
@@ -13419,7 +13431,7 @@
         <v>1</v>
       </c>
       <c r="AQ60">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR60">
         <v>1.49</v>
@@ -13622,7 +13634,7 @@
         <v>0.86</v>
       </c>
       <c r="AP61">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AQ61">
         <v>0.93</v>
@@ -13828,7 +13840,7 @@
         <v>1.29</v>
       </c>
       <c r="AP62">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ62">
         <v>1.33</v>
@@ -13956,7 +13968,7 @@
         <v>140</v>
       </c>
       <c r="P63" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q63">
         <v>2.88</v>
@@ -14037,7 +14049,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ63">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AR63">
         <v>2.01</v>
@@ -14368,7 +14380,7 @@
         <v>142</v>
       </c>
       <c r="P65" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q65">
         <v>4.5</v>
@@ -14574,7 +14586,7 @@
         <v>143</v>
       </c>
       <c r="P66" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q66">
         <v>5.2</v>
@@ -14652,10 +14664,10 @@
         <v>2.13</v>
       </c>
       <c r="AP66">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AQ66">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AR66">
         <v>1.26</v>
@@ -14780,7 +14792,7 @@
         <v>144</v>
       </c>
       <c r="P67" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q67">
         <v>3.22</v>
@@ -14986,7 +14998,7 @@
         <v>88</v>
       </c>
       <c r="P68" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q68">
         <v>3.24</v>
@@ -15067,7 +15079,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ68">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AR68">
         <v>2.01</v>
@@ -15192,7 +15204,7 @@
         <v>145</v>
       </c>
       <c r="P69" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q69">
         <v>3.18</v>
@@ -15270,10 +15282,10 @@
         <v>1.63</v>
       </c>
       <c r="AP69">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ69">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AR69">
         <v>1.4</v>
@@ -15398,7 +15410,7 @@
         <v>124</v>
       </c>
       <c r="P70" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q70">
         <v>3.22</v>
@@ -15476,10 +15488,10 @@
         <v>1.38</v>
       </c>
       <c r="AP70">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AQ70">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR70">
         <v>1.18</v>
@@ -15604,7 +15616,7 @@
         <v>146</v>
       </c>
       <c r="P71" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q71">
         <v>2.1</v>
@@ -15685,7 +15697,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ71">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR71">
         <v>1.44</v>
@@ -15810,7 +15822,7 @@
         <v>147</v>
       </c>
       <c r="P72" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q72">
         <v>2.75</v>
@@ -16097,7 +16109,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ73">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AR73">
         <v>1.3</v>
@@ -16222,7 +16234,7 @@
         <v>148</v>
       </c>
       <c r="P74" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q74">
         <v>2.2</v>
@@ -16303,7 +16315,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ74">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR74">
         <v>1.39</v>
@@ -16428,7 +16440,7 @@
         <v>149</v>
       </c>
       <c r="P75" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -16509,7 +16521,7 @@
         <v>1</v>
       </c>
       <c r="AQ75">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR75">
         <v>1.39</v>
@@ -16634,7 +16646,7 @@
         <v>150</v>
       </c>
       <c r="P76" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q76">
         <v>1.57</v>
@@ -16715,7 +16727,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ76">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR76">
         <v>1.9</v>
@@ -16840,7 +16852,7 @@
         <v>151</v>
       </c>
       <c r="P77" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q77">
         <v>2.63</v>
@@ -17124,10 +17136,10 @@
         <v>1.33</v>
       </c>
       <c r="AP78">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ78">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR78">
         <v>1.25</v>
@@ -17330,10 +17342,10 @@
         <v>2.56</v>
       </c>
       <c r="AP79">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ79">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AR79">
         <v>2.1</v>
@@ -17458,7 +17470,7 @@
         <v>88</v>
       </c>
       <c r="P80" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q80">
         <v>3.6</v>
@@ -17664,7 +17676,7 @@
         <v>154</v>
       </c>
       <c r="P81" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q81">
         <v>2.6</v>
@@ -17745,7 +17757,7 @@
         <v>1</v>
       </c>
       <c r="AQ81">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AR81">
         <v>1.44</v>
@@ -17870,7 +17882,7 @@
         <v>88</v>
       </c>
       <c r="P82" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q82">
         <v>4.5</v>
@@ -17948,7 +17960,7 @@
         <v>1.89</v>
       </c>
       <c r="AP82">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ82">
         <v>2.07</v>
@@ -18154,10 +18166,10 @@
         <v>0.5</v>
       </c>
       <c r="AP83">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AQ83">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR83">
         <v>1.24</v>
@@ -18360,7 +18372,7 @@
         <v>1.5</v>
       </c>
       <c r="AP84">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ84">
         <v>1.33</v>
@@ -18488,7 +18500,7 @@
         <v>157</v>
       </c>
       <c r="P85" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q85">
         <v>4</v>
@@ -18694,7 +18706,7 @@
         <v>114</v>
       </c>
       <c r="P86" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q86">
         <v>5.5</v>
@@ -18772,10 +18784,10 @@
         <v>2.3</v>
       </c>
       <c r="AP86">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AQ86">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AR86">
         <v>1.67</v>
@@ -18978,7 +18990,7 @@
         <v>1</v>
       </c>
       <c r="AP87">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ87">
         <v>0.93</v>
@@ -19106,7 +19118,7 @@
         <v>158</v>
       </c>
       <c r="P88" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q88">
         <v>1.53</v>
@@ -19187,7 +19199,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ88">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR88">
         <v>1.91</v>
@@ -19390,10 +19402,10 @@
         <v>1.6</v>
       </c>
       <c r="AP89">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ89">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR89">
         <v>2.1</v>
@@ -19518,7 +19530,7 @@
         <v>88</v>
       </c>
       <c r="P90" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q90">
         <v>6</v>
@@ -19596,10 +19608,10 @@
         <v>2.36</v>
       </c>
       <c r="AP90">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AQ90">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AR90">
         <v>1.67</v>
@@ -19724,7 +19736,7 @@
         <v>160</v>
       </c>
       <c r="P91" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q91">
         <v>2.2</v>
@@ -19930,7 +19942,7 @@
         <v>161</v>
       </c>
       <c r="P92" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q92">
         <v>1.8</v>
@@ -20136,7 +20148,7 @@
         <v>88</v>
       </c>
       <c r="P93" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="Q93">
         <v>3.5</v>
@@ -20214,7 +20226,7 @@
         <v>0.7</v>
       </c>
       <c r="AP93">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AQ93">
         <v>1</v>
@@ -20420,7 +20432,7 @@
         <v>1.09</v>
       </c>
       <c r="AP94">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ94">
         <v>1.33</v>
@@ -20548,7 +20560,7 @@
         <v>162</v>
       </c>
       <c r="P95" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q95">
         <v>2.88</v>
@@ -20626,7 +20638,7 @@
         <v>1.18</v>
       </c>
       <c r="AP95">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ95">
         <v>1.13</v>
@@ -20754,7 +20766,7 @@
         <v>163</v>
       </c>
       <c r="P96" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q96">
         <v>2.38</v>
@@ -21041,7 +21053,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ97">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR97">
         <v>1.47</v>
@@ -21166,7 +21178,7 @@
         <v>88</v>
       </c>
       <c r="P98" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q98">
         <v>5.25</v>
@@ -21247,7 +21259,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ98">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AR98">
         <v>1.52</v>
@@ -21372,7 +21384,7 @@
         <v>165</v>
       </c>
       <c r="P99" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q99">
         <v>3.52</v>
@@ -21450,10 +21462,10 @@
         <v>1.33</v>
       </c>
       <c r="AP99">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AQ99">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AR99">
         <v>1.24</v>
@@ -21578,7 +21590,7 @@
         <v>166</v>
       </c>
       <c r="P100" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q100">
         <v>1.79</v>
@@ -21656,10 +21668,10 @@
         <v>1.45</v>
       </c>
       <c r="AP100">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ100">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR100">
         <v>2.07</v>
@@ -21784,7 +21796,7 @@
         <v>127</v>
       </c>
       <c r="P101" t="s">
-        <v>242</v>
+        <v>181</v>
       </c>
       <c r="Q101">
         <v>5.55</v>
@@ -21862,7 +21874,7 @@
         <v>2.27</v>
       </c>
       <c r="AP101">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AQ101">
         <v>2.33</v>
@@ -21990,7 +22002,7 @@
         <v>114</v>
       </c>
       <c r="P102" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q102">
         <v>2.3</v>
@@ -22277,7 +22289,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ103">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR103">
         <v>1.53</v>
@@ -22480,10 +22492,10 @@
         <v>0.62</v>
       </c>
       <c r="AP104">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ104">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR104">
         <v>1.54</v>
@@ -22608,7 +22620,7 @@
         <v>168</v>
       </c>
       <c r="P105" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q105">
         <v>3.54</v>
@@ -22892,7 +22904,7 @@
         <v>1.38</v>
       </c>
       <c r="AP106">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ106">
         <v>1.33</v>
@@ -23020,7 +23032,7 @@
         <v>169</v>
       </c>
       <c r="P107" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q107">
         <v>1.49</v>
@@ -23101,7 +23113,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ107">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR107">
         <v>1.68</v>
@@ -23307,7 +23319,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ108">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AR108">
         <v>1.19</v>
@@ -23432,7 +23444,7 @@
         <v>171</v>
       </c>
       <c r="P109" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q109">
         <v>5.2</v>
@@ -23513,7 +23525,7 @@
         <v>1</v>
       </c>
       <c r="AQ109">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AR109">
         <v>1.54</v>
@@ -23716,7 +23728,7 @@
         <v>1.62</v>
       </c>
       <c r="AP110">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ110">
         <v>1.6</v>
@@ -23925,7 +23937,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ111">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR111">
         <v>1.69</v>
@@ -24050,7 +24062,7 @@
         <v>174</v>
       </c>
       <c r="P112" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24256,7 +24268,7 @@
         <v>175</v>
       </c>
       <c r="P113" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q113">
         <v>3.04</v>
@@ -24337,7 +24349,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ113">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR113">
         <v>1.19</v>
@@ -24540,10 +24552,10 @@
         <v>1.57</v>
       </c>
       <c r="AP114">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ114">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AR114">
         <v>2.1</v>
@@ -24668,7 +24680,7 @@
         <v>88</v>
       </c>
       <c r="P115" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q115">
         <v>3.5</v>
@@ -24746,7 +24758,7 @@
         <v>1.21</v>
       </c>
       <c r="AP115">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AQ115">
         <v>1.33</v>
@@ -24952,10 +24964,10 @@
         <v>1.29</v>
       </c>
       <c r="AP116">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AQ116">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR116">
         <v>1.24</v>
@@ -25080,7 +25092,7 @@
         <v>178</v>
       </c>
       <c r="P117" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q117">
         <v>1.95</v>
@@ -25161,7 +25173,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ117">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR117">
         <v>1.89</v>
@@ -25286,7 +25298,7 @@
         <v>88</v>
       </c>
       <c r="P118" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q118">
         <v>5.5</v>
@@ -25364,7 +25376,7 @@
         <v>2.29</v>
       </c>
       <c r="AP118">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AQ118">
         <v>2.33</v>
@@ -25570,7 +25582,7 @@
         <v>1</v>
       </c>
       <c r="AP119">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ119">
         <v>0.93</v>
@@ -25904,7 +25916,7 @@
         <v>144</v>
       </c>
       <c r="P121" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q121">
         <v>3</v>
@@ -26061,6 +26073,830 @@
       </c>
       <c r="BP121">
         <v>1.43</v>
+      </c>
+    </row>
+    <row r="122" spans="1:68">
+      <c r="A122" s="1">
+        <v>121</v>
+      </c>
+      <c r="B122">
+        <v>7825312</v>
+      </c>
+      <c r="C122" t="s">
+        <v>68</v>
+      </c>
+      <c r="D122" t="s">
+        <v>69</v>
+      </c>
+      <c r="E122" s="2">
+        <v>45837.3125</v>
+      </c>
+      <c r="F122">
+        <v>16</v>
+      </c>
+      <c r="G122" t="s">
+        <v>85</v>
+      </c>
+      <c r="H122" t="s">
+        <v>71</v>
+      </c>
+      <c r="I122">
+        <v>0</v>
+      </c>
+      <c r="J122">
+        <v>2</v>
+      </c>
+      <c r="K122">
+        <v>2</v>
+      </c>
+      <c r="L122">
+        <v>1</v>
+      </c>
+      <c r="M122">
+        <v>2</v>
+      </c>
+      <c r="N122">
+        <v>3</v>
+      </c>
+      <c r="O122" t="s">
+        <v>181</v>
+      </c>
+      <c r="P122" t="s">
+        <v>255</v>
+      </c>
+      <c r="Q122">
+        <v>7.1</v>
+      </c>
+      <c r="R122">
+        <v>2.57</v>
+      </c>
+      <c r="S122">
+        <v>1.74</v>
+      </c>
+      <c r="T122">
+        <v>1.24</v>
+      </c>
+      <c r="U122">
+        <v>3.5</v>
+      </c>
+      <c r="V122">
+        <v>2.29</v>
+      </c>
+      <c r="W122">
+        <v>1.58</v>
+      </c>
+      <c r="X122">
+        <v>5.1</v>
+      </c>
+      <c r="Y122">
+        <v>1.12</v>
+      </c>
+      <c r="Z122">
+        <v>7.4</v>
+      </c>
+      <c r="AA122">
+        <v>5.3</v>
+      </c>
+      <c r="AB122">
+        <v>1.29</v>
+      </c>
+      <c r="AC122">
+        <v>1.01</v>
+      </c>
+      <c r="AD122">
+        <v>13</v>
+      </c>
+      <c r="AE122">
+        <v>1.13</v>
+      </c>
+      <c r="AF122">
+        <v>4.6</v>
+      </c>
+      <c r="AG122">
+        <v>1.58</v>
+      </c>
+      <c r="AH122">
+        <v>2.37</v>
+      </c>
+      <c r="AI122">
+        <v>1.85</v>
+      </c>
+      <c r="AJ122">
+        <v>1.85</v>
+      </c>
+      <c r="AK122">
+        <v>3.28</v>
+      </c>
+      <c r="AL122">
+        <v>1.14</v>
+      </c>
+      <c r="AM122">
+        <v>1.06</v>
+      </c>
+      <c r="AN122">
+        <v>0.53</v>
+      </c>
+      <c r="AO122">
+        <v>2.33</v>
+      </c>
+      <c r="AP122">
+        <v>0.5</v>
+      </c>
+      <c r="AQ122">
+        <v>2.38</v>
+      </c>
+      <c r="AR122">
+        <v>1.26</v>
+      </c>
+      <c r="AS122">
+        <v>2.12</v>
+      </c>
+      <c r="AT122">
+        <v>3.38</v>
+      </c>
+      <c r="AU122">
+        <v>6</v>
+      </c>
+      <c r="AV122">
+        <v>6</v>
+      </c>
+      <c r="AW122">
+        <v>6</v>
+      </c>
+      <c r="AX122">
+        <v>10</v>
+      </c>
+      <c r="AY122">
+        <v>12</v>
+      </c>
+      <c r="AZ122">
+        <v>16</v>
+      </c>
+      <c r="BA122">
+        <v>4</v>
+      </c>
+      <c r="BB122">
+        <v>7</v>
+      </c>
+      <c r="BC122">
+        <v>11</v>
+      </c>
+      <c r="BD122">
+        <v>3.65</v>
+      </c>
+      <c r="BE122">
+        <v>7.5</v>
+      </c>
+      <c r="BF122">
+        <v>1.32</v>
+      </c>
+      <c r="BG122">
+        <v>1.25</v>
+      </c>
+      <c r="BH122">
+        <v>3.45</v>
+      </c>
+      <c r="BI122">
+        <v>1.44</v>
+      </c>
+      <c r="BJ122">
+        <v>2.55</v>
+      </c>
+      <c r="BK122">
+        <v>1.71</v>
+      </c>
+      <c r="BL122">
+        <v>2</v>
+      </c>
+      <c r="BM122">
+        <v>2.08</v>
+      </c>
+      <c r="BN122">
+        <v>1.65</v>
+      </c>
+      <c r="BO122">
+        <v>2.65</v>
+      </c>
+      <c r="BP122">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="123" spans="1:68">
+      <c r="A123" s="1">
+        <v>122</v>
+      </c>
+      <c r="B123">
+        <v>7825313</v>
+      </c>
+      <c r="C123" t="s">
+        <v>68</v>
+      </c>
+      <c r="D123" t="s">
+        <v>69</v>
+      </c>
+      <c r="E123" s="2">
+        <v>45837.3125</v>
+      </c>
+      <c r="F123">
+        <v>16</v>
+      </c>
+      <c r="G123" t="s">
+        <v>79</v>
+      </c>
+      <c r="H123" t="s">
+        <v>73</v>
+      </c>
+      <c r="I123">
+        <v>1</v>
+      </c>
+      <c r="J123">
+        <v>0</v>
+      </c>
+      <c r="K123">
+        <v>1</v>
+      </c>
+      <c r="L123">
+        <v>1</v>
+      </c>
+      <c r="M123">
+        <v>0</v>
+      </c>
+      <c r="N123">
+        <v>1</v>
+      </c>
+      <c r="O123" t="s">
+        <v>182</v>
+      </c>
+      <c r="P123" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q123">
+        <v>1.98</v>
+      </c>
+      <c r="R123">
+        <v>2.35</v>
+      </c>
+      <c r="S123">
+        <v>5.7</v>
+      </c>
+      <c r="T123">
+        <v>1.3</v>
+      </c>
+      <c r="U123">
+        <v>3.22</v>
+      </c>
+      <c r="V123">
+        <v>2.5</v>
+      </c>
+      <c r="W123">
+        <v>1.47</v>
+      </c>
+      <c r="X123">
+        <v>5.75</v>
+      </c>
+      <c r="Y123">
+        <v>1.08</v>
+      </c>
+      <c r="Z123">
+        <v>1.5</v>
+      </c>
+      <c r="AA123">
+        <v>4.33</v>
+      </c>
+      <c r="AB123">
+        <v>6.25</v>
+      </c>
+      <c r="AC123">
+        <v>1.01</v>
+      </c>
+      <c r="AD123">
+        <v>11</v>
+      </c>
+      <c r="AE123">
+        <v>1.18</v>
+      </c>
+      <c r="AF123">
+        <v>3.92</v>
+      </c>
+      <c r="AG123">
+        <v>1.71</v>
+      </c>
+      <c r="AH123">
+        <v>2.09</v>
+      </c>
+      <c r="AI123">
+        <v>1.8</v>
+      </c>
+      <c r="AJ123">
+        <v>1.9</v>
+      </c>
+      <c r="AK123">
+        <v>1.11</v>
+      </c>
+      <c r="AL123">
+        <v>1.2</v>
+      </c>
+      <c r="AM123">
+        <v>2.52</v>
+      </c>
+      <c r="AN123">
+        <v>1.2</v>
+      </c>
+      <c r="AO123">
+        <v>0.53</v>
+      </c>
+      <c r="AP123">
+        <v>1.31</v>
+      </c>
+      <c r="AQ123">
+        <v>0.5</v>
+      </c>
+      <c r="AR123">
+        <v>1.27</v>
+      </c>
+      <c r="AS123">
+        <v>1.33</v>
+      </c>
+      <c r="AT123">
+        <v>2.6</v>
+      </c>
+      <c r="AU123">
+        <v>6</v>
+      </c>
+      <c r="AV123">
+        <v>5</v>
+      </c>
+      <c r="AW123">
+        <v>6</v>
+      </c>
+      <c r="AX123">
+        <v>15</v>
+      </c>
+      <c r="AY123">
+        <v>12</v>
+      </c>
+      <c r="AZ123">
+        <v>20</v>
+      </c>
+      <c r="BA123">
+        <v>8</v>
+      </c>
+      <c r="BB123">
+        <v>8</v>
+      </c>
+      <c r="BC123">
+        <v>16</v>
+      </c>
+      <c r="BD123">
+        <v>1.45</v>
+      </c>
+      <c r="BE123">
+        <v>7</v>
+      </c>
+      <c r="BF123">
+        <v>3.05</v>
+      </c>
+      <c r="BG123">
+        <v>1.3</v>
+      </c>
+      <c r="BH123">
+        <v>3.15</v>
+      </c>
+      <c r="BI123">
+        <v>1.5</v>
+      </c>
+      <c r="BJ123">
+        <v>2.33</v>
+      </c>
+      <c r="BK123">
+        <v>1.84</v>
+      </c>
+      <c r="BL123">
+        <v>1.84</v>
+      </c>
+      <c r="BM123">
+        <v>2.3</v>
+      </c>
+      <c r="BN123">
+        <v>1.54</v>
+      </c>
+      <c r="BO123">
+        <v>2.9</v>
+      </c>
+      <c r="BP123">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="124" spans="1:68">
+      <c r="A124" s="1">
+        <v>123</v>
+      </c>
+      <c r="B124">
+        <v>7825314</v>
+      </c>
+      <c r="C124" t="s">
+        <v>68</v>
+      </c>
+      <c r="D124" t="s">
+        <v>69</v>
+      </c>
+      <c r="E124" s="2">
+        <v>45837.33333333334</v>
+      </c>
+      <c r="F124">
+        <v>16</v>
+      </c>
+      <c r="G124" t="s">
+        <v>78</v>
+      </c>
+      <c r="H124" t="s">
+        <v>76</v>
+      </c>
+      <c r="I124">
+        <v>0</v>
+      </c>
+      <c r="J124">
+        <v>2</v>
+      </c>
+      <c r="K124">
+        <v>2</v>
+      </c>
+      <c r="L124">
+        <v>1</v>
+      </c>
+      <c r="M124">
+        <v>2</v>
+      </c>
+      <c r="N124">
+        <v>3</v>
+      </c>
+      <c r="O124" t="s">
+        <v>183</v>
+      </c>
+      <c r="P124" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q124">
+        <v>2.63</v>
+      </c>
+      <c r="R124">
+        <v>2.38</v>
+      </c>
+      <c r="S124">
+        <v>3.6</v>
+      </c>
+      <c r="T124">
+        <v>1.29</v>
+      </c>
+      <c r="U124">
+        <v>3.5</v>
+      </c>
+      <c r="V124">
+        <v>2.38</v>
+      </c>
+      <c r="W124">
+        <v>1.53</v>
+      </c>
+      <c r="X124">
+        <v>5.5</v>
+      </c>
+      <c r="Y124">
+        <v>1.14</v>
+      </c>
+      <c r="Z124">
+        <v>2.59</v>
+      </c>
+      <c r="AA124">
+        <v>3.68</v>
+      </c>
+      <c r="AB124">
+        <v>2.27</v>
+      </c>
+      <c r="AC124">
+        <v>1.03</v>
+      </c>
+      <c r="AD124">
+        <v>10</v>
+      </c>
+      <c r="AE124">
+        <v>1.18</v>
+      </c>
+      <c r="AF124">
+        <v>4.5</v>
+      </c>
+      <c r="AG124">
+        <v>1.58</v>
+      </c>
+      <c r="AH124">
+        <v>2.23</v>
+      </c>
+      <c r="AI124">
+        <v>1.57</v>
+      </c>
+      <c r="AJ124">
+        <v>2.25</v>
+      </c>
+      <c r="AK124">
+        <v>1.36</v>
+      </c>
+      <c r="AL124">
+        <v>1.22</v>
+      </c>
+      <c r="AM124">
+        <v>1.7</v>
+      </c>
+      <c r="AN124">
+        <v>0.8</v>
+      </c>
+      <c r="AO124">
+        <v>1.47</v>
+      </c>
+      <c r="AP124">
+        <v>0.75</v>
+      </c>
+      <c r="AQ124">
+        <v>1.56</v>
+      </c>
+      <c r="AR124">
+        <v>1.51</v>
+      </c>
+      <c r="AS124">
+        <v>1.69</v>
+      </c>
+      <c r="AT124">
+        <v>3.2</v>
+      </c>
+      <c r="AU124">
+        <v>5</v>
+      </c>
+      <c r="AV124">
+        <v>3</v>
+      </c>
+      <c r="AW124">
+        <v>6</v>
+      </c>
+      <c r="AX124">
+        <v>1</v>
+      </c>
+      <c r="AY124">
+        <v>11</v>
+      </c>
+      <c r="AZ124">
+        <v>4</v>
+      </c>
+      <c r="BA124">
+        <v>7</v>
+      </c>
+      <c r="BB124">
+        <v>2</v>
+      </c>
+      <c r="BC124">
+        <v>9</v>
+      </c>
+      <c r="BD124">
+        <v>1.85</v>
+      </c>
+      <c r="BE124">
+        <v>6.75</v>
+      </c>
+      <c r="BF124">
+        <v>2.1</v>
+      </c>
+      <c r="BG124">
+        <v>1.16</v>
+      </c>
+      <c r="BH124">
+        <v>4.3</v>
+      </c>
+      <c r="BI124">
+        <v>1.3</v>
+      </c>
+      <c r="BJ124">
+        <v>3.05</v>
+      </c>
+      <c r="BK124">
+        <v>1.52</v>
+      </c>
+      <c r="BL124">
+        <v>2.33</v>
+      </c>
+      <c r="BM124">
+        <v>1.81</v>
+      </c>
+      <c r="BN124">
+        <v>1.88</v>
+      </c>
+      <c r="BO124">
+        <v>2.23</v>
+      </c>
+      <c r="BP124">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="125" spans="1:68">
+      <c r="A125" s="1">
+        <v>124</v>
+      </c>
+      <c r="B125">
+        <v>7825315</v>
+      </c>
+      <c r="C125" t="s">
+        <v>68</v>
+      </c>
+      <c r="D125" t="s">
+        <v>69</v>
+      </c>
+      <c r="E125" s="2">
+        <v>45837.35763888889</v>
+      </c>
+      <c r="F125">
+        <v>16</v>
+      </c>
+      <c r="G125" t="s">
+        <v>80</v>
+      </c>
+      <c r="H125" t="s">
+        <v>70</v>
+      </c>
+      <c r="I125">
+        <v>1</v>
+      </c>
+      <c r="J125">
+        <v>0</v>
+      </c>
+      <c r="K125">
+        <v>1</v>
+      </c>
+      <c r="L125">
+        <v>2</v>
+      </c>
+      <c r="M125">
+        <v>1</v>
+      </c>
+      <c r="N125">
+        <v>3</v>
+      </c>
+      <c r="O125" t="s">
+        <v>184</v>
+      </c>
+      <c r="P125" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q125">
+        <v>5.55</v>
+      </c>
+      <c r="R125">
+        <v>2.46</v>
+      </c>
+      <c r="S125">
+        <v>1.93</v>
+      </c>
+      <c r="T125">
+        <v>1.26</v>
+      </c>
+      <c r="U125">
+        <v>3.34</v>
+      </c>
+      <c r="V125">
+        <v>2.31</v>
+      </c>
+      <c r="W125">
+        <v>1.57</v>
+      </c>
+      <c r="X125">
+        <v>5</v>
+      </c>
+      <c r="Y125">
+        <v>1.12</v>
+      </c>
+      <c r="Z125">
+        <v>5.1</v>
+      </c>
+      <c r="AA125">
+        <v>4.4</v>
+      </c>
+      <c r="AB125">
+        <v>1.48</v>
+      </c>
+      <c r="AC125">
+        <v>1.01</v>
+      </c>
+      <c r="AD125">
+        <v>13</v>
+      </c>
+      <c r="AE125">
+        <v>1.14</v>
+      </c>
+      <c r="AF125">
+        <v>4.4</v>
+      </c>
+      <c r="AG125">
+        <v>1.55</v>
+      </c>
+      <c r="AH125">
+        <v>2.3</v>
+      </c>
+      <c r="AI125">
+        <v>1.69</v>
+      </c>
+      <c r="AJ125">
+        <v>2.04</v>
+      </c>
+      <c r="AK125">
+        <v>2.61</v>
+      </c>
+      <c r="AL125">
+        <v>1.18</v>
+      </c>
+      <c r="AM125">
+        <v>1.11</v>
+      </c>
+      <c r="AN125">
+        <v>1.2</v>
+      </c>
+      <c r="AO125">
+        <v>2.2</v>
+      </c>
+      <c r="AP125">
+        <v>1.31</v>
+      </c>
+      <c r="AQ125">
+        <v>2.06</v>
+      </c>
+      <c r="AR125">
+        <v>1.53</v>
+      </c>
+      <c r="AS125">
+        <v>2.05</v>
+      </c>
+      <c r="AT125">
+        <v>3.58</v>
+      </c>
+      <c r="AU125">
+        <v>4</v>
+      </c>
+      <c r="AV125">
+        <v>7</v>
+      </c>
+      <c r="AW125">
+        <v>2</v>
+      </c>
+      <c r="AX125">
+        <v>9</v>
+      </c>
+      <c r="AY125">
+        <v>6</v>
+      </c>
+      <c r="AZ125">
+        <v>16</v>
+      </c>
+      <c r="BA125">
+        <v>2</v>
+      </c>
+      <c r="BB125">
+        <v>6</v>
+      </c>
+      <c r="BC125">
+        <v>8</v>
+      </c>
+      <c r="BD125">
+        <v>3.15</v>
+      </c>
+      <c r="BE125">
+        <v>7</v>
+      </c>
+      <c r="BF125">
+        <v>1.43</v>
+      </c>
+      <c r="BG125">
+        <v>1.26</v>
+      </c>
+      <c r="BH125">
+        <v>3.4</v>
+      </c>
+      <c r="BI125">
+        <v>1.46</v>
+      </c>
+      <c r="BJ125">
+        <v>2.5</v>
+      </c>
+      <c r="BK125">
+        <v>1.73</v>
+      </c>
+      <c r="BL125">
+        <v>1.96</v>
+      </c>
+      <c r="BM125">
+        <v>2.12</v>
+      </c>
+      <c r="BN125">
+        <v>1.63</v>
+      </c>
+      <c r="BO125">
+        <v>2.7</v>
+      </c>
+      <c r="BP125">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
@@ -26833,22 +26833,22 @@
         <v>3.58</v>
       </c>
       <c r="AU125">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV125">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW125">
         <v>2</v>
       </c>
       <c r="AX125">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY125">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ125">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BA125">
         <v>2</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="262">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -571,6 +571,15 @@
     <t>['15', '75']</t>
   </si>
   <si>
+    <t>['50', '85']</t>
+  </si>
+  <si>
+    <t>['55', '83']</t>
+  </si>
+  <si>
+    <t>['9']</t>
+  </si>
+  <si>
     <t>['53', '79']</t>
   </si>
   <si>
@@ -785,6 +794,12 @@
   </si>
   <si>
     <t>['6', '10']</t>
+  </si>
+  <si>
+    <t>['6', '32']</t>
+  </si>
+  <si>
+    <t>['63', '77']</t>
   </si>
 </sst>
 </file>
@@ -1146,7 +1161,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP125"/>
+  <dimension ref="A1:BP129"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1814,7 +1829,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -1892,10 +1907,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ4">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2020,7 +2035,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q5">
         <v>2.85</v>
@@ -2226,7 +2241,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q6">
         <v>2.2</v>
@@ -2304,10 +2319,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ6">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2510,7 +2525,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AQ7">
         <v>1</v>
@@ -2638,7 +2653,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q8">
         <v>2.04</v>
@@ -2844,7 +2859,7 @@
         <v>92</v>
       </c>
       <c r="P9" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q9">
         <v>1.5</v>
@@ -2922,10 +2937,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ9">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3050,7 +3065,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q10">
         <v>2.1</v>
@@ -3128,10 +3143,10 @@
         <v>1</v>
       </c>
       <c r="AP10">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AQ10">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AR10">
         <v>2.21</v>
@@ -3334,7 +3349,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ11">
         <v>0.5</v>
@@ -3462,7 +3477,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q12">
         <v>3.1</v>
@@ -3543,7 +3558,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ12">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR12">
         <v>1.44</v>
@@ -3874,7 +3889,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q14">
         <v>2.13</v>
@@ -3955,7 +3970,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ14">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AR14">
         <v>2.29</v>
@@ -4080,7 +4095,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q15">
         <v>3.2</v>
@@ -4158,10 +4173,10 @@
         <v>1</v>
       </c>
       <c r="AP15">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ15">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR15">
         <v>1.22</v>
@@ -4286,7 +4301,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q16">
         <v>1.78</v>
@@ -4698,7 +4713,7 @@
         <v>100</v>
       </c>
       <c r="P18" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q18">
         <v>5.5</v>
@@ -4779,7 +4794,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ18">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AR18">
         <v>1.22</v>
@@ -4904,7 +4919,7 @@
         <v>88</v>
       </c>
       <c r="P19" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q19">
         <v>3.75</v>
@@ -4985,7 +5000,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ19">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR19">
         <v>0.5600000000000001</v>
@@ -5110,7 +5125,7 @@
         <v>101</v>
       </c>
       <c r="P20" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q20">
         <v>3.25</v>
@@ -5188,10 +5203,10 @@
         <v>0.5</v>
       </c>
       <c r="AP20">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AQ20">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR20">
         <v>1.47</v>
@@ -5394,7 +5409,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AQ21">
         <v>0.5</v>
@@ -5728,7 +5743,7 @@
         <v>104</v>
       </c>
       <c r="P23" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q23">
         <v>4</v>
@@ -5934,7 +5949,7 @@
         <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q24">
         <v>4.75</v>
@@ -6015,7 +6030,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ24">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AR24">
         <v>1.66</v>
@@ -6140,7 +6155,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -6218,7 +6233,7 @@
         <v>1.5</v>
       </c>
       <c r="AP25">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ25">
         <v>2.06</v>
@@ -6346,7 +6361,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q26">
         <v>2.88</v>
@@ -6630,10 +6645,10 @@
         <v>1</v>
       </c>
       <c r="AP27">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ27">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR27">
         <v>1.48</v>
@@ -6964,7 +6979,7 @@
         <v>110</v>
       </c>
       <c r="P29" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q29">
         <v>1.83</v>
@@ -7045,7 +7060,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ29">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR29">
         <v>1.96</v>
@@ -7251,7 +7266,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ30">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AR30">
         <v>1.15</v>
@@ -7376,7 +7391,7 @@
         <v>88</v>
       </c>
       <c r="P31" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q31">
         <v>2.9</v>
@@ -7454,7 +7469,7 @@
         <v>1.33</v>
       </c>
       <c r="AP31">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AQ31">
         <v>2.06</v>
@@ -7582,7 +7597,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q32">
         <v>3.42</v>
@@ -7663,7 +7678,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ32">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AR32">
         <v>2.5</v>
@@ -7788,7 +7803,7 @@
         <v>113</v>
       </c>
       <c r="P33" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q33">
         <v>1.56</v>
@@ -7866,7 +7881,7 @@
         <v>1.33</v>
       </c>
       <c r="AP33">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ33">
         <v>0.75</v>
@@ -7994,7 +8009,7 @@
         <v>114</v>
       </c>
       <c r="P34" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q34">
         <v>3.25</v>
@@ -8072,7 +8087,7 @@
         <v>0.25</v>
       </c>
       <c r="AP34">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AQ34">
         <v>1</v>
@@ -8200,7 +8215,7 @@
         <v>115</v>
       </c>
       <c r="P35" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q35">
         <v>4.25</v>
@@ -8281,7 +8296,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ35">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AR35">
         <v>0.9</v>
@@ -8406,7 +8421,7 @@
         <v>116</v>
       </c>
       <c r="P36" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q36">
         <v>3.15</v>
@@ -8612,7 +8627,7 @@
         <v>117</v>
       </c>
       <c r="P37" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q37">
         <v>2.75</v>
@@ -8899,7 +8914,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ38">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AR38">
         <v>2.27</v>
@@ -9024,7 +9039,7 @@
         <v>119</v>
       </c>
       <c r="P39" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q39">
         <v>2.88</v>
@@ -9102,7 +9117,7 @@
         <v>2.5</v>
       </c>
       <c r="AP39">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ39">
         <v>2.38</v>
@@ -9308,10 +9323,10 @@
         <v>2</v>
       </c>
       <c r="AP40">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ40">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR40">
         <v>1.25</v>
@@ -9514,7 +9529,7 @@
         <v>0.5</v>
       </c>
       <c r="AP41">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ41">
         <v>0.5</v>
@@ -9720,10 +9735,10 @@
         <v>0.6</v>
       </c>
       <c r="AP42">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AQ42">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR42">
         <v>2.14</v>
@@ -9848,7 +9863,7 @@
         <v>123</v>
       </c>
       <c r="P43" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q43">
         <v>3</v>
@@ -10054,7 +10069,7 @@
         <v>124</v>
       </c>
       <c r="P44" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q44">
         <v>3.2</v>
@@ -10132,7 +10147,7 @@
         <v>1.8</v>
       </c>
       <c r="AP44">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AQ44">
         <v>1.56</v>
@@ -10260,7 +10275,7 @@
         <v>88</v>
       </c>
       <c r="P45" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q45">
         <v>7.5</v>
@@ -10547,7 +10562,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ46">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR46">
         <v>1.12</v>
@@ -10672,7 +10687,7 @@
         <v>126</v>
       </c>
       <c r="P47" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q47">
         <v>1.95</v>
@@ -10753,7 +10768,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ47">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR47">
         <v>2.44</v>
@@ -10878,7 +10893,7 @@
         <v>127</v>
       </c>
       <c r="P48" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q48">
         <v>3.7</v>
@@ -10959,7 +10974,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ48">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AR48">
         <v>1.34</v>
@@ -11084,7 +11099,7 @@
         <v>128</v>
       </c>
       <c r="P49" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q49">
         <v>4.33</v>
@@ -11165,7 +11180,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ49">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AR49">
         <v>1.24</v>
@@ -11290,7 +11305,7 @@
         <v>129</v>
       </c>
       <c r="P50" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q50">
         <v>2.65</v>
@@ -11368,7 +11383,7 @@
         <v>0.67</v>
       </c>
       <c r="AP50">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AQ50">
         <v>0.5</v>
@@ -11496,7 +11511,7 @@
         <v>130</v>
       </c>
       <c r="P51" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q51">
         <v>4.15</v>
@@ -11577,7 +11592,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ51">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AR51">
         <v>1.97</v>
@@ -11780,7 +11795,7 @@
         <v>0.8</v>
       </c>
       <c r="AP52">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AQ52">
         <v>1</v>
@@ -11908,7 +11923,7 @@
         <v>132</v>
       </c>
       <c r="P53" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q53">
         <v>1.8</v>
@@ -11986,7 +12001,7 @@
         <v>1.17</v>
       </c>
       <c r="AP53">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ53">
         <v>0.75</v>
@@ -12114,7 +12129,7 @@
         <v>104</v>
       </c>
       <c r="P54" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q54">
         <v>1.71</v>
@@ -12195,7 +12210,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ54">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR54">
         <v>2.17</v>
@@ -12320,7 +12335,7 @@
         <v>133</v>
       </c>
       <c r="P55" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q55">
         <v>1.45</v>
@@ -12732,7 +12747,7 @@
         <v>135</v>
       </c>
       <c r="P57" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -12810,10 +12825,10 @@
         <v>2.29</v>
       </c>
       <c r="AP57">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ57">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AR57">
         <v>1.59</v>
@@ -13019,7 +13034,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ58">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR58">
         <v>1.25</v>
@@ -13225,7 +13240,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ59">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AR59">
         <v>1.35</v>
@@ -13637,7 +13652,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ61">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR61">
         <v>1.72</v>
@@ -13843,7 +13858,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ62">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR62">
         <v>1.85</v>
@@ -13968,7 +13983,7 @@
         <v>140</v>
       </c>
       <c r="P63" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q63">
         <v>2.88</v>
@@ -14046,7 +14061,7 @@
         <v>2</v>
       </c>
       <c r="AP63">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ63">
         <v>2.06</v>
@@ -14252,7 +14267,7 @@
         <v>1</v>
       </c>
       <c r="AP64">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ64">
         <v>1</v>
@@ -14380,7 +14395,7 @@
         <v>142</v>
       </c>
       <c r="P65" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q65">
         <v>4.5</v>
@@ -14458,10 +14473,10 @@
         <v>2</v>
       </c>
       <c r="AP65">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ65">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AR65">
         <v>1.32</v>
@@ -14586,7 +14601,7 @@
         <v>143</v>
       </c>
       <c r="P66" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q66">
         <v>5.2</v>
@@ -14792,7 +14807,7 @@
         <v>144</v>
       </c>
       <c r="P67" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q67">
         <v>3.22</v>
@@ -14870,10 +14885,10 @@
         <v>1.13</v>
       </c>
       <c r="AP67">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AQ67">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AR67">
         <v>1.29</v>
@@ -14998,7 +15013,7 @@
         <v>88</v>
       </c>
       <c r="P68" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q68">
         <v>3.24</v>
@@ -15076,7 +15091,7 @@
         <v>2.5</v>
       </c>
       <c r="AP68">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AQ68">
         <v>2.38</v>
@@ -15204,7 +15219,7 @@
         <v>145</v>
       </c>
       <c r="P69" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q69">
         <v>3.18</v>
@@ -15410,7 +15425,7 @@
         <v>124</v>
       </c>
       <c r="P70" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q70">
         <v>3.22</v>
@@ -15616,7 +15631,7 @@
         <v>146</v>
       </c>
       <c r="P71" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q71">
         <v>2.1</v>
@@ -15694,7 +15709,7 @@
         <v>1.71</v>
       </c>
       <c r="AP71">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ71">
         <v>1.31</v>
@@ -15822,7 +15837,7 @@
         <v>147</v>
       </c>
       <c r="P72" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q72">
         <v>2.75</v>
@@ -15900,10 +15915,10 @@
         <v>1</v>
       </c>
       <c r="AP72">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AQ72">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR72">
         <v>1.53</v>
@@ -16106,7 +16121,7 @@
         <v>1.44</v>
       </c>
       <c r="AP73">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AQ73">
         <v>1.56</v>
@@ -16234,7 +16249,7 @@
         <v>148</v>
       </c>
       <c r="P74" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q74">
         <v>2.2</v>
@@ -16312,7 +16327,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP74">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ74">
         <v>0.5</v>
@@ -16440,7 +16455,7 @@
         <v>149</v>
       </c>
       <c r="P75" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -16646,7 +16661,7 @@
         <v>150</v>
       </c>
       <c r="P76" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q76">
         <v>1.57</v>
@@ -16724,7 +16739,7 @@
         <v>0.33</v>
       </c>
       <c r="AP76">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AQ76">
         <v>0.5</v>
@@ -16852,7 +16867,7 @@
         <v>151</v>
       </c>
       <c r="P77" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q77">
         <v>2.63</v>
@@ -16930,10 +16945,10 @@
         <v>2</v>
       </c>
       <c r="AP77">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ77">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AR77">
         <v>1.84</v>
@@ -17470,7 +17485,7 @@
         <v>88</v>
       </c>
       <c r="P80" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q80">
         <v>3.6</v>
@@ -17548,10 +17563,10 @@
         <v>2.11</v>
       </c>
       <c r="AP80">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AQ80">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AR80">
         <v>1.6</v>
@@ -17676,7 +17691,7 @@
         <v>154</v>
       </c>
       <c r="P81" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q81">
         <v>2.6</v>
@@ -17882,7 +17897,7 @@
         <v>88</v>
       </c>
       <c r="P82" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q82">
         <v>4.5</v>
@@ -17963,7 +17978,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ82">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AR82">
         <v>1.44</v>
@@ -18375,7 +18390,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ84">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR84">
         <v>2.04</v>
@@ -18500,7 +18515,7 @@
         <v>157</v>
       </c>
       <c r="P85" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q85">
         <v>4</v>
@@ -18578,10 +18593,10 @@
         <v>1.7</v>
       </c>
       <c r="AP85">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ85">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AR85">
         <v>1.44</v>
@@ -18706,7 +18721,7 @@
         <v>114</v>
       </c>
       <c r="P86" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q86">
         <v>5.5</v>
@@ -18993,7 +19008,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ87">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR87">
         <v>1.27</v>
@@ -19118,7 +19133,7 @@
         <v>158</v>
       </c>
       <c r="P88" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q88">
         <v>1.53</v>
@@ -19196,7 +19211,7 @@
         <v>0.64</v>
       </c>
       <c r="AP88">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ88">
         <v>0.5</v>
@@ -19530,7 +19545,7 @@
         <v>88</v>
       </c>
       <c r="P90" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q90">
         <v>6</v>
@@ -19736,7 +19751,7 @@
         <v>160</v>
       </c>
       <c r="P91" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q91">
         <v>2.2</v>
@@ -19814,10 +19829,10 @@
         <v>1.36</v>
       </c>
       <c r="AP91">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AQ91">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR91">
         <v>1.94</v>
@@ -19942,7 +19957,7 @@
         <v>161</v>
       </c>
       <c r="P92" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q92">
         <v>1.8</v>
@@ -20020,10 +20035,10 @@
         <v>1</v>
       </c>
       <c r="AP92">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ92">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR92">
         <v>1.66</v>
@@ -20435,7 +20450,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ94">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR94">
         <v>1.67</v>
@@ -20560,7 +20575,7 @@
         <v>162</v>
       </c>
       <c r="P95" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q95">
         <v>2.88</v>
@@ -20641,7 +20656,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ95">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AR95">
         <v>1.49</v>
@@ -20766,7 +20781,7 @@
         <v>163</v>
       </c>
       <c r="P96" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q96">
         <v>2.38</v>
@@ -20844,7 +20859,7 @@
         <v>0.91</v>
       </c>
       <c r="AP96">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ96">
         <v>1</v>
@@ -21050,7 +21065,7 @@
         <v>1</v>
       </c>
       <c r="AP97">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ97">
         <v>0.75</v>
@@ -21178,7 +21193,7 @@
         <v>88</v>
       </c>
       <c r="P98" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q98">
         <v>5.25</v>
@@ -21256,7 +21271,7 @@
         <v>2.42</v>
       </c>
       <c r="AP98">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AQ98">
         <v>2.38</v>
@@ -21384,7 +21399,7 @@
         <v>165</v>
       </c>
       <c r="P99" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q99">
         <v>3.52</v>
@@ -21590,7 +21605,7 @@
         <v>166</v>
       </c>
       <c r="P100" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q100">
         <v>1.79</v>
@@ -21877,7 +21892,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ101">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AR101">
         <v>1.32</v>
@@ -22002,7 +22017,7 @@
         <v>114</v>
       </c>
       <c r="P102" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q102">
         <v>2.3</v>
@@ -22080,10 +22095,10 @@
         <v>1.67</v>
       </c>
       <c r="AP102">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ102">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AR102">
         <v>2.01</v>
@@ -22286,7 +22301,7 @@
         <v>0.92</v>
       </c>
       <c r="AP103">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AQ103">
         <v>0.75</v>
@@ -22620,7 +22635,7 @@
         <v>168</v>
       </c>
       <c r="P105" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q105">
         <v>3.54</v>
@@ -22698,10 +22713,10 @@
         <v>2</v>
       </c>
       <c r="AP105">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ105">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AR105">
         <v>1.42</v>
@@ -22907,7 +22922,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ106">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR106">
         <v>1.23</v>
@@ -23032,7 +23047,7 @@
         <v>169</v>
       </c>
       <c r="P107" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q107">
         <v>1.49</v>
@@ -23110,7 +23125,7 @@
         <v>0.38</v>
       </c>
       <c r="AP107">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ107">
         <v>0.5</v>
@@ -23316,7 +23331,7 @@
         <v>2.46</v>
       </c>
       <c r="AP108">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AQ108">
         <v>2.38</v>
@@ -23444,7 +23459,7 @@
         <v>171</v>
       </c>
       <c r="P109" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q109">
         <v>5.2</v>
@@ -23731,7 +23746,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ110">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AR110">
         <v>1.71</v>
@@ -23934,7 +23949,7 @@
         <v>1.38</v>
       </c>
       <c r="AP111">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ111">
         <v>1.31</v>
@@ -24062,7 +24077,7 @@
         <v>174</v>
       </c>
       <c r="P112" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24143,7 +24158,7 @@
         <v>1</v>
       </c>
       <c r="AQ112">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AR112">
         <v>1.58</v>
@@ -24268,7 +24283,7 @@
         <v>175</v>
       </c>
       <c r="P113" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q113">
         <v>3.04</v>
@@ -24346,7 +24361,7 @@
         <v>1.15</v>
       </c>
       <c r="AP113">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AQ113">
         <v>1.31</v>
@@ -24680,7 +24695,7 @@
         <v>88</v>
       </c>
       <c r="P115" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q115">
         <v>3.5</v>
@@ -24761,7 +24776,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ115">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR115">
         <v>1.33</v>
@@ -25092,7 +25107,7 @@
         <v>178</v>
       </c>
       <c r="P117" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q117">
         <v>1.95</v>
@@ -25170,7 +25185,7 @@
         <v>1.29</v>
       </c>
       <c r="AP117">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AQ117">
         <v>1.31</v>
@@ -25298,7 +25313,7 @@
         <v>88</v>
       </c>
       <c r="P118" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q118">
         <v>5.5</v>
@@ -25379,7 +25394,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ118">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AR118">
         <v>1.52</v>
@@ -25585,7 +25600,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ119">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR119">
         <v>2.07</v>
@@ -25788,10 +25803,10 @@
         <v>1.21</v>
       </c>
       <c r="AP120">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ120">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AR120">
         <v>1.91</v>
@@ -25916,7 +25931,7 @@
         <v>144</v>
       </c>
       <c r="P121" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q121">
         <v>3</v>
@@ -25994,7 +26009,7 @@
         <v>1</v>
       </c>
       <c r="AP121">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ121">
         <v>1</v>
@@ -26122,7 +26137,7 @@
         <v>181</v>
       </c>
       <c r="P122" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q122">
         <v>7.1</v>
@@ -26534,7 +26549,7 @@
         <v>183</v>
       </c>
       <c r="P124" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q124">
         <v>2.63</v>
@@ -26897,6 +26912,830 @@
       </c>
       <c r="BP125">
         <v>1.4</v>
+      </c>
+    </row>
+    <row r="126" spans="1:68">
+      <c r="A126" s="1">
+        <v>125</v>
+      </c>
+      <c r="B126">
+        <v>7825316</v>
+      </c>
+      <c r="C126" t="s">
+        <v>68</v>
+      </c>
+      <c r="D126" t="s">
+        <v>69</v>
+      </c>
+      <c r="E126" s="2">
+        <v>45838.33333333334</v>
+      </c>
+      <c r="F126">
+        <v>16</v>
+      </c>
+      <c r="G126" t="s">
+        <v>83</v>
+      </c>
+      <c r="H126" t="s">
+        <v>75</v>
+      </c>
+      <c r="I126">
+        <v>0</v>
+      </c>
+      <c r="J126">
+        <v>2</v>
+      </c>
+      <c r="K126">
+        <v>2</v>
+      </c>
+      <c r="L126">
+        <v>2</v>
+      </c>
+      <c r="M126">
+        <v>2</v>
+      </c>
+      <c r="N126">
+        <v>4</v>
+      </c>
+      <c r="O126" t="s">
+        <v>185</v>
+      </c>
+      <c r="P126" t="s">
+        <v>260</v>
+      </c>
+      <c r="Q126">
+        <v>3</v>
+      </c>
+      <c r="R126">
+        <v>2.5</v>
+      </c>
+      <c r="S126">
+        <v>2.88</v>
+      </c>
+      <c r="T126">
+        <v>1.22</v>
+      </c>
+      <c r="U126">
+        <v>4</v>
+      </c>
+      <c r="V126">
+        <v>2.1</v>
+      </c>
+      <c r="W126">
+        <v>1.67</v>
+      </c>
+      <c r="X126">
+        <v>4.5</v>
+      </c>
+      <c r="Y126">
+        <v>1.18</v>
+      </c>
+      <c r="Z126">
+        <v>2.67</v>
+      </c>
+      <c r="AA126">
+        <v>3.83</v>
+      </c>
+      <c r="AB126">
+        <v>2.16</v>
+      </c>
+      <c r="AC126">
+        <v>1.01</v>
+      </c>
+      <c r="AD126">
+        <v>17</v>
+      </c>
+      <c r="AE126">
+        <v>1.06</v>
+      </c>
+      <c r="AF126">
+        <v>6.15</v>
+      </c>
+      <c r="AG126">
+        <v>1.43</v>
+      </c>
+      <c r="AH126">
+        <v>2.62</v>
+      </c>
+      <c r="AI126">
+        <v>1.4</v>
+      </c>
+      <c r="AJ126">
+        <v>2.75</v>
+      </c>
+      <c r="AK126">
+        <v>1.54</v>
+      </c>
+      <c r="AL126">
+        <v>1.24</v>
+      </c>
+      <c r="AM126">
+        <v>1.5</v>
+      </c>
+      <c r="AN126">
+        <v>1</v>
+      </c>
+      <c r="AO126">
+        <v>1.6</v>
+      </c>
+      <c r="AP126">
+        <v>1</v>
+      </c>
+      <c r="AQ126">
+        <v>1.56</v>
+      </c>
+      <c r="AR126">
+        <v>1.68</v>
+      </c>
+      <c r="AS126">
+        <v>2.04</v>
+      </c>
+      <c r="AT126">
+        <v>3.72</v>
+      </c>
+      <c r="AU126">
+        <v>11</v>
+      </c>
+      <c r="AV126">
+        <v>6</v>
+      </c>
+      <c r="AW126">
+        <v>20</v>
+      </c>
+      <c r="AX126">
+        <v>3</v>
+      </c>
+      <c r="AY126">
+        <v>31</v>
+      </c>
+      <c r="AZ126">
+        <v>9</v>
+      </c>
+      <c r="BA126">
+        <v>8</v>
+      </c>
+      <c r="BB126">
+        <v>0</v>
+      </c>
+      <c r="BC126">
+        <v>8</v>
+      </c>
+      <c r="BD126">
+        <v>1.9</v>
+      </c>
+      <c r="BE126">
+        <v>6.75</v>
+      </c>
+      <c r="BF126">
+        <v>2.07</v>
+      </c>
+      <c r="BG126">
+        <v>1.15</v>
+      </c>
+      <c r="BH126">
+        <v>4.4</v>
+      </c>
+      <c r="BI126">
+        <v>1.29</v>
+      </c>
+      <c r="BJ126">
+        <v>3.15</v>
+      </c>
+      <c r="BK126">
+        <v>1.49</v>
+      </c>
+      <c r="BL126">
+        <v>2.4</v>
+      </c>
+      <c r="BM126">
+        <v>1.77</v>
+      </c>
+      <c r="BN126">
+        <v>1.92</v>
+      </c>
+      <c r="BO126">
+        <v>2.18</v>
+      </c>
+      <c r="BP126">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="127" spans="1:68">
+      <c r="A127" s="1">
+        <v>126</v>
+      </c>
+      <c r="B127">
+        <v>7825317</v>
+      </c>
+      <c r="C127" t="s">
+        <v>68</v>
+      </c>
+      <c r="D127" t="s">
+        <v>69</v>
+      </c>
+      <c r="E127" s="2">
+        <v>45838.35763888889</v>
+      </c>
+      <c r="F127">
+        <v>16</v>
+      </c>
+      <c r="G127" t="s">
+        <v>82</v>
+      </c>
+      <c r="H127" t="s">
+        <v>74</v>
+      </c>
+      <c r="I127">
+        <v>1</v>
+      </c>
+      <c r="J127">
+        <v>0</v>
+      </c>
+      <c r="K127">
+        <v>1</v>
+      </c>
+      <c r="L127">
+        <v>1</v>
+      </c>
+      <c r="M127">
+        <v>0</v>
+      </c>
+      <c r="N127">
+        <v>1</v>
+      </c>
+      <c r="O127" t="s">
+        <v>104</v>
+      </c>
+      <c r="P127" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q127">
+        <v>3.1</v>
+      </c>
+      <c r="R127">
+        <v>2.3</v>
+      </c>
+      <c r="S127">
+        <v>3.1</v>
+      </c>
+      <c r="T127">
+        <v>1.33</v>
+      </c>
+      <c r="U127">
+        <v>3.25</v>
+      </c>
+      <c r="V127">
+        <v>2.5</v>
+      </c>
+      <c r="W127">
+        <v>1.5</v>
+      </c>
+      <c r="X127">
+        <v>6.5</v>
+      </c>
+      <c r="Y127">
+        <v>1.11</v>
+      </c>
+      <c r="Z127">
+        <v>2.45</v>
+      </c>
+      <c r="AA127">
+        <v>3.45</v>
+      </c>
+      <c r="AB127">
+        <v>2.48</v>
+      </c>
+      <c r="AC127">
+        <v>1.01</v>
+      </c>
+      <c r="AD127">
+        <v>11</v>
+      </c>
+      <c r="AE127">
+        <v>1.18</v>
+      </c>
+      <c r="AF127">
+        <v>3.9</v>
+      </c>
+      <c r="AG127">
+        <v>1.7</v>
+      </c>
+      <c r="AH127">
+        <v>1.95</v>
+      </c>
+      <c r="AI127">
+        <v>1.62</v>
+      </c>
+      <c r="AJ127">
+        <v>2.2</v>
+      </c>
+      <c r="AK127">
+        <v>1.5</v>
+      </c>
+      <c r="AL127">
+        <v>1.28</v>
+      </c>
+      <c r="AM127">
+        <v>1.49</v>
+      </c>
+      <c r="AN127">
+        <v>1.13</v>
+      </c>
+      <c r="AO127">
+        <v>1.33</v>
+      </c>
+      <c r="AP127">
+        <v>1.25</v>
+      </c>
+      <c r="AQ127">
+        <v>1.25</v>
+      </c>
+      <c r="AR127">
+        <v>1.49</v>
+      </c>
+      <c r="AS127">
+        <v>1.46</v>
+      </c>
+      <c r="AT127">
+        <v>2.95</v>
+      </c>
+      <c r="AU127">
+        <v>6</v>
+      </c>
+      <c r="AV127">
+        <v>4</v>
+      </c>
+      <c r="AW127">
+        <v>5</v>
+      </c>
+      <c r="AX127">
+        <v>4</v>
+      </c>
+      <c r="AY127">
+        <v>11</v>
+      </c>
+      <c r="AZ127">
+        <v>8</v>
+      </c>
+      <c r="BA127">
+        <v>7</v>
+      </c>
+      <c r="BB127">
+        <v>4</v>
+      </c>
+      <c r="BC127">
+        <v>11</v>
+      </c>
+      <c r="BD127">
+        <v>1.89</v>
+      </c>
+      <c r="BE127">
+        <v>6.5</v>
+      </c>
+      <c r="BF127">
+        <v>2.08</v>
+      </c>
+      <c r="BG127">
+        <v>1.25</v>
+      </c>
+      <c r="BH127">
+        <v>3.45</v>
+      </c>
+      <c r="BI127">
+        <v>1.44</v>
+      </c>
+      <c r="BJ127">
+        <v>2.55</v>
+      </c>
+      <c r="BK127">
+        <v>1.72</v>
+      </c>
+      <c r="BL127">
+        <v>1.98</v>
+      </c>
+      <c r="BM127">
+        <v>2.12</v>
+      </c>
+      <c r="BN127">
+        <v>1.63</v>
+      </c>
+      <c r="BO127">
+        <v>2.65</v>
+      </c>
+      <c r="BP127">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="128" spans="1:68">
+      <c r="A128" s="1">
+        <v>127</v>
+      </c>
+      <c r="B128">
+        <v>7825318</v>
+      </c>
+      <c r="C128" t="s">
+        <v>68</v>
+      </c>
+      <c r="D128" t="s">
+        <v>69</v>
+      </c>
+      <c r="E128" s="2">
+        <v>45838.35763888889</v>
+      </c>
+      <c r="F128">
+        <v>16</v>
+      </c>
+      <c r="G128" t="s">
+        <v>84</v>
+      </c>
+      <c r="H128" t="s">
+        <v>72</v>
+      </c>
+      <c r="I128">
+        <v>0</v>
+      </c>
+      <c r="J128">
+        <v>1</v>
+      </c>
+      <c r="K128">
+        <v>1</v>
+      </c>
+      <c r="L128">
+        <v>2</v>
+      </c>
+      <c r="M128">
+        <v>1</v>
+      </c>
+      <c r="N128">
+        <v>3</v>
+      </c>
+      <c r="O128" t="s">
+        <v>186</v>
+      </c>
+      <c r="P128" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q128">
+        <v>1.8</v>
+      </c>
+      <c r="R128">
+        <v>2.75</v>
+      </c>
+      <c r="S128">
+        <v>6.5</v>
+      </c>
+      <c r="T128">
+        <v>1.22</v>
+      </c>
+      <c r="U128">
+        <v>4</v>
+      </c>
+      <c r="V128">
+        <v>2.1</v>
+      </c>
+      <c r="W128">
+        <v>1.67</v>
+      </c>
+      <c r="X128">
+        <v>4.5</v>
+      </c>
+      <c r="Y128">
+        <v>1.18</v>
+      </c>
+      <c r="Z128">
+        <v>1.35</v>
+      </c>
+      <c r="AA128">
+        <v>5</v>
+      </c>
+      <c r="AB128">
+        <v>6.3</v>
+      </c>
+      <c r="AC128">
+        <v>1.01</v>
+      </c>
+      <c r="AD128">
+        <v>23</v>
+      </c>
+      <c r="AE128">
+        <v>1.1</v>
+      </c>
+      <c r="AF128">
+        <v>5.1</v>
+      </c>
+      <c r="AG128">
+        <v>1.4</v>
+      </c>
+      <c r="AH128">
+        <v>2.73</v>
+      </c>
+      <c r="AI128">
+        <v>1.67</v>
+      </c>
+      <c r="AJ128">
+        <v>2.1</v>
+      </c>
+      <c r="AK128">
+        <v>1.09</v>
+      </c>
+      <c r="AL128">
+        <v>1.17</v>
+      </c>
+      <c r="AM128">
+        <v>2.86</v>
+      </c>
+      <c r="AN128">
+        <v>2.33</v>
+      </c>
+      <c r="AO128">
+        <v>1.33</v>
+      </c>
+      <c r="AP128">
+        <v>2.38</v>
+      </c>
+      <c r="AQ128">
+        <v>1.25</v>
+      </c>
+      <c r="AR128">
+        <v>1.65</v>
+      </c>
+      <c r="AS128">
+        <v>1.46</v>
+      </c>
+      <c r="AT128">
+        <v>3.11</v>
+      </c>
+      <c r="AU128">
+        <v>8</v>
+      </c>
+      <c r="AV128">
+        <v>5</v>
+      </c>
+      <c r="AW128">
+        <v>12</v>
+      </c>
+      <c r="AX128">
+        <v>3</v>
+      </c>
+      <c r="AY128">
+        <v>20</v>
+      </c>
+      <c r="AZ128">
+        <v>8</v>
+      </c>
+      <c r="BA128">
+        <v>10</v>
+      </c>
+      <c r="BB128">
+        <v>3</v>
+      </c>
+      <c r="BC128">
+        <v>13</v>
+      </c>
+      <c r="BD128">
+        <v>1.3</v>
+      </c>
+      <c r="BE128">
+        <v>7.5</v>
+      </c>
+      <c r="BF128">
+        <v>3.8</v>
+      </c>
+      <c r="BG128">
+        <v>1.25</v>
+      </c>
+      <c r="BH128">
+        <v>3.45</v>
+      </c>
+      <c r="BI128">
+        <v>1.43</v>
+      </c>
+      <c r="BJ128">
+        <v>2.55</v>
+      </c>
+      <c r="BK128">
+        <v>1.71</v>
+      </c>
+      <c r="BL128">
+        <v>2</v>
+      </c>
+      <c r="BM128">
+        <v>2.08</v>
+      </c>
+      <c r="BN128">
+        <v>1.65</v>
+      </c>
+      <c r="BO128">
+        <v>2.63</v>
+      </c>
+      <c r="BP128">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="129" spans="1:68">
+      <c r="A129" s="1">
+        <v>128</v>
+      </c>
+      <c r="B129">
+        <v>7825319</v>
+      </c>
+      <c r="C129" t="s">
+        <v>68</v>
+      </c>
+      <c r="D129" t="s">
+        <v>69</v>
+      </c>
+      <c r="E129" s="2">
+        <v>45838.375</v>
+      </c>
+      <c r="F129">
+        <v>16</v>
+      </c>
+      <c r="G129" t="s">
+        <v>81</v>
+      </c>
+      <c r="H129" t="s">
+        <v>77</v>
+      </c>
+      <c r="I129">
+        <v>1</v>
+      </c>
+      <c r="J129">
+        <v>0</v>
+      </c>
+      <c r="K129">
+        <v>1</v>
+      </c>
+      <c r="L129">
+        <v>1</v>
+      </c>
+      <c r="M129">
+        <v>2</v>
+      </c>
+      <c r="N129">
+        <v>3</v>
+      </c>
+      <c r="O129" t="s">
+        <v>187</v>
+      </c>
+      <c r="P129" t="s">
+        <v>261</v>
+      </c>
+      <c r="Q129">
+        <v>3.75</v>
+      </c>
+      <c r="R129">
+        <v>2.3</v>
+      </c>
+      <c r="S129">
+        <v>2.63</v>
+      </c>
+      <c r="T129">
+        <v>1.33</v>
+      </c>
+      <c r="U129">
+        <v>3.25</v>
+      </c>
+      <c r="V129">
+        <v>2.5</v>
+      </c>
+      <c r="W129">
+        <v>1.5</v>
+      </c>
+      <c r="X129">
+        <v>6</v>
+      </c>
+      <c r="Y129">
+        <v>1.13</v>
+      </c>
+      <c r="Z129">
+        <v>3.25</v>
+      </c>
+      <c r="AA129">
+        <v>3.9</v>
+      </c>
+      <c r="AB129">
+        <v>1.95</v>
+      </c>
+      <c r="AC129">
+        <v>1.01</v>
+      </c>
+      <c r="AD129">
+        <v>13</v>
+      </c>
+      <c r="AE129">
+        <v>1.15</v>
+      </c>
+      <c r="AF129">
+        <v>4.25</v>
+      </c>
+      <c r="AG129">
+        <v>1.7</v>
+      </c>
+      <c r="AH129">
+        <v>2.1</v>
+      </c>
+      <c r="AI129">
+        <v>1.67</v>
+      </c>
+      <c r="AJ129">
+        <v>2.1</v>
+      </c>
+      <c r="AK129">
+        <v>1.73</v>
+      </c>
+      <c r="AL129">
+        <v>1.26</v>
+      </c>
+      <c r="AM129">
+        <v>1.33</v>
+      </c>
+      <c r="AN129">
+        <v>0.93</v>
+      </c>
+      <c r="AO129">
+        <v>2.07</v>
+      </c>
+      <c r="AP129">
+        <v>0.88</v>
+      </c>
+      <c r="AQ129">
+        <v>2.13</v>
+      </c>
+      <c r="AR129">
+        <v>1.17</v>
+      </c>
+      <c r="AS129">
+        <v>1.87</v>
+      </c>
+      <c r="AT129">
+        <v>3.04</v>
+      </c>
+      <c r="AU129">
+        <v>4</v>
+      </c>
+      <c r="AV129">
+        <v>10</v>
+      </c>
+      <c r="AW129">
+        <v>5</v>
+      </c>
+      <c r="AX129">
+        <v>11</v>
+      </c>
+      <c r="AY129">
+        <v>9</v>
+      </c>
+      <c r="AZ129">
+        <v>21</v>
+      </c>
+      <c r="BA129">
+        <v>2</v>
+      </c>
+      <c r="BB129">
+        <v>7</v>
+      </c>
+      <c r="BC129">
+        <v>9</v>
+      </c>
+      <c r="BD129">
+        <v>2.43</v>
+      </c>
+      <c r="BE129">
+        <v>6.5</v>
+      </c>
+      <c r="BF129">
+        <v>1.68</v>
+      </c>
+      <c r="BG129">
+        <v>1.27</v>
+      </c>
+      <c r="BH129">
+        <v>3.3</v>
+      </c>
+      <c r="BI129">
+        <v>1.48</v>
+      </c>
+      <c r="BJ129">
+        <v>2.45</v>
+      </c>
+      <c r="BK129">
+        <v>1.77</v>
+      </c>
+      <c r="BL129">
+        <v>1.92</v>
+      </c>
+      <c r="BM129">
+        <v>2.18</v>
+      </c>
+      <c r="BN129">
+        <v>1.58</v>
+      </c>
+      <c r="BO129">
+        <v>2.8</v>
+      </c>
+      <c r="BP129">
+        <v>1.37</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="264">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -520,13 +520,13 @@
     <t>['12', '32']</t>
   </si>
   <si>
-    <t>['80', '9012']</t>
+    <t>['80', '90+12']</t>
   </si>
   <si>
     <t>['18', '25']</t>
   </si>
   <si>
-    <t>['36', '50', '9004']</t>
+    <t>['36', '50', '90+4']</t>
   </si>
   <si>
     <t>['15', '27', '69']</t>
@@ -544,19 +544,22 @@
     <t>['50']</t>
   </si>
   <si>
-    <t>['42', '4504', '9005']</t>
+    <t>['42', '45+4', '90+5']</t>
   </si>
   <si>
     <t>['77']</t>
   </si>
   <si>
-    <t>['26', '70', '9005']</t>
+    <t>['26', '70', '90+5']</t>
   </si>
   <si>
     <t>['9', '16', '62', '75', '83']</t>
   </si>
   <si>
-    <t>['18', '4501', '9004']</t>
+    <t>['18', '45+1', '90+4']</t>
+  </si>
+  <si>
+    <t>['59', '84']</t>
   </si>
   <si>
     <t>['53']</t>
@@ -772,16 +775,16 @@
     <t>['8', '21']</t>
   </si>
   <si>
-    <t>['32', '44', '4501']</t>
+    <t>['32', '44', '45+1']</t>
   </si>
   <si>
     <t>['63', '75']</t>
   </si>
   <si>
-    <t>['47', '69', '9004']</t>
+    <t>['47', '69', '90+4']</t>
   </si>
   <si>
-    <t>['9002']</t>
+    <t>['90+2']</t>
   </si>
   <si>
     <t>['21', '45', '55', '69']</t>
@@ -794,6 +797,9 @@
   </si>
   <si>
     <t>['6', '10']</t>
+  </si>
+  <si>
+    <t>['40', '81']</t>
   </si>
   <si>
     <t>['6', '32']</t>
@@ -1495,10 +1501,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="AQ2">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1829,7 +1835,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -1907,7 +1913,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ4">
         <v>2.38</v>
@@ -2035,7 +2041,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q5">
         <v>2.85</v>
@@ -2241,7 +2247,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q6">
         <v>2.2</v>
@@ -2528,7 +2534,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ7">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2653,7 +2659,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q8">
         <v>2.04</v>
@@ -2859,7 +2865,7 @@
         <v>92</v>
       </c>
       <c r="P9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q9">
         <v>1.5</v>
@@ -3065,7 +3071,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q10">
         <v>2.1</v>
@@ -3477,7 +3483,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q12">
         <v>3.1</v>
@@ -3683,7 +3689,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -3764,7 +3770,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ13">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR13">
         <v>1.39</v>
@@ -3889,7 +3895,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q14">
         <v>2.13</v>
@@ -4095,7 +4101,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q15">
         <v>3.2</v>
@@ -4173,7 +4179,7 @@
         <v>1</v>
       </c>
       <c r="AP15">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ15">
         <v>1.25</v>
@@ -4301,7 +4307,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q16">
         <v>1.78</v>
@@ -4379,7 +4385,7 @@
         <v>1</v>
       </c>
       <c r="AP16">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="AQ16">
         <v>1.56</v>
@@ -4588,7 +4594,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ17">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="AR17">
         <v>1.65</v>
@@ -4713,7 +4719,7 @@
         <v>100</v>
       </c>
       <c r="P18" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q18">
         <v>5.5</v>
@@ -4919,7 +4925,7 @@
         <v>88</v>
       </c>
       <c r="P19" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q19">
         <v>3.75</v>
@@ -4997,7 +5003,7 @@
         <v>1</v>
       </c>
       <c r="AP19">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="AQ19">
         <v>1.25</v>
@@ -5125,7 +5131,7 @@
         <v>101</v>
       </c>
       <c r="P20" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q20">
         <v>3.25</v>
@@ -5206,7 +5212,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ20">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR20">
         <v>1.47</v>
@@ -5743,7 +5749,7 @@
         <v>104</v>
       </c>
       <c r="P23" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q23">
         <v>4</v>
@@ -5821,7 +5827,7 @@
         <v>2</v>
       </c>
       <c r="AP23">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ23">
         <v>2.38</v>
@@ -5949,7 +5955,7 @@
         <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q24">
         <v>4.75</v>
@@ -6155,7 +6161,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -6236,7 +6242,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ25">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="AR25">
         <v>1.2</v>
@@ -6361,7 +6367,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q26">
         <v>2.88</v>
@@ -6439,7 +6445,7 @@
         <v>1.67</v>
       </c>
       <c r="AP26">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ26">
         <v>1.31</v>
@@ -6854,7 +6860,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ28">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="AR28">
         <v>0.84</v>
@@ -6979,7 +6985,7 @@
         <v>110</v>
       </c>
       <c r="P29" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q29">
         <v>1.83</v>
@@ -7060,7 +7066,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ29">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR29">
         <v>1.96</v>
@@ -7391,7 +7397,7 @@
         <v>88</v>
       </c>
       <c r="P31" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q31">
         <v>2.9</v>
@@ -7472,7 +7478,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ31">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="AR31">
         <v>2.34</v>
@@ -7597,7 +7603,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q32">
         <v>3.42</v>
@@ -7803,7 +7809,7 @@
         <v>113</v>
       </c>
       <c r="P33" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q33">
         <v>1.56</v>
@@ -8009,7 +8015,7 @@
         <v>114</v>
       </c>
       <c r="P34" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q34">
         <v>3.25</v>
@@ -8090,7 +8096,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ34">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR34">
         <v>1.55</v>
@@ -8215,7 +8221,7 @@
         <v>115</v>
       </c>
       <c r="P35" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q35">
         <v>4.25</v>
@@ -8421,7 +8427,7 @@
         <v>116</v>
       </c>
       <c r="P36" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q36">
         <v>3.15</v>
@@ -8627,7 +8633,7 @@
         <v>117</v>
       </c>
       <c r="P37" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q37">
         <v>2.75</v>
@@ -8708,7 +8714,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ37">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="AR37">
         <v>1.47</v>
@@ -8911,7 +8917,7 @@
         <v>1.25</v>
       </c>
       <c r="AP38">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="AQ38">
         <v>1.25</v>
@@ -9039,7 +9045,7 @@
         <v>119</v>
       </c>
       <c r="P39" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q39">
         <v>2.88</v>
@@ -9529,7 +9535,7 @@
         <v>0.5</v>
       </c>
       <c r="AP41">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ41">
         <v>0.5</v>
@@ -9863,7 +9869,7 @@
         <v>123</v>
       </c>
       <c r="P43" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q43">
         <v>3</v>
@@ -10069,7 +10075,7 @@
         <v>124</v>
       </c>
       <c r="P44" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q44">
         <v>3.2</v>
@@ -10275,7 +10281,7 @@
         <v>88</v>
       </c>
       <c r="P45" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q45">
         <v>7.5</v>
@@ -10356,7 +10362,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ45">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="AR45">
         <v>1.31</v>
@@ -10559,10 +10565,10 @@
         <v>1.4</v>
       </c>
       <c r="AP46">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="AQ46">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR46">
         <v>1.12</v>
@@ -10687,7 +10693,7 @@
         <v>126</v>
       </c>
       <c r="P47" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q47">
         <v>1.95</v>
@@ -10893,7 +10899,7 @@
         <v>127</v>
       </c>
       <c r="P48" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q48">
         <v>3.7</v>
@@ -11099,7 +11105,7 @@
         <v>128</v>
       </c>
       <c r="P49" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q49">
         <v>4.33</v>
@@ -11177,7 +11183,7 @@
         <v>1.8</v>
       </c>
       <c r="AP49">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="AQ49">
         <v>2.38</v>
@@ -11305,7 +11311,7 @@
         <v>129</v>
       </c>
       <c r="P50" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q50">
         <v>2.65</v>
@@ -11511,7 +11517,7 @@
         <v>130</v>
       </c>
       <c r="P51" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q51">
         <v>4.15</v>
@@ -11798,7 +11804,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ52">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR52">
         <v>1.53</v>
@@ -11923,7 +11929,7 @@
         <v>132</v>
       </c>
       <c r="P53" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q53">
         <v>1.8</v>
@@ -12129,7 +12135,7 @@
         <v>104</v>
       </c>
       <c r="P54" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q54">
         <v>1.71</v>
@@ -12207,10 +12213,10 @@
         <v>1.17</v>
       </c>
       <c r="AP54">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="AQ54">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR54">
         <v>2.17</v>
@@ -12335,7 +12341,7 @@
         <v>133</v>
       </c>
       <c r="P55" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q55">
         <v>1.45</v>
@@ -12622,7 +12628,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ56">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="AR56">
         <v>2.35</v>
@@ -12747,7 +12753,7 @@
         <v>135</v>
       </c>
       <c r="P57" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -13034,7 +13040,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ58">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR58">
         <v>1.25</v>
@@ -13443,7 +13449,7 @@
         <v>0.29</v>
       </c>
       <c r="AP60">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ60">
         <v>0.5</v>
@@ -13983,7 +13989,7 @@
         <v>140</v>
       </c>
       <c r="P63" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q63">
         <v>2.88</v>
@@ -14064,7 +14070,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ63">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="AR63">
         <v>2.01</v>
@@ -14270,7 +14276,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ64">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR64">
         <v>1.73</v>
@@ -14395,7 +14401,7 @@
         <v>142</v>
       </c>
       <c r="P65" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q65">
         <v>4.5</v>
@@ -14473,7 +14479,7 @@
         <v>2</v>
       </c>
       <c r="AP65">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ65">
         <v>2.13</v>
@@ -14601,7 +14607,7 @@
         <v>143</v>
       </c>
       <c r="P66" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q66">
         <v>5.2</v>
@@ -14682,7 +14688,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ66">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="AR66">
         <v>1.26</v>
@@ -14807,7 +14813,7 @@
         <v>144</v>
       </c>
       <c r="P67" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q67">
         <v>3.22</v>
@@ -15013,7 +15019,7 @@
         <v>88</v>
       </c>
       <c r="P68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q68">
         <v>3.24</v>
@@ -15219,7 +15225,7 @@
         <v>145</v>
       </c>
       <c r="P69" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q69">
         <v>3.18</v>
@@ -15297,7 +15303,7 @@
         <v>1.63</v>
       </c>
       <c r="AP69">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="AQ69">
         <v>1.56</v>
@@ -15425,7 +15431,7 @@
         <v>124</v>
       </c>
       <c r="P70" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q70">
         <v>3.22</v>
@@ -15631,7 +15637,7 @@
         <v>146</v>
       </c>
       <c r="P71" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q71">
         <v>2.1</v>
@@ -15837,7 +15843,7 @@
         <v>147</v>
       </c>
       <c r="P72" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q72">
         <v>2.75</v>
@@ -15918,7 +15924,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ72">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR72">
         <v>1.53</v>
@@ -16249,7 +16255,7 @@
         <v>148</v>
       </c>
       <c r="P74" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q74">
         <v>2.2</v>
@@ -16455,7 +16461,7 @@
         <v>149</v>
       </c>
       <c r="P75" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -16533,10 +16539,10 @@
         <v>0.89</v>
       </c>
       <c r="AP75">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ75">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="AR75">
         <v>1.39</v>
@@ -16661,7 +16667,7 @@
         <v>150</v>
       </c>
       <c r="P76" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q76">
         <v>1.57</v>
@@ -16867,7 +16873,7 @@
         <v>151</v>
       </c>
       <c r="P77" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q77">
         <v>2.63</v>
@@ -17357,7 +17363,7 @@
         <v>2.56</v>
       </c>
       <c r="AP79">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="AQ79">
         <v>2.38</v>
@@ -17485,7 +17491,7 @@
         <v>88</v>
       </c>
       <c r="P80" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q80">
         <v>3.6</v>
@@ -17691,7 +17697,7 @@
         <v>154</v>
       </c>
       <c r="P81" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q81">
         <v>2.6</v>
@@ -17769,7 +17775,7 @@
         <v>1.3</v>
       </c>
       <c r="AP81">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ81">
         <v>1.56</v>
@@ -17897,7 +17903,7 @@
         <v>88</v>
       </c>
       <c r="P82" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q82">
         <v>4.5</v>
@@ -17975,7 +17981,7 @@
         <v>1.89</v>
       </c>
       <c r="AP82">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="AQ82">
         <v>2.13</v>
@@ -18387,7 +18393,7 @@
         <v>1.5</v>
       </c>
       <c r="AP84">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="AQ84">
         <v>1.25</v>
@@ -18515,7 +18521,7 @@
         <v>157</v>
       </c>
       <c r="P85" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q85">
         <v>4</v>
@@ -18593,7 +18599,7 @@
         <v>1.7</v>
       </c>
       <c r="AP85">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ85">
         <v>1.56</v>
@@ -18721,7 +18727,7 @@
         <v>114</v>
       </c>
       <c r="P86" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q86">
         <v>5.5</v>
@@ -19133,7 +19139,7 @@
         <v>158</v>
       </c>
       <c r="P88" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q88">
         <v>1.53</v>
@@ -19545,7 +19551,7 @@
         <v>88</v>
       </c>
       <c r="P90" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q90">
         <v>6</v>
@@ -19626,7 +19632,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ90">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="AR90">
         <v>1.67</v>
@@ -19751,7 +19757,7 @@
         <v>160</v>
       </c>
       <c r="P91" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q91">
         <v>2.2</v>
@@ -19957,7 +19963,7 @@
         <v>161</v>
       </c>
       <c r="P92" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q92">
         <v>1.8</v>
@@ -20163,7 +20169,7 @@
         <v>88</v>
       </c>
       <c r="P93" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q93">
         <v>3.5</v>
@@ -20244,7 +20250,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ93">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR93">
         <v>1.27</v>
@@ -20450,7 +20456,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ94">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR94">
         <v>1.67</v>
@@ -20575,7 +20581,7 @@
         <v>162</v>
       </c>
       <c r="P95" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q95">
         <v>2.88</v>
@@ -20653,7 +20659,7 @@
         <v>1.18</v>
       </c>
       <c r="AP95">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="AQ95">
         <v>1.25</v>
@@ -20781,7 +20787,7 @@
         <v>163</v>
       </c>
       <c r="P96" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q96">
         <v>2.38</v>
@@ -20862,7 +20868,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ96">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR96">
         <v>1.43</v>
@@ -21065,7 +21071,7 @@
         <v>1</v>
       </c>
       <c r="AP97">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ97">
         <v>0.75</v>
@@ -21193,7 +21199,7 @@
         <v>88</v>
       </c>
       <c r="P98" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q98">
         <v>5.25</v>
@@ -21399,7 +21405,7 @@
         <v>165</v>
       </c>
       <c r="P99" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q99">
         <v>3.52</v>
@@ -21605,7 +21611,7 @@
         <v>166</v>
       </c>
       <c r="P100" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q100">
         <v>1.79</v>
@@ -21683,7 +21689,7 @@
         <v>1.45</v>
       </c>
       <c r="AP100">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="AQ100">
         <v>1.31</v>
@@ -21811,7 +21817,7 @@
         <v>127</v>
       </c>
       <c r="P101" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q101">
         <v>5.55</v>
@@ -22017,7 +22023,7 @@
         <v>114</v>
       </c>
       <c r="P102" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q102">
         <v>2.3</v>
@@ -22507,7 +22513,7 @@
         <v>0.62</v>
       </c>
       <c r="AP104">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="AQ104">
         <v>0.5</v>
@@ -22635,7 +22641,7 @@
         <v>168</v>
       </c>
       <c r="P105" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q105">
         <v>3.54</v>
@@ -22922,7 +22928,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ106">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR106">
         <v>1.23</v>
@@ -23047,7 +23053,7 @@
         <v>169</v>
       </c>
       <c r="P107" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q107">
         <v>1.49</v>
@@ -23459,7 +23465,7 @@
         <v>171</v>
       </c>
       <c r="P109" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q109">
         <v>5.2</v>
@@ -23537,10 +23543,10 @@
         <v>2.31</v>
       </c>
       <c r="AP109">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ109">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="AR109">
         <v>1.54</v>
@@ -24077,7 +24083,7 @@
         <v>174</v>
       </c>
       <c r="P112" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24155,7 +24161,7 @@
         <v>1.92</v>
       </c>
       <c r="AP112">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ112">
         <v>2.13</v>
@@ -24283,7 +24289,7 @@
         <v>175</v>
       </c>
       <c r="P113" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q113">
         <v>3.04</v>
@@ -24364,7 +24370,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ113">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="AR113">
         <v>1.19</v>
@@ -24695,7 +24701,7 @@
         <v>88</v>
       </c>
       <c r="P115" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q115">
         <v>3.5</v>
@@ -25107,7 +25113,7 @@
         <v>178</v>
       </c>
       <c r="P117" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q117">
         <v>1.95</v>
@@ -25188,7 +25194,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ117">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="AR117">
         <v>1.89</v>
@@ -25313,7 +25319,7 @@
         <v>88</v>
       </c>
       <c r="P118" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q118">
         <v>5.5</v>
@@ -25597,7 +25603,7 @@
         <v>1</v>
       </c>
       <c r="AP119">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="AQ119">
         <v>0.88</v>
@@ -25919,19 +25925,19 @@
         <v>1</v>
       </c>
       <c r="L121">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M121">
         <v>1</v>
       </c>
       <c r="N121">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O121" t="s">
-        <v>144</v>
+        <v>181</v>
       </c>
       <c r="P121" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q121">
         <v>3</v>
@@ -26009,10 +26015,10 @@
         <v>1</v>
       </c>
       <c r="AP121">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ121">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR121">
         <v>1.46</v>
@@ -26134,10 +26140,10 @@
         <v>3</v>
       </c>
       <c r="O122" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P122" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q122">
         <v>7.1</v>
@@ -26340,7 +26346,7 @@
         <v>1</v>
       </c>
       <c r="O123" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P123" t="s">
         <v>88</v>
@@ -26546,10 +26552,10 @@
         <v>3</v>
       </c>
       <c r="O124" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P124" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q124">
         <v>2.63</v>
@@ -26737,25 +26743,25 @@
         <v>1</v>
       </c>
       <c r="J125">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K125">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L125">
         <v>2</v>
       </c>
       <c r="M125">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N125">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O125" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P125" t="s">
-        <v>124</v>
+        <v>261</v>
       </c>
       <c r="Q125">
         <v>5.55</v>
@@ -26833,10 +26839,10 @@
         <v>2.2</v>
       </c>
       <c r="AP125">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="AQ125">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="AR125">
         <v>1.53</v>
@@ -26958,10 +26964,10 @@
         <v>4</v>
       </c>
       <c r="O126" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P126" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q126">
         <v>3</v>
@@ -27033,13 +27039,13 @@
         <v>1.5</v>
       </c>
       <c r="AN126">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AO126">
         <v>1.6</v>
       </c>
       <c r="AP126">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ126">
         <v>1.56</v>
@@ -27370,10 +27376,10 @@
         <v>3</v>
       </c>
       <c r="O128" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P128" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q128">
         <v>1.8</v>
@@ -27448,13 +27454,13 @@
         <v>2.33</v>
       </c>
       <c r="AO128">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="AP128">
         <v>2.38</v>
       </c>
       <c r="AQ128">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR128">
         <v>1.65</v>
@@ -27576,10 +27582,10 @@
         <v>3</v>
       </c>
       <c r="O129" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P129" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q129">
         <v>3.75</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
@@ -1504,7 +1504,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ2">
-        <v>1.19</v>
+        <v>0.88</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1707,10 +1707,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="AQ3">
-        <v>0.5</v>
+        <v>0.38</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1913,10 +1913,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.38</v>
+        <v>1.86</v>
       </c>
       <c r="AQ4">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2119,10 +2119,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0.5</v>
+        <v>0.88</v>
       </c>
       <c r="AQ5">
-        <v>1.31</v>
+        <v>0.71</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2325,10 +2325,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.25</v>
+        <v>1.86</v>
       </c>
       <c r="AQ6">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2531,10 +2531,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="AQ7">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2737,10 +2737,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AQ8">
-        <v>0.75</v>
+        <v>0.43</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2943,10 +2943,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AQ9">
-        <v>0.88</v>
+        <v>0.5</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>1</v>
       </c>
       <c r="AP10">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="AQ10">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="AR10">
         <v>2.21</v>
@@ -3355,10 +3355,10 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AQ11">
-        <v>0.5</v>
+        <v>0.38</v>
       </c>
       <c r="AR11">
         <v>1.91</v>
@@ -3561,10 +3561,10 @@
         <v>0</v>
       </c>
       <c r="AP12">
+        <v>0.88</v>
+      </c>
+      <c r="AQ12">
         <v>0.5</v>
-      </c>
-      <c r="AQ12">
-        <v>0.88</v>
       </c>
       <c r="AR12">
         <v>1.44</v>
@@ -3761,25 +3761,25 @@
         <v>1.35</v>
       </c>
       <c r="AN13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO13">
         <v>1</v>
       </c>
       <c r="AP13">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ13">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="AR13">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AS13">
         <v>1.57</v>
       </c>
       <c r="AT13">
-        <v>2.96</v>
+        <v>1.57</v>
       </c>
       <c r="AU13">
         <v>8</v>
@@ -3973,10 +3973,10 @@
         <v>3</v>
       </c>
       <c r="AP14">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="AQ14">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AR14">
         <v>2.29</v>
@@ -4176,22 +4176,22 @@
         <v>0</v>
       </c>
       <c r="AO15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.38</v>
+        <v>1.86</v>
       </c>
       <c r="AQ15">
-        <v>1.25</v>
+        <v>0.78</v>
       </c>
       <c r="AR15">
         <v>1.22</v>
       </c>
       <c r="AS15">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AT15">
-        <v>2.59</v>
+        <v>1.22</v>
       </c>
       <c r="AU15">
         <v>4</v>
@@ -4382,7 +4382,7 @@
         <v>3</v>
       </c>
       <c r="AO16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP16">
         <v>2.13</v>
@@ -4394,10 +4394,10 @@
         <v>2.91</v>
       </c>
       <c r="AS16">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AT16">
-        <v>6.33</v>
+        <v>2.91</v>
       </c>
       <c r="AU16">
         <v>5</v>
@@ -4585,25 +4585,25 @@
         <v>1.6</v>
       </c>
       <c r="AN17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO17">
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.31</v>
+        <v>1.78</v>
       </c>
       <c r="AQ17">
-        <v>1.19</v>
+        <v>0.88</v>
       </c>
       <c r="AR17">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AS17">
         <v>0.95</v>
       </c>
       <c r="AT17">
-        <v>2.6</v>
+        <v>0.95</v>
       </c>
       <c r="AU17">
         <v>3</v>
@@ -4791,25 +4791,25 @@
         <v>1.1</v>
       </c>
       <c r="AN18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO18">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.31</v>
+        <v>1.78</v>
       </c>
       <c r="AQ18">
-        <v>2.13</v>
+        <v>2.43</v>
       </c>
       <c r="AR18">
-        <v>1.22</v>
+        <v>0.8</v>
       </c>
       <c r="AS18">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AT18">
-        <v>3.52</v>
+        <v>0.8</v>
       </c>
       <c r="AU18">
         <v>5</v>
@@ -5003,19 +5003,19 @@
         <v>1</v>
       </c>
       <c r="AP19">
-        <v>1.19</v>
+        <v>1.5</v>
       </c>
       <c r="AQ19">
-        <v>1.25</v>
+        <v>0.78</v>
       </c>
       <c r="AR19">
-        <v>0.5600000000000001</v>
+        <v>0</v>
       </c>
       <c r="AS19">
         <v>1.38</v>
       </c>
       <c r="AT19">
-        <v>1.94</v>
+        <v>1.38</v>
       </c>
       <c r="AU19">
         <v>5</v>
@@ -5203,25 +5203,25 @@
         <v>1.5</v>
       </c>
       <c r="AN20">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO20">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AP20">
-        <v>0.88</v>
+        <v>1.25</v>
       </c>
       <c r="AQ20">
-        <v>1.38</v>
+        <v>1</v>
       </c>
       <c r="AR20">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AS20">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AT20">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AU20">
         <v>9</v>
@@ -5409,25 +5409,25 @@
         <v>1.44</v>
       </c>
       <c r="AN21">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AO21">
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="AQ21">
-        <v>0.5</v>
+        <v>0.38</v>
       </c>
       <c r="AR21">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AS21">
         <v>0.88</v>
       </c>
       <c r="AT21">
-        <v>2.13</v>
+        <v>0.88</v>
       </c>
       <c r="AU21">
         <v>7</v>
@@ -5615,25 +5615,25 @@
         <v>2.2</v>
       </c>
       <c r="AN22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO22">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AQ22">
-        <v>0.5</v>
+        <v>0.13</v>
       </c>
       <c r="AR22">
-        <v>2.35</v>
+        <v>3.42</v>
       </c>
       <c r="AS22">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AT22">
-        <v>3.67</v>
+        <v>3.42</v>
       </c>
       <c r="AU22">
         <v>11</v>
@@ -5821,25 +5821,25 @@
         <v>1.25</v>
       </c>
       <c r="AN23">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AO23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AP23">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="AQ23">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AR23">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AS23">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AT23">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AU23">
         <v>5</v>
@@ -6027,25 +6027,25 @@
         <v>1.18</v>
       </c>
       <c r="AN24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AP24">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ24">
-        <v>1.56</v>
+        <v>1.38</v>
       </c>
       <c r="AR24">
-        <v>1.66</v>
+        <v>1.93</v>
       </c>
       <c r="AS24">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AT24">
-        <v>4.12</v>
+        <v>1.93</v>
       </c>
       <c r="AU24">
         <v>7</v>
@@ -6233,25 +6233,25 @@
         <v>1.6</v>
       </c>
       <c r="AN25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO25">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AP25">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="AQ25">
         <v>2.13</v>
       </c>
       <c r="AR25">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AS25">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AT25">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="AU25">
         <v>3</v>
@@ -6439,25 +6439,25 @@
         <v>1.68</v>
       </c>
       <c r="AN26">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AO26">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="AP26">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="AQ26">
-        <v>1.31</v>
+        <v>0.71</v>
       </c>
       <c r="AR26">
-        <v>1.38</v>
+        <v>1.09</v>
       </c>
       <c r="AS26">
-        <v>1.26</v>
+        <v>1.65</v>
       </c>
       <c r="AT26">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
       <c r="AU26">
         <v>6</v>
@@ -6645,25 +6645,25 @@
         <v>2.1</v>
       </c>
       <c r="AN27">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="AO27">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AP27">
-        <v>1.25</v>
+        <v>1.86</v>
       </c>
       <c r="AQ27">
-        <v>0.88</v>
+        <v>0.5</v>
       </c>
       <c r="AR27">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="AS27">
-        <v>1.73</v>
+        <v>1.47</v>
       </c>
       <c r="AT27">
-        <v>3.21</v>
+        <v>2.84</v>
       </c>
       <c r="AU27">
         <v>7</v>
@@ -6857,19 +6857,19 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>0.5</v>
+        <v>0.63</v>
       </c>
       <c r="AQ28">
-        <v>1.19</v>
+        <v>0.88</v>
       </c>
       <c r="AR28">
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="AS28">
-        <v>0.98</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AT28">
-        <v>1.82</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AU28">
         <v>4</v>
@@ -7057,25 +7057,25 @@
         <v>2.95</v>
       </c>
       <c r="AN29">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AO29">
-        <v>1.33</v>
+        <v>3</v>
       </c>
       <c r="AP29">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="AQ29">
-        <v>1.38</v>
+        <v>1</v>
       </c>
       <c r="AR29">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="AS29">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AT29">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="AU29">
         <v>11</v>
@@ -7263,25 +7263,25 @@
         <v>1.33</v>
       </c>
       <c r="AN30">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AO30">
-        <v>1.33</v>
+        <v>0.5</v>
       </c>
       <c r="AP30">
+        <v>0.88</v>
+      </c>
+      <c r="AQ30">
         <v>0.5</v>
       </c>
-      <c r="AQ30">
+      <c r="AR30">
+        <v>1.32</v>
+      </c>
+      <c r="AS30">
         <v>1.25</v>
       </c>
-      <c r="AR30">
-        <v>1.15</v>
-      </c>
-      <c r="AS30">
-        <v>1.59</v>
-      </c>
       <c r="AT30">
-        <v>2.74</v>
+        <v>2.57</v>
       </c>
       <c r="AU30">
         <v>6</v>
@@ -7469,25 +7469,25 @@
         <v>1.56</v>
       </c>
       <c r="AN31">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AO31">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AP31">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="AQ31">
         <v>2.13</v>
       </c>
       <c r="AR31">
-        <v>2.34</v>
+        <v>2.46</v>
       </c>
       <c r="AS31">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AT31">
-        <v>4.65</v>
+        <v>4.6</v>
       </c>
       <c r="AU31">
         <v>3</v>
@@ -7675,25 +7675,25 @@
         <v>1.42</v>
       </c>
       <c r="AN32">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AO32">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AP32">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AQ32">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AR32">
-        <v>2.5</v>
+        <v>3.11</v>
       </c>
       <c r="AS32">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="AT32">
-        <v>3.55</v>
+        <v>4.31</v>
       </c>
       <c r="AU32">
         <v>10</v>
@@ -7881,25 +7881,25 @@
         <v>4.1</v>
       </c>
       <c r="AN33">
-        <v>2.33</v>
+        <v>3</v>
       </c>
       <c r="AO33">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AP33">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AQ33">
-        <v>0.75</v>
+        <v>0.43</v>
       </c>
       <c r="AR33">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="AS33">
-        <v>1.54</v>
+        <v>1.39</v>
       </c>
       <c r="AT33">
-        <v>3.66</v>
+        <v>3.69</v>
       </c>
       <c r="AU33">
         <v>12</v>
@@ -8087,25 +8087,25 @@
         <v>1.49</v>
       </c>
       <c r="AN34">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AO34">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="AP34">
-        <v>0.88</v>
+        <v>1.25</v>
       </c>
       <c r="AQ34">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="AR34">
-        <v>1.55</v>
+        <v>2.26</v>
       </c>
       <c r="AS34">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AT34">
-        <v>2.88</v>
+        <v>3.79</v>
       </c>
       <c r="AU34">
         <v>3</v>
@@ -8293,25 +8293,25 @@
         <v>1.23</v>
       </c>
       <c r="AN35">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="AO35">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="AP35">
-        <v>0.5</v>
+        <v>0.63</v>
       </c>
       <c r="AQ35">
-        <v>1.56</v>
+        <v>1.38</v>
       </c>
       <c r="AR35">
-        <v>0.9</v>
+        <v>1.08</v>
       </c>
       <c r="AS35">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AT35">
-        <v>2.95</v>
+        <v>3.18</v>
       </c>
       <c r="AU35">
         <v>6</v>
@@ -8502,22 +8502,22 @@
         <v>2</v>
       </c>
       <c r="AO36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP36">
-        <v>1.31</v>
+        <v>1.78</v>
       </c>
       <c r="AQ36">
         <v>1.56</v>
       </c>
       <c r="AR36">
-        <v>1.35</v>
+        <v>1.07</v>
       </c>
       <c r="AS36">
-        <v>2.47</v>
+        <v>1.28</v>
       </c>
       <c r="AT36">
-        <v>3.82</v>
+        <v>2.35</v>
       </c>
       <c r="AU36">
         <v>4</v>
@@ -8705,25 +8705,25 @@
         <v>1.66</v>
       </c>
       <c r="AN37">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AO37">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AP37">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ37">
-        <v>1.19</v>
+        <v>0.88</v>
       </c>
       <c r="AR37">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="AS37">
-        <v>1.17</v>
+        <v>0.96</v>
       </c>
       <c r="AT37">
-        <v>2.64</v>
+        <v>2.57</v>
       </c>
       <c r="AU37">
         <v>9</v>
@@ -8911,25 +8911,25 @@
         <v>3.54</v>
       </c>
       <c r="AN38">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AO38">
-        <v>1.25</v>
+        <v>0.67</v>
       </c>
       <c r="AP38">
         <v>2.13</v>
       </c>
       <c r="AQ38">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="AR38">
-        <v>2.27</v>
+        <v>2.39</v>
       </c>
       <c r="AS38">
-        <v>1.58</v>
+        <v>1.36</v>
       </c>
       <c r="AT38">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="AU38">
         <v>9</v>
@@ -9117,25 +9117,25 @@
         <v>1.56</v>
       </c>
       <c r="AN39">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AO39">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AP39">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AQ39">
+        <v>2</v>
+      </c>
+      <c r="AR39">
         <v>2.38</v>
       </c>
-      <c r="AR39">
-        <v>2.23</v>
-      </c>
       <c r="AS39">
-        <v>2.55</v>
+        <v>2.07</v>
       </c>
       <c r="AT39">
-        <v>4.78</v>
+        <v>4.45</v>
       </c>
       <c r="AU39">
         <v>2</v>
@@ -9323,25 +9323,25 @@
         <v>2.19</v>
       </c>
       <c r="AN40">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AO40">
         <v>2</v>
       </c>
       <c r="AP40">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="AQ40">
-        <v>1.25</v>
+        <v>0.78</v>
       </c>
       <c r="AR40">
-        <v>1.25</v>
+        <v>0.75</v>
       </c>
       <c r="AS40">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AT40">
-        <v>2.77</v>
+        <v>2.28</v>
       </c>
       <c r="AU40">
         <v>12</v>
@@ -9529,25 +9529,25 @@
         <v>2.09</v>
       </c>
       <c r="AN41">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AO41">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AP41">
-        <v>1.38</v>
+        <v>1.86</v>
       </c>
       <c r="AQ41">
-        <v>0.5</v>
+        <v>0.13</v>
       </c>
       <c r="AR41">
         <v>1.18</v>
       </c>
       <c r="AS41">
-        <v>1.27</v>
+        <v>0.8</v>
       </c>
       <c r="AT41">
-        <v>2.45</v>
+        <v>1.98</v>
       </c>
       <c r="AU41">
         <v>6</v>
@@ -9735,25 +9735,25 @@
         <v>2.7</v>
       </c>
       <c r="AN42">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AO42">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AP42">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="AQ42">
-        <v>0.88</v>
+        <v>0.5</v>
       </c>
       <c r="AR42">
-        <v>2.14</v>
+        <v>2.03</v>
       </c>
       <c r="AS42">
-        <v>1.51</v>
+        <v>1.31</v>
       </c>
       <c r="AT42">
-        <v>3.65</v>
+        <v>3.34</v>
       </c>
       <c r="AU42">
         <v>11</v>
@@ -9941,25 +9941,25 @@
         <v>1.53</v>
       </c>
       <c r="AN43">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="AO43">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AP43">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ43">
-        <v>0.5</v>
+        <v>0.38</v>
       </c>
       <c r="AR43">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="AS43">
-        <v>1.06</v>
+        <v>0.84</v>
       </c>
       <c r="AT43">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="AU43">
         <v>7</v>
@@ -10147,25 +10147,25 @@
         <v>1.44</v>
       </c>
       <c r="AN44">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AO44">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AP44">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="AQ44">
         <v>1.56</v>
       </c>
       <c r="AR44">
-        <v>1.42</v>
+        <v>2.26</v>
       </c>
       <c r="AS44">
-        <v>2.19</v>
+        <v>1.16</v>
       </c>
       <c r="AT44">
-        <v>3.61</v>
+        <v>3.42</v>
       </c>
       <c r="AU44">
         <v>7</v>
@@ -10353,25 +10353,25 @@
         <v>1.06</v>
       </c>
       <c r="AN45">
-        <v>0.4</v>
+        <v>0.67</v>
       </c>
       <c r="AO45">
         <v>2</v>
       </c>
       <c r="AP45">
-        <v>0.5</v>
+        <v>0.88</v>
       </c>
       <c r="AQ45">
         <v>2.13</v>
       </c>
       <c r="AR45">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AS45">
-        <v>2.27</v>
+        <v>2.14</v>
       </c>
       <c r="AT45">
-        <v>3.58</v>
+        <v>3.57</v>
       </c>
       <c r="AU45">
         <v>4</v>
@@ -10559,25 +10559,25 @@
         <v>1.5</v>
       </c>
       <c r="AN46">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AO46">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AP46">
+        <v>1.5</v>
+      </c>
+      <c r="AQ46">
+        <v>1</v>
+      </c>
+      <c r="AR46">
+        <v>1.82</v>
+      </c>
+      <c r="AS46">
         <v>1.19</v>
       </c>
-      <c r="AQ46">
-        <v>1.38</v>
-      </c>
-      <c r="AR46">
-        <v>1.12</v>
-      </c>
-      <c r="AS46">
-        <v>1.37</v>
-      </c>
       <c r="AT46">
-        <v>2.49</v>
+        <v>3.01</v>
       </c>
       <c r="AU46">
         <v>9</v>
@@ -10765,25 +10765,25 @@
         <v>2.7</v>
       </c>
       <c r="AN47">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AO47">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AP47">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="AQ47">
-        <v>1.25</v>
+        <v>0.78</v>
       </c>
       <c r="AR47">
-        <v>2.44</v>
+        <v>2.72</v>
       </c>
       <c r="AS47">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AT47">
-        <v>3.92</v>
+        <v>4.18</v>
       </c>
       <c r="AU47">
         <v>7</v>
@@ -10971,25 +10971,25 @@
         <v>1.3</v>
       </c>
       <c r="AN48">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AO48">
-        <v>2.17</v>
+        <v>3</v>
       </c>
       <c r="AP48">
-        <v>1.31</v>
+        <v>1.78</v>
       </c>
       <c r="AQ48">
-        <v>1.56</v>
+        <v>1.38</v>
       </c>
       <c r="AR48">
-        <v>1.34</v>
+        <v>1.15</v>
       </c>
       <c r="AS48">
-        <v>2.18</v>
+        <v>2.31</v>
       </c>
       <c r="AT48">
-        <v>3.52</v>
+        <v>3.46</v>
       </c>
       <c r="AU48">
         <v>4</v>
@@ -11177,25 +11177,25 @@
         <v>1.24</v>
       </c>
       <c r="AN49">
-        <v>0.67</v>
+        <v>1.5</v>
       </c>
       <c r="AO49">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AP49">
-        <v>1.19</v>
+        <v>1.5</v>
       </c>
       <c r="AQ49">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AR49">
-        <v>1.24</v>
+        <v>1.83</v>
       </c>
       <c r="AS49">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="AT49">
-        <v>2.82</v>
+        <v>3.25</v>
       </c>
       <c r="AU49">
         <v>14</v>
@@ -11383,25 +11383,25 @@
         <v>1.67</v>
       </c>
       <c r="AN50">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AO50">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="AP50">
-        <v>0.88</v>
+        <v>1.25</v>
       </c>
       <c r="AQ50">
-        <v>0.5</v>
+        <v>0.38</v>
       </c>
       <c r="AR50">
-        <v>1.42</v>
+        <v>1.81</v>
       </c>
       <c r="AS50">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="AT50">
-        <v>2.55</v>
+        <v>2.82</v>
       </c>
       <c r="AU50">
         <v>6</v>
@@ -11592,22 +11592,22 @@
         <v>1.67</v>
       </c>
       <c r="AO51">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="AP51">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AQ51">
-        <v>2.13</v>
+        <v>2.43</v>
       </c>
       <c r="AR51">
-        <v>1.97</v>
+        <v>2.87</v>
       </c>
       <c r="AS51">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AT51">
-        <v>3.97</v>
+        <v>4.64</v>
       </c>
       <c r="AU51">
         <v>3</v>
@@ -11795,25 +11795,25 @@
         <v>1.52</v>
       </c>
       <c r="AN52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO52">
-        <v>0.8</v>
+        <v>1.33</v>
       </c>
       <c r="AP52">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="AQ52">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="AR52">
-        <v>1.53</v>
+        <v>2.18</v>
       </c>
       <c r="AS52">
-        <v>1.49</v>
+        <v>1.73</v>
       </c>
       <c r="AT52">
-        <v>3.02</v>
+        <v>3.91</v>
       </c>
       <c r="AU52">
         <v>4</v>
@@ -12001,25 +12001,25 @@
         <v>2.75</v>
       </c>
       <c r="AN53">
+        <v>2</v>
+      </c>
+      <c r="AO53">
+        <v>0.5</v>
+      </c>
+      <c r="AP53">
+        <v>1.86</v>
+      </c>
+      <c r="AQ53">
+        <v>0.43</v>
+      </c>
+      <c r="AR53">
+        <v>1.5</v>
+      </c>
+      <c r="AS53">
         <v>1.33</v>
       </c>
-      <c r="AO53">
-        <v>1.17</v>
-      </c>
-      <c r="AP53">
-        <v>1.25</v>
-      </c>
-      <c r="AQ53">
-        <v>0.75</v>
-      </c>
-      <c r="AR53">
-        <v>1.35</v>
-      </c>
-      <c r="AS53">
-        <v>1.8</v>
-      </c>
       <c r="AT53">
-        <v>3.15</v>
+        <v>2.83</v>
       </c>
       <c r="AU53">
         <v>4</v>
@@ -12207,25 +12207,25 @@
         <v>3.4</v>
       </c>
       <c r="AN54">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AO54">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AP54">
         <v>2.13</v>
       </c>
       <c r="AQ54">
-        <v>1.38</v>
+        <v>1</v>
       </c>
       <c r="AR54">
-        <v>2.17</v>
+        <v>2.36</v>
       </c>
       <c r="AS54">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AT54">
-        <v>3.55</v>
+        <v>3.63</v>
       </c>
       <c r="AU54">
         <v>6</v>
@@ -12413,25 +12413,25 @@
         <v>5.65</v>
       </c>
       <c r="AN55">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AO55">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AP55">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="AQ55">
-        <v>0.5</v>
+        <v>0.13</v>
       </c>
       <c r="AR55">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="AS55">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="AT55">
-        <v>3.54</v>
+        <v>3.57</v>
       </c>
       <c r="AU55">
         <v>10</v>
@@ -12619,25 +12619,25 @@
         <v>0</v>
       </c>
       <c r="AN56">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="AO56">
-        <v>0.71</v>
+        <v>0.25</v>
       </c>
       <c r="AP56">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="AQ56">
-        <v>1.19</v>
+        <v>0.88</v>
       </c>
       <c r="AR56">
-        <v>2.35</v>
+        <v>2.49</v>
       </c>
       <c r="AS56">
-        <v>1.43</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AT56">
-        <v>3.78</v>
+        <v>3.43</v>
       </c>
       <c r="AU56">
         <v>7</v>
@@ -12825,25 +12825,25 @@
         <v>0</v>
       </c>
       <c r="AN57">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AO57">
-        <v>2.29</v>
+        <v>3</v>
       </c>
       <c r="AP57">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="AQ57">
-        <v>1.56</v>
+        <v>1.38</v>
       </c>
       <c r="AR57">
-        <v>1.59</v>
+        <v>1.81</v>
       </c>
       <c r="AS57">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AT57">
-        <v>3.74</v>
+        <v>4</v>
       </c>
       <c r="AU57">
         <v>9</v>
@@ -13031,25 +13031,25 @@
         <v>1.48</v>
       </c>
       <c r="AN58">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AO58">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AP58">
-        <v>0.5</v>
+        <v>0.63</v>
       </c>
       <c r="AQ58">
+        <v>1</v>
+      </c>
+      <c r="AR58">
         <v>1.38</v>
       </c>
-      <c r="AR58">
-        <v>1.25</v>
-      </c>
       <c r="AS58">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AT58">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="AU58">
         <v>4</v>
@@ -13237,25 +13237,25 @@
         <v>1.6</v>
       </c>
       <c r="AN59">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AO59">
-        <v>1.29</v>
+        <v>0.5</v>
       </c>
       <c r="AP59">
-        <v>1.31</v>
+        <v>1.78</v>
       </c>
       <c r="AQ59">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="AR59">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AS59">
-        <v>1.53</v>
+        <v>1.21</v>
       </c>
       <c r="AT59">
-        <v>2.88</v>
+        <v>2.43</v>
       </c>
       <c r="AU59">
         <v>3</v>
@@ -13443,25 +13443,25 @@
         <v>2.15</v>
       </c>
       <c r="AN60">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AO60">
-        <v>0.29</v>
+        <v>0</v>
       </c>
       <c r="AP60">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="AQ60">
-        <v>0.5</v>
+        <v>0.13</v>
       </c>
       <c r="AR60">
-        <v>1.49</v>
+        <v>1.14</v>
       </c>
       <c r="AS60">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AT60">
-        <v>2.72</v>
+        <v>2.27</v>
       </c>
       <c r="AU60">
         <v>4</v>
@@ -13649,25 +13649,25 @@
         <v>1.65</v>
       </c>
       <c r="AN61">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="AO61">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AP61">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ61">
-        <v>0.88</v>
+        <v>0.5</v>
       </c>
       <c r="AR61">
-        <v>1.72</v>
+        <v>2.04</v>
       </c>
       <c r="AS61">
-        <v>1.41</v>
+        <v>1.23</v>
       </c>
       <c r="AT61">
-        <v>3.13</v>
+        <v>3.27</v>
       </c>
       <c r="AU61">
         <v>6</v>
@@ -13855,25 +13855,25 @@
         <v>1.8</v>
       </c>
       <c r="AN62">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AO62">
-        <v>1.29</v>
+        <v>1</v>
       </c>
       <c r="AP62">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AQ62">
-        <v>1.25</v>
+        <v>0.78</v>
       </c>
       <c r="AR62">
-        <v>1.85</v>
+        <v>2.42</v>
       </c>
       <c r="AS62">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="AT62">
-        <v>3.27</v>
+        <v>3.7</v>
       </c>
       <c r="AU62">
         <v>5</v>
@@ -14061,25 +14061,25 @@
         <v>1.65</v>
       </c>
       <c r="AN63">
+        <v>2.5</v>
+      </c>
+      <c r="AO63">
         <v>2.33</v>
       </c>
-      <c r="AO63">
-        <v>2</v>
-      </c>
       <c r="AP63">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AQ63">
         <v>2.13</v>
       </c>
       <c r="AR63">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="AS63">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="AT63">
-        <v>4.16</v>
+        <v>4.04</v>
       </c>
       <c r="AU63">
         <v>7</v>
@@ -14267,25 +14267,25 @@
         <v>2.25</v>
       </c>
       <c r="AN64">
-        <v>1.86</v>
+        <v>2.33</v>
       </c>
       <c r="AO64">
         <v>1</v>
       </c>
       <c r="AP64">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="AQ64">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="AR64">
-        <v>1.73</v>
+        <v>2.07</v>
       </c>
       <c r="AS64">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="AT64">
-        <v>3.22</v>
+        <v>3.74</v>
       </c>
       <c r="AU64">
         <v>4</v>
@@ -14473,25 +14473,25 @@
         <v>1.14</v>
       </c>
       <c r="AN65">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AO65">
         <v>2</v>
       </c>
       <c r="AP65">
-        <v>1.38</v>
+        <v>1.86</v>
       </c>
       <c r="AQ65">
-        <v>2.13</v>
+        <v>2.43</v>
       </c>
       <c r="AR65">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="AS65">
-        <v>1.97</v>
+        <v>1.89</v>
       </c>
       <c r="AT65">
-        <v>3.29</v>
+        <v>3.39</v>
       </c>
       <c r="AU65">
         <v>6</v>
@@ -14679,25 +14679,25 @@
         <v>1.13</v>
       </c>
       <c r="AN66">
+        <v>0.67</v>
+      </c>
+      <c r="AO66">
+        <v>2.5</v>
+      </c>
+      <c r="AP66">
         <v>0.63</v>
-      </c>
-      <c r="AO66">
-        <v>2.13</v>
-      </c>
-      <c r="AP66">
-        <v>0.5</v>
       </c>
       <c r="AQ66">
         <v>2.13</v>
       </c>
       <c r="AR66">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="AS66">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AT66">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AU66">
         <v>4</v>
@@ -14885,25 +14885,25 @@
         <v>1.47</v>
       </c>
       <c r="AN67">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AO67">
-        <v>1.13</v>
+        <v>0.4</v>
       </c>
       <c r="AP67">
-        <v>0.88</v>
+        <v>1.25</v>
       </c>
       <c r="AQ67">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="AR67">
-        <v>1.29</v>
+        <v>1.64</v>
       </c>
       <c r="AS67">
-        <v>1.55</v>
+        <v>1.31</v>
       </c>
       <c r="AT67">
-        <v>2.84</v>
+        <v>2.95</v>
       </c>
       <c r="AU67">
         <v>5</v>
@@ -15091,25 +15091,25 @@
         <v>1.43</v>
       </c>
       <c r="AN68">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AO68">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AP68">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="AQ68">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AR68">
+        <v>2.12</v>
+      </c>
+      <c r="AS68">
         <v>2.01</v>
       </c>
-      <c r="AS68">
-        <v>2.3</v>
-      </c>
       <c r="AT68">
-        <v>4.31</v>
+        <v>4.13</v>
       </c>
       <c r="AU68">
         <v>2</v>
@@ -15297,25 +15297,25 @@
         <v>1.47</v>
       </c>
       <c r="AN69">
-        <v>0.63</v>
+        <v>1.33</v>
       </c>
       <c r="AO69">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AP69">
-        <v>1.19</v>
+        <v>1.5</v>
       </c>
       <c r="AQ69">
         <v>1.56</v>
       </c>
       <c r="AR69">
-        <v>1.4</v>
+        <v>2.08</v>
       </c>
       <c r="AS69">
-        <v>1.81</v>
+        <v>1.07</v>
       </c>
       <c r="AT69">
-        <v>3.21</v>
+        <v>3.15</v>
       </c>
       <c r="AU69">
         <v>11</v>
@@ -15503,25 +15503,25 @@
         <v>1.46</v>
       </c>
       <c r="AN70">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="AO70">
-        <v>1.38</v>
+        <v>0.67</v>
       </c>
       <c r="AP70">
-        <v>0.5</v>
+        <v>0.88</v>
       </c>
       <c r="AQ70">
-        <v>0.75</v>
+        <v>0.43</v>
       </c>
       <c r="AR70">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AS70">
-        <v>1.75</v>
+        <v>1.29</v>
       </c>
       <c r="AT70">
-        <v>2.93</v>
+        <v>2.59</v>
       </c>
       <c r="AU70">
         <v>3</v>
@@ -15709,25 +15709,25 @@
         <v>2.19</v>
       </c>
       <c r="AN71">
-        <v>1.13</v>
+        <v>1.67</v>
       </c>
       <c r="AO71">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="AP71">
-        <v>1.25</v>
+        <v>1.86</v>
       </c>
       <c r="AQ71">
-        <v>1.31</v>
+        <v>0.71</v>
       </c>
       <c r="AR71">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AS71">
-        <v>1.26</v>
+        <v>1.63</v>
       </c>
       <c r="AT71">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="AU71">
         <v>3</v>
@@ -15915,25 +15915,25 @@
         <v>1.68</v>
       </c>
       <c r="AN72">
-        <v>1.11</v>
+        <v>2.33</v>
       </c>
       <c r="AO72">
         <v>1</v>
       </c>
       <c r="AP72">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="AQ72">
-        <v>1.38</v>
+        <v>1</v>
       </c>
       <c r="AR72">
-        <v>1.53</v>
+        <v>1.95</v>
       </c>
       <c r="AS72">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="AT72">
-        <v>2.91</v>
+        <v>3.16</v>
       </c>
       <c r="AU72">
         <v>8</v>
@@ -16121,25 +16121,25 @@
         <v>1.36</v>
       </c>
       <c r="AN73">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AO73">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AP73">
-        <v>0.88</v>
+        <v>1.25</v>
       </c>
       <c r="AQ73">
         <v>1.56</v>
       </c>
       <c r="AR73">
-        <v>1.3</v>
+        <v>1.59</v>
       </c>
       <c r="AS73">
-        <v>1.75</v>
+        <v>1.12</v>
       </c>
       <c r="AT73">
-        <v>3.05</v>
+        <v>2.71</v>
       </c>
       <c r="AU73">
         <v>4</v>
@@ -16327,25 +16327,25 @@
         <v>2.15</v>
       </c>
       <c r="AN74">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="AO74">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AP74">
-        <v>1.25</v>
+        <v>1.86</v>
       </c>
       <c r="AQ74">
-        <v>0.5</v>
+        <v>0.38</v>
       </c>
       <c r="AR74">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="AS74">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AT74">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="AU74">
         <v>8</v>
@@ -16533,25 +16533,25 @@
         <v>1.77</v>
       </c>
       <c r="AN75">
+        <v>1</v>
+      </c>
+      <c r="AO75">
+        <v>0.2</v>
+      </c>
+      <c r="AP75">
         <v>0.88</v>
       </c>
-      <c r="AO75">
-        <v>0.89</v>
-      </c>
-      <c r="AP75">
-        <v>0.9399999999999999</v>
-      </c>
       <c r="AQ75">
-        <v>1.19</v>
+        <v>0.88</v>
       </c>
       <c r="AR75">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AS75">
-        <v>1.48</v>
+        <v>0.99</v>
       </c>
       <c r="AT75">
-        <v>2.87</v>
+        <v>2.25</v>
       </c>
       <c r="AU75">
         <v>6</v>
@@ -16739,25 +16739,25 @@
         <v>3.9</v>
       </c>
       <c r="AN76">
-        <v>1.78</v>
+        <v>1.4</v>
       </c>
       <c r="AO76">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AP76">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="AQ76">
-        <v>0.5</v>
+        <v>0.13</v>
       </c>
       <c r="AR76">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AS76">
-        <v>1.26</v>
+        <v>1.07</v>
       </c>
       <c r="AT76">
-        <v>3.16</v>
+        <v>2.96</v>
       </c>
       <c r="AU76">
         <v>5</v>
@@ -16945,25 +16945,25 @@
         <v>1.67</v>
       </c>
       <c r="AN77">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AO77">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AP77">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AQ77">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AR77">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AS77">
-        <v>1.69</v>
+        <v>1.48</v>
       </c>
       <c r="AT77">
-        <v>3.53</v>
+        <v>3.48</v>
       </c>
       <c r="AU77">
         <v>8</v>
@@ -17151,25 +17151,25 @@
         <v>1.8</v>
       </c>
       <c r="AN78">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AO78">
-        <v>1.33</v>
+        <v>0.75</v>
       </c>
       <c r="AP78">
-        <v>1.31</v>
+        <v>1.78</v>
       </c>
       <c r="AQ78">
-        <v>0.75</v>
+        <v>0.43</v>
       </c>
       <c r="AR78">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AS78">
-        <v>1.68</v>
+        <v>1.26</v>
       </c>
       <c r="AT78">
-        <v>2.93</v>
+        <v>2.38</v>
       </c>
       <c r="AU78">
         <v>6</v>
@@ -17357,25 +17357,25 @@
         <v>1.65</v>
       </c>
       <c r="AN79">
-        <v>2.22</v>
+        <v>1.75</v>
       </c>
       <c r="AO79">
-        <v>2.56</v>
+        <v>2.33</v>
       </c>
       <c r="AP79">
         <v>2.13</v>
       </c>
       <c r="AQ79">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AR79">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="AS79">
-        <v>2.17</v>
+        <v>1.71</v>
       </c>
       <c r="AT79">
-        <v>4.27</v>
+        <v>3.99</v>
       </c>
       <c r="AU79">
         <v>3</v>
@@ -17563,25 +17563,25 @@
         <v>0</v>
       </c>
       <c r="AN80">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="AO80">
-        <v>2.11</v>
+        <v>1.8</v>
       </c>
       <c r="AP80">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="AQ80">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AR80">
-        <v>1.6</v>
+        <v>2.04</v>
       </c>
       <c r="AS80">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AT80">
-        <v>3.27</v>
+        <v>3.54</v>
       </c>
       <c r="AU80">
         <v>2</v>
@@ -17769,25 +17769,25 @@
         <v>0</v>
       </c>
       <c r="AN81">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="AO81">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="AP81">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="AQ81">
         <v>1.56</v>
       </c>
       <c r="AR81">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AS81">
-        <v>1.69</v>
+        <v>1.14</v>
       </c>
       <c r="AT81">
-        <v>3.13</v>
+        <v>2.55</v>
       </c>
       <c r="AU81">
         <v>5</v>
@@ -17975,25 +17975,25 @@
         <v>0</v>
       </c>
       <c r="AN82">
-        <v>1.1</v>
+        <v>1.75</v>
       </c>
       <c r="AO82">
-        <v>1.89</v>
+        <v>2.33</v>
       </c>
       <c r="AP82">
-        <v>1.19</v>
+        <v>1.5</v>
       </c>
       <c r="AQ82">
-        <v>2.13</v>
+        <v>2.43</v>
       </c>
       <c r="AR82">
-        <v>1.44</v>
+        <v>2.09</v>
       </c>
       <c r="AS82">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AT82">
-        <v>3.35</v>
+        <v>3.66</v>
       </c>
       <c r="AU82">
         <v>7</v>
@@ -18181,25 +18181,25 @@
         <v>0</v>
       </c>
       <c r="AN83">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="AO83">
         <v>0.5</v>
       </c>
       <c r="AP83">
-        <v>0.5</v>
+        <v>0.88</v>
       </c>
       <c r="AQ83">
-        <v>0.5</v>
+        <v>0.38</v>
       </c>
       <c r="AR83">
-        <v>1.24</v>
+        <v>1.41</v>
       </c>
       <c r="AS83">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AT83">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="AU83">
         <v>7</v>
@@ -18387,25 +18387,25 @@
         <v>0</v>
       </c>
       <c r="AN84">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AO84">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="AP84">
         <v>2.13</v>
       </c>
       <c r="AQ84">
-        <v>1.25</v>
+        <v>0.78</v>
       </c>
       <c r="AR84">
-        <v>2.04</v>
+        <v>2.13</v>
       </c>
       <c r="AS84">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="AT84">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="AU84">
         <v>6</v>
@@ -18593,25 +18593,25 @@
         <v>0</v>
       </c>
       <c r="AN85">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AO85">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="AP85">
+        <v>1.86</v>
+      </c>
+      <c r="AQ85">
         <v>1.38</v>
       </c>
-      <c r="AQ85">
-        <v>1.56</v>
-      </c>
       <c r="AR85">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AS85">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AT85">
-        <v>3.36</v>
+        <v>3.5</v>
       </c>
       <c r="AU85">
         <v>8</v>
@@ -18799,25 +18799,25 @@
         <v>0</v>
       </c>
       <c r="AN86">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="AO86">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="AP86">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ86">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AR86">
-        <v>1.67</v>
+        <v>2.02</v>
       </c>
       <c r="AS86">
-        <v>2.08</v>
+        <v>1.59</v>
       </c>
       <c r="AT86">
-        <v>3.75</v>
+        <v>3.61</v>
       </c>
       <c r="AU86">
         <v>3</v>
@@ -19005,25 +19005,25 @@
         <v>0</v>
       </c>
       <c r="AN87">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AO87">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="AP87">
-        <v>1.31</v>
+        <v>1.78</v>
       </c>
       <c r="AQ87">
-        <v>0.88</v>
+        <v>0.5</v>
       </c>
       <c r="AR87">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AS87">
-        <v>1.3</v>
+        <v>1.07</v>
       </c>
       <c r="AT87">
-        <v>2.57</v>
+        <v>2.24</v>
       </c>
       <c r="AU87">
         <v>3</v>
@@ -19211,25 +19211,25 @@
         <v>0</v>
       </c>
       <c r="AN88">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AO88">
-        <v>0.64</v>
+        <v>0.2</v>
       </c>
       <c r="AP88">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AQ88">
-        <v>0.5</v>
+        <v>0.13</v>
       </c>
       <c r="AR88">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="AS88">
-        <v>1.31</v>
+        <v>1.07</v>
       </c>
       <c r="AT88">
-        <v>3.22</v>
+        <v>3.15</v>
       </c>
       <c r="AU88">
         <v>8</v>
@@ -19417,25 +19417,25 @@
         <v>0</v>
       </c>
       <c r="AN89">
-        <v>2.36</v>
+        <v>2.67</v>
       </c>
       <c r="AO89">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AP89">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="AQ89">
-        <v>1.31</v>
+        <v>0.71</v>
       </c>
       <c r="AR89">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AS89">
-        <v>1.31</v>
+        <v>1.47</v>
       </c>
       <c r="AT89">
-        <v>3.41</v>
+        <v>3.87</v>
       </c>
       <c r="AU89">
         <v>10</v>
@@ -19623,25 +19623,25 @@
         <v>0</v>
       </c>
       <c r="AN90">
-        <v>1.09</v>
+        <v>1.5</v>
       </c>
       <c r="AO90">
-        <v>2.36</v>
+        <v>2.6</v>
       </c>
       <c r="AP90">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ90">
         <v>2.13</v>
       </c>
       <c r="AR90">
-        <v>1.67</v>
+        <v>1.96</v>
       </c>
       <c r="AS90">
-        <v>2.03</v>
+        <v>1.96</v>
       </c>
       <c r="AT90">
-        <v>3.7</v>
+        <v>3.92</v>
       </c>
       <c r="AU90">
         <v>0</v>
@@ -19829,25 +19829,25 @@
         <v>0</v>
       </c>
       <c r="AN91">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="AO91">
-        <v>1.36</v>
+        <v>0.67</v>
       </c>
       <c r="AP91">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="AQ91">
-        <v>1.25</v>
+        <v>0.78</v>
       </c>
       <c r="AR91">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AS91">
-        <v>1.37</v>
+        <v>1.2</v>
       </c>
       <c r="AT91">
-        <v>3.31</v>
+        <v>3.13</v>
       </c>
       <c r="AU91">
         <v>9</v>
@@ -20035,25 +20035,25 @@
         <v>0</v>
       </c>
       <c r="AN92">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AO92">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AP92">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="AQ92">
-        <v>0.88</v>
+        <v>0.5</v>
       </c>
       <c r="AR92">
-        <v>1.66</v>
+        <v>1.9</v>
       </c>
       <c r="AS92">
-        <v>1.22</v>
+        <v>0.96</v>
       </c>
       <c r="AT92">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="AU92">
         <v>7</v>
@@ -20241,25 +20241,25 @@
         <v>1.35</v>
       </c>
       <c r="AN93">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="AO93">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="AP93">
-        <v>0.5</v>
+        <v>0.63</v>
       </c>
       <c r="AQ93">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="AR93">
         <v>1.27</v>
       </c>
       <c r="AS93">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AT93">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="AU93">
         <v>3</v>
@@ -20447,25 +20447,25 @@
         <v>1.83</v>
       </c>
       <c r="AN94">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="AO94">
-        <v>1.09</v>
+        <v>0.83</v>
       </c>
       <c r="AP94">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AQ94">
-        <v>1.38</v>
+        <v>1</v>
       </c>
       <c r="AR94">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="AS94">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AT94">
-        <v>3.13</v>
+        <v>3.58</v>
       </c>
       <c r="AU94">
         <v>8</v>
@@ -20653,25 +20653,25 @@
         <v>1.62</v>
       </c>
       <c r="AN95">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AO95">
-        <v>1.18</v>
+        <v>0.5</v>
       </c>
       <c r="AP95">
-        <v>1.19</v>
+        <v>1.5</v>
       </c>
       <c r="AQ95">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="AR95">
-        <v>1.49</v>
+        <v>2.07</v>
       </c>
       <c r="AS95">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="AT95">
-        <v>3.06</v>
+        <v>3.39</v>
       </c>
       <c r="AU95">
         <v>5</v>
@@ -20859,25 +20859,25 @@
         <v>1.83</v>
       </c>
       <c r="AN96">
-        <v>1.25</v>
+        <v>2.2</v>
       </c>
       <c r="AO96">
-        <v>0.91</v>
+        <v>1.17</v>
       </c>
       <c r="AP96">
-        <v>1.25</v>
+        <v>1.86</v>
       </c>
       <c r="AQ96">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="AR96">
-        <v>1.43</v>
+        <v>1.59</v>
       </c>
       <c r="AS96">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AT96">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="AU96">
         <v>5</v>
@@ -21065,25 +21065,25 @@
         <v>1.83</v>
       </c>
       <c r="AN97">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AO97">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="AP97">
-        <v>1.38</v>
+        <v>1.86</v>
       </c>
       <c r="AQ97">
-        <v>0.75</v>
+        <v>0.43</v>
       </c>
       <c r="AR97">
-        <v>1.47</v>
+        <v>1.63</v>
       </c>
       <c r="AS97">
-        <v>1.6</v>
+        <v>1.32</v>
       </c>
       <c r="AT97">
-        <v>3.07</v>
+        <v>2.95</v>
       </c>
       <c r="AU97">
         <v>5</v>
@@ -21271,25 +21271,25 @@
         <v>1.14</v>
       </c>
       <c r="AN98">
-        <v>1.17</v>
+        <v>2</v>
       </c>
       <c r="AO98">
-        <v>2.42</v>
+        <v>2</v>
       </c>
       <c r="AP98">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="AQ98">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AR98">
-        <v>1.52</v>
+        <v>1.87</v>
       </c>
       <c r="AS98">
-        <v>2.1</v>
+        <v>1.74</v>
       </c>
       <c r="AT98">
-        <v>3.62</v>
+        <v>3.61</v>
       </c>
       <c r="AU98">
         <v>6</v>
@@ -21477,25 +21477,25 @@
         <v>1.36</v>
       </c>
       <c r="AN99">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="AO99">
         <v>1.33</v>
       </c>
       <c r="AP99">
-        <v>0.5</v>
+        <v>0.63</v>
       </c>
       <c r="AQ99">
         <v>1.56</v>
       </c>
       <c r="AR99">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AS99">
-        <v>1.76</v>
+        <v>1.19</v>
       </c>
       <c r="AT99">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="AU99">
         <v>6</v>
@@ -21683,25 +21683,25 @@
         <v>3.05</v>
       </c>
       <c r="AN100">
-        <v>2.42</v>
+        <v>2.17</v>
       </c>
       <c r="AO100">
-        <v>1.45</v>
+        <v>1</v>
       </c>
       <c r="AP100">
         <v>2.13</v>
       </c>
       <c r="AQ100">
-        <v>1.31</v>
+        <v>0.71</v>
       </c>
       <c r="AR100">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="AS100">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AT100">
-        <v>3.34</v>
+        <v>3.43</v>
       </c>
       <c r="AU100">
         <v>9</v>
@@ -21889,25 +21889,25 @@
         <v>1.11</v>
       </c>
       <c r="AN101">
-        <v>0.58</v>
+        <v>1</v>
       </c>
       <c r="AO101">
-        <v>2.27</v>
+        <v>2</v>
       </c>
       <c r="AP101">
-        <v>0.5</v>
+        <v>0.88</v>
       </c>
       <c r="AQ101">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AR101">
-        <v>1.32</v>
+        <v>1.51</v>
       </c>
       <c r="AS101">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AT101">
-        <v>3.05</v>
+        <v>3.01</v>
       </c>
       <c r="AU101">
         <v>3</v>
@@ -22095,25 +22095,25 @@
         <v>1.89</v>
       </c>
       <c r="AN102">
-        <v>2.09</v>
+        <v>1.86</v>
       </c>
       <c r="AO102">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AP102">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AQ102">
-        <v>1.56</v>
+        <v>1.38</v>
       </c>
       <c r="AR102">
-        <v>2.01</v>
+        <v>2.21</v>
       </c>
       <c r="AS102">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AT102">
-        <v>3.93</v>
+        <v>4.15</v>
       </c>
       <c r="AU102">
         <v>3</v>
@@ -22301,25 +22301,25 @@
         <v>2.38</v>
       </c>
       <c r="AN103">
-        <v>1.08</v>
+        <v>1.67</v>
       </c>
       <c r="AO103">
-        <v>0.92</v>
+        <v>0.5</v>
       </c>
       <c r="AP103">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="AQ103">
-        <v>0.75</v>
+        <v>0.43</v>
       </c>
       <c r="AR103">
-        <v>1.53</v>
+        <v>1.84</v>
       </c>
       <c r="AS103">
-        <v>1.58</v>
+        <v>1.31</v>
       </c>
       <c r="AT103">
-        <v>3.11</v>
+        <v>3.15</v>
       </c>
       <c r="AU103">
         <v>2</v>
@@ -22507,25 +22507,25 @@
         <v>1.94</v>
       </c>
       <c r="AN104">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AO104">
-        <v>0.62</v>
+        <v>0.17</v>
       </c>
       <c r="AP104">
-        <v>1.19</v>
+        <v>1.5</v>
       </c>
       <c r="AQ104">
-        <v>0.5</v>
+        <v>0.13</v>
       </c>
       <c r="AR104">
-        <v>1.54</v>
+        <v>2.06</v>
       </c>
       <c r="AS104">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="AT104">
-        <v>2.86</v>
+        <v>3.2</v>
       </c>
       <c r="AU104">
         <v>6</v>
@@ -22713,25 +22713,25 @@
         <v>1.32</v>
       </c>
       <c r="AN105">
-        <v>1.23</v>
+        <v>2</v>
       </c>
       <c r="AO105">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AP105">
-        <v>1.25</v>
+        <v>1.86</v>
       </c>
       <c r="AQ105">
-        <v>2.13</v>
+        <v>2.43</v>
       </c>
       <c r="AR105">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="AS105">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AT105">
-        <v>3.37</v>
+        <v>3.23</v>
       </c>
       <c r="AU105">
         <v>8</v>
@@ -22919,25 +22919,25 @@
         <v>1.6</v>
       </c>
       <c r="AN106">
-        <v>1.42</v>
+        <v>1.71</v>
       </c>
       <c r="AO106">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="AP106">
-        <v>1.31</v>
+        <v>1.78</v>
       </c>
       <c r="AQ106">
-        <v>1.38</v>
+        <v>1</v>
       </c>
       <c r="AR106">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AS106">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AT106">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AU106">
         <v>3</v>
@@ -23125,25 +23125,25 @@
         <v>4.8</v>
       </c>
       <c r="AN107">
-        <v>2.17</v>
+        <v>2.6</v>
       </c>
       <c r="AO107">
+        <v>0.43</v>
+      </c>
+      <c r="AP107">
+        <v>2.75</v>
+      </c>
+      <c r="AQ107">
         <v>0.38</v>
       </c>
-      <c r="AP107">
-        <v>2.38</v>
-      </c>
-      <c r="AQ107">
-        <v>0.5</v>
-      </c>
       <c r="AR107">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AS107">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AT107">
-        <v>2.94</v>
+        <v>3.28</v>
       </c>
       <c r="AU107">
         <v>6</v>
@@ -23331,25 +23331,25 @@
         <v>0</v>
       </c>
       <c r="AN108">
-        <v>0.92</v>
+        <v>1.4</v>
       </c>
       <c r="AO108">
-        <v>2.46</v>
+        <v>2.17</v>
       </c>
       <c r="AP108">
-        <v>0.88</v>
+        <v>1.25</v>
       </c>
       <c r="AQ108">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AR108">
-        <v>1.19</v>
+        <v>1.54</v>
       </c>
       <c r="AS108">
-        <v>2.11</v>
+        <v>1.81</v>
       </c>
       <c r="AT108">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AU108">
         <v>5</v>
@@ -23537,25 +23537,25 @@
         <v>1.14</v>
       </c>
       <c r="AN109">
-        <v>0.92</v>
+        <v>0.6</v>
       </c>
       <c r="AO109">
-        <v>2.31</v>
+        <v>2.67</v>
       </c>
       <c r="AP109">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="AQ109">
         <v>2.13</v>
       </c>
       <c r="AR109">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="AS109">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AT109">
-        <v>3.64</v>
+        <v>3.53</v>
       </c>
       <c r="AU109">
         <v>9</v>
@@ -23743,25 +23743,25 @@
         <v>1.3</v>
       </c>
       <c r="AN110">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AO110">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AP110">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AQ110">
-        <v>1.56</v>
+        <v>1.38</v>
       </c>
       <c r="AR110">
-        <v>1.71</v>
+        <v>2.32</v>
       </c>
       <c r="AS110">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AT110">
-        <v>3.66</v>
+        <v>4.32</v>
       </c>
       <c r="AU110">
         <v>5</v>
@@ -23949,25 +23949,25 @@
         <v>2.7</v>
       </c>
       <c r="AN111">
-        <v>2.23</v>
+        <v>2.67</v>
       </c>
       <c r="AO111">
-        <v>1.38</v>
+        <v>1</v>
       </c>
       <c r="AP111">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="AQ111">
-        <v>1.31</v>
+        <v>0.71</v>
       </c>
       <c r="AR111">
-        <v>1.69</v>
+        <v>1.97</v>
       </c>
       <c r="AS111">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AT111">
-        <v>2.94</v>
+        <v>3.19</v>
       </c>
       <c r="AU111">
         <v>5</v>
@@ -24155,25 +24155,25 @@
         <v>1.2</v>
       </c>
       <c r="AN112">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AO112">
-        <v>1.92</v>
+        <v>2.2</v>
       </c>
       <c r="AP112">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="AQ112">
-        <v>2.13</v>
+        <v>2.43</v>
       </c>
       <c r="AR112">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AS112">
-        <v>1.92</v>
+        <v>1.64</v>
       </c>
       <c r="AT112">
-        <v>3.5</v>
+        <v>3.23</v>
       </c>
       <c r="AU112">
         <v>7</v>
@@ -24361,25 +24361,25 @@
         <v>1.51</v>
       </c>
       <c r="AN113">
-        <v>1.08</v>
+        <v>1.67</v>
       </c>
       <c r="AO113">
-        <v>1.15</v>
+        <v>0.67</v>
       </c>
       <c r="AP113">
+        <v>1.25</v>
+      </c>
+      <c r="AQ113">
         <v>0.88</v>
       </c>
-      <c r="AQ113">
-        <v>1.19</v>
-      </c>
       <c r="AR113">
-        <v>1.19</v>
+        <v>1.49</v>
       </c>
       <c r="AS113">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="AT113">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="AU113">
         <v>5</v>
@@ -24567,25 +24567,25 @@
         <v>3.05</v>
       </c>
       <c r="AN114">
-        <v>2.29</v>
+        <v>2.71</v>
       </c>
       <c r="AO114">
         <v>1.57</v>
       </c>
       <c r="AP114">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="AQ114">
         <v>1.56</v>
       </c>
       <c r="AR114">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="AS114">
-        <v>1.7</v>
+        <v>1.18</v>
       </c>
       <c r="AT114">
-        <v>3.8</v>
+        <v>3.54</v>
       </c>
       <c r="AU114">
         <v>7</v>
@@ -24773,25 +24773,25 @@
         <v>1.34</v>
       </c>
       <c r="AN115">
+        <v>1</v>
+      </c>
+      <c r="AO115">
         <v>0.57</v>
       </c>
-      <c r="AO115">
-        <v>1.21</v>
-      </c>
       <c r="AP115">
-        <v>0.5</v>
+        <v>0.88</v>
       </c>
       <c r="AQ115">
-        <v>1.25</v>
+        <v>0.78</v>
       </c>
       <c r="AR115">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="AS115">
-        <v>1.45</v>
+        <v>1.31</v>
       </c>
       <c r="AT115">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="AU115">
         <v>4</v>
@@ -24979,25 +24979,25 @@
         <v>1.38</v>
       </c>
       <c r="AN116">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AO116">
-        <v>1.29</v>
+        <v>0.83</v>
       </c>
       <c r="AP116">
-        <v>0.5</v>
+        <v>0.63</v>
       </c>
       <c r="AQ116">
-        <v>1.31</v>
+        <v>0.71</v>
       </c>
       <c r="AR116">
         <v>1.24</v>
       </c>
       <c r="AS116">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AT116">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="AU116">
         <v>6</v>
@@ -25185,25 +25185,25 @@
         <v>2.55</v>
       </c>
       <c r="AN117">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AO117">
-        <v>1.29</v>
+        <v>1</v>
       </c>
       <c r="AP117">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="AQ117">
-        <v>1.19</v>
+        <v>0.88</v>
       </c>
       <c r="AR117">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AS117">
-        <v>1.53</v>
+        <v>1.09</v>
       </c>
       <c r="AT117">
-        <v>3.42</v>
+        <v>2.99</v>
       </c>
       <c r="AU117">
         <v>18</v>
@@ -25391,25 +25391,25 @@
         <v>1.12</v>
       </c>
       <c r="AN118">
-        <v>0.86</v>
+        <v>1.29</v>
       </c>
       <c r="AO118">
-        <v>2.29</v>
+        <v>1.86</v>
       </c>
       <c r="AP118">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ118">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AR118">
-        <v>1.52</v>
+        <v>1.81</v>
       </c>
       <c r="AS118">
-        <v>1.65</v>
+        <v>1.46</v>
       </c>
       <c r="AT118">
-        <v>3.17</v>
+        <v>3.27</v>
       </c>
       <c r="AU118">
         <v>5</v>
@@ -25597,25 +25597,25 @@
         <v>4.7</v>
       </c>
       <c r="AN119">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AO119">
-        <v>1</v>
+        <v>0.57</v>
       </c>
       <c r="AP119">
         <v>2.13</v>
       </c>
       <c r="AQ119">
-        <v>0.88</v>
+        <v>0.5</v>
       </c>
       <c r="AR119">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AS119">
-        <v>1.21</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AT119">
-        <v>3.28</v>
+        <v>3.09</v>
       </c>
       <c r="AU119">
         <v>9</v>
@@ -25803,25 +25803,25 @@
         <v>3.2</v>
       </c>
       <c r="AN120">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AO120">
-        <v>1.21</v>
+        <v>0.57</v>
       </c>
       <c r="AP120">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AQ120">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="AR120">
-        <v>1.91</v>
+        <v>2.09</v>
       </c>
       <c r="AS120">
-        <v>1.51</v>
+        <v>1.27</v>
       </c>
       <c r="AT120">
-        <v>3.42</v>
+        <v>3.36</v>
       </c>
       <c r="AU120">
         <v>4</v>
@@ -26009,25 +26009,25 @@
         <v>1.57</v>
       </c>
       <c r="AN121">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="AO121">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AP121">
-        <v>1.38</v>
+        <v>1.86</v>
       </c>
       <c r="AQ121">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="AR121">
-        <v>1.46</v>
+        <v>1.59</v>
       </c>
       <c r="AS121">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AT121">
-        <v>3.09</v>
+        <v>3.16</v>
       </c>
       <c r="AU121">
         <v>5</v>
@@ -26215,25 +26215,25 @@
         <v>1.06</v>
       </c>
       <c r="AN122">
-        <v>0.53</v>
+        <v>0.71</v>
       </c>
       <c r="AO122">
-        <v>2.33</v>
+        <v>1.86</v>
       </c>
       <c r="AP122">
-        <v>0.5</v>
+        <v>0.63</v>
       </c>
       <c r="AQ122">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AR122">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AS122">
-        <v>2.12</v>
+        <v>1.85</v>
       </c>
       <c r="AT122">
-        <v>3.38</v>
+        <v>3.14</v>
       </c>
       <c r="AU122">
         <v>6</v>
@@ -26421,25 +26421,25 @@
         <v>2.52</v>
       </c>
       <c r="AN123">
-        <v>1.2</v>
+        <v>1.63</v>
       </c>
       <c r="AO123">
-        <v>0.53</v>
+        <v>0.14</v>
       </c>
       <c r="AP123">
-        <v>1.31</v>
+        <v>1.78</v>
       </c>
       <c r="AQ123">
-        <v>0.5</v>
+        <v>0.13</v>
       </c>
       <c r="AR123">
         <v>1.27</v>
       </c>
       <c r="AS123">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AT123">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="AU123">
         <v>6</v>
@@ -26627,25 +26627,25 @@
         <v>1.7</v>
       </c>
       <c r="AN124">
-        <v>0.8</v>
+        <v>1.13</v>
       </c>
       <c r="AO124">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AP124">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ124">
         <v>1.56</v>
       </c>
       <c r="AR124">
-        <v>1.51</v>
+        <v>1.76</v>
       </c>
       <c r="AS124">
-        <v>1.69</v>
+        <v>1.24</v>
       </c>
       <c r="AT124">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AU124">
         <v>5</v>
@@ -26833,25 +26833,25 @@
         <v>1.11</v>
       </c>
       <c r="AN125">
-        <v>1.2</v>
+        <v>1.57</v>
       </c>
       <c r="AO125">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="AP125">
-        <v>1.19</v>
+        <v>1.5</v>
       </c>
       <c r="AQ125">
         <v>2.13</v>
       </c>
       <c r="AR125">
-        <v>1.53</v>
+        <v>1.97</v>
       </c>
       <c r="AS125">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AT125">
-        <v>3.58</v>
+        <v>3.97</v>
       </c>
       <c r="AU125">
         <v>3</v>
@@ -27039,25 +27039,25 @@
         <v>1.5</v>
       </c>
       <c r="AN126">
-        <v>0.93</v>
+        <v>0.86</v>
       </c>
       <c r="AO126">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="AP126">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="AQ126">
-        <v>1.56</v>
+        <v>1.38</v>
       </c>
       <c r="AR126">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AS126">
-        <v>2.04</v>
+        <v>1.88</v>
       </c>
       <c r="AT126">
-        <v>3.72</v>
+        <v>3.57</v>
       </c>
       <c r="AU126">
         <v>11</v>
@@ -27245,25 +27245,25 @@
         <v>1.49</v>
       </c>
       <c r="AN127">
-        <v>1.13</v>
+        <v>1.86</v>
       </c>
       <c r="AO127">
-        <v>1.33</v>
+        <v>0.88</v>
       </c>
       <c r="AP127">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="AQ127">
-        <v>1.25</v>
+        <v>0.78</v>
       </c>
       <c r="AR127">
-        <v>1.49</v>
+        <v>1.76</v>
       </c>
       <c r="AS127">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AT127">
-        <v>2.95</v>
+        <v>3.12</v>
       </c>
       <c r="AU127">
         <v>6</v>
@@ -27451,25 +27451,25 @@
         <v>2.86</v>
       </c>
       <c r="AN128">
-        <v>2.33</v>
+        <v>2.71</v>
       </c>
       <c r="AO128">
-        <v>1.47</v>
+        <v>1.13</v>
       </c>
       <c r="AP128">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="AQ128">
-        <v>1.38</v>
+        <v>1</v>
       </c>
       <c r="AR128">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AS128">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="AT128">
-        <v>3.11</v>
+        <v>3.22</v>
       </c>
       <c r="AU128">
         <v>8</v>
@@ -27657,25 +27657,25 @@
         <v>1.33</v>
       </c>
       <c r="AN129">
-        <v>0.93</v>
+        <v>1.43</v>
       </c>
       <c r="AO129">
-        <v>2.07</v>
+        <v>2.33</v>
       </c>
       <c r="AP129">
-        <v>0.88</v>
+        <v>1.25</v>
       </c>
       <c r="AQ129">
-        <v>2.13</v>
+        <v>2.43</v>
       </c>
       <c r="AR129">
-        <v>1.17</v>
+        <v>1.48</v>
       </c>
       <c r="AS129">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AT129">
-        <v>3.04</v>
+        <v>3.15</v>
       </c>
       <c r="AU129">
         <v>4</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="842" uniqueCount="265">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -807,6 +807,9 @@
   <si>
     <t>['63', '77']</t>
   </si>
+  <si>
+    <t>['45+1', '71', '90+12']</t>
+  </si>
 </sst>
 </file>
 
@@ -1167,7 +1170,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP129"/>
+  <dimension ref="A1:BP130"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -4800,7 +4803,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ18">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AR18">
         <v>0.8</v>
@@ -6857,7 +6860,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ28">
         <v>0.88</v>
@@ -8299,7 +8302,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ35">
         <v>1.38</v>
@@ -11598,7 +11601,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ51">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AR51">
         <v>2.87</v>
@@ -13037,7 +13040,7 @@
         <v>1</v>
       </c>
       <c r="AP58">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ58">
         <v>1</v>
@@ -14482,7 +14485,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ65">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AR65">
         <v>1.5</v>
@@ -14685,7 +14688,7 @@
         <v>2.5</v>
       </c>
       <c r="AP66">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ66">
         <v>2.13</v>
@@ -17984,7 +17987,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ82">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AR82">
         <v>2.09</v>
@@ -20247,7 +20250,7 @@
         <v>0.8</v>
       </c>
       <c r="AP93">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ93">
         <v>1</v>
@@ -21483,7 +21486,7 @@
         <v>1.33</v>
       </c>
       <c r="AP99">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ99">
         <v>1.56</v>
@@ -22722,7 +22725,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ105">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AR105">
         <v>1.56</v>
@@ -24164,7 +24167,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ112">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AR112">
         <v>1.59</v>
@@ -24985,7 +24988,7 @@
         <v>0.83</v>
       </c>
       <c r="AP116">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ116">
         <v>0.71</v>
@@ -26221,7 +26224,7 @@
         <v>1.86</v>
       </c>
       <c r="AP122">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ122">
         <v>2</v>
@@ -27666,7 +27669,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ129">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AR129">
         <v>1.48</v>
@@ -27742,6 +27745,212 @@
       </c>
       <c r="BP129">
         <v>1.37</v>
+      </c>
+    </row>
+    <row r="130" spans="1:68">
+      <c r="A130" s="1">
+        <v>129</v>
+      </c>
+      <c r="B130">
+        <v>7825321</v>
+      </c>
+      <c r="C130" t="s">
+        <v>68</v>
+      </c>
+      <c r="D130" t="s">
+        <v>69</v>
+      </c>
+      <c r="E130" s="2">
+        <v>45856.22916666666</v>
+      </c>
+      <c r="F130">
+        <v>17</v>
+      </c>
+      <c r="G130" t="s">
+        <v>85</v>
+      </c>
+      <c r="H130" t="s">
+        <v>77</v>
+      </c>
+      <c r="I130">
+        <v>0</v>
+      </c>
+      <c r="J130">
+        <v>1</v>
+      </c>
+      <c r="K130">
+        <v>1</v>
+      </c>
+      <c r="L130">
+        <v>1</v>
+      </c>
+      <c r="M130">
+        <v>3</v>
+      </c>
+      <c r="N130">
+        <v>4</v>
+      </c>
+      <c r="O130" t="s">
+        <v>124</v>
+      </c>
+      <c r="P130" t="s">
+        <v>264</v>
+      </c>
+      <c r="Q130">
+        <v>6.05</v>
+      </c>
+      <c r="R130">
+        <v>2.71</v>
+      </c>
+      <c r="S130">
+        <v>1.75</v>
+      </c>
+      <c r="T130">
+        <v>1.17</v>
+      </c>
+      <c r="U130">
+        <v>4.2</v>
+      </c>
+      <c r="V130">
+        <v>1.93</v>
+      </c>
+      <c r="W130">
+        <v>1.82</v>
+      </c>
+      <c r="X130">
+        <v>3.75</v>
+      </c>
+      <c r="Y130">
+        <v>1.21</v>
+      </c>
+      <c r="Z130">
+        <v>5.9</v>
+      </c>
+      <c r="AA130">
+        <v>5.1</v>
+      </c>
+      <c r="AB130">
+        <v>1.36</v>
+      </c>
+      <c r="AC130">
+        <v>1.01</v>
+      </c>
+      <c r="AD130">
+        <v>23</v>
+      </c>
+      <c r="AE130">
+        <v>1.05</v>
+      </c>
+      <c r="AF130">
+        <v>6.6</v>
+      </c>
+      <c r="AG130">
+        <v>1.31</v>
+      </c>
+      <c r="AH130">
+        <v>3.15</v>
+      </c>
+      <c r="AI130">
+        <v>1.51</v>
+      </c>
+      <c r="AJ130">
+        <v>2.39</v>
+      </c>
+      <c r="AK130">
+        <v>3.1</v>
+      </c>
+      <c r="AL130">
+        <v>1.14</v>
+      </c>
+      <c r="AM130">
+        <v>1.08</v>
+      </c>
+      <c r="AN130">
+        <v>0.63</v>
+      </c>
+      <c r="AO130">
+        <v>2.43</v>
+      </c>
+      <c r="AP130">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AQ130">
+        <v>2.5</v>
+      </c>
+      <c r="AR130">
+        <v>1.3</v>
+      </c>
+      <c r="AS130">
+        <v>1.78</v>
+      </c>
+      <c r="AT130">
+        <v>3.08</v>
+      </c>
+      <c r="AU130">
+        <v>6</v>
+      </c>
+      <c r="AV130">
+        <v>10</v>
+      </c>
+      <c r="AW130">
+        <v>12</v>
+      </c>
+      <c r="AX130">
+        <v>4</v>
+      </c>
+      <c r="AY130">
+        <v>18</v>
+      </c>
+      <c r="AZ130">
+        <v>14</v>
+      </c>
+      <c r="BA130">
+        <v>4</v>
+      </c>
+      <c r="BB130">
+        <v>3</v>
+      </c>
+      <c r="BC130">
+        <v>7</v>
+      </c>
+      <c r="BD130">
+        <v>3.85</v>
+      </c>
+      <c r="BE130">
+        <v>10</v>
+      </c>
+      <c r="BF130">
+        <v>1.38</v>
+      </c>
+      <c r="BG130">
+        <v>1.18</v>
+      </c>
+      <c r="BH130">
+        <v>4.1</v>
+      </c>
+      <c r="BI130">
+        <v>1.33</v>
+      </c>
+      <c r="BJ130">
+        <v>3</v>
+      </c>
+      <c r="BK130">
+        <v>1.54</v>
+      </c>
+      <c r="BL130">
+        <v>2.28</v>
+      </c>
+      <c r="BM130">
+        <v>1.84</v>
+      </c>
+      <c r="BN130">
+        <v>1.85</v>
+      </c>
+      <c r="BO130">
+        <v>2.25</v>
+      </c>
+      <c r="BP130">
+        <v>1.55</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="842" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="268">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -581,6 +581,15 @@
   </si>
   <si>
     <t>['9']</t>
+  </si>
+  <si>
+    <t>['8']</t>
+  </si>
+  <si>
+    <t>['53', '65']</t>
+  </si>
+  <si>
+    <t>['66', '81', '87']</t>
   </si>
   <si>
     <t>['53', '79']</t>
@@ -1170,7 +1179,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP130"/>
+  <dimension ref="A1:BP133"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1838,7 +1847,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2044,7 +2053,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q5">
         <v>2.85</v>
@@ -2125,7 +2134,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ5">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2250,7 +2259,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q6">
         <v>2.2</v>
@@ -2328,7 +2337,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ6">
         <v>0.5</v>
@@ -2662,7 +2671,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q8">
         <v>2.04</v>
@@ -2740,7 +2749,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AQ8">
         <v>0.43</v>
@@ -2868,7 +2877,7 @@
         <v>92</v>
       </c>
       <c r="P9" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q9">
         <v>1.5</v>
@@ -3074,7 +3083,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q10">
         <v>2.1</v>
@@ -3486,7 +3495,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q12">
         <v>3.1</v>
@@ -3898,7 +3907,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q14">
         <v>2.13</v>
@@ -4104,7 +4113,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q15">
         <v>3.2</v>
@@ -4310,7 +4319,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q16">
         <v>1.78</v>
@@ -4722,7 +4731,7 @@
         <v>100</v>
       </c>
       <c r="P18" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q18">
         <v>5.5</v>
@@ -4928,7 +4937,7 @@
         <v>88</v>
       </c>
       <c r="P19" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q19">
         <v>3.75</v>
@@ -5006,7 +5015,7 @@
         <v>1</v>
       </c>
       <c r="AP19">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ19">
         <v>0.78</v>
@@ -5134,7 +5143,7 @@
         <v>101</v>
       </c>
       <c r="P20" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q20">
         <v>3.25</v>
@@ -5215,7 +5224,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ20">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -5624,7 +5633,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AQ22">
         <v>0.13</v>
@@ -5752,7 +5761,7 @@
         <v>104</v>
       </c>
       <c r="P23" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q23">
         <v>4</v>
@@ -5958,7 +5967,7 @@
         <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q24">
         <v>4.75</v>
@@ -6164,7 +6173,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -6245,7 +6254,7 @@
         <v>2.75</v>
       </c>
       <c r="AQ25">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AR25">
         <v>0</v>
@@ -6370,7 +6379,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q26">
         <v>2.88</v>
@@ -6451,7 +6460,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ26">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AR26">
         <v>1.09</v>
@@ -6654,7 +6663,7 @@
         <v>1.5</v>
       </c>
       <c r="AP27">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ27">
         <v>0.5</v>
@@ -6988,7 +6997,7 @@
         <v>110</v>
       </c>
       <c r="P29" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q29">
         <v>1.83</v>
@@ -7069,7 +7078,7 @@
         <v>2.75</v>
       </c>
       <c r="AQ29">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR29">
         <v>1.91</v>
@@ -7400,7 +7409,7 @@
         <v>88</v>
       </c>
       <c r="P31" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q31">
         <v>2.9</v>
@@ -7481,7 +7490,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ31">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AR31">
         <v>2.46</v>
@@ -7606,7 +7615,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q32">
         <v>3.42</v>
@@ -7684,7 +7693,7 @@
         <v>2</v>
       </c>
       <c r="AP32">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AQ32">
         <v>2</v>
@@ -7812,7 +7821,7 @@
         <v>113</v>
       </c>
       <c r="P33" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q33">
         <v>1.56</v>
@@ -8018,7 +8027,7 @@
         <v>114</v>
       </c>
       <c r="P34" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q34">
         <v>3.25</v>
@@ -8224,7 +8233,7 @@
         <v>115</v>
       </c>
       <c r="P35" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q35">
         <v>4.25</v>
@@ -8430,7 +8439,7 @@
         <v>116</v>
       </c>
       <c r="P36" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q36">
         <v>3.15</v>
@@ -8636,7 +8645,7 @@
         <v>117</v>
       </c>
       <c r="P37" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q37">
         <v>2.75</v>
@@ -9048,7 +9057,7 @@
         <v>119</v>
       </c>
       <c r="P39" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q39">
         <v>2.88</v>
@@ -9872,7 +9881,7 @@
         <v>123</v>
       </c>
       <c r="P43" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q43">
         <v>3</v>
@@ -10078,7 +10087,7 @@
         <v>124</v>
       </c>
       <c r="P44" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q44">
         <v>3.2</v>
@@ -10284,7 +10293,7 @@
         <v>88</v>
       </c>
       <c r="P45" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q45">
         <v>7.5</v>
@@ -10365,7 +10374,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ45">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AR45">
         <v>1.43</v>
@@ -10568,10 +10577,10 @@
         <v>1.5</v>
       </c>
       <c r="AP46">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ46">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR46">
         <v>1.82</v>
@@ -10696,7 +10705,7 @@
         <v>126</v>
       </c>
       <c r="P47" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q47">
         <v>1.95</v>
@@ -10902,7 +10911,7 @@
         <v>127</v>
       </c>
       <c r="P48" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q48">
         <v>3.7</v>
@@ -11108,7 +11117,7 @@
         <v>128</v>
       </c>
       <c r="P49" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q49">
         <v>4.33</v>
@@ -11186,7 +11195,7 @@
         <v>1.67</v>
       </c>
       <c r="AP49">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ49">
         <v>2</v>
@@ -11314,7 +11323,7 @@
         <v>129</v>
       </c>
       <c r="P50" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q50">
         <v>2.65</v>
@@ -11520,7 +11529,7 @@
         <v>130</v>
       </c>
       <c r="P51" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q51">
         <v>4.15</v>
@@ -11598,7 +11607,7 @@
         <v>1</v>
       </c>
       <c r="AP51">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AQ51">
         <v>2.5</v>
@@ -11932,7 +11941,7 @@
         <v>132</v>
       </c>
       <c r="P53" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q53">
         <v>1.8</v>
@@ -12010,7 +12019,7 @@
         <v>0.5</v>
       </c>
       <c r="AP53">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ53">
         <v>0.43</v>
@@ -12138,7 +12147,7 @@
         <v>104</v>
       </c>
       <c r="P54" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q54">
         <v>1.71</v>
@@ -12219,7 +12228,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ54">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR54">
         <v>2.36</v>
@@ -12344,7 +12353,7 @@
         <v>133</v>
       </c>
       <c r="P55" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q55">
         <v>1.45</v>
@@ -12756,7 +12765,7 @@
         <v>135</v>
       </c>
       <c r="P57" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -13043,7 +13052,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ58">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR58">
         <v>1.38</v>
@@ -13864,7 +13873,7 @@
         <v>1</v>
       </c>
       <c r="AP62">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AQ62">
         <v>0.78</v>
@@ -13992,7 +14001,7 @@
         <v>140</v>
       </c>
       <c r="P63" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q63">
         <v>2.88</v>
@@ -14073,7 +14082,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ63">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AR63">
         <v>2.06</v>
@@ -14404,7 +14413,7 @@
         <v>142</v>
       </c>
       <c r="P65" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q65">
         <v>4.5</v>
@@ -14610,7 +14619,7 @@
         <v>143</v>
       </c>
       <c r="P66" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q66">
         <v>5.2</v>
@@ -14691,7 +14700,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ66">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AR66">
         <v>1.35</v>
@@ -14816,7 +14825,7 @@
         <v>144</v>
       </c>
       <c r="P67" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q67">
         <v>3.22</v>
@@ -15022,7 +15031,7 @@
         <v>88</v>
       </c>
       <c r="P68" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q68">
         <v>3.24</v>
@@ -15228,7 +15237,7 @@
         <v>145</v>
       </c>
       <c r="P69" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q69">
         <v>3.18</v>
@@ -15306,7 +15315,7 @@
         <v>1.67</v>
       </c>
       <c r="AP69">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ69">
         <v>1.56</v>
@@ -15434,7 +15443,7 @@
         <v>124</v>
       </c>
       <c r="P70" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q70">
         <v>3.22</v>
@@ -15640,7 +15649,7 @@
         <v>146</v>
       </c>
       <c r="P71" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q71">
         <v>2.1</v>
@@ -15718,10 +15727,10 @@
         <v>2</v>
       </c>
       <c r="AP71">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ71">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AR71">
         <v>1.62</v>
@@ -15846,7 +15855,7 @@
         <v>147</v>
       </c>
       <c r="P72" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q72">
         <v>2.75</v>
@@ -15927,7 +15936,7 @@
         <v>2</v>
       </c>
       <c r="AQ72">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR72">
         <v>1.95</v>
@@ -16258,7 +16267,7 @@
         <v>148</v>
       </c>
       <c r="P74" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q74">
         <v>2.2</v>
@@ -16336,7 +16345,7 @@
         <v>0.6</v>
       </c>
       <c r="AP74">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ74">
         <v>0.38</v>
@@ -16464,7 +16473,7 @@
         <v>149</v>
       </c>
       <c r="P75" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -16670,7 +16679,7 @@
         <v>150</v>
       </c>
       <c r="P76" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q76">
         <v>1.57</v>
@@ -16876,7 +16885,7 @@
         <v>151</v>
       </c>
       <c r="P77" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q77">
         <v>2.63</v>
@@ -17494,7 +17503,7 @@
         <v>88</v>
       </c>
       <c r="P80" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q80">
         <v>3.6</v>
@@ -17700,7 +17709,7 @@
         <v>154</v>
       </c>
       <c r="P81" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q81">
         <v>2.6</v>
@@ -17906,7 +17915,7 @@
         <v>88</v>
       </c>
       <c r="P82" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q82">
         <v>4.5</v>
@@ -17984,7 +17993,7 @@
         <v>2.33</v>
       </c>
       <c r="AP82">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ82">
         <v>2.5</v>
@@ -18524,7 +18533,7 @@
         <v>157</v>
       </c>
       <c r="P85" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q85">
         <v>4</v>
@@ -18730,7 +18739,7 @@
         <v>114</v>
       </c>
       <c r="P86" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q86">
         <v>5.5</v>
@@ -19142,7 +19151,7 @@
         <v>158</v>
       </c>
       <c r="P88" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q88">
         <v>1.53</v>
@@ -19429,7 +19438,7 @@
         <v>2.75</v>
       </c>
       <c r="AQ89">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AR89">
         <v>2.4</v>
@@ -19554,7 +19563,7 @@
         <v>88</v>
       </c>
       <c r="P90" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q90">
         <v>6</v>
@@ -19635,7 +19644,7 @@
         <v>1</v>
       </c>
       <c r="AQ90">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AR90">
         <v>1.96</v>
@@ -19760,7 +19769,7 @@
         <v>160</v>
       </c>
       <c r="P91" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q91">
         <v>2.2</v>
@@ -19966,7 +19975,7 @@
         <v>161</v>
       </c>
       <c r="P92" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q92">
         <v>1.8</v>
@@ -20456,10 +20465,10 @@
         <v>0.83</v>
       </c>
       <c r="AP94">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AQ94">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR94">
         <v>2.25</v>
@@ -20584,7 +20593,7 @@
         <v>162</v>
       </c>
       <c r="P95" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q95">
         <v>2.88</v>
@@ -20662,7 +20671,7 @@
         <v>0.5</v>
       </c>
       <c r="AP95">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ95">
         <v>0.5</v>
@@ -20790,7 +20799,7 @@
         <v>163</v>
       </c>
       <c r="P96" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q96">
         <v>2.38</v>
@@ -20868,7 +20877,7 @@
         <v>1.17</v>
       </c>
       <c r="AP96">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ96">
         <v>1</v>
@@ -21202,7 +21211,7 @@
         <v>88</v>
       </c>
       <c r="P98" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q98">
         <v>5.25</v>
@@ -21408,7 +21417,7 @@
         <v>165</v>
       </c>
       <c r="P99" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q99">
         <v>3.52</v>
@@ -21614,7 +21623,7 @@
         <v>166</v>
       </c>
       <c r="P100" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q100">
         <v>1.79</v>
@@ -21695,7 +21704,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ100">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AR100">
         <v>2.09</v>
@@ -22026,7 +22035,7 @@
         <v>114</v>
       </c>
       <c r="P102" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q102">
         <v>2.3</v>
@@ -22516,7 +22525,7 @@
         <v>0.17</v>
       </c>
       <c r="AP104">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ104">
         <v>0.13</v>
@@ -22644,7 +22653,7 @@
         <v>168</v>
       </c>
       <c r="P105" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q105">
         <v>3.54</v>
@@ -22722,7 +22731,7 @@
         <v>2.5</v>
       </c>
       <c r="AP105">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ105">
         <v>2.5</v>
@@ -22931,7 +22940,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ106">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR106">
         <v>1.24</v>
@@ -23056,7 +23065,7 @@
         <v>169</v>
       </c>
       <c r="P107" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q107">
         <v>1.49</v>
@@ -23468,7 +23477,7 @@
         <v>171</v>
       </c>
       <c r="P109" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q109">
         <v>5.2</v>
@@ -23549,7 +23558,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ109">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AR109">
         <v>1.49</v>
@@ -23752,7 +23761,7 @@
         <v>1.67</v>
       </c>
       <c r="AP110">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AQ110">
         <v>1.38</v>
@@ -23961,7 +23970,7 @@
         <v>2.75</v>
       </c>
       <c r="AQ111">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AR111">
         <v>1.97</v>
@@ -24086,7 +24095,7 @@
         <v>174</v>
       </c>
       <c r="P112" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24292,7 +24301,7 @@
         <v>175</v>
       </c>
       <c r="P113" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q113">
         <v>3.04</v>
@@ -24704,7 +24713,7 @@
         <v>88</v>
       </c>
       <c r="P115" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q115">
         <v>3.5</v>
@@ -24991,7 +25000,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ116">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AR116">
         <v>1.24</v>
@@ -25116,7 +25125,7 @@
         <v>178</v>
       </c>
       <c r="P117" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q117">
         <v>1.95</v>
@@ -25322,7 +25331,7 @@
         <v>88</v>
       </c>
       <c r="P118" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q118">
         <v>5.5</v>
@@ -25940,7 +25949,7 @@
         <v>181</v>
       </c>
       <c r="P121" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q121">
         <v>3</v>
@@ -26146,7 +26155,7 @@
         <v>182</v>
       </c>
       <c r="P122" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q122">
         <v>7.1</v>
@@ -26558,7 +26567,7 @@
         <v>184</v>
       </c>
       <c r="P124" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q124">
         <v>2.63</v>
@@ -26764,7 +26773,7 @@
         <v>185</v>
       </c>
       <c r="P125" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q125">
         <v>5.55</v>
@@ -26842,10 +26851,10 @@
         <v>2.29</v>
       </c>
       <c r="AP125">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ125">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AR125">
         <v>1.97</v>
@@ -26970,7 +26979,7 @@
         <v>186</v>
       </c>
       <c r="P126" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q126">
         <v>3</v>
@@ -27382,7 +27391,7 @@
         <v>187</v>
       </c>
       <c r="P128" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q128">
         <v>1.8</v>
@@ -27463,7 +27472,7 @@
         <v>2.75</v>
       </c>
       <c r="AQ128">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR128">
         <v>1.85</v>
@@ -27588,7 +27597,7 @@
         <v>188</v>
       </c>
       <c r="P129" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q129">
         <v>3.75</v>
@@ -27794,7 +27803,7 @@
         <v>124</v>
       </c>
       <c r="P130" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q130">
         <v>6.05</v>
@@ -27951,6 +27960,624 @@
       </c>
       <c r="BP130">
         <v>1.55</v>
+      </c>
+    </row>
+    <row r="131" spans="1:68">
+      <c r="A131" s="1">
+        <v>130</v>
+      </c>
+      <c r="B131">
+        <v>7825320</v>
+      </c>
+      <c r="C131" t="s">
+        <v>68</v>
+      </c>
+      <c r="D131" t="s">
+        <v>69</v>
+      </c>
+      <c r="E131" s="2">
+        <v>45856.33333333334</v>
+      </c>
+      <c r="F131">
+        <v>17</v>
+      </c>
+      <c r="G131" t="s">
+        <v>80</v>
+      </c>
+      <c r="H131" t="s">
+        <v>79</v>
+      </c>
+      <c r="I131">
+        <v>1</v>
+      </c>
+      <c r="J131">
+        <v>0</v>
+      </c>
+      <c r="K131">
+        <v>1</v>
+      </c>
+      <c r="L131">
+        <v>1</v>
+      </c>
+      <c r="M131">
+        <v>1</v>
+      </c>
+      <c r="N131">
+        <v>2</v>
+      </c>
+      <c r="O131" t="s">
+        <v>189</v>
+      </c>
+      <c r="P131" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q131">
+        <v>2.63</v>
+      </c>
+      <c r="R131">
+        <v>2.2</v>
+      </c>
+      <c r="S131">
+        <v>3.7</v>
+      </c>
+      <c r="T131">
+        <v>1.3</v>
+      </c>
+      <c r="U131">
+        <v>3.22</v>
+      </c>
+      <c r="V131">
+        <v>2.47</v>
+      </c>
+      <c r="W131">
+        <v>1.48</v>
+      </c>
+      <c r="X131">
+        <v>6.1</v>
+      </c>
+      <c r="Y131">
+        <v>1.06</v>
+      </c>
+      <c r="Z131">
+        <v>2.01</v>
+      </c>
+      <c r="AA131">
+        <v>3.56</v>
+      </c>
+      <c r="AB131">
+        <v>3.11</v>
+      </c>
+      <c r="AC131">
+        <v>1.01</v>
+      </c>
+      <c r="AD131">
+        <v>11</v>
+      </c>
+      <c r="AE131">
+        <v>1.15</v>
+      </c>
+      <c r="AF131">
+        <v>4.25</v>
+      </c>
+      <c r="AG131">
+        <v>1.65</v>
+      </c>
+      <c r="AH131">
+        <v>2.05</v>
+      </c>
+      <c r="AI131">
+        <v>1.56</v>
+      </c>
+      <c r="AJ131">
+        <v>2.27</v>
+      </c>
+      <c r="AK131">
+        <v>1.33</v>
+      </c>
+      <c r="AL131">
+        <v>1.28</v>
+      </c>
+      <c r="AM131">
+        <v>1.71</v>
+      </c>
+      <c r="AN131">
+        <v>1.5</v>
+      </c>
+      <c r="AO131">
+        <v>0.71</v>
+      </c>
+      <c r="AP131">
+        <v>1.44</v>
+      </c>
+      <c r="AQ131">
+        <v>0.75</v>
+      </c>
+      <c r="AR131">
+        <v>1.81</v>
+      </c>
+      <c r="AS131">
+        <v>1.27</v>
+      </c>
+      <c r="AT131">
+        <v>3.08</v>
+      </c>
+      <c r="AU131">
+        <v>5</v>
+      </c>
+      <c r="AV131">
+        <v>4</v>
+      </c>
+      <c r="AW131">
+        <v>11</v>
+      </c>
+      <c r="AX131">
+        <v>6</v>
+      </c>
+      <c r="AY131">
+        <v>16</v>
+      </c>
+      <c r="AZ131">
+        <v>10</v>
+      </c>
+      <c r="BA131">
+        <v>11</v>
+      </c>
+      <c r="BB131">
+        <v>3</v>
+      </c>
+      <c r="BC131">
+        <v>14</v>
+      </c>
+      <c r="BD131">
+        <v>1.74</v>
+      </c>
+      <c r="BE131">
+        <v>8.5</v>
+      </c>
+      <c r="BF131">
+        <v>2.55</v>
+      </c>
+      <c r="BG131">
+        <v>1.3</v>
+      </c>
+      <c r="BH131">
+        <v>3.1</v>
+      </c>
+      <c r="BI131">
+        <v>1.52</v>
+      </c>
+      <c r="BJ131">
+        <v>2.32</v>
+      </c>
+      <c r="BK131">
+        <v>1.85</v>
+      </c>
+      <c r="BL131">
+        <v>1.83</v>
+      </c>
+      <c r="BM131">
+        <v>2.3</v>
+      </c>
+      <c r="BN131">
+        <v>1.53</v>
+      </c>
+      <c r="BO131">
+        <v>3</v>
+      </c>
+      <c r="BP131">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="132" spans="1:68">
+      <c r="A132" s="1">
+        <v>131</v>
+      </c>
+      <c r="B132">
+        <v>7825322</v>
+      </c>
+      <c r="C132" t="s">
+        <v>68</v>
+      </c>
+      <c r="D132" t="s">
+        <v>69</v>
+      </c>
+      <c r="E132" s="2">
+        <v>45856.35763888889</v>
+      </c>
+      <c r="F132">
+        <v>17</v>
+      </c>
+      <c r="G132" t="s">
+        <v>76</v>
+      </c>
+      <c r="H132" t="s">
+        <v>70</v>
+      </c>
+      <c r="I132">
+        <v>0</v>
+      </c>
+      <c r="J132">
+        <v>0</v>
+      </c>
+      <c r="K132">
+        <v>0</v>
+      </c>
+      <c r="L132">
+        <v>2</v>
+      </c>
+      <c r="M132">
+        <v>1</v>
+      </c>
+      <c r="N132">
+        <v>3</v>
+      </c>
+      <c r="O132" t="s">
+        <v>190</v>
+      </c>
+      <c r="P132" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q132">
+        <v>5.3</v>
+      </c>
+      <c r="R132">
+        <v>2.4</v>
+      </c>
+      <c r="S132">
+        <v>2</v>
+      </c>
+      <c r="T132">
+        <v>1.25</v>
+      </c>
+      <c r="U132">
+        <v>3.42</v>
+      </c>
+      <c r="V132">
+        <v>2.31</v>
+      </c>
+      <c r="W132">
+        <v>1.57</v>
+      </c>
+      <c r="X132">
+        <v>5.3</v>
+      </c>
+      <c r="Y132">
+        <v>1.11</v>
+      </c>
+      <c r="Z132">
+        <v>5.55</v>
+      </c>
+      <c r="AA132">
+        <v>4.4</v>
+      </c>
+      <c r="AB132">
+        <v>1.52</v>
+      </c>
+      <c r="AC132">
+        <v>1.01</v>
+      </c>
+      <c r="AD132">
+        <v>13</v>
+      </c>
+      <c r="AE132">
+        <v>1.12</v>
+      </c>
+      <c r="AF132">
+        <v>4.65</v>
+      </c>
+      <c r="AG132">
+        <v>1.57</v>
+      </c>
+      <c r="AH132">
+        <v>2.35</v>
+      </c>
+      <c r="AI132">
+        <v>1.64</v>
+      </c>
+      <c r="AJ132">
+        <v>2.12</v>
+      </c>
+      <c r="AK132">
+        <v>2.47</v>
+      </c>
+      <c r="AL132">
+        <v>1.2</v>
+      </c>
+      <c r="AM132">
+        <v>1.13</v>
+      </c>
+      <c r="AN132">
+        <v>1.57</v>
+      </c>
+      <c r="AO132">
+        <v>2.13</v>
+      </c>
+      <c r="AP132">
+        <v>1.75</v>
+      </c>
+      <c r="AQ132">
+        <v>1.89</v>
+      </c>
+      <c r="AR132">
+        <v>2.21</v>
+      </c>
+      <c r="AS132">
+        <v>2.02</v>
+      </c>
+      <c r="AT132">
+        <v>4.23</v>
+      </c>
+      <c r="AU132">
+        <v>4</v>
+      </c>
+      <c r="AV132">
+        <v>9</v>
+      </c>
+      <c r="AW132">
+        <v>3</v>
+      </c>
+      <c r="AX132">
+        <v>9</v>
+      </c>
+      <c r="AY132">
+        <v>7</v>
+      </c>
+      <c r="AZ132">
+        <v>18</v>
+      </c>
+      <c r="BA132">
+        <v>3</v>
+      </c>
+      <c r="BB132">
+        <v>3</v>
+      </c>
+      <c r="BC132">
+        <v>6</v>
+      </c>
+      <c r="BD132">
+        <v>3.05</v>
+      </c>
+      <c r="BE132">
+        <v>9</v>
+      </c>
+      <c r="BF132">
+        <v>1.55</v>
+      </c>
+      <c r="BG132">
+        <v>1.26</v>
+      </c>
+      <c r="BH132">
+        <v>3.4</v>
+      </c>
+      <c r="BI132">
+        <v>1.44</v>
+      </c>
+      <c r="BJ132">
+        <v>2.55</v>
+      </c>
+      <c r="BK132">
+        <v>1.72</v>
+      </c>
+      <c r="BL132">
+        <v>1.97</v>
+      </c>
+      <c r="BM132">
+        <v>2</v>
+      </c>
+      <c r="BN132">
+        <v>1.8</v>
+      </c>
+      <c r="BO132">
+        <v>2.65</v>
+      </c>
+      <c r="BP132">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="133" spans="1:68">
+      <c r="A133" s="1">
+        <v>132</v>
+      </c>
+      <c r="B133">
+        <v>7825323</v>
+      </c>
+      <c r="C133" t="s">
+        <v>68</v>
+      </c>
+      <c r="D133" t="s">
+        <v>69</v>
+      </c>
+      <c r="E133" s="2">
+        <v>45856.375</v>
+      </c>
+      <c r="F133">
+        <v>17</v>
+      </c>
+      <c r="G133" t="s">
+        <v>74</v>
+      </c>
+      <c r="H133" t="s">
+        <v>72</v>
+      </c>
+      <c r="I133">
+        <v>0</v>
+      </c>
+      <c r="J133">
+        <v>1</v>
+      </c>
+      <c r="K133">
+        <v>1</v>
+      </c>
+      <c r="L133">
+        <v>3</v>
+      </c>
+      <c r="M133">
+        <v>1</v>
+      </c>
+      <c r="N133">
+        <v>4</v>
+      </c>
+      <c r="O133" t="s">
+        <v>191</v>
+      </c>
+      <c r="P133" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q133">
+        <v>2.34</v>
+      </c>
+      <c r="R133">
+        <v>2.36</v>
+      </c>
+      <c r="S133">
+        <v>3.92</v>
+      </c>
+      <c r="T133">
+        <v>1.21</v>
+      </c>
+      <c r="U133">
+        <v>3.75</v>
+      </c>
+      <c r="V133">
+        <v>2.14</v>
+      </c>
+      <c r="W133">
+        <v>1.66</v>
+      </c>
+      <c r="X133">
+        <v>4.8</v>
+      </c>
+      <c r="Y133">
+        <v>1.13</v>
+      </c>
+      <c r="Z133">
+        <v>1.85</v>
+      </c>
+      <c r="AA133">
+        <v>3.83</v>
+      </c>
+      <c r="AB133">
+        <v>3.36</v>
+      </c>
+      <c r="AC133">
+        <v>1.01</v>
+      </c>
+      <c r="AD133">
+        <v>17</v>
+      </c>
+      <c r="AE133">
+        <v>1.08</v>
+      </c>
+      <c r="AF133">
+        <v>5.7</v>
+      </c>
+      <c r="AG133">
+        <v>1.42</v>
+      </c>
+      <c r="AH133">
+        <v>2.65</v>
+      </c>
+      <c r="AI133">
+        <v>1.42</v>
+      </c>
+      <c r="AJ133">
+        <v>2.65</v>
+      </c>
+      <c r="AK133">
+        <v>1.26</v>
+      </c>
+      <c r="AL133">
+        <v>1.24</v>
+      </c>
+      <c r="AM133">
+        <v>1.92</v>
+      </c>
+      <c r="AN133">
+        <v>1.86</v>
+      </c>
+      <c r="AO133">
+        <v>1</v>
+      </c>
+      <c r="AP133">
+        <v>2</v>
+      </c>
+      <c r="AQ133">
+        <v>0.9</v>
+      </c>
+      <c r="AR133">
+        <v>1.58</v>
+      </c>
+      <c r="AS133">
+        <v>1.33</v>
+      </c>
+      <c r="AT133">
+        <v>2.91</v>
+      </c>
+      <c r="AU133">
+        <v>13</v>
+      </c>
+      <c r="AV133">
+        <v>5</v>
+      </c>
+      <c r="AW133">
+        <v>13</v>
+      </c>
+      <c r="AX133">
+        <v>8</v>
+      </c>
+      <c r="AY133">
+        <v>26</v>
+      </c>
+      <c r="AZ133">
+        <v>13</v>
+      </c>
+      <c r="BA133">
+        <v>7</v>
+      </c>
+      <c r="BB133">
+        <v>8</v>
+      </c>
+      <c r="BC133">
+        <v>15</v>
+      </c>
+      <c r="BD133">
+        <v>1.57</v>
+      </c>
+      <c r="BE133">
+        <v>8.5</v>
+      </c>
+      <c r="BF133">
+        <v>3</v>
+      </c>
+      <c r="BG133">
+        <v>1.25</v>
+      </c>
+      <c r="BH133">
+        <v>3.5</v>
+      </c>
+      <c r="BI133">
+        <v>1.43</v>
+      </c>
+      <c r="BJ133">
+        <v>2.6</v>
+      </c>
+      <c r="BK133">
+        <v>1.7</v>
+      </c>
+      <c r="BL133">
+        <v>2</v>
+      </c>
+      <c r="BM133">
+        <v>2.07</v>
+      </c>
+      <c r="BN133">
+        <v>1.66</v>
+      </c>
+      <c r="BO133">
+        <v>2.6</v>
+      </c>
+      <c r="BP133">
+        <v>1.42</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/China Chinese Super League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="273">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -592,6 +592,18 @@
     <t>['66', '81', '87']</t>
   </si>
   <si>
+    <t>['36', '82']</t>
+  </si>
+  <si>
+    <t>['26']</t>
+  </si>
+  <si>
+    <t>['3', '44', '51', '87']</t>
+  </si>
+  <si>
+    <t>['63']</t>
+  </si>
+  <si>
     <t>['53', '79']</t>
   </si>
   <si>
@@ -818,6 +830,9 @@
   </si>
   <si>
     <t>['45+1', '71', '90+12']</t>
+  </si>
+  <si>
+    <t>['7', '21', '90+7']</t>
   </si>
 </sst>
 </file>
@@ -1179,7 +1194,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP133"/>
+  <dimension ref="A1:BP137"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1847,7 +1862,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2053,7 +2068,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="Q5">
         <v>2.85</v>
@@ -2259,7 +2274,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="Q6">
         <v>2.2</v>
@@ -2671,7 +2686,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="Q8">
         <v>2.04</v>
@@ -2752,7 +2767,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ8">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2877,7 +2892,7 @@
         <v>92</v>
       </c>
       <c r="P9" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="Q9">
         <v>1.5</v>
@@ -3083,7 +3098,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="Q10">
         <v>2.1</v>
@@ -3495,7 +3510,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="Q12">
         <v>3.1</v>
@@ -3907,7 +3922,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="Q14">
         <v>2.13</v>
@@ -4113,7 +4128,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="Q15">
         <v>3.2</v>
@@ -4319,7 +4334,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="Q16">
         <v>1.78</v>
@@ -4731,7 +4746,7 @@
         <v>100</v>
       </c>
       <c r="P18" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="Q18">
         <v>5.5</v>
@@ -4937,7 +4952,7 @@
         <v>88</v>
       </c>
       <c r="P19" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="Q19">
         <v>3.75</v>
@@ -5143,7 +5158,7 @@
         <v>101</v>
       </c>
       <c r="P20" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="Q20">
         <v>3.25</v>
@@ -5221,7 +5236,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ20">
         <v>0.9</v>
@@ -5427,7 +5442,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ21">
         <v>0.38</v>
@@ -5636,7 +5651,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ22">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="AR22">
         <v>3.42</v>
@@ -5761,7 +5776,7 @@
         <v>104</v>
       </c>
       <c r="P23" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="Q23">
         <v>4</v>
@@ -5839,10 +5854,10 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AQ23">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AR23">
         <v>0</v>
@@ -5967,7 +5982,7 @@
         <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="Q24">
         <v>4.75</v>
@@ -6048,7 +6063,7 @@
         <v>1</v>
       </c>
       <c r="AQ24">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR24">
         <v>1.93</v>
@@ -6173,7 +6188,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -6251,7 +6266,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="AQ25">
         <v>1.89</v>
@@ -6379,7 +6394,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="Q26">
         <v>2.88</v>
@@ -6457,7 +6472,7 @@
         <v>1</v>
       </c>
       <c r="AP26">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AQ26">
         <v>0.75</v>
@@ -6997,7 +7012,7 @@
         <v>110</v>
       </c>
       <c r="P29" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="Q29">
         <v>1.83</v>
@@ -7409,7 +7424,7 @@
         <v>88</v>
       </c>
       <c r="P31" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="Q31">
         <v>2.9</v>
@@ -7615,7 +7630,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="Q32">
         <v>3.42</v>
@@ -7821,7 +7836,7 @@
         <v>113</v>
       </c>
       <c r="P33" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="Q33">
         <v>1.56</v>
@@ -7902,7 +7917,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ33">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AR33">
         <v>2.3</v>
@@ -8027,7 +8042,7 @@
         <v>114</v>
       </c>
       <c r="P34" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="Q34">
         <v>3.25</v>
@@ -8105,7 +8120,7 @@
         <v>0.5</v>
       </c>
       <c r="AP34">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ34">
         <v>1</v>
@@ -8233,7 +8248,7 @@
         <v>115</v>
       </c>
       <c r="P35" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="Q35">
         <v>4.25</v>
@@ -8314,7 +8329,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ35">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR35">
         <v>1.08</v>
@@ -8439,7 +8454,7 @@
         <v>116</v>
       </c>
       <c r="P36" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="Q36">
         <v>3.15</v>
@@ -8645,7 +8660,7 @@
         <v>117</v>
       </c>
       <c r="P37" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="Q37">
         <v>2.75</v>
@@ -9057,7 +9072,7 @@
         <v>119</v>
       </c>
       <c r="P39" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="Q39">
         <v>2.88</v>
@@ -9138,7 +9153,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ39">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AR39">
         <v>2.38</v>
@@ -9341,7 +9356,7 @@
         <v>2</v>
       </c>
       <c r="AP40">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="AQ40">
         <v>0.78</v>
@@ -9550,7 +9565,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ41">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="AR41">
         <v>1.18</v>
@@ -9881,7 +9896,7 @@
         <v>123</v>
       </c>
       <c r="P43" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="Q43">
         <v>3</v>
@@ -10087,7 +10102,7 @@
         <v>124</v>
       </c>
       <c r="P44" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="Q44">
         <v>3.2</v>
@@ -10165,7 +10180,7 @@
         <v>2</v>
       </c>
       <c r="AP44">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ44">
         <v>1.56</v>
@@ -10293,7 +10308,7 @@
         <v>88</v>
       </c>
       <c r="P45" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="Q45">
         <v>7.5</v>
@@ -10705,7 +10720,7 @@
         <v>126</v>
       </c>
       <c r="P47" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="Q47">
         <v>1.95</v>
@@ -10911,7 +10926,7 @@
         <v>127</v>
       </c>
       <c r="P48" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="Q48">
         <v>3.7</v>
@@ -10992,7 +11007,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ48">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR48">
         <v>1.15</v>
@@ -11117,7 +11132,7 @@
         <v>128</v>
       </c>
       <c r="P49" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="Q49">
         <v>4.33</v>
@@ -11323,7 +11338,7 @@
         <v>129</v>
       </c>
       <c r="P50" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="Q50">
         <v>2.65</v>
@@ -11401,7 +11416,7 @@
         <v>0.75</v>
       </c>
       <c r="AP50">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ50">
         <v>0.38</v>
@@ -11529,7 +11544,7 @@
         <v>130</v>
       </c>
       <c r="P51" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="Q51">
         <v>4.15</v>
@@ -11813,7 +11828,7 @@
         <v>1.33</v>
       </c>
       <c r="AP52">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ52">
         <v>1</v>
@@ -11941,7 +11956,7 @@
         <v>132</v>
       </c>
       <c r="P53" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Q53">
         <v>1.8</v>
@@ -12022,7 +12037,7 @@
         <v>2</v>
       </c>
       <c r="AQ53">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AR53">
         <v>1.5</v>
@@ -12147,7 +12162,7 @@
         <v>104</v>
       </c>
       <c r="P54" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="Q54">
         <v>1.71</v>
@@ -12353,7 +12368,7 @@
         <v>133</v>
       </c>
       <c r="P55" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="Q55">
         <v>1.45</v>
@@ -12434,7 +12449,7 @@
         <v>2.75</v>
       </c>
       <c r="AQ55">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="AR55">
         <v>2.44</v>
@@ -12765,7 +12780,7 @@
         <v>135</v>
       </c>
       <c r="P57" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -12843,10 +12858,10 @@
         <v>3</v>
       </c>
       <c r="AP57">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="AQ57">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR57">
         <v>1.81</v>
@@ -13461,10 +13476,10 @@
         <v>0</v>
       </c>
       <c r="AP60">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AQ60">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="AR60">
         <v>1.14</v>
@@ -14001,7 +14016,7 @@
         <v>140</v>
       </c>
       <c r="P63" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="Q63">
         <v>2.88</v>
@@ -14285,7 +14300,7 @@
         <v>1</v>
       </c>
       <c r="AP64">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="AQ64">
         <v>1</v>
@@ -14413,7 +14428,7 @@
         <v>142</v>
       </c>
       <c r="P65" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="Q65">
         <v>4.5</v>
@@ -14619,7 +14634,7 @@
         <v>143</v>
       </c>
       <c r="P66" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="Q66">
         <v>5.2</v>
@@ -14825,7 +14840,7 @@
         <v>144</v>
       </c>
       <c r="P67" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Q67">
         <v>3.22</v>
@@ -14903,7 +14918,7 @@
         <v>0.4</v>
       </c>
       <c r="AP67">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ67">
         <v>0.5</v>
@@ -15031,7 +15046,7 @@
         <v>88</v>
       </c>
       <c r="P68" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="Q68">
         <v>3.24</v>
@@ -15112,7 +15127,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ68">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AR68">
         <v>2.12</v>
@@ -15237,7 +15252,7 @@
         <v>145</v>
       </c>
       <c r="P69" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="Q69">
         <v>3.18</v>
@@ -15443,7 +15458,7 @@
         <v>124</v>
       </c>
       <c r="P70" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="Q70">
         <v>3.22</v>
@@ -15524,7 +15539,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ70">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AR70">
         <v>1.3</v>
@@ -15649,7 +15664,7 @@
         <v>146</v>
       </c>
       <c r="P71" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="Q71">
         <v>2.1</v>
@@ -15855,7 +15870,7 @@
         <v>147</v>
       </c>
       <c r="P72" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="Q72">
         <v>2.75</v>
@@ -15933,7 +15948,7 @@
         <v>1</v>
       </c>
       <c r="AP72">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ72">
         <v>0.9</v>
@@ -16139,7 +16154,7 @@
         <v>1.25</v>
       </c>
       <c r="AP73">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ73">
         <v>1.56</v>
@@ -16267,7 +16282,7 @@
         <v>148</v>
       </c>
       <c r="P74" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q74">
         <v>2.2</v>
@@ -16473,7 +16488,7 @@
         <v>149</v>
       </c>
       <c r="P75" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -16551,7 +16566,7 @@
         <v>0.2</v>
       </c>
       <c r="AP75">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AQ75">
         <v>0.88</v>
@@ -16679,7 +16694,7 @@
         <v>150</v>
       </c>
       <c r="P76" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="Q76">
         <v>1.57</v>
@@ -16760,7 +16775,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ76">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="AR76">
         <v>1.89</v>
@@ -16885,7 +16900,7 @@
         <v>151</v>
       </c>
       <c r="P77" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="Q77">
         <v>2.63</v>
@@ -17172,7 +17187,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ78">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AR78">
         <v>1.12</v>
@@ -17378,7 +17393,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ79">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AR79">
         <v>2.28</v>
@@ -17503,7 +17518,7 @@
         <v>88</v>
       </c>
       <c r="P80" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="Q80">
         <v>3.6</v>
@@ -17581,7 +17596,7 @@
         <v>1.8</v>
       </c>
       <c r="AP80">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ80">
         <v>2</v>
@@ -17709,7 +17724,7 @@
         <v>154</v>
       </c>
       <c r="P81" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="Q81">
         <v>2.6</v>
@@ -17787,7 +17802,7 @@
         <v>1</v>
       </c>
       <c r="AP81">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AQ81">
         <v>1.56</v>
@@ -17915,7 +17930,7 @@
         <v>88</v>
       </c>
       <c r="P82" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="Q82">
         <v>4.5</v>
@@ -18533,7 +18548,7 @@
         <v>157</v>
       </c>
       <c r="P85" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="Q85">
         <v>4</v>
@@ -18614,7 +18629,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ85">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR85">
         <v>1.6</v>
@@ -18739,7 +18754,7 @@
         <v>114</v>
       </c>
       <c r="P86" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="Q86">
         <v>5.5</v>
@@ -18820,7 +18835,7 @@
         <v>1</v>
       </c>
       <c r="AQ86">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AR86">
         <v>2.02</v>
@@ -19151,7 +19166,7 @@
         <v>158</v>
       </c>
       <c r="P88" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="Q88">
         <v>1.53</v>
@@ -19232,7 +19247,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ88">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="AR88">
         <v>2.08</v>
@@ -19563,7 +19578,7 @@
         <v>88</v>
       </c>
       <c r="P90" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="Q90">
         <v>6</v>
@@ -19769,7 +19784,7 @@
         <v>160</v>
       </c>
       <c r="P91" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="Q91">
         <v>2.2</v>
@@ -19975,7 +19990,7 @@
         <v>161</v>
       </c>
       <c r="P92" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="Q92">
         <v>1.8</v>
@@ -20053,7 +20068,7 @@
         <v>0.67</v>
       </c>
       <c r="AP92">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="AQ92">
         <v>0.5</v>
@@ -20593,7 +20608,7 @@
         <v>162</v>
       </c>
       <c r="P95" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="Q95">
         <v>2.88</v>
@@ -20799,7 +20814,7 @@
         <v>163</v>
       </c>
       <c r="P96" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="Q96">
         <v>2.38</v>
@@ -21086,7 +21101,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ97">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AR97">
         <v>1.63</v>
@@ -21211,7 +21226,7 @@
         <v>88</v>
       </c>
       <c r="P98" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="Q98">
         <v>5.25</v>
@@ -21289,10 +21304,10 @@
         <v>2</v>
       </c>
       <c r="AP98">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ98">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AR98">
         <v>1.87</v>
@@ -21417,7 +21432,7 @@
         <v>165</v>
       </c>
       <c r="P99" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="Q99">
         <v>3.52</v>
@@ -21623,7 +21638,7 @@
         <v>166</v>
       </c>
       <c r="P100" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="Q100">
         <v>1.79</v>
@@ -22035,7 +22050,7 @@
         <v>114</v>
       </c>
       <c r="P102" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Q102">
         <v>2.3</v>
@@ -22116,7 +22131,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ102">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR102">
         <v>2.21</v>
@@ -22319,10 +22334,10 @@
         <v>0.5</v>
       </c>
       <c r="AP103">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ103">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AR103">
         <v>1.84</v>
@@ -22528,7 +22543,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ104">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="AR104">
         <v>2.06</v>
@@ -22653,7 +22668,7 @@
         <v>168</v>
       </c>
       <c r="P105" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="Q105">
         <v>3.54</v>
@@ -23065,7 +23080,7 @@
         <v>169</v>
       </c>
       <c r="P107" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="Q107">
         <v>1.49</v>
@@ -23143,7 +23158,7 @@
         <v>0.43</v>
       </c>
       <c r="AP107">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="AQ107">
         <v>0.38</v>
@@ -23349,10 +23364,10 @@
         <v>2.17</v>
       </c>
       <c r="AP108">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ108">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AR108">
         <v>1.54</v>
@@ -23477,7 +23492,7 @@
         <v>171</v>
       </c>
       <c r="P109" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="Q109">
         <v>5.2</v>
@@ -23555,7 +23570,7 @@
         <v>2.67</v>
       </c>
       <c r="AP109">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AQ109">
         <v>1.89</v>
@@ -23764,7 +23779,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ110">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR110">
         <v>2.32</v>
@@ -23967,7 +23982,7 @@
         <v>1</v>
       </c>
       <c r="AP111">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="AQ111">
         <v>0.75</v>
@@ -24095,7 +24110,7 @@
         <v>174</v>
       </c>
       <c r="P112" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24173,7 +24188,7 @@
         <v>2.2</v>
       </c>
       <c r="AP112">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AQ112">
         <v>2.5</v>
@@ -24301,7 +24316,7 @@
         <v>175</v>
       </c>
       <c r="P113" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Q113">
         <v>3.04</v>
@@ -24379,7 +24394,7 @@
         <v>0.67</v>
       </c>
       <c r="AP113">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ113">
         <v>0.88</v>
@@ -24713,7 +24728,7 @@
         <v>88</v>
       </c>
       <c r="P115" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="Q115">
         <v>3.5</v>
@@ -25125,7 +25140,7 @@
         <v>178</v>
       </c>
       <c r="P117" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="Q117">
         <v>1.95</v>
@@ -25331,7 +25346,7 @@
         <v>88</v>
       </c>
       <c r="P118" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="Q118">
         <v>5.5</v>
@@ -25949,7 +25964,7 @@
         <v>181</v>
       </c>
       <c r="P121" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="Q121">
         <v>3</v>
@@ -26155,7 +26170,7 @@
         <v>182</v>
       </c>
       <c r="P122" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="Q122">
         <v>7.1</v>
@@ -26236,7 +26251,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ122">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AR122">
         <v>1.29</v>
@@ -26442,7 +26457,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ123">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="AR123">
         <v>1.27</v>
@@ -26567,7 +26582,7 @@
         <v>184</v>
       </c>
       <c r="P124" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="Q124">
         <v>2.63</v>
@@ -26773,7 +26788,7 @@
         <v>185</v>
       </c>
       <c r="P125" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="Q125">
         <v>5.55</v>
@@ -26979,7 +26994,7 @@
         <v>186</v>
       </c>
       <c r="P126" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Q126">
         <v>3</v>
@@ -27057,10 +27072,10 @@
         <v>1.43</v>
       </c>
       <c r="AP126">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AQ126">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR126">
         <v>1.69</v>
@@ -27263,7 +27278,7 @@
         <v>0.88</v>
       </c>
       <c r="AP127">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ127">
         <v>0.78</v>
@@ -27391,7 +27406,7 @@
         <v>187</v>
       </c>
       <c r="P128" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="Q128">
         <v>1.8</v>
@@ -27469,7 +27484,7 @@
         <v>1.13</v>
       </c>
       <c r="AP128">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="AQ128">
         <v>0.9</v>
@@ -27597,7 +27612,7 @@
         <v>188</v>
       </c>
       <c r="P129" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="Q129">
         <v>3.75</v>
@@ -27675,7 +27690,7 @@
         <v>2.33</v>
       </c>
       <c r="AP129">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ129">
         <v>2.5</v>
@@ -27803,7 +27818,7 @@
         <v>124</v>
       </c>
       <c r="P130" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="Q130">
         <v>6.05</v>
@@ -27914,13 +27929,13 @@
         <v>14</v>
       </c>
       <c r="BA130">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB130">
         <v>3</v>
       </c>
       <c r="BC130">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD130">
         <v>3.85</v>
@@ -28421,7 +28436,7 @@
         <v>191</v>
       </c>
       <c r="P133" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="Q133">
         <v>2.34</v>
@@ -28578,6 +28593,830 @@
       </c>
       <c r="BP133">
         <v>1.42</v>
+      </c>
+    </row>
+    <row r="134" spans="1:68">
+      <c r="A134" s="1">
+        <v>133</v>
+      </c>
+      <c r="B134">
+        <v>7825324</v>
+      </c>
+      <c r="C134" t="s">
+        <v>68</v>
+      </c>
+      <c r="D134" t="s">
+        <v>69</v>
+      </c>
+      <c r="E134" s="2">
+        <v>45857.33333333334</v>
+      </c>
+      <c r="F134">
+        <v>17</v>
+      </c>
+      <c r="G134" t="s">
+        <v>82</v>
+      </c>
+      <c r="H134" t="s">
+        <v>75</v>
+      </c>
+      <c r="I134">
+        <v>1</v>
+      </c>
+      <c r="J134">
+        <v>0</v>
+      </c>
+      <c r="K134">
+        <v>1</v>
+      </c>
+      <c r="L134">
+        <v>2</v>
+      </c>
+      <c r="M134">
+        <v>0</v>
+      </c>
+      <c r="N134">
+        <v>2</v>
+      </c>
+      <c r="O134" t="s">
+        <v>192</v>
+      </c>
+      <c r="P134" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q134">
+        <v>4</v>
+      </c>
+      <c r="R134">
+        <v>2.4</v>
+      </c>
+      <c r="S134">
+        <v>2.4</v>
+      </c>
+      <c r="T134">
+        <v>1.25</v>
+      </c>
+      <c r="U134">
+        <v>3.75</v>
+      </c>
+      <c r="V134">
+        <v>2.25</v>
+      </c>
+      <c r="W134">
+        <v>1.57</v>
+      </c>
+      <c r="X134">
+        <v>5.5</v>
+      </c>
+      <c r="Y134">
+        <v>1.14</v>
+      </c>
+      <c r="Z134">
+        <v>2.98</v>
+      </c>
+      <c r="AA134">
+        <v>3.74</v>
+      </c>
+      <c r="AB134">
+        <v>2.01</v>
+      </c>
+      <c r="AC134">
+        <v>1.01</v>
+      </c>
+      <c r="AD134">
+        <v>13</v>
+      </c>
+      <c r="AE134">
+        <v>1.1</v>
+      </c>
+      <c r="AF134">
+        <v>5</v>
+      </c>
+      <c r="AG134">
+        <v>1.53</v>
+      </c>
+      <c r="AH134">
+        <v>2.25</v>
+      </c>
+      <c r="AI134">
+        <v>1.53</v>
+      </c>
+      <c r="AJ134">
+        <v>2.38</v>
+      </c>
+      <c r="AK134">
+        <v>1.89</v>
+      </c>
+      <c r="AL134">
+        <v>1.25</v>
+      </c>
+      <c r="AM134">
+        <v>1.26</v>
+      </c>
+      <c r="AN134">
+        <v>2</v>
+      </c>
+      <c r="AO134">
+        <v>1.38</v>
+      </c>
+      <c r="AP134">
+        <v>2.11</v>
+      </c>
+      <c r="AQ134">
+        <v>1.22</v>
+      </c>
+      <c r="AR134">
+        <v>1.72</v>
+      </c>
+      <c r="AS134">
+        <v>1.79</v>
+      </c>
+      <c r="AT134">
+        <v>3.51</v>
+      </c>
+      <c r="AU134">
+        <v>10</v>
+      </c>
+      <c r="AV134">
+        <v>5</v>
+      </c>
+      <c r="AW134">
+        <v>5</v>
+      </c>
+      <c r="AX134">
+        <v>9</v>
+      </c>
+      <c r="AY134">
+        <v>15</v>
+      </c>
+      <c r="AZ134">
+        <v>14</v>
+      </c>
+      <c r="BA134">
+        <v>7</v>
+      </c>
+      <c r="BB134">
+        <v>8</v>
+      </c>
+      <c r="BC134">
+        <v>15</v>
+      </c>
+      <c r="BD134">
+        <v>2.02</v>
+      </c>
+      <c r="BE134">
+        <v>8.5</v>
+      </c>
+      <c r="BF134">
+        <v>2.12</v>
+      </c>
+      <c r="BG134">
+        <v>1.21</v>
+      </c>
+      <c r="BH134">
+        <v>3.8</v>
+      </c>
+      <c r="BI134">
+        <v>1.37</v>
+      </c>
+      <c r="BJ134">
+        <v>2.8</v>
+      </c>
+      <c r="BK134">
+        <v>1.6</v>
+      </c>
+      <c r="BL134">
+        <v>2.16</v>
+      </c>
+      <c r="BM134">
+        <v>1.94</v>
+      </c>
+      <c r="BN134">
+        <v>1.75</v>
+      </c>
+      <c r="BO134">
+        <v>2.4</v>
+      </c>
+      <c r="BP134">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="135" spans="1:68">
+      <c r="A135" s="1">
+        <v>134</v>
+      </c>
+      <c r="B135">
+        <v>7825326</v>
+      </c>
+      <c r="C135" t="s">
+        <v>68</v>
+      </c>
+      <c r="D135" t="s">
+        <v>69</v>
+      </c>
+      <c r="E135" s="2">
+        <v>45857.35763888889</v>
+      </c>
+      <c r="F135">
+        <v>17</v>
+      </c>
+      <c r="G135" t="s">
+        <v>84</v>
+      </c>
+      <c r="H135" t="s">
+        <v>71</v>
+      </c>
+      <c r="I135">
+        <v>1</v>
+      </c>
+      <c r="J135">
+        <v>2</v>
+      </c>
+      <c r="K135">
+        <v>3</v>
+      </c>
+      <c r="L135">
+        <v>1</v>
+      </c>
+      <c r="M135">
+        <v>3</v>
+      </c>
+      <c r="N135">
+        <v>4</v>
+      </c>
+      <c r="O135" t="s">
+        <v>193</v>
+      </c>
+      <c r="P135" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q135">
+        <v>3.1</v>
+      </c>
+      <c r="R135">
+        <v>2.3</v>
+      </c>
+      <c r="S135">
+        <v>3.1</v>
+      </c>
+      <c r="T135">
+        <v>1.3</v>
+      </c>
+      <c r="U135">
+        <v>3.4</v>
+      </c>
+      <c r="V135">
+        <v>2.5</v>
+      </c>
+      <c r="W135">
+        <v>1.5</v>
+      </c>
+      <c r="X135">
+        <v>6</v>
+      </c>
+      <c r="Y135">
+        <v>1.13</v>
+      </c>
+      <c r="Z135">
+        <v>2.2</v>
+      </c>
+      <c r="AA135">
+        <v>3.58</v>
+      </c>
+      <c r="AB135">
+        <v>2.73</v>
+      </c>
+      <c r="AC135">
+        <v>1</v>
+      </c>
+      <c r="AD135">
+        <v>9.1</v>
+      </c>
+      <c r="AE135">
+        <v>1.18</v>
+      </c>
+      <c r="AF135">
+        <v>3.88</v>
+      </c>
+      <c r="AG135">
+        <v>1.62</v>
+      </c>
+      <c r="AH135">
+        <v>2.15</v>
+      </c>
+      <c r="AI135">
+        <v>1.53</v>
+      </c>
+      <c r="AJ135">
+        <v>2.38</v>
+      </c>
+      <c r="AK135">
+        <v>1.42</v>
+      </c>
+      <c r="AL135">
+        <v>1.35</v>
+      </c>
+      <c r="AM135">
+        <v>1.47</v>
+      </c>
+      <c r="AN135">
+        <v>2.75</v>
+      </c>
+      <c r="AO135">
+        <v>2</v>
+      </c>
+      <c r="AP135">
+        <v>2.44</v>
+      </c>
+      <c r="AQ135">
+        <v>2.11</v>
+      </c>
+      <c r="AR135">
+        <v>1.93</v>
+      </c>
+      <c r="AS135">
+        <v>1.82</v>
+      </c>
+      <c r="AT135">
+        <v>3.75</v>
+      </c>
+      <c r="AU135">
+        <v>5</v>
+      </c>
+      <c r="AV135">
+        <v>9</v>
+      </c>
+      <c r="AW135">
+        <v>11</v>
+      </c>
+      <c r="AX135">
+        <v>9</v>
+      </c>
+      <c r="AY135">
+        <v>16</v>
+      </c>
+      <c r="AZ135">
+        <v>18</v>
+      </c>
+      <c r="BA135">
+        <v>8</v>
+      </c>
+      <c r="BB135">
+        <v>2</v>
+      </c>
+      <c r="BC135">
+        <v>10</v>
+      </c>
+      <c r="BD135">
+        <v>2.08</v>
+      </c>
+      <c r="BE135">
+        <v>8.5</v>
+      </c>
+      <c r="BF135">
+        <v>2.07</v>
+      </c>
+      <c r="BG135">
+        <v>1.25</v>
+      </c>
+      <c r="BH135">
+        <v>3.45</v>
+      </c>
+      <c r="BI135">
+        <v>1.44</v>
+      </c>
+      <c r="BJ135">
+        <v>2.55</v>
+      </c>
+      <c r="BK135">
+        <v>1.72</v>
+      </c>
+      <c r="BL135">
+        <v>1.98</v>
+      </c>
+      <c r="BM135">
+        <v>2</v>
+      </c>
+      <c r="BN135">
+        <v>1.8</v>
+      </c>
+      <c r="BO135">
+        <v>2.65</v>
+      </c>
+      <c r="BP135">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="136" spans="1:68">
+      <c r="A136" s="1">
+        <v>135</v>
+      </c>
+      <c r="B136">
+        <v>7825325</v>
+      </c>
+      <c r="C136" t="s">
+        <v>68</v>
+      </c>
+      <c r="D136" t="s">
+        <v>69</v>
+      </c>
+      <c r="E136" s="2">
+        <v>45857.35763888889</v>
+      </c>
+      <c r="F136">
+        <v>17</v>
+      </c>
+      <c r="G136" t="s">
+        <v>81</v>
+      </c>
+      <c r="H136" t="s">
+        <v>73</v>
+      </c>
+      <c r="I136">
+        <v>2</v>
+      </c>
+      <c r="J136">
+        <v>0</v>
+      </c>
+      <c r="K136">
+        <v>2</v>
+      </c>
+      <c r="L136">
+        <v>4</v>
+      </c>
+      <c r="M136">
+        <v>0</v>
+      </c>
+      <c r="N136">
+        <v>4</v>
+      </c>
+      <c r="O136" t="s">
+        <v>194</v>
+      </c>
+      <c r="P136" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q136">
+        <v>2.6</v>
+      </c>
+      <c r="R136">
+        <v>2.2</v>
+      </c>
+      <c r="S136">
+        <v>4.33</v>
+      </c>
+      <c r="T136">
+        <v>1.36</v>
+      </c>
+      <c r="U136">
+        <v>3</v>
+      </c>
+      <c r="V136">
+        <v>2.75</v>
+      </c>
+      <c r="W136">
+        <v>1.4</v>
+      </c>
+      <c r="X136">
+        <v>7</v>
+      </c>
+      <c r="Y136">
+        <v>1.1</v>
+      </c>
+      <c r="Z136">
+        <v>1.9</v>
+      </c>
+      <c r="AA136">
+        <v>3.74</v>
+      </c>
+      <c r="AB136">
+        <v>3.78</v>
+      </c>
+      <c r="AC136">
+        <v>1</v>
+      </c>
+      <c r="AD136">
+        <v>9.1</v>
+      </c>
+      <c r="AE136">
+        <v>1.27</v>
+      </c>
+      <c r="AF136">
+        <v>3.15</v>
+      </c>
+      <c r="AG136">
+        <v>1.97</v>
+      </c>
+      <c r="AH136">
+        <v>1.85</v>
+      </c>
+      <c r="AI136">
+        <v>1.8</v>
+      </c>
+      <c r="AJ136">
+        <v>1.95</v>
+      </c>
+      <c r="AK136">
+        <v>1.26</v>
+      </c>
+      <c r="AL136">
+        <v>1.26</v>
+      </c>
+      <c r="AM136">
+        <v>1.86</v>
+      </c>
+      <c r="AN136">
+        <v>1.25</v>
+      </c>
+      <c r="AO136">
+        <v>0.13</v>
+      </c>
+      <c r="AP136">
+        <v>1.44</v>
+      </c>
+      <c r="AQ136">
+        <v>0.11</v>
+      </c>
+      <c r="AR136">
+        <v>1.41</v>
+      </c>
+      <c r="AS136">
+        <v>1.3</v>
+      </c>
+      <c r="AT136">
+        <v>2.71</v>
+      </c>
+      <c r="AU136">
+        <v>7</v>
+      </c>
+      <c r="AV136">
+        <v>2</v>
+      </c>
+      <c r="AW136">
+        <v>12</v>
+      </c>
+      <c r="AX136">
+        <v>14</v>
+      </c>
+      <c r="AY136">
+        <v>19</v>
+      </c>
+      <c r="AZ136">
+        <v>16</v>
+      </c>
+      <c r="BA136">
+        <v>5</v>
+      </c>
+      <c r="BB136">
+        <v>7</v>
+      </c>
+      <c r="BC136">
+        <v>12</v>
+      </c>
+      <c r="BD136">
+        <v>1.61</v>
+      </c>
+      <c r="BE136">
+        <v>9</v>
+      </c>
+      <c r="BF136">
+        <v>2.88</v>
+      </c>
+      <c r="BG136">
+        <v>1.28</v>
+      </c>
+      <c r="BH136">
+        <v>3.3</v>
+      </c>
+      <c r="BI136">
+        <v>1.48</v>
+      </c>
+      <c r="BJ136">
+        <v>2.43</v>
+      </c>
+      <c r="BK136">
+        <v>1.77</v>
+      </c>
+      <c r="BL136">
+        <v>1.92</v>
+      </c>
+      <c r="BM136">
+        <v>2.18</v>
+      </c>
+      <c r="BN136">
+        <v>1.58</v>
+      </c>
+      <c r="BO136">
+        <v>2.75</v>
+      </c>
+      <c r="BP136">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="137" spans="1:68">
+      <c r="A137" s="1">
+        <v>136</v>
+      </c>
+      <c r="B137">
+        <v>7825327</v>
+      </c>
+      <c r="C137" t="s">
+        <v>68</v>
+      </c>
+      <c r="D137" t="s">
+        <v>69</v>
+      </c>
+      <c r="E137" s="2">
+        <v>45857.375</v>
+      </c>
+      <c r="F137">
+        <v>17</v>
+      </c>
+      <c r="G137" t="s">
+        <v>83</v>
+      </c>
+      <c r="H137" t="s">
+        <v>78</v>
+      </c>
+      <c r="I137">
+        <v>0</v>
+      </c>
+      <c r="J137">
+        <v>0</v>
+      </c>
+      <c r="K137">
+        <v>0</v>
+      </c>
+      <c r="L137">
+        <v>1</v>
+      </c>
+      <c r="M137">
+        <v>1</v>
+      </c>
+      <c r="N137">
+        <v>2</v>
+      </c>
+      <c r="O137" t="s">
+        <v>195</v>
+      </c>
+      <c r="P137" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q137">
+        <v>1.91</v>
+      </c>
+      <c r="R137">
+        <v>2.63</v>
+      </c>
+      <c r="S137">
+        <v>6</v>
+      </c>
+      <c r="T137">
+        <v>1.22</v>
+      </c>
+      <c r="U137">
+        <v>4</v>
+      </c>
+      <c r="V137">
+        <v>2.1</v>
+      </c>
+      <c r="W137">
+        <v>1.67</v>
+      </c>
+      <c r="X137">
+        <v>4.5</v>
+      </c>
+      <c r="Y137">
+        <v>1.18</v>
+      </c>
+      <c r="Z137">
+        <v>1.44</v>
+      </c>
+      <c r="AA137">
+        <v>4.5</v>
+      </c>
+      <c r="AB137">
+        <v>5.3</v>
+      </c>
+      <c r="AC137">
+        <v>1.01</v>
+      </c>
+      <c r="AD137">
+        <v>17</v>
+      </c>
+      <c r="AE137">
+        <v>1.08</v>
+      </c>
+      <c r="AF137">
+        <v>5.55</v>
+      </c>
+      <c r="AG137">
+        <v>1.43</v>
+      </c>
+      <c r="AH137">
+        <v>2.62</v>
+      </c>
+      <c r="AI137">
+        <v>1.62</v>
+      </c>
+      <c r="AJ137">
+        <v>2.2</v>
+      </c>
+      <c r="AK137">
+        <v>1.1</v>
+      </c>
+      <c r="AL137">
+        <v>1.16</v>
+      </c>
+      <c r="AM137">
+        <v>2.78</v>
+      </c>
+      <c r="AN137">
+        <v>0.88</v>
+      </c>
+      <c r="AO137">
+        <v>0.43</v>
+      </c>
+      <c r="AP137">
+        <v>0.89</v>
+      </c>
+      <c r="AQ137">
+        <v>0.5</v>
+      </c>
+      <c r="AR137">
+        <v>1.87</v>
+      </c>
+      <c r="AS137">
+        <v>1.23</v>
+      </c>
+      <c r="AT137">
+        <v>3.1</v>
+      </c>
+      <c r="AU137">
+        <v>8</v>
+      </c>
+      <c r="AV137">
+        <v>3</v>
+      </c>
+      <c r="AW137">
+        <v>9</v>
+      </c>
+      <c r="AX137">
+        <v>7</v>
+      </c>
+      <c r="AY137">
+        <v>17</v>
+      </c>
+      <c r="AZ137">
+        <v>10</v>
+      </c>
+      <c r="BA137">
+        <v>9</v>
+      </c>
+      <c r="BB137">
+        <v>5</v>
+      </c>
+      <c r="BC137">
+        <v>14</v>
+      </c>
+      <c r="BD137">
+        <v>1.44</v>
+      </c>
+      <c r="BE137">
+        <v>9.5</v>
+      </c>
+      <c r="BF137">
+        <v>3.5</v>
+      </c>
+      <c r="BG137">
+        <v>1.12</v>
+      </c>
+      <c r="BH137">
+        <v>4.75</v>
+      </c>
+      <c r="BI137">
+        <v>1.28</v>
+      </c>
+      <c r="BJ137">
+        <v>3.25</v>
+      </c>
+      <c r="BK137">
+        <v>1.47</v>
+      </c>
+      <c r="BL137">
+        <v>2.48</v>
+      </c>
+      <c r="BM137">
+        <v>1.92</v>
+      </c>
+      <c r="BN137">
+        <v>1.88</v>
+      </c>
+      <c r="BO137">
+        <v>2.1</v>
+      </c>
+      <c r="BP137">
+        <v>1.63</v>
       </c>
     </row>
   </sheetData>
